--- a/forms/app/postpartum.xlsx
+++ b/forms/app/postpartum.xlsx
@@ -13,44 +13,44 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1289" uniqueCount="687">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1309" uniqueCount="698">
+  <si>
+    <t>list_name</t>
+  </si>
   <si>
     <t>form_title</t>
   </si>
   <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
     <t>form_id</t>
   </si>
   <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>list_name</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
     <t>version</t>
   </si>
   <si>
     <t>label::en</t>
   </si>
   <si>
+    <t>style</t>
+  </si>
+  <si>
+    <t>path</t>
+  </si>
+  <si>
     <t>label::sw</t>
   </si>
   <si>
+    <t>instance_name</t>
+  </si>
+  <si>
     <t>choice_filter</t>
   </si>
   <si>
-    <t>style</t>
-  </si>
-  <si>
-    <t>path</t>
-  </si>
-  <si>
-    <t>instance_name</t>
-  </si>
-  <si>
     <t>Postpartum Screening</t>
   </si>
   <si>
@@ -132,27 +132,27 @@
     <t>repeat_count</t>
   </si>
   <si>
+    <t>begin group</t>
+  </si>
+  <si>
+    <t>inputs</t>
+  </si>
+  <si>
+    <t>NO_LABEL</t>
+  </si>
+  <si>
     <t>discharge_swelling</t>
   </si>
   <si>
     <t>Discharge or swelling of scar</t>
   </si>
   <si>
-    <t>begin group</t>
-  </si>
-  <si>
     <t>Uchafu au kovu imevimba</t>
   </si>
   <si>
-    <t>inputs</t>
-  </si>
-  <si>
     <t>facility_island</t>
   </si>
   <si>
-    <t>NO_LABEL</t>
-  </si>
-  <si>
     <t>unguja</t>
   </si>
   <si>
@@ -201,12 +201,12 @@
     <t>North A</t>
   </si>
   <si>
+    <t>visit_id</t>
+  </si>
+  <si>
     <t>Kaskazini A</t>
   </si>
   <si>
-    <t>visit_id</t>
-  </si>
-  <si>
     <t>north_b</t>
   </si>
   <si>
@@ -216,6 +216,9 @@
     <t>Kaskazini B</t>
   </si>
   <si>
+    <t>is_atleast_one_baby_alive</t>
+  </si>
+  <si>
     <t>user</t>
   </si>
   <si>
@@ -231,18 +234,27 @@
     <t>south</t>
   </si>
   <si>
+    <t>contact_id</t>
+  </si>
+  <si>
     <t>South</t>
   </si>
   <si>
     <t>Wilaya ya kusini</t>
   </si>
   <si>
-    <t>contact_id</t>
-  </si>
-  <si>
     <t>Contact ID of the logged in user</t>
   </si>
   <si>
+    <t>facility_id</t>
+  </si>
+  <si>
+    <t>Facility ID for the parent user</t>
+  </si>
+  <si>
+    <t>Name of the logged in user</t>
+  </si>
+  <si>
     <t>west_a</t>
   </si>
   <si>
@@ -252,15 +264,6 @@
     <t>Magharibi  A</t>
   </si>
   <si>
-    <t>facility_id</t>
-  </si>
-  <si>
-    <t>Facility ID for the parent user</t>
-  </si>
-  <si>
-    <t>Name of the logged in user</t>
-  </si>
-  <si>
     <t>end group</t>
   </si>
   <si>
@@ -306,27 +309,27 @@
     <t>Micheweni</t>
   </si>
   <si>
+    <t>mkoani</t>
+  </si>
+  <si>
+    <t>Mkoani</t>
+  </si>
+  <si>
+    <t>wete</t>
+  </si>
+  <si>
+    <t>Wete</t>
+  </si>
+  <si>
     <t>calculate</t>
   </si>
   <si>
     <t>client_name</t>
   </si>
   <si>
-    <t>mkoani</t>
-  </si>
-  <si>
-    <t>Mkoani</t>
-  </si>
-  <si>
     <t>../inputs/contact/name</t>
   </si>
   <si>
-    <t>wete</t>
-  </si>
-  <si>
-    <t>Wete</t>
-  </si>
-  <si>
     <t>anc_visit_facility</t>
   </si>
   <si>
@@ -363,12 +366,12 @@
     <t>../inputs/user/facility_id</t>
   </si>
   <si>
+    <t>had_c_section</t>
+  </si>
+  <si>
     <t>Pujini PHCU+</t>
   </si>
   <si>
-    <t>had_c_section</t>
-  </si>
-  <si>
     <t>Tundauwa PHCU+</t>
   </si>
   <si>
@@ -390,19 +393,22 @@
     <t>age_days</t>
   </si>
   <si>
+    <t>Konde PHCU+</t>
+  </si>
+  <si>
     <t>int(decimal-date-time(now())-decimal-date-time(${date_of_birth_c}))</t>
   </si>
   <si>
-    <t>Konde PHCU+</t>
-  </si>
-  <si>
     <t>Makangale PHCU+</t>
   </si>
   <si>
+    <t>Maziwa Ngombe PHCU+</t>
+  </si>
+  <si>
     <t>age_months</t>
   </si>
   <si>
-    <t>Maziwa Ngombe PHCU+</t>
+    <t>Micheweni PHCC</t>
   </si>
   <si>
     <t>int((${age_days} - (${age_years} * 12 * 30)) div 30,0)</t>
@@ -417,57 +423,63 @@
     <t>age_in_years</t>
   </si>
   <si>
-    <t>Micheweni PHCC</t>
+    <t>Wingwi PHCU+</t>
   </si>
   <si>
     <t>round((decimal-date-time(today()) - decimal-date-time(${date_of_birth_c})) div 365,0)</t>
   </si>
   <si>
-    <t>Wingwi PHCU+</t>
+    <t>Kiuyu Mbuyuni PHCU+</t>
+  </si>
+  <si>
+    <t>Bogoa PHCU+</t>
   </si>
   <si>
     <t>age_days_display</t>
   </si>
   <si>
-    <t>Kiuyu Mbuyuni PHCU+</t>
-  </si>
-  <si>
     <t>${age_days} - (${age_months} * 30) - (${age_years} *12*30)</t>
   </si>
   <si>
     <t>week</t>
   </si>
   <si>
-    <t>Bogoa PHCU+</t>
+    <t>Kengeja PHCU+</t>
+  </si>
+  <si>
+    <t>Abdallah Mzee District Hospital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hospitali ya wilaya ya Abdallah Mzee </t>
   </si>
   <si>
     <t>month</t>
   </si>
   <si>
-    <t>Kengeja PHCU+</t>
-  </si>
-  <si>
     <t>household_head</t>
   </si>
   <si>
+    <t>Michenzani PHCU+</t>
+  </si>
+  <si>
     <t>instance('contact-summary')/context/household_head</t>
   </si>
   <si>
-    <t>Abdallah Mzee District Hospital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hospitali ya wilaya ya Abdallah Mzee </t>
+    <t>Fundo PHCU+</t>
+  </si>
+  <si>
+    <t>Kojani PHCU+</t>
   </si>
   <si>
     <t>house_number</t>
   </si>
   <si>
+    <t>Makongeni PHCU+</t>
+  </si>
+  <si>
     <t>instance('contact-summary')/context/house_number</t>
   </si>
   <si>
-    <t>Michenzani PHCU+</t>
-  </si>
-  <si>
     <t>kitongoji</t>
   </si>
   <si>
@@ -477,40 +489,37 @@
     <t>phone</t>
   </si>
   <si>
-    <t>Fundo PHCU+</t>
+    <t>Wete District Hospital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hospitali ya wilaya ya Wete </t>
   </si>
   <si>
     <t>instance('contact-summary')/context/phone</t>
   </si>
   <si>
-    <t>Kojani PHCU+</t>
-  </si>
-  <si>
     <t>../inputs/due_date</t>
   </si>
   <si>
+    <t>Mzambarauni PHCU+</t>
+  </si>
+  <si>
     <t>due_date_pretty_print</t>
   </si>
   <si>
-    <t>Makongeni PHCU+</t>
-  </si>
-  <si>
     <t>../inputs/due_date_human_readable</t>
   </si>
   <si>
-    <t>Wete District Hospital</t>
+    <t>Junguni PHCU+</t>
   </si>
   <si>
     <t>show_research_questions</t>
   </si>
   <si>
-    <t xml:space="preserve">Hospitali ya wilaya ya Wete </t>
-  </si>
-  <si>
     <t xml:space="preserve">instance('contact-summary')/context/show_research_questions </t>
   </si>
   <si>
-    <t>Mzambarauni PHCU+</t>
+    <t>Ukunjwi PHCU+</t>
   </si>
   <si>
     <t>show_quality_care_c</t>
@@ -519,13 +528,25 @@
     <t>../inputs/show_quality_care</t>
   </si>
   <si>
-    <t>Junguni PHCU+</t>
+    <t>Uondwe PHCU+</t>
+  </si>
+  <si>
+    <t>Chwaka PHCU+</t>
   </si>
   <si>
     <t>if(../inputs/visit_id != "", ../inputs/visit_id, "pregnancy_consent_visit")</t>
   </si>
   <si>
-    <t>Ukunjwi PHCU+</t>
+    <t>Mwera PHCU+</t>
+  </si>
+  <si>
+    <t>is_atleast_one_baby_alive_c</t>
+  </si>
+  <si>
+    <t>Unguja Ukuu PHCU+</t>
+  </si>
+  <si>
+    <t>../inputs/is_atleast_one_baby_alive</t>
   </si>
   <si>
     <t>client_information</t>
@@ -535,9 +556,6 @@
   </si>
   <si>
     <t>Taarifa za mteja</t>
-  </si>
-  <si>
-    <t>Uondwe PHCU+</t>
   </si>
   <si>
     <t>field-list</t>
@@ -565,6 +583,9 @@
 Kitongoji: &lt;span style="font-weight:bold"&gt;${kitongoji}&lt;/span&gt;</t>
   </si>
   <si>
+    <t>Uzini PHCU+</t>
+  </si>
+  <si>
     <t>Jina: &lt;span style=""font-weight:bold""&gt;${client_name}&lt;/span&gt;
 Umri: &lt;span style=""font-weight:bold""&gt;${age_years} miaka, ${age_months} miezi, ${age_days_display} siku&lt;/span&gt;
 Mtu wa karibu kwa mawasiliano: &lt;span style=""font-weight:bold""&gt;${household_head}&lt;/span&gt; 
@@ -581,19 +602,22 @@
     <t>Mawasiliano: &lt;span style="font-weight:bold"&gt;${phone}&lt;/span&gt;</t>
   </si>
   <si>
-    <t>Chwaka PHCU+</t>
-  </si>
-  <si>
     <t>due_date_note</t>
   </si>
   <si>
+    <t>Uroa PHCU+</t>
+  </si>
+  <si>
     <t>Due date: &lt;span style="font-weight:bold"&gt;${due_date_pretty_print}&lt;/span&gt;</t>
   </si>
   <si>
     <t>Tarehe ya mwisho ya tembeleo: &lt;span style="font-weight:bold"&gt;${due_date_pretty_print}&lt;/span&gt;</t>
   </si>
   <si>
-    <t>Mwera PHCU+</t>
+    <t>Kivunge District Hospital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hospitali ya wilaya wa Kivunge </t>
   </si>
   <si>
     <t>visit_introduction</t>
@@ -602,7 +626,7 @@
     <t>Visit Introduction</t>
   </si>
   <si>
-    <t>Unguja Ukuu PHCU+</t>
+    <t>Matemwe PHCU+</t>
   </si>
   <si>
     <t>Utambulisho</t>
@@ -611,10 +635,10 @@
     <t>postpartum_intro_note</t>
   </si>
   <si>
-    <t>Hi ${client_name}, I'd like to check up on you to see how you are doing following the birth of your baby.</t>
-  </si>
-  <si>
-    <t>Habari ${client_name}, ningependa kukuangalia na kujua maendeleo yako baada ya kujifungua</t>
+    <t>Hi ${client_name}, I'd like to check up on you to see how you are doing following your delivery.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Habari ${client_name}, ningependa kukuangalia na kujua maendeleo yako baada ya kujifungua. </t>
   </si>
   <si>
     <t>begin_group</t>
@@ -623,6 +647,9 @@
     <t>postpartum_danger_signs</t>
   </si>
   <si>
+    <t>Nungwi PHCU+</t>
+  </si>
+  <si>
     <t>Postpartum Danger Signs</t>
   </si>
   <si>
@@ -632,9 +659,6 @@
     <t>postpartum_danger_signs_note</t>
   </si>
   <si>
-    <t>Uzini PHCU+</t>
-  </si>
-  <si>
     <t>First, I'm going to check for any postpartum danger signs.</t>
   </si>
   <si>
@@ -644,6 +668,9 @@
     <t>postpartum_emergency_danger_signs</t>
   </si>
   <si>
+    <t>Pwani Mchangani PHCU+</t>
+  </si>
+  <si>
     <t>postpartum_emergency_danger_signs_note</t>
   </si>
   <si>
@@ -659,9 +686,6 @@
     <t>table-list</t>
   </si>
   <si>
-    <t>Uroa PHCU+</t>
-  </si>
-  <si>
     <t>select_one yes_no</t>
   </si>
   <si>
@@ -671,6 +695,9 @@
     <t>Severe vaginal bleeding</t>
   </si>
   <si>
+    <t>Tumbatu Gomani PHCU+</t>
+  </si>
+  <si>
     <t>Kutokwa na damu nyingi ukeni</t>
   </si>
   <si>
@@ -683,10 +710,7 @@
     <t>Kifafa cha mimba</t>
   </si>
   <si>
-    <t>Kivunge District Hospital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hospitali ya wilaya wa Kivunge </t>
+    <t>Kendwa PHCU+</t>
   </si>
   <si>
     <t>postpartum_unconscious</t>
@@ -698,7 +722,7 @@
     <t>Kupoteza fahamu</t>
   </si>
   <si>
-    <t>Matemwe PHCU+</t>
+    <t>Bumbwini Misufini PHCU+</t>
   </si>
   <si>
     <t>postpartum_bleeding_right_now</t>
@@ -729,7 +753,7 @@
     <t>postpartum_emergency_referral_note</t>
   </si>
   <si>
-    <t>Nungwi PHCU+</t>
+    <t>Donge Vijibweni PHCU+</t>
   </si>
   <si>
     <t xml:space="preserve">This is an URGENT and serious emergency. You should go to the nearest facility immediately. If it is near closing time for this facility, you should directly to nearest hospital.
@@ -751,12 +775,12 @@
     <t>Other Postpartum Danger Signs</t>
   </si>
   <si>
+    <t>Kiongwe PHCU</t>
+  </si>
+  <si>
     <t>Dalili nyengine za hatari baada ya kujifungua</t>
   </si>
   <si>
-    <t>Pwani Mchangani PHCU+</t>
-  </si>
-  <si>
     <t>${refer_postpartum_emergency_danger_sign_flag}=0</t>
   </si>
   <si>
@@ -772,6 +796,9 @@
     <t>postpartum_other_danger_signs_table</t>
   </si>
   <si>
+    <t>Kitope PHCU</t>
+  </si>
+  <si>
     <t>postpartum_pale_pallor</t>
   </si>
   <si>
@@ -781,9 +808,6 @@
     <t>Mpauko/kupiga rangi (Angalia: viganja na mdomo ya mama)</t>
   </si>
   <si>
-    <t>Tumbatu Gomani PHCU+</t>
-  </si>
-  <si>
     <t>postpartum_severe_frontal_headache</t>
   </si>
   <si>
@@ -799,15 +823,15 @@
     <t>Blurred vision</t>
   </si>
   <si>
+    <t>Mahonda PHCU+</t>
+  </si>
+  <si>
     <t>Kutokuona vizuri</t>
   </si>
   <si>
     <t>postpartum_urine</t>
   </si>
   <si>
-    <t>Kendwa PHCU+</t>
-  </si>
-  <si>
     <t>Low urine output or leaking of urine</t>
   </si>
   <si>
@@ -823,6 +847,9 @@
     <t>Kizunguzungu</t>
   </si>
   <si>
+    <t>Jambiani PHCU+</t>
+  </si>
+  <si>
     <t>postpartum_exhaustion</t>
   </si>
   <si>
@@ -841,9 +868,6 @@
     <t>Kuumwa san tumbo sehemu ya chini</t>
   </si>
   <si>
-    <t>Bumbwini Misufini PHCU+</t>
-  </si>
-  <si>
     <t>postpartum_vaginal_discharge</t>
   </si>
   <si>
@@ -853,9 +877,18 @@
     <t>Harufu mbaya au isyoyakawaida sehemu za siri</t>
   </si>
   <si>
+    <t>Makunduchi District Hospital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hospitali ya wilaya ya Makunduchi </t>
+  </si>
+  <si>
     <t>postpartum_fever_chills</t>
   </si>
   <si>
+    <t>Muyuni PHCU+</t>
+  </si>
+  <si>
     <t>Fever or chills</t>
   </si>
   <si>
@@ -865,15 +898,15 @@
     <t>postpartum_breathing_difficulty</t>
   </si>
   <si>
-    <t>Donge Vijibweni PHCU+</t>
-  </si>
-  <si>
     <t>Breathing difficulty</t>
   </si>
   <si>
     <t>Kupumua kwa shida</t>
   </si>
   <si>
+    <t>Bwejuu PHCU+</t>
+  </si>
+  <si>
     <t>postpartum_severe_pain_foot</t>
   </si>
   <si>
@@ -892,15 +925,15 @@
     <t>Tabia zisizokawaida,Huzuni au kuchanganyikiwa</t>
   </si>
   <si>
+    <t>Chumbuni PHCU+</t>
+  </si>
+  <si>
     <t>postpartum_breast</t>
   </si>
   <si>
     <t>Tenderness of the breast or cracked nipples</t>
   </si>
   <si>
-    <t>Kiongwe PHCU</t>
-  </si>
-  <si>
     <t>Kukakamaa kwa matiti au chuchu zilizopasuka</t>
   </si>
   <si>
@@ -916,10 +949,13 @@
     <t>${had_c_section}="yes"</t>
   </si>
   <si>
+    <t>Mnazi Mmoja Hospital</t>
+  </si>
+  <si>
     <t>client_been_facility_3_days</t>
   </si>
   <si>
-    <t>Kitope PHCU</t>
+    <t xml:space="preserve">Hospitali ya Mnazimmoja </t>
   </si>
   <si>
     <t>We've identified that you have a danger sign.  Do not worry, because these conditions will be managed when you get to a health facilty.
@@ -952,6 +988,9 @@
 &lt;span style="color:red;font-style: italic"&gt;To be answered by the CHV &lt;/span&gt;</t>
   </si>
   <si>
+    <t>Mwembeladu MCH Clinic</t>
+  </si>
+  <si>
     <t>&lt;span style="color:#f58a1f"&gt;Jadiliana na mteja juu ya ushauri aliopatiwa kituo cha afya kwa tatizo lake,ushauri,huduma na ufatiliaji
 &lt;/span&gt;
 &lt;span style="color:red;font-style: italic"&gt;Usimsomee, jaza wewe&lt;/span&gt;</t>
@@ -960,9 +999,6 @@
     <t>selected(${client_been_facility_3_days},"yes")</t>
   </si>
   <si>
-    <t>Mahonda PHCU+</t>
-  </si>
-  <si>
     <t>chv_thinks_needs_return_facility</t>
   </si>
   <si>
@@ -973,6 +1009,9 @@
   </si>
   <si>
     <t>postpartum_other_danger_sign_referral_note</t>
+  </si>
+  <si>
+    <t>Sebleni PHCU+</t>
   </si>
   <si>
     <t xml:space="preserve">You should go to a health facility as soon as possible and within 24 hours for further screening. 
@@ -985,9 +1024,6 @@
     <t>Tafadhalihudhuria kituo cha afya haraka iwezekanavyo.</t>
   </si>
   <si>
-    <t>Jambiani PHCU+</t>
-  </si>
-  <si>
     <t>${refer_postpartum_other_danger_sign_flag} = 1</t>
   </si>
   <si>
@@ -1006,16 +1042,13 @@
     <t>postpartum_other_danger_sign_not_found_note</t>
   </si>
   <si>
+    <t>Chukwani PHCU+</t>
+  </si>
+  <si>
     <t>No danger signs were identified, but if you develop any of the signs we discussed, you should go to a health facility immediately.</t>
   </si>
   <si>
     <t>Hakuna dalili za hatari zilizogundulika,iwapo utaona dalili yeyote kati zile tulizojadili, basi wahi kituo cha afya haraka.</t>
-  </si>
-  <si>
-    <t>Makunduchi District Hospital</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hospitali ya wilaya ya Makunduchi </t>
   </si>
   <si>
     <t xml:space="preserve">(${had_c_section} = "yes" and
@@ -1063,15 +1096,33 @@
     <t>eat_healthy_note</t>
   </si>
   <si>
-    <t>Muyuni PHCU+</t>
-  </si>
-  <si>
     <t>Please continue to eat healthy and have more snacks to make sure that your baby gets enough milk from breastfeeding. It is very important for you to eat a balanced diet with a lot of vegetables and fruits and drink lots of water.</t>
   </si>
   <si>
     <t>Tafadhali endelea kula vyakula vya afya na kupata asusa mara nyingi zaidi ili mtoto aendelee kupata maziwa mengi zaidi, Ni Muhimu kulamlo kamili wenye wingi wa mbogamboga,matunda na kunywa maji mengi.</t>
   </si>
   <si>
+    <t>Fuoni PHCU+</t>
+  </si>
+  <si>
+    <t>${is_atleast_one_baby_alive_c} = "true"</t>
+  </si>
+  <si>
+    <t>eat_healthy_note_no_baby</t>
+  </si>
+  <si>
+    <t>Please continue to eat healthy and have more snacks. It is very important for you to eat a balanced diet with a lot of vegetables and fruits and drink lots of water.</t>
+  </si>
+  <si>
+    <t>Kombeni PHCU+</t>
+  </si>
+  <si>
+    <t>Tafadhali endelea kula vyakula vya afya na kupata asusa mara nyingi zaidi. Ni Muhimu kula mlo kamili wenye wingi wa mbogamboga,matunda na kunywa maji mengi.</t>
+  </si>
+  <si>
+    <t>${is_atleast_one_baby_alive_c} = "false"</t>
+  </si>
+  <si>
     <t>iron_folic_acid_note</t>
   </si>
   <si>
@@ -1081,6 +1132,18 @@
     <t>Ni muhimu kumeza vidonge vya kuongeza damu kwa ajili ya kuzuia upungufu wa damu miezi miatatu baada ya mtoto kuzaliwa,daktari atashauri jinsi ya kuendelea kumeza vidonge vya kuongeza damu.</t>
   </si>
   <si>
+    <t>iron_folic_acid_note_no_baby</t>
+  </si>
+  <si>
+    <t>It’s very important to Take iron and folic acid tablets to prevent anemia for at least 3 months. Continue taking your iron and folic acid as directed by physician.</t>
+  </si>
+  <si>
+    <t>Mtofaani PHCU+ (Kinuni)</t>
+  </si>
+  <si>
+    <t>Ni muhimu kumeza vidonge vya kuongeza damu kwa ajili ya kuzuia upungufu wa damu kwa muda wa miezi miatatu, daktari atashauri jinsi ya kuendelea kumeza vidonge vya kuongeza damu.</t>
+  </si>
+  <si>
     <t>vitamin_a_note</t>
   </si>
   <si>
@@ -1090,12 +1153,12 @@
     <t>Ndani ya wiki sita baada ya kujifungua,unatakiwa uhudhurie kliniki ya mama waliojifungua kwa kupata vitamini A.</t>
   </si>
   <si>
-    <t>Bwejuu PHCU+</t>
-  </si>
-  <si>
     <t>check_facility_pnc</t>
   </si>
   <si>
+    <t>Bumbwisudi PHCU+</t>
+  </si>
+  <si>
     <t>Facility PNC</t>
   </si>
   <si>
@@ -1114,12 +1177,12 @@
     <t>Je ulishawahi kuhudhuria kliniki kwa ajili ya uchunguzi baada ya kujifungua?</t>
   </si>
   <si>
-    <t>Chumbuni PHCU+</t>
-  </si>
-  <si>
     <t>quality_of_care_consent</t>
   </si>
   <si>
+    <t>Selem PHCU+</t>
+  </si>
+  <si>
     <t>I’d like to ask you a few questions about the quality of the services you received last time you went to the health facility. We will anonymously share this information with DHMT or other persons in the MOH so that they can improve the services that are provided. You can choose not to answer any question you don’t want to. Is it ok for us to proceed?</t>
   </si>
   <si>
@@ -1132,18 +1195,15 @@
     <t>quality_of_care</t>
   </si>
   <si>
+    <t>Nyegine</t>
+  </si>
+  <si>
     <t>Quality of Care</t>
   </si>
   <si>
-    <t>Mnazi Mmoja Hospital</t>
-  </si>
-  <si>
     <t>Ubora wa Huduma</t>
   </si>
   <si>
-    <t xml:space="preserve">Hospitali ya Mnazimmoja </t>
-  </si>
-  <si>
     <t>${refer_postpartum_emergency_danger_sign_flag}=0 and selected(${quality_of_care_consent},"yes") and selected(${has_attended_facility_pnc},"yes")</t>
   </si>
   <si>
@@ -1156,12 +1216,6 @@
     <t>Kitu kiko wapi?</t>
   </si>
   <si>
-    <t>Mwembeladu MCH Clinic</t>
-  </si>
-  <si>
-    <t>Sebleni PHCU+</t>
-  </si>
-  <si>
     <t>select_one facility_district</t>
   </si>
   <si>
@@ -1177,9 +1231,6 @@
     <t>choice_filter=${facility_island}</t>
   </si>
   <si>
-    <t>Chukwani PHCU+</t>
-  </si>
-  <si>
     <t>subgroup_facility</t>
   </si>
   <si>
@@ -1187,9 +1238,6 @@
   </si>
   <si>
     <t xml:space="preserve">Which facility did you visit? </t>
-  </si>
-  <si>
-    <t>Fuoni PHCU+</t>
   </si>
   <si>
     <t>Ni kituo gani ulitembelea?</t>
@@ -1214,9 +1262,6 @@
     <t>choice_filter=${facility_district}</t>
   </si>
   <si>
-    <t>Kombeni PHCU+</t>
-  </si>
-  <si>
     <t>text</t>
   </si>
   <si>
@@ -1244,9 +1289,6 @@
     <t>Je ulipata huduma katika kituo ulichotembelea?</t>
   </si>
   <si>
-    <t>Mtofaani PHCU+ (Kinuni)</t>
-  </si>
-  <si>
     <t>select_multiple service_reason</t>
   </si>
   <si>
@@ -1262,9 +1304,6 @@
     <t>selected(${is_service_received},"yes_but") or selected(${is_service_received},"no")</t>
   </si>
   <si>
-    <t>Bumbwisudi PHCU+</t>
-  </si>
-  <si>
     <t>select_multiple second_facility</t>
   </si>
   <si>
@@ -1298,9 +1337,6 @@
     <t>baby_services_recevied</t>
   </si>
   <si>
-    <t>Selem PHCU+</t>
-  </si>
-  <si>
     <t>During your most recent Post-natal visit, which services did your baby receive?</t>
   </si>
   <si>
@@ -1313,9 +1349,15 @@
     <t>personal_information_consent</t>
   </si>
   <si>
+    <t xml:space="preserve">Yes, I got all the services at the faciltiy </t>
+  </si>
+  <si>
     <t>Personal Information</t>
   </si>
   <si>
+    <t>Ndio, nilipata huduma zote katika kituo cha afya.</t>
+  </si>
+  <si>
     <t>Taarifa Binafsi</t>
   </si>
   <si>
@@ -1328,33 +1370,123 @@
     <t xml:space="preserve">I would like to ask you a few questions that will help us improve the health services provided in your community in the future. You can decide you do not want to answer a question – just let me know if you prefer not to answer. Can we proceed? </t>
   </si>
   <si>
-    <t>Nyegine</t>
-  </si>
-  <si>
     <t>Ningependa kuuliza maswali machache yatayosaidia kuboresha hudumakatika jamii yako hapo baadae, unaweza kuamua kutojibu maswali, ni vizuri kunijulisha kama hutapenda kujibu, Je tunaweza kuendelea?</t>
   </si>
   <si>
+    <t>yes_but</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes, I got some services but also had to go to another place as well for tests/invenstigations/other services. </t>
+  </si>
+  <si>
+    <t>Ndio, nilipata baadhi ya huduma lakini nilienda kituo cha afya kingine kufanaya vipimo</t>
+  </si>
+  <si>
     <t>research_questions</t>
   </si>
   <si>
     <t>selected(${research_questions_consent},"yes")</t>
   </si>
   <si>
+    <t xml:space="preserve">No, I didn't get a service </t>
+  </si>
+  <si>
     <t>select_one travel_time</t>
   </si>
   <si>
+    <t>Hapana, Sikupata huduma.</t>
+  </si>
+  <si>
     <t>travel_time</t>
   </si>
   <si>
+    <t>service_reason</t>
+  </si>
+  <si>
+    <t>no_staff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There was no staff </t>
+  </si>
+  <si>
+    <t>Kulikuwa hakuna mfanyakazi.</t>
+  </si>
+  <si>
     <t>Typically, how long does it take for you to travel from your home to the nearest healthcare facility for a routine/non-emergency visit?</t>
   </si>
   <si>
+    <t>closed_facility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The facility was closed </t>
+  </si>
+  <si>
+    <t>Kituo cha afya kilikuwa kimefungwa.</t>
+  </si>
+  <si>
+    <t>no_reagents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There was no regeants/tests at the faciltiy </t>
+  </si>
+  <si>
+    <t>Kulikuwa hakuna vifaa vya kufanyia vipimo katika kituo cha afya.</t>
+  </si>
+  <si>
+    <t>waiting_too_long</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The waiting time was too long. I decided to come back home. </t>
+  </si>
+  <si>
+    <t>Nilisubiri muda mrefu sana. Nikaamuwa nirudi bila kupata huduma.</t>
+  </si>
+  <si>
     <t>Kikawaida, Inachukua muda gani kusafiri kutokea nyumbani kwenda kituo cha afya cha karibu kwa ajili ya huduma za kawaida zisizo za dharura?</t>
   </si>
   <si>
+    <t>no_money</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I had no money to pay for the services </t>
+  </si>
+  <si>
+    <t>Nilikuwa sina pesa za kulipia huduma.</t>
+  </si>
+  <si>
+    <t>Nyengine</t>
+  </si>
+  <si>
     <t xml:space="preserve">transport </t>
   </si>
   <si>
+    <t>pregnancy_supplements</t>
+  </si>
+  <si>
+    <t>Pregnancy supplements/FeFol</t>
+  </si>
+  <si>
+    <t>Dawa za kuongeza damu kwa mama wajawazito.</t>
+  </si>
+  <si>
+    <t>bp_reading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blood pressure reading </t>
+  </si>
+  <si>
+    <t>Kupima pressure</t>
+  </si>
+  <si>
+    <t>hb_test</t>
+  </si>
+  <si>
+    <t>Hb Test</t>
+  </si>
+  <si>
+    <t>Kupima wingi wa wadamu</t>
+  </si>
+  <si>
     <t>select_one travel_means</t>
   </si>
   <si>
@@ -1364,9 +1496,36 @@
     <t>How do you typically travel from your home to the healthcare facility for routine/non-emergency visits?</t>
   </si>
   <si>
+    <t>bp_test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blood group test </t>
+  </si>
+  <si>
+    <t>Kupima group la damu</t>
+  </si>
+  <si>
+    <t>urine_test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urine Test (Urinalysis) </t>
+  </si>
+  <si>
+    <t>Kupima mkoja kama mchafu.</t>
+  </si>
+  <si>
+    <t>ultrasound</t>
+  </si>
+  <si>
     <t>Unatumia usafiri gani kutoka nyumbani kwenda kituo cha afya kwa huduma za kawaida zisizo za dharura?</t>
   </si>
   <si>
+    <t>Ultrasound</t>
+  </si>
+  <si>
+    <t>Kupiga utrasound</t>
+  </si>
+  <si>
     <t>other_means</t>
   </si>
   <si>
@@ -1376,9 +1535,78 @@
     <t>selected(${travel_means},"other")</t>
   </si>
   <si>
+    <t>bp_measured</t>
+  </si>
+  <si>
+    <t>Blood pressure measured</t>
+  </si>
+  <si>
+    <t>temp_measured</t>
+  </si>
+  <si>
+    <t>Temperature measured</t>
+  </si>
+  <si>
+    <t>Kupima jito la mwili</t>
+  </si>
+  <si>
+    <t>checked_anemia</t>
+  </si>
+  <si>
+    <t>Checked for anemia</t>
+  </si>
+  <si>
+    <t>Kuangalia upungufu wa damu</t>
+  </si>
+  <si>
+    <t>breast_exam</t>
+  </si>
+  <si>
+    <t>Examined breast</t>
+  </si>
+  <si>
+    <t>Kufanya uchunguzi wa maziwa</t>
+  </si>
+  <si>
+    <t>abdominal_exam</t>
+  </si>
+  <si>
+    <t>Abdominal examination</t>
+  </si>
+  <si>
+    <t>Uchunguzi wa tumbo</t>
+  </si>
+  <si>
+    <t>genital_exam</t>
+  </si>
+  <si>
+    <t>Genitalia examination</t>
+  </si>
+  <si>
+    <t>Kuchunguza maeneo ya uzazi</t>
+  </si>
+  <si>
+    <t>lower_extremity_exam</t>
+  </si>
+  <si>
+    <t>Examination of lower extremities</t>
+  </si>
+  <si>
+    <t>Kuchunguzwa miguu</t>
+  </si>
+  <si>
+    <t>health_education_counseling</t>
+  </si>
+  <si>
     <t>select_one highest_school_level</t>
   </si>
   <si>
+    <t>Health education and counselling</t>
+  </si>
+  <si>
+    <t>Elimu ya afya na ushauri</t>
+  </si>
+  <si>
     <t>highest_school_level</t>
   </si>
   <si>
@@ -1388,43 +1616,133 @@
     <t>Una kiwango gani cha elimu?</t>
   </si>
   <si>
+    <t>Nyingine</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>None of the above</t>
+  </si>
+  <si>
+    <t>Hakuna kati ya hao hapo juu.</t>
+  </si>
+  <si>
+    <t>baby_services_received</t>
+  </si>
+  <si>
+    <t>check_abnormalities</t>
+  </si>
+  <si>
+    <t>Check for any abnormalities</t>
+  </si>
+  <si>
+    <t>Kuangaliwa kama kuna matatizo</t>
+  </si>
+  <si>
     <t>select_one yes_no_decline_to_answer</t>
   </si>
   <si>
     <t>previous_uzazi_salama_enrollment</t>
   </si>
   <si>
+    <t>check_reflexes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Were you previously/ever enrolled in Safer Deliveries Program? </t>
   </si>
   <si>
+    <t>Check reflexes</t>
+  </si>
+  <si>
     <t>Je ulishawahi kusajiliwa kwenye mradi wa Uzazi salama?</t>
   </si>
   <si>
+    <t>Kuangaliwa uchangamfu wa baadhi ya viungo.</t>
+  </si>
+  <si>
+    <t>cord_exam</t>
+  </si>
+  <si>
+    <t>Cord examination</t>
+  </si>
+  <si>
+    <t>Kuchunguzwa kitovu</t>
+  </si>
+  <si>
+    <t>breast_feed_demo</t>
+  </si>
+  <si>
+    <t>Breast feeding demonstration (attachment and positioning)</t>
+  </si>
+  <si>
+    <t>Kuelekezwa mbinu za unyonyeshaji (Jinsi ya kumpakata na kumueka mtoto katika matiti)</t>
+  </si>
+  <si>
     <t>enrollment_via_phone</t>
   </si>
   <si>
     <t>Did someone come to your house and register you using a phone during a previous pregnancy?</t>
   </si>
   <si>
-    <t xml:space="preserve">Yes, I got all the services at the faciltiy </t>
-  </si>
-  <si>
-    <t>Ndio, nilipata huduma zote katika kituo cha afya.</t>
+    <t>less_than_30</t>
+  </si>
+  <si>
+    <t>less than  30 mins</t>
+  </si>
+  <si>
+    <t>Chini ya dakika thelathini</t>
+  </si>
+  <si>
+    <t>30_to_1hr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 mins - 1 hr </t>
+  </si>
+  <si>
+    <t>Kati ya dakika 30 na saa mmoja</t>
   </si>
   <si>
     <t>Je kuna mtu yeyote alikuja kukusajili kwa simu ya mkononi wakati wa uja uzito wako uliopita?</t>
   </si>
   <si>
-    <t>yes_but</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes, I got some services but also had to go to another place as well for tests/invenstigations/other services. </t>
+    <t>more_than_1hr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">more than 1 hr </t>
+  </si>
+  <si>
+    <t>Zaidi ya saa mmoja</t>
+  </si>
+  <si>
+    <t>travel_time_dont_know_decline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Don't know/Decline to answer </t>
+  </si>
+  <si>
+    <t>Sijui / Siwezi kujibu</t>
+  </si>
+  <si>
+    <t>walk</t>
+  </si>
+  <si>
+    <t>Walk</t>
+  </si>
+  <si>
+    <t>Kutembea</t>
   </si>
   <si>
     <t>subgroup_decision_maker</t>
   </si>
   <si>
-    <t>Ndio, nilipata baadhi ya huduma lakini nilienda kituo cha afya kingine kufanaya vipimo</t>
+    <t>bicycle</t>
+  </si>
+  <si>
+    <t>Bicycle</t>
+  </si>
+  <si>
+    <t>Kwa baskeli</t>
   </si>
   <si>
     <t>select_one decision_maker</t>
@@ -1436,52 +1754,61 @@
     <t>Who usually makes decisions about your health care? [Primary or ultimate decision-maker]</t>
   </si>
   <si>
-    <t xml:space="preserve">No, I didn't get a service </t>
-  </si>
-  <si>
     <t>Kwa kawaida ni nani huwa anafanya maamuzi kuhusu afya yako? (maamuzi Makuu na ya msingi)</t>
   </si>
   <si>
-    <t>Hapana, Sikupata huduma.</t>
+    <t>moto</t>
+  </si>
+  <si>
+    <t>Moto</t>
+  </si>
+  <si>
+    <t>Honda</t>
   </si>
   <si>
     <t>some_other_decision_maker</t>
   </si>
   <si>
-    <t>service_reason</t>
-  </si>
-  <si>
-    <t>no_staff</t>
+    <t>private_car</t>
+  </si>
+  <si>
+    <t>Private Car</t>
+  </si>
+  <si>
+    <t>Gari binafsi</t>
   </si>
   <si>
     <t>selected(${decision_maker},"other")</t>
   </si>
   <si>
-    <t xml:space="preserve">There was no staff </t>
-  </si>
-  <si>
-    <t>Kulikuwa hakuna mfanyakazi.</t>
-  </si>
-  <si>
-    <t>closed_facility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The facility was closed </t>
-  </si>
-  <si>
-    <t>Kituo cha afya kilikuwa kimefungwa.</t>
+    <t>public_bus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public Bus </t>
+  </si>
+  <si>
+    <t>Daladala</t>
+  </si>
+  <si>
+    <t>health_facility_vehicle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Health facility vehicle </t>
+  </si>
+  <si>
+    <t>Gari ya kituo cha afya</t>
   </si>
   <si>
     <t>subgroup_married_or_livein_relation</t>
   </si>
   <si>
-    <t>no_reagents</t>
-  </si>
-  <si>
-    <t xml:space="preserve">There was no regeants/tests at the faciltiy </t>
-  </si>
-  <si>
-    <t>Kulikuwa hakuna vifaa vya kufanyia vipimo katika kituo cha afya.</t>
+    <t>boat</t>
+  </si>
+  <si>
+    <t>Boat</t>
+  </si>
+  <si>
+    <t>Bot</t>
   </si>
   <si>
     <t>msg_for_chv_married_or_livein_relation</t>
@@ -1490,25 +1817,34 @@
     <t>&lt;span style="color:red;font-style: italic"&gt;To be answered by the CHV &lt;/span&gt;</t>
   </si>
   <si>
-    <t>waiting_too_long</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The waiting time was too long. I decided to come back home. </t>
-  </si>
-  <si>
-    <t>Nilisubiri muda mrefu sana. Nikaamuwa nirudi bila kupata huduma.</t>
+    <t xml:space="preserve">Other </t>
+  </si>
+  <si>
+    <t>travel_means_dont_know_decline</t>
+  </si>
+  <si>
+    <t>Don't know/Decline to answer</t>
   </si>
   <si>
     <t>&lt;span style="color:red;font-style: italic"&gt;Usimsomee, jaza wewe (CHV). &lt;/span&gt;</t>
   </si>
   <si>
-    <t>no_money</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I had no money to pay for the services </t>
-  </si>
-  <si>
-    <t>Nilikuwa sina pesa za kulipia huduma.</t>
+    <t>no_formal_education</t>
+  </si>
+  <si>
+    <t>No formal education/None</t>
+  </si>
+  <si>
+    <t>Hakusoma skuli/Hakusoma</t>
+  </si>
+  <si>
+    <t>incomplete_primary</t>
+  </si>
+  <si>
+    <t>Incomplete/some primary school (KG-Standard 5)</t>
+  </si>
+  <si>
+    <t>Hakumaliza/ kapata elimu ya nasari kaishia darasa la tano.</t>
   </si>
   <si>
     <t>married_or_livein_relation</t>
@@ -1517,54 +1853,168 @@
     <t>Is the client you are attending currently married or living together with a man as if married?</t>
   </si>
   <si>
-    <t>Nyengine</t>
-  </si>
-  <si>
     <t>Je mteja unaemuhudumia sasa ana mume/mwenza ambae wanaishi pamoja?</t>
   </si>
   <si>
+    <t>primary_education</t>
+  </si>
+  <si>
+    <t>Completed primary education (Standard 6)</t>
+  </si>
+  <si>
+    <t>Kamalizia elimu ya msingi (darasa la sita)</t>
+  </si>
+  <si>
     <t>subgroup_marital_status</t>
   </si>
   <si>
+    <t>incomplete_secondary</t>
+  </si>
+  <si>
+    <t>Incomplete/some secondary school (Form 1-3)</t>
+  </si>
+  <si>
+    <t>Hakumaliza elimu ya secondari kaishia darasa la kumi na moja</t>
+  </si>
+  <si>
+    <t>secondary</t>
+  </si>
+  <si>
+    <t>Completed secondary school (Form 4)</t>
+  </si>
+  <si>
     <t>msg_for_chv_marital_status</t>
   </si>
   <si>
+    <t>Kaliza darasa la kumi na mbili</t>
+  </si>
+  <si>
     <t>selected(${married_or_livein_relation},"no")</t>
   </si>
   <si>
+    <t>completed_high_school</t>
+  </si>
+  <si>
     <t>select_one marital_status</t>
   </si>
   <si>
+    <t>Completed high school (Form 6)</t>
+  </si>
+  <si>
     <t>marital_status</t>
   </si>
   <si>
+    <t>Kamaliza kidatu cha sita</t>
+  </si>
+  <si>
     <t xml:space="preserve">What is the woman's marital status? </t>
   </si>
   <si>
     <t>Je ni ipi hali ya ndoa ya mama?</t>
   </si>
   <si>
+    <t>more_than_high_school</t>
+  </si>
+  <si>
+    <t>More than high school</t>
+  </si>
+  <si>
+    <t>Elimu yake zaidi ya elimu ya juu/ zaidi ya kidatu cha sita</t>
+  </si>
+  <si>
+    <t>school_level_dont_know_decline</t>
+  </si>
+  <si>
     <t>subgroup_partner_info</t>
   </si>
   <si>
+    <t>herself</t>
+  </si>
+  <si>
+    <t>You only</t>
+  </si>
+  <si>
+    <t>Wewe peke yako</t>
+  </si>
+  <si>
     <t>msg_for_chv_partner_live_together</t>
   </si>
   <si>
     <t>selected(${married_or_livein_relation},"yes")</t>
   </si>
   <si>
+    <t>husband</t>
+  </si>
+  <si>
+    <t>Your husband/partner only</t>
+  </si>
+  <si>
+    <t>Mwenza wako</t>
+  </si>
+  <si>
     <t>does_partner_live_together</t>
   </si>
   <si>
+    <t>herself_and_husband</t>
+  </si>
+  <si>
     <t xml:space="preserve">Does the woman's (husband/partner) usually live here with her? </t>
   </si>
   <si>
+    <t>You and your husband/partner (or other family member) jointly</t>
+  </si>
+  <si>
+    <t>Ulifuatana na mume/mweza wako (or wanafamilia wengine)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Someone else </t>
+  </si>
+  <si>
+    <t>Na mtu mwengine</t>
+  </si>
+  <si>
+    <t>decision_maker_dont_know_decline</t>
+  </si>
+  <si>
+    <t>Don't know / Decline to answer</t>
+  </si>
+  <si>
     <t>Je mwenza wa mama huyu wanaishi pamoja?</t>
   </si>
   <si>
+    <t>single</t>
+  </si>
+  <si>
+    <t>Single</t>
+  </si>
+  <si>
+    <t>Sina mume</t>
+  </si>
+  <si>
+    <t>widowed</t>
+  </si>
+  <si>
+    <t>Widowed</t>
+  </si>
+  <si>
+    <t>Mjane</t>
+  </si>
+  <si>
+    <t>divorced</t>
+  </si>
+  <si>
+    <t>Divorced</t>
+  </si>
+  <si>
+    <t>Mume amefariki</t>
+  </si>
+  <si>
     <t>partner_info</t>
   </si>
   <si>
+    <t>marital_status_dont_know_decline</t>
+  </si>
+  <si>
     <t>integer</t>
   </si>
   <si>
@@ -1577,25 +2027,22 @@
     <t>Ni upi umri wa mwenza wako?</t>
   </si>
   <si>
+    <t>partner_highest_school_level</t>
+  </si>
+  <si>
+    <t>partner_no_formal_education</t>
+  </si>
+  <si>
     <t xml:space="preserve">. &gt;= 18 and .&lt;= 90 </t>
   </si>
   <si>
     <t xml:space="preserve">Please enter an age between 18 and 90 </t>
   </si>
   <si>
-    <t>pregnancy_supplements</t>
-  </si>
-  <si>
-    <t>Pregnancy supplements/FeFol</t>
-  </si>
-  <si>
-    <t>Dawa za kuongeza damu kwa mama wajawazito.</t>
-  </si>
-  <si>
     <t>select_one partner_highest_school_level</t>
   </si>
   <si>
-    <t>partner_highest_school_level</t>
+    <t>partner_incomplete_primary</t>
   </si>
   <si>
     <t xml:space="preserve">What is the highest level of school your husband/partner has attended? </t>
@@ -1604,34 +2051,13 @@
     <t>Ni kiwango gani cha elimu mume/mwenza amehitimu?</t>
   </si>
   <si>
-    <t>bp_reading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blood pressure reading </t>
-  </si>
-  <si>
-    <t>Kupima pressure</t>
-  </si>
-  <si>
-    <t>hb_test</t>
-  </si>
-  <si>
-    <t>Hb Test</t>
-  </si>
-  <si>
-    <t>Kupima wingi wa wadamu</t>
+    <t>partner_primary_education</t>
   </si>
   <si>
     <t>subgroup_multiple_wives</t>
   </si>
   <si>
-    <t>bp_test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blood group test </t>
-  </si>
-  <si>
-    <t>Kupima group la damu</t>
+    <t>partner_incomplete_secondary</t>
   </si>
   <si>
     <t>more_than_one_wife</t>
@@ -1643,112 +2069,64 @@
     <t>Je mwenza wa mama huyu ana wake wengine/wenzaambao wanaishi pamoja?</t>
   </si>
   <si>
-    <t>urine_test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Urine Test (Urinalysis) </t>
-  </si>
-  <si>
-    <t>Kupima mkoja kama mchafu.</t>
+    <t>partner_secondary</t>
   </si>
   <si>
     <t>num_wives</t>
   </si>
   <si>
+    <t>partner_completed_high_school</t>
+  </si>
+  <si>
     <t>Including you, in total, how many wives or live-in partners does your partner have?</t>
   </si>
   <si>
     <t>Ukijumuisha na wewe, kwa pamoja mume wako ana wenza wangapi?</t>
   </si>
   <si>
-    <t>ultrasound</t>
-  </si>
-  <si>
     <t>selected(${more_than_one_wife},"yes")</t>
   </si>
   <si>
-    <t>Ultrasound</t>
-  </si>
-  <si>
-    <t>Kupiga utrasound</t>
-  </si>
-  <si>
     <t xml:space="preserve">.&gt;= 1 and .&lt;= 10 </t>
   </si>
   <si>
     <t xml:space="preserve">Please enter a value between 1 and 10. </t>
   </si>
   <si>
-    <t>bp_measured</t>
-  </si>
-  <si>
-    <t>Blood pressure measured</t>
+    <t>partner_more_than_high_school</t>
+  </si>
+  <si>
+    <t>partner_school_level_dont_know_decline</t>
+  </si>
+  <si>
+    <t>yes_no_decline_to_answer</t>
   </si>
   <si>
     <t>refer_postpartum_emergency_danger_sign_flag</t>
   </si>
   <si>
-    <t>temp_measured</t>
-  </si>
-  <si>
-    <t>Temperature measured</t>
+    <t>Ndio</t>
   </si>
   <si>
     <t>if((selected(${postpartum_severe_vaginal_bleeding},"yes") and selected(${postpartum_bleeding_right_now},"yes")) or selected(${postpartum_convulsions},"yes") or selected(${postpartum_unconscious},"yes"),1,0)</t>
   </si>
   <si>
-    <t>Kupima jito la mwili</t>
-  </si>
-  <si>
     <t>refer_postpartum_other_danger_sign_flag</t>
   </si>
   <si>
-    <t>checked_anemia</t>
-  </si>
-  <si>
-    <t>Checked for anemia</t>
-  </si>
-  <si>
     <t>if(selected(${chv_thinks_needs_return_facility},"yes") or selected(${client_been_facility_3_days},"no"),1,0)</t>
   </si>
   <si>
-    <t>Kuangalia upungufu wa damu</t>
-  </si>
-  <si>
     <t>any_referral</t>
   </si>
   <si>
-    <t>breast_exam</t>
-  </si>
-  <si>
     <t>if(${refer_postpartum_emergency_danger_sign_flag}=1 or ${refer_postpartum_other_danger_sign_flag}=1,1,0)</t>
   </si>
   <si>
-    <t>Examined breast</t>
-  </si>
-  <si>
-    <t>Kufanya uchunguzi wa maziwa</t>
-  </si>
-  <si>
     <t>group_summary</t>
   </si>
   <si>
-    <t>abdominal_exam</t>
-  </si>
-  <si>
-    <t>Abdominal examination</t>
-  </si>
-  <si>
-    <t>Uchunguzi wa tumbo</t>
-  </si>
-  <si>
-    <t>genital_exam</t>
-  </si>
-  <si>
-    <t>Genitalia examination</t>
-  </si>
-  <si>
-    <t>Kuchunguza maeneo ya uzazi</t>
+    <t>decline_to_answer</t>
   </si>
   <si>
     <t>Visit Summary</t>
@@ -1772,382 +2150,37 @@
     <t>needs_referral_note</t>
   </si>
   <si>
-    <t>lower_extremity_exam</t>
-  </si>
-  <si>
     <t>You need to go to the health facility for the following reasons:</t>
   </si>
   <si>
     <t>Unahitaji kwenda kituo cha afya kwa sababu zifuatazo</t>
   </si>
   <si>
-    <t>Examination of lower extremities</t>
-  </si>
-  <si>
-    <t>Kuchunguzwa miguu</t>
-  </si>
-  <si>
     <t>${any_referral}=1</t>
   </si>
   <si>
     <t>needs_referral_emergency_danger_sign_note</t>
   </si>
   <si>
-    <t>health_education_counseling</t>
-  </si>
-  <si>
     <t>To address an emergency postpartum danger sign</t>
   </si>
   <si>
-    <t>Health education and counselling</t>
-  </si>
-  <si>
     <t>Kushughulikia dalili za hatari za dharura baada ya kujifungua</t>
   </si>
   <si>
-    <t>Elimu ya afya na ushauri</t>
-  </si>
-  <si>
     <t>${refer_postpartum_emergency_danger_sign_flag}=1</t>
   </si>
   <si>
     <t>needs_referral_other_danger_sign_note</t>
   </si>
   <si>
-    <t>Nyingine</t>
-  </si>
-  <si>
     <t>To address a postpartum danger sign</t>
   </si>
   <si>
     <t>Kushughulikia dalili za hatari baada ya kujifungua.</t>
   </si>
   <si>
-    <t>none</t>
-  </si>
-  <si>
-    <t>None of the above</t>
-  </si>
-  <si>
-    <t>Hakuna kati ya hao hapo juu.</t>
-  </si>
-  <si>
     <t>${refer_postpartum_other_danger_sign_flag}=1</t>
-  </si>
-  <si>
-    <t>baby_services_received</t>
-  </si>
-  <si>
-    <t>check_abnormalities</t>
-  </si>
-  <si>
-    <t>Check for any abnormalities</t>
-  </si>
-  <si>
-    <t>Kuangaliwa kama kuna matatizo</t>
-  </si>
-  <si>
-    <t>check_reflexes</t>
-  </si>
-  <si>
-    <t>Check reflexes</t>
-  </si>
-  <si>
-    <t>Kuangaliwa uchangamfu wa baadhi ya viungo.</t>
-  </si>
-  <si>
-    <t>cord_exam</t>
-  </si>
-  <si>
-    <t>Cord examination</t>
-  </si>
-  <si>
-    <t>Kuchunguzwa kitovu</t>
-  </si>
-  <si>
-    <t>breast_feed_demo</t>
-  </si>
-  <si>
-    <t>Breast feeding demonstration (attachment and positioning)</t>
-  </si>
-  <si>
-    <t>Kuelekezwa mbinu za unyonyeshaji (Jinsi ya kumpakata na kumueka mtoto katika matiti)</t>
-  </si>
-  <si>
-    <t>less_than_30</t>
-  </si>
-  <si>
-    <t>less than  30 mins</t>
-  </si>
-  <si>
-    <t>Chini ya dakika thelathini</t>
-  </si>
-  <si>
-    <t>30_to_1hr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30 mins - 1 hr </t>
-  </si>
-  <si>
-    <t>Kati ya dakika 30 na saa mmoja</t>
-  </si>
-  <si>
-    <t>more_than_1hr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">more than 1 hr </t>
-  </si>
-  <si>
-    <t>Zaidi ya saa mmoja</t>
-  </si>
-  <si>
-    <t>travel_time_dont_know_decline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Don't know/Decline to answer </t>
-  </si>
-  <si>
-    <t>Sijui / Siwezi kujibu</t>
-  </si>
-  <si>
-    <t>walk</t>
-  </si>
-  <si>
-    <t>Walk</t>
-  </si>
-  <si>
-    <t>Kutembea</t>
-  </si>
-  <si>
-    <t>bicycle</t>
-  </si>
-  <si>
-    <t>Bicycle</t>
-  </si>
-  <si>
-    <t>Kwa baskeli</t>
-  </si>
-  <si>
-    <t>moto</t>
-  </si>
-  <si>
-    <t>Moto</t>
-  </si>
-  <si>
-    <t>Honda</t>
-  </si>
-  <si>
-    <t>private_car</t>
-  </si>
-  <si>
-    <t>Private Car</t>
-  </si>
-  <si>
-    <t>Gari binafsi</t>
-  </si>
-  <si>
-    <t>public_bus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public Bus </t>
-  </si>
-  <si>
-    <t>Daladala</t>
-  </si>
-  <si>
-    <t>health_facility_vehicle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Health facility vehicle </t>
-  </si>
-  <si>
-    <t>Gari ya kituo cha afya</t>
-  </si>
-  <si>
-    <t>boat</t>
-  </si>
-  <si>
-    <t>Boat</t>
-  </si>
-  <si>
-    <t>Bot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other </t>
-  </si>
-  <si>
-    <t>travel_means_dont_know_decline</t>
-  </si>
-  <si>
-    <t>Don't know/Decline to answer</t>
-  </si>
-  <si>
-    <t>no_formal_education</t>
-  </si>
-  <si>
-    <t>No formal education/None</t>
-  </si>
-  <si>
-    <t>Hakusoma skuli/Hakusoma</t>
-  </si>
-  <si>
-    <t>incomplete_primary</t>
-  </si>
-  <si>
-    <t>Incomplete/some primary school (KG-Standard 5)</t>
-  </si>
-  <si>
-    <t>Hakumaliza/ kapata elimu ya nasari kaishia darasa la tano.</t>
-  </si>
-  <si>
-    <t>primary_education</t>
-  </si>
-  <si>
-    <t>Completed primary education (Standard 6)</t>
-  </si>
-  <si>
-    <t>Kamalizia elimu ya msingi (darasa la sita)</t>
-  </si>
-  <si>
-    <t>incomplete_secondary</t>
-  </si>
-  <si>
-    <t>Incomplete/some secondary school (Form 1-3)</t>
-  </si>
-  <si>
-    <t>Hakumaliza elimu ya secondari kaishia darasa la kumi na moja</t>
-  </si>
-  <si>
-    <t>secondary</t>
-  </si>
-  <si>
-    <t>Completed secondary school (Form 4)</t>
-  </si>
-  <si>
-    <t>Kaliza darasa la kumi na mbili</t>
-  </si>
-  <si>
-    <t>completed_high_school</t>
-  </si>
-  <si>
-    <t>Completed high school (Form 6)</t>
-  </si>
-  <si>
-    <t>Kamaliza kidatu cha sita</t>
-  </si>
-  <si>
-    <t>more_than_high_school</t>
-  </si>
-  <si>
-    <t>More than high school</t>
-  </si>
-  <si>
-    <t>Elimu yake zaidi ya elimu ya juu/ zaidi ya kidatu cha sita</t>
-  </si>
-  <si>
-    <t>school_level_dont_know_decline</t>
-  </si>
-  <si>
-    <t>herself</t>
-  </si>
-  <si>
-    <t>You only</t>
-  </si>
-  <si>
-    <t>Wewe peke yako</t>
-  </si>
-  <si>
-    <t>husband</t>
-  </si>
-  <si>
-    <t>Your husband/partner only</t>
-  </si>
-  <si>
-    <t>Mwenza wako</t>
-  </si>
-  <si>
-    <t>herself_and_husband</t>
-  </si>
-  <si>
-    <t>You and your husband/partner (or other family member) jointly</t>
-  </si>
-  <si>
-    <t>Ulifuatana na mume/mweza wako (or wanafamilia wengine)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Someone else </t>
-  </si>
-  <si>
-    <t>Na mtu mwengine</t>
-  </si>
-  <si>
-    <t>decision_maker_dont_know_decline</t>
-  </si>
-  <si>
-    <t>Don't know / Decline to answer</t>
-  </si>
-  <si>
-    <t>single</t>
-  </si>
-  <si>
-    <t>Single</t>
-  </si>
-  <si>
-    <t>Sina mume</t>
-  </si>
-  <si>
-    <t>widowed</t>
-  </si>
-  <si>
-    <t>Widowed</t>
-  </si>
-  <si>
-    <t>Mjane</t>
-  </si>
-  <si>
-    <t>divorced</t>
-  </si>
-  <si>
-    <t>Divorced</t>
-  </si>
-  <si>
-    <t>Mume amefariki</t>
-  </si>
-  <si>
-    <t>marital_status_dont_know_decline</t>
-  </si>
-  <si>
-    <t>partner_no_formal_education</t>
-  </si>
-  <si>
-    <t>partner_incomplete_primary</t>
-  </si>
-  <si>
-    <t>partner_primary_education</t>
-  </si>
-  <si>
-    <t>partner_incomplete_secondary</t>
-  </si>
-  <si>
-    <t>partner_secondary</t>
-  </si>
-  <si>
-    <t>partner_completed_high_school</t>
-  </si>
-  <si>
-    <t>partner_more_than_high_school</t>
-  </si>
-  <si>
-    <t>partner_school_level_dont_know_decline</t>
-  </si>
-  <si>
-    <t>yes_no_decline_to_answer</t>
-  </si>
-  <si>
-    <t>Ndio</t>
-  </si>
-  <si>
-    <t>decline_to_answer</t>
   </si>
 </sst>
 </file>
@@ -2404,13 +2437,13 @@
         <v>2</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>27</v>
@@ -2437,7 +2470,7 @@
         <v>34</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>35</v>
@@ -2454,13 +2487,13 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="F2" s="6" t="b">
         <f>FALSE()</f>
@@ -2475,7 +2508,7 @@
         <v>54</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
@@ -2486,7 +2519,7 @@
         <v>56</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
@@ -2497,7 +2530,7 @@
         <v>57</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6">
@@ -2508,7 +2541,7 @@
         <v>58</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -2516,10 +2549,10 @@
         <v>55</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
@@ -2547,24 +2580,24 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>75</v>
+      <c r="A9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -2572,10 +2605,10 @@
         <v>55</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11">
@@ -2583,123 +2616,100 @@
         <v>55</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="s">
-        <v>82</v>
+        <v>55</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" s="9"/>
+        <v>3</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>45</v>
-      </c>
+      <c r="A13" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="9"/>
     </row>
     <row r="14">
       <c r="A14" s="10" t="s">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="s">
+      <c r="B16" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C17" s="5"/>
+      <c r="B17" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="3"/>
+      <c r="A18" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" s="5"/>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="5"/>
-      <c r="R19" s="5"/>
-      <c r="S19" s="5"/>
-      <c r="T19" s="5"/>
-      <c r="U19" s="5"/>
-      <c r="V19" s="5"/>
-      <c r="W19" s="5"/>
-      <c r="X19" s="5"/>
-      <c r="Y19" s="5"/>
-      <c r="Z19" s="5"/>
+      <c r="A19" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="3"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="s">
-        <v>97</v>
+      <c r="A20" s="10" t="s">
+        <v>102</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
@@ -2711,34 +2721,41 @@
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
       <c r="L20" s="13" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="M20" s="5"/>
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>
       <c r="P20" s="5"/>
       <c r="Q20" s="5"/>
+      <c r="R20" s="5"/>
+      <c r="S20" s="5"/>
+      <c r="T20" s="5"/>
+      <c r="U20" s="5"/>
+      <c r="V20" s="5"/>
+      <c r="W20" s="5"/>
+      <c r="X20" s="5"/>
+      <c r="Y20" s="5"/>
+      <c r="Z20" s="5"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>107</v>
+        <v>102</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>106</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
-      <c r="G21" s="5" t="s">
-        <v>108</v>
-      </c>
+      <c r="G21" s="5"/>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
       <c r="L21" s="13" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M21" s="5"/>
       <c r="N21" s="5"/>
@@ -2748,24 +2765,24 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>110</v>
+        <v>102</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>108</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
       <c r="L22" s="13" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
@@ -2775,24 +2792,24 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
       <c r="L23" s="13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M23" s="5"/>
       <c r="N23" s="5"/>
@@ -2802,22 +2819,24 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B24" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="C24" s="15"/>
+        <v>102</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" s="5"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
+      <c r="G24" s="5" t="s">
+        <v>109</v>
+      </c>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
-      <c r="L24" s="16" t="s">
-        <v>119</v>
+      <c r="L24" s="13" t="s">
+        <v>116</v>
       </c>
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
@@ -2827,10 +2846,10 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>121</v>
+        <v>102</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>117</v>
       </c>
       <c r="C25" s="15"/>
       <c r="D25" s="5"/>
@@ -2841,8 +2860,8 @@
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
-      <c r="L25" s="13" t="s">
-        <v>123</v>
+      <c r="L25" s="16" t="s">
+        <v>120</v>
       </c>
       <c r="M25" s="5"/>
       <c r="N25" s="5"/>
@@ -2852,12 +2871,12 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="C26" s="5"/>
+        <v>102</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C26" s="15"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -2866,21 +2885,21 @@
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
-      <c r="L26" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="M26" s="18"/>
-      <c r="N26" s="18"/>
+      <c r="L26" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
       <c r="O26" s="5"/>
       <c r="P26" s="5"/>
       <c r="Q26" s="5"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>128</v>
+        <v>102</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>125</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
@@ -2891,8 +2910,8 @@
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
-      <c r="L27" s="13" t="s">
-        <v>130</v>
+      <c r="L27" s="17" t="s">
+        <v>127</v>
       </c>
       <c r="M27" s="18"/>
       <c r="N27" s="18"/>
@@ -2902,10 +2921,10 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
@@ -2919,15 +2938,15 @@
       <c r="L28" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="M28" s="5"/>
-      <c r="N28" s="5"/>
+      <c r="M28" s="18"/>
+      <c r="N28" s="18"/>
       <c r="O28" s="5"/>
       <c r="P28" s="5"/>
       <c r="Q28" s="5"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>133</v>
@@ -2941,16 +2960,21 @@
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
-      <c r="L29" s="19" t="s">
-        <v>135</v>
-      </c>
+      <c r="L29" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="5"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
@@ -2961,20 +2985,15 @@
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
       <c r="K30" s="5"/>
-      <c r="L30" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="M30" s="18"/>
-      <c r="N30" s="18"/>
-      <c r="O30" s="5"/>
-      <c r="P30" s="5"/>
-      <c r="Q30" s="5"/>
+      <c r="L30" s="19" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B31" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B31" s="11" t="s">
         <v>140</v>
       </c>
       <c r="C31" s="5"/>
@@ -2986,18 +3005,18 @@
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
-      <c r="L31" s="20">
-        <v>7.0</v>
-      </c>
-      <c r="M31" s="5"/>
-      <c r="N31" s="5"/>
+      <c r="L31" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="M31" s="18"/>
+      <c r="N31" s="18"/>
       <c r="O31" s="5"/>
       <c r="P31" s="5"/>
       <c r="Q31" s="5"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B32" s="10" t="s">
         <v>142</v>
@@ -3012,7 +3031,7 @@
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
       <c r="L32" s="20">
-        <v>30.0</v>
+        <v>7.0</v>
       </c>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
@@ -3022,10 +3041,10 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>144</v>
+        <v>102</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>146</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
@@ -3036,21 +3055,21 @@
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
-      <c r="L33" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="M33" s="18"/>
-      <c r="N33" s="18"/>
+      <c r="L33" s="20">
+        <v>30.0</v>
+      </c>
+      <c r="M33" s="5"/>
+      <c r="N33" s="5"/>
       <c r="O33" s="5"/>
       <c r="P33" s="5"/>
       <c r="Q33" s="5"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
@@ -3072,10 +3091,10 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
@@ -3087,20 +3106,20 @@
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
       <c r="L35" s="21" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M35" s="18"/>
-      <c r="N35" s="5"/>
+      <c r="N35" s="18"/>
       <c r="O35" s="5"/>
       <c r="P35" s="5"/>
       <c r="Q35" s="5"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
@@ -3112,7 +3131,7 @@
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
       <c r="L36" s="21" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M36" s="18"/>
       <c r="N36" s="5"/>
@@ -3122,10 +3141,10 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>57</v>
+        <v>102</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>157</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
@@ -3136,8 +3155,8 @@
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
-      <c r="L37" s="16" t="s">
-        <v>157</v>
+      <c r="L37" s="21" t="s">
+        <v>160</v>
       </c>
       <c r="M37" s="18"/>
       <c r="N37" s="5"/>
@@ -3147,10 +3166,10 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>158</v>
+        <v>102</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>57</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
@@ -3161,8 +3180,8 @@
       <c r="I38" s="5"/>
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
-      <c r="L38" s="13" t="s">
-        <v>160</v>
+      <c r="L38" s="16" t="s">
+        <v>161</v>
       </c>
       <c r="M38" s="18"/>
       <c r="N38" s="5"/>
@@ -3171,21 +3190,33 @@
       <c r="Q38" s="5"/>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>162</v>
+      <c r="A39" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>163</v>
       </c>
       <c r="C39" s="5"/>
-      <c r="G39" s="2"/>
-      <c r="L39" s="22" t="s">
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="13" t="s">
         <v>164</v>
       </c>
+      <c r="M39" s="18"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="5"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>166</v>
@@ -3197,263 +3228,256 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>63</v>
+      <c r="A41" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>169</v>
       </c>
       <c r="C41" s="5"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="23"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5"/>
-      <c r="J41" s="5"/>
-      <c r="K41" s="5"/>
-      <c r="L41" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="M41" s="18"/>
-      <c r="N41" s="18"/>
-      <c r="O41" s="5"/>
-      <c r="P41" s="5"/>
-      <c r="Q41" s="5"/>
-      <c r="R41" s="5"/>
-      <c r="S41" s="5"/>
-      <c r="T41" s="5"/>
-      <c r="U41" s="5"/>
-      <c r="V41" s="5"/>
-      <c r="W41" s="5"/>
-      <c r="X41" s="5"/>
-      <c r="Y41" s="5"/>
-      <c r="Z41" s="5"/>
+      <c r="G41" s="2"/>
+      <c r="L41" s="22" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="s">
-        <v>41</v>
+        <v>102</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="D42" s="24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C42" s="5"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="23"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="5"/>
+      <c r="L42" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="G42" s="2" t="s">
+      <c r="M42" s="18"/>
+      <c r="N42" s="18"/>
+      <c r="O42" s="5"/>
+      <c r="P42" s="5"/>
+      <c r="Q42" s="5"/>
+      <c r="R42" s="5"/>
+      <c r="S42" s="5"/>
+      <c r="T42" s="5"/>
+      <c r="U42" s="5"/>
+      <c r="V42" s="5"/>
+      <c r="W42" s="5"/>
+      <c r="X42" s="5"/>
+      <c r="Y42" s="5"/>
+      <c r="Z42" s="5"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="B43" s="5" t="s">
+      <c r="C43" s="5"/>
+      <c r="D43" s="24"/>
+      <c r="G43" s="2"/>
+      <c r="L43" s="22" t="s">
         <v>177</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="D43" s="22" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="s">
-        <v>176</v>
+        <v>39</v>
       </c>
       <c r="B44" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="D44" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="C44" s="13" t="s">
+      <c r="G44" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="D44" s="16" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="D45" s="13" t="s">
+      <c r="D45" s="22" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B46" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C46" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="C46" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="D46" s="7" t="s">
+      <c r="D46" s="16" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B47" s="25" t="s">
-        <v>171</v>
+      <c r="A47" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="D47" s="13" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="25" t="s">
-        <v>191</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>194</v>
+      <c r="A48" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>176</v>
+        <v>83</v>
       </c>
       <c r="B49" s="25" t="s">
-        <v>195</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="B50" s="25" t="s">
-        <v>191</v>
+        <v>199</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>198</v>
+        <v>182</v>
       </c>
       <c r="B51" s="25" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>176</v>
+        <v>83</v>
       </c>
       <c r="B52" s="25" t="s">
-        <v>202</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>41</v>
+        <v>206</v>
       </c>
       <c r="B53" s="25" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>175</v>
+        <v>209</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B54" s="25" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B55" s="25" t="s">
-        <v>210</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="G55" s="2" t="s">
-        <v>211</v>
+        <v>181</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>213</v>
+        <v>182</v>
       </c>
       <c r="B56" s="25" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>17</v>
+        <v>217</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>213</v>
+        <v>39</v>
       </c>
       <c r="B57" s="25" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="D57" s="26" t="s">
-        <v>219</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>17</v>
+        <v>41</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B58" s="25" t="s">
         <v>222</v>
@@ -3462,7 +3486,7 @@
         <v>223</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>17</v>
@@ -3470,179 +3494,179 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>82</v>
+        <v>221</v>
       </c>
       <c r="B59" s="25" t="s">
-        <v>210</v>
+        <v>226</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D59" s="26" t="s">
+        <v>228</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B60" s="25" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F60" s="2" t="s">
-        <v>229</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>176</v>
+        <v>83</v>
       </c>
       <c r="B61" s="25" t="s">
-        <v>230</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="62" ht="15.75" customHeight="1">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="62">
       <c r="A62" s="2" t="s">
-        <v>176</v>
+        <v>221</v>
       </c>
       <c r="B62" s="25" t="s">
         <v>234</v>
       </c>
       <c r="C62" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D62" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="E62" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F62" s="2" t="s">
         <v>237</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>82</v>
+        <v>182</v>
       </c>
       <c r="B63" s="25" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="64">
+        <v>238</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>82</v>
+        <v>182</v>
       </c>
       <c r="B64" s="25" t="s">
-        <v>199</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="B65" s="25" t="s">
-        <v>239</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>175</v>
+        <v>214</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>176</v>
+        <v>83</v>
       </c>
       <c r="B66" s="25" t="s">
-        <v>244</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>246</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B67" s="25" t="s">
         <v>247</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>45</v>
+        <v>248</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>251</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>211</v>
+        <v>181</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>213</v>
+        <v>182</v>
       </c>
       <c r="B68" s="25" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>17</v>
+        <v>253</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>213</v>
+        <v>39</v>
       </c>
       <c r="B69" s="25" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>17</v>
+        <v>41</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B70" s="25" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>17</v>
@@ -3650,16 +3674,16 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B71" s="25" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>17</v>
@@ -3667,16 +3691,16 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B72" s="25" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>17</v>
@@ -3684,16 +3708,16 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B73" s="25" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>269</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>17</v>
@@ -3701,16 +3725,16 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B74" s="25" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>17</v>
@@ -3718,16 +3742,16 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B75" s="25" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>276</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>17</v>
@@ -3735,16 +3759,16 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B76" s="25" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>279</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>17</v>
@@ -3752,16 +3776,16 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B77" s="25" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>17</v>
@@ -3769,16 +3793,16 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B78" s="25" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>284</v>
+        <v>287</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>288</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>17</v>
@@ -3786,16 +3810,16 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B79" s="25" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>17</v>
@@ -3803,16 +3827,16 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B80" s="25" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>17</v>
@@ -3820,118 +3844,118 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>82</v>
+        <v>221</v>
       </c>
       <c r="B81" s="25" t="s">
-        <v>247</v>
+        <v>296</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>292</v>
+        <v>221</v>
       </c>
       <c r="B82" s="25" t="s">
-        <v>23</v>
+        <v>300</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F82" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="83" ht="15.75" customHeight="1">
+    </row>
+    <row r="83">
       <c r="A83" s="2" t="s">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="B83" s="25" t="s">
-        <v>296</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="D83" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="E83" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B84" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="E84" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F83" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="B84" s="25" t="s">
-        <v>301</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>303</v>
-      </c>
       <c r="F84" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="85">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="2" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B85" s="25" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="2" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B86" s="25" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>311</v>
+        <v>314</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>316</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>176</v>
+        <v>221</v>
       </c>
       <c r="B87" s="25" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>317</v>
@@ -3939,365 +3963,284 @@
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="2" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B88" s="25" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>82</v>
+        <v>182</v>
       </c>
       <c r="B89" s="25" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="90">
+        <v>326</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="2" t="s">
-        <v>41</v>
+        <v>182</v>
       </c>
       <c r="B90" s="25" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="G90" s="2"/>
+        <v>334</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>176</v>
+        <v>83</v>
       </c>
       <c r="B91" s="25" t="s">
-        <v>327</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="G91" s="2"/>
+        <v>247</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>176</v>
+        <v>39</v>
       </c>
       <c r="B92" s="25" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>333</v>
+        <v>337</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>251</v>
       </c>
       <c r="G92" s="2"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B93" s="25" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>336</v>
+        <v>340</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>342</v>
       </c>
       <c r="G93" s="2"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>82</v>
+        <v>182</v>
       </c>
       <c r="B94" s="25" t="s">
-        <v>324</v>
-      </c>
-      <c r="C94" s="2"/>
+        <v>343</v>
+      </c>
+      <c r="C94" s="22" t="s">
+        <v>344</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>347</v>
+      </c>
       <c r="G94" s="2"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>41</v>
+        <v>182</v>
       </c>
       <c r="B95" s="25" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>340</v>
+        <v>349</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>350</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>175</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="G95" s="2"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>213</v>
+        <v>182</v>
       </c>
       <c r="B96" s="25" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="D96" s="4" t="s">
-        <v>344</v>
+        <v>352</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>347</v>
       </c>
       <c r="G96" s="2"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>213</v>
+        <v>182</v>
       </c>
       <c r="B97" s="25" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="F97" s="22" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="G97" s="2"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B98" s="25" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C98" s="2"/>
-      <c r="F98" s="22"/>
       <c r="G98" s="2"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B99" s="25" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="D99" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="F99" s="22" t="s">
-        <v>355</v>
+        <v>360</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>362</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="B100" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C100" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="D100" s="27" t="s">
+      <c r="A100" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B100" s="25" t="s">
+        <v>363</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G100" s="2"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B101" s="25" t="s">
+        <v>366</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="F101" s="22" t="s">
+        <v>370</v>
+      </c>
+      <c r="G101" s="2"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B102" s="25" t="s">
         <v>358</v>
       </c>
-      <c r="E100" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="F100" s="8"/>
-      <c r="G100" s="10"/>
-      <c r="H100" s="5"/>
-      <c r="I100" s="5"/>
-      <c r="J100" s="5"/>
-      <c r="K100" s="5"/>
-      <c r="L100" s="5"/>
-      <c r="M100" s="5"/>
-      <c r="N100" s="5"/>
-      <c r="O100" s="5"/>
-      <c r="P100" s="5"/>
-      <c r="Q100" s="5"/>
-      <c r="R100" s="5"/>
-      <c r="S100" s="5"/>
-      <c r="T100" s="5"/>
-      <c r="U100" s="5"/>
-      <c r="V100" s="5"/>
-      <c r="W100" s="5"/>
-      <c r="X100" s="5"/>
-      <c r="Y100" s="5"/>
-      <c r="Z100" s="5"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="B101" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C101" s="8" t="s">
-        <v>362</v>
-      </c>
-      <c r="D101" s="27" t="s">
-        <v>363</v>
-      </c>
-      <c r="E101" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="F101" s="8" t="s">
-        <v>364</v>
-      </c>
-      <c r="G101" s="10"/>
-      <c r="H101" s="5"/>
-      <c r="I101" s="5"/>
-      <c r="J101" s="5"/>
-      <c r="K101" s="5"/>
-      <c r="L101" s="5"/>
-      <c r="M101" s="13" t="s">
-        <v>365</v>
-      </c>
-      <c r="N101" s="5"/>
-      <c r="O101" s="5"/>
-      <c r="P101" s="5"/>
-      <c r="Q101" s="5"/>
-      <c r="R101" s="5"/>
-      <c r="S101" s="5"/>
-      <c r="T101" s="5"/>
-      <c r="U101" s="5"/>
-      <c r="V101" s="5"/>
-      <c r="W101" s="5"/>
-      <c r="X101" s="5"/>
-      <c r="Y101" s="5"/>
-      <c r="Z101" s="5"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B102" s="14" t="s">
-        <v>367</v>
-      </c>
-      <c r="C102" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D102" s="5"/>
-      <c r="E102" s="15"/>
-      <c r="F102" s="8"/>
-      <c r="G102" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="H102" s="5"/>
-      <c r="I102" s="5"/>
-      <c r="J102" s="5"/>
-      <c r="K102" s="5"/>
-      <c r="L102" s="5"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="5"/>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="5"/>
-      <c r="R102" s="5"/>
-      <c r="S102" s="5"/>
-      <c r="T102" s="5"/>
-      <c r="U102" s="5"/>
-      <c r="V102" s="5"/>
-      <c r="W102" s="5"/>
-      <c r="X102" s="5"/>
-      <c r="Y102" s="5"/>
-      <c r="Z102" s="5"/>
-    </row>
-    <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="B103" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="C103" s="8" t="s">
-        <v>369</v>
-      </c>
-      <c r="D103" s="7" t="s">
+      <c r="C102" s="2"/>
+      <c r="F102" s="22"/>
+      <c r="G102" s="2"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B103" s="25" t="s">
         <v>371</v>
       </c>
-      <c r="E103" s="15" t="s">
-        <v>372</v>
-      </c>
-      <c r="F103" s="8" t="s">
+      <c r="C103" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="G103" s="10"/>
-      <c r="H103" s="5"/>
-      <c r="I103" s="5"/>
-      <c r="J103" s="5"/>
-      <c r="K103" s="5"/>
-      <c r="L103" s="5"/>
-      <c r="M103" s="13" t="s">
+      <c r="D103" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="N103" s="5"/>
-      <c r="O103" s="5"/>
-      <c r="P103" s="5"/>
-      <c r="Q103" s="5"/>
-      <c r="R103" s="5"/>
-      <c r="S103" s="5"/>
-      <c r="T103" s="5"/>
-      <c r="U103" s="5"/>
-      <c r="V103" s="5"/>
-      <c r="W103" s="5"/>
-      <c r="X103" s="5"/>
-      <c r="Y103" s="5"/>
-      <c r="Z103" s="5"/>
+      <c r="F103" s="22" t="s">
+        <v>375</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="8" t="s">
         <v>376</v>
       </c>
       <c r="B104" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C104" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="C104" s="8" t="s">
+      <c r="D104" s="27" t="s">
         <v>378</v>
       </c>
-      <c r="D104" s="14" t="s">
-        <v>379</v>
-      </c>
-      <c r="E104" s="8" t="s">
+      <c r="E104" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="F104" s="8" t="s">
-        <v>380</v>
-      </c>
-      <c r="G104" s="8"/>
-      <c r="H104" s="8"/>
+      <c r="F104" s="8"/>
+      <c r="G104" s="10"/>
+      <c r="H104" s="5"/>
       <c r="I104" s="5"/>
       <c r="J104" s="5"/>
       <c r="K104" s="5"/>
@@ -4319,22 +4262,32 @@
     </row>
     <row r="105">
       <c r="A105" s="8" t="s">
-        <v>82</v>
+        <v>379</v>
       </c>
       <c r="B105" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="C105" s="8"/>
-      <c r="D105" s="8"/>
-      <c r="E105" s="8"/>
-      <c r="F105" s="8"/>
-      <c r="G105" s="8"/>
-      <c r="H105" s="8"/>
+        <v>59</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>380</v>
+      </c>
+      <c r="D105" s="27" t="s">
+        <v>381</v>
+      </c>
+      <c r="E105" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="F105" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="G105" s="10"/>
+      <c r="H105" s="5"/>
       <c r="I105" s="5"/>
       <c r="J105" s="5"/>
       <c r="K105" s="5"/>
       <c r="L105" s="5"/>
-      <c r="M105" s="5"/>
+      <c r="M105" s="13" t="s">
+        <v>383</v>
+      </c>
       <c r="N105" s="5"/>
       <c r="O105" s="5"/>
       <c r="P105" s="5"/>
@@ -4351,23 +4304,21 @@
     </row>
     <row r="106">
       <c r="A106" s="8" t="s">
-        <v>381</v>
-      </c>
-      <c r="B106" s="8" t="s">
-        <v>382</v>
+        <v>39</v>
+      </c>
+      <c r="B106" s="14" t="s">
+        <v>384</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>383</v>
-      </c>
-      <c r="D106" s="14" t="s">
-        <v>384</v>
-      </c>
-      <c r="E106" s="8" t="s">
-        <v>17</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="D106" s="5"/>
+      <c r="E106" s="15"/>
       <c r="F106" s="8"/>
-      <c r="G106" s="8"/>
-      <c r="H106" s="8"/>
+      <c r="G106" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="H106" s="5"/>
       <c r="I106" s="5"/>
       <c r="J106" s="5"/>
       <c r="K106" s="5"/>
@@ -4387,32 +4338,34 @@
       <c r="Y106" s="5"/>
       <c r="Z106" s="5"/>
     </row>
-    <row r="107">
+    <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="B107" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C107" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="B107" s="8" t="s">
+      <c r="D107" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="C107" s="8" t="s">
+      <c r="E107" s="15" t="s">
         <v>388</v>
       </c>
-      <c r="D107" s="14" t="s">
+      <c r="F107" s="8" t="s">
         <v>389</v>
       </c>
-      <c r="E107" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F107" s="8" t="s">
-        <v>390</v>
-      </c>
-      <c r="G107" s="8"/>
-      <c r="H107" s="8"/>
+      <c r="G107" s="10"/>
+      <c r="H107" s="5"/>
       <c r="I107" s="5"/>
       <c r="J107" s="5"/>
       <c r="K107" s="5"/>
       <c r="L107" s="5"/>
-      <c r="M107" s="5"/>
+      <c r="M107" s="13" t="s">
+        <v>390</v>
+      </c>
       <c r="N107" s="5"/>
       <c r="O107" s="5"/>
       <c r="P107" s="5"/>
@@ -4429,22 +4382,22 @@
     </row>
     <row r="108">
       <c r="A108" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="B108" s="8" t="s">
         <v>392</v>
       </c>
-      <c r="B108" s="8" t="s">
+      <c r="C108" s="8" t="s">
         <v>393</v>
       </c>
-      <c r="C108" s="8" t="s">
+      <c r="D108" s="14" t="s">
         <v>394</v>
-      </c>
-      <c r="D108" s="14" t="s">
-        <v>395</v>
       </c>
       <c r="E108" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F108" s="8" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G108" s="8"/>
       <c r="H108" s="8"/>
@@ -4469,36 +4422,48 @@
     </row>
     <row r="109">
       <c r="A109" s="8" t="s">
-        <v>397</v>
+        <v>83</v>
       </c>
       <c r="B109" s="8" t="s">
-        <v>398</v>
-      </c>
-      <c r="C109" s="8" t="s">
-        <v>399</v>
-      </c>
-      <c r="D109" s="14" t="s">
-        <v>400</v>
-      </c>
-      <c r="E109" s="8" t="s">
-        <v>17</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="C109" s="8"/>
+      <c r="D109" s="8"/>
+      <c r="E109" s="8"/>
       <c r="F109" s="8"/>
       <c r="G109" s="8"/>
       <c r="H109" s="8"/>
+      <c r="I109" s="5"/>
+      <c r="J109" s="5"/>
+      <c r="K109" s="5"/>
+      <c r="L109" s="5"/>
+      <c r="M109" s="5"/>
+      <c r="N109" s="5"/>
+      <c r="O109" s="5"/>
+      <c r="P109" s="5"/>
+      <c r="Q109" s="5"/>
+      <c r="R109" s="5"/>
+      <c r="S109" s="5"/>
+      <c r="T109" s="5"/>
+      <c r="U109" s="5"/>
+      <c r="V109" s="5"/>
+      <c r="W109" s="5"/>
+      <c r="X109" s="5"/>
+      <c r="Y109" s="5"/>
+      <c r="Z109" s="5"/>
     </row>
     <row r="110">
       <c r="A110" s="8" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="B110" s="8" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C110" s="8" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="D110" s="14" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="E110" s="8" t="s">
         <v>17</v>
@@ -4506,55 +4471,119 @@
       <c r="F110" s="8"/>
       <c r="G110" s="8"/>
       <c r="H110" s="8"/>
+      <c r="I110" s="5"/>
+      <c r="J110" s="5"/>
+      <c r="K110" s="5"/>
+      <c r="L110" s="5"/>
+      <c r="M110" s="5"/>
+      <c r="N110" s="5"/>
+      <c r="O110" s="5"/>
+      <c r="P110" s="5"/>
+      <c r="Q110" s="5"/>
+      <c r="R110" s="5"/>
+      <c r="S110" s="5"/>
+      <c r="T110" s="5"/>
+      <c r="U110" s="5"/>
+      <c r="V110" s="5"/>
+      <c r="W110" s="5"/>
+      <c r="X110" s="5"/>
+      <c r="Y110" s="5"/>
+      <c r="Z110" s="5"/>
     </row>
     <row r="111">
       <c r="A111" s="8" t="s">
-        <v>82</v>
+        <v>400</v>
       </c>
       <c r="B111" s="8" t="s">
-        <v>350</v>
-      </c>
-      <c r="C111" s="8"/>
-      <c r="D111" s="8"/>
-      <c r="E111" s="8"/>
-      <c r="F111" s="8"/>
+        <v>401</v>
+      </c>
+      <c r="C111" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="D111" s="14" t="s">
+        <v>403</v>
+      </c>
+      <c r="E111" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F111" s="8" t="s">
+        <v>404</v>
+      </c>
       <c r="G111" s="8"/>
       <c r="H111" s="8"/>
+      <c r="I111" s="5"/>
+      <c r="J111" s="5"/>
+      <c r="K111" s="5"/>
+      <c r="L111" s="5"/>
+      <c r="M111" s="5"/>
+      <c r="N111" s="5"/>
+      <c r="O111" s="5"/>
+      <c r="P111" s="5"/>
+      <c r="Q111" s="5"/>
+      <c r="R111" s="5"/>
+      <c r="S111" s="5"/>
+      <c r="T111" s="5"/>
+      <c r="U111" s="5"/>
+      <c r="V111" s="5"/>
+      <c r="W111" s="5"/>
+      <c r="X111" s="5"/>
+      <c r="Y111" s="5"/>
+      <c r="Z111" s="5"/>
     </row>
     <row r="112">
       <c r="A112" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="B112" s="8" t="s">
         <v>406</v>
       </c>
-      <c r="B112" s="14" t="s">
+      <c r="C112" s="8" t="s">
         <v>407</v>
       </c>
-      <c r="C112" s="8" t="s">
+      <c r="D112" s="14" t="s">
         <v>408</v>
       </c>
-      <c r="D112" s="14" t="s">
+      <c r="E112" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F112" s="8" t="s">
         <v>409</v>
-      </c>
-      <c r="E112" s="8"/>
-      <c r="F112" s="14" t="s">
-        <v>410</v>
       </c>
       <c r="G112" s="8"/>
       <c r="H112" s="8"/>
+      <c r="I112" s="5"/>
+      <c r="J112" s="5"/>
+      <c r="K112" s="5"/>
+      <c r="L112" s="5"/>
+      <c r="M112" s="5"/>
+      <c r="N112" s="5"/>
+      <c r="O112" s="5"/>
+      <c r="P112" s="5"/>
+      <c r="Q112" s="5"/>
+      <c r="R112" s="5"/>
+      <c r="S112" s="5"/>
+      <c r="T112" s="5"/>
+      <c r="U112" s="5"/>
+      <c r="V112" s="5"/>
+      <c r="W112" s="5"/>
+      <c r="X112" s="5"/>
+      <c r="Y112" s="5"/>
+      <c r="Z112" s="5"/>
     </row>
     <row r="113">
-      <c r="A113" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="B113" s="14" t="s">
+      <c r="A113" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="B113" s="8" t="s">
         <v>411</v>
       </c>
-      <c r="C113" s="14" t="s">
+      <c r="C113" s="8" t="s">
         <v>412</v>
       </c>
       <c r="D113" s="14" t="s">
-        <v>414</v>
-      </c>
-      <c r="E113" s="14" t="s">
+        <v>413</v>
+      </c>
+      <c r="E113" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F113" s="8"/>
@@ -4562,201 +4591,131 @@
       <c r="H113" s="8"/>
     </row>
     <row r="114">
-      <c r="A114" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="B114" s="14" t="s">
-        <v>407</v>
-      </c>
-      <c r="C114" s="8"/>
-      <c r="D114" s="8"/>
-      <c r="E114" s="8"/>
-      <c r="F114" s="8"/>
+      <c r="A114" s="8" t="s">
+        <v>414</v>
+      </c>
+      <c r="B114" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="C114" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="D114" s="14" t="s">
+        <v>417</v>
+      </c>
+      <c r="E114" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F114" s="14" t="s">
+        <v>347</v>
+      </c>
       <c r="G114" s="8"/>
       <c r="H114" s="8"/>
     </row>
     <row r="115">
-      <c r="A115" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="B115" s="14" t="s">
-        <v>415</v>
-      </c>
-      <c r="C115" s="8" t="s">
-        <v>408</v>
-      </c>
-      <c r="D115" s="14" t="s">
-        <v>409</v>
-      </c>
+      <c r="A115" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B115" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="C115" s="8"/>
+      <c r="D115" s="8"/>
       <c r="E115" s="8"/>
-      <c r="F115" s="14" t="s">
-        <v>416</v>
-      </c>
+      <c r="F115" s="8"/>
       <c r="G115" s="8"/>
       <c r="H115" s="8"/>
     </row>
     <row r="116">
-      <c r="A116" s="10" t="s">
-        <v>417</v>
-      </c>
-      <c r="B116" s="28" t="s">
+      <c r="A116" s="8" t="s">
         <v>418</v>
       </c>
-      <c r="C116" s="29" t="s">
+      <c r="B116" s="14" t="s">
         <v>419</v>
       </c>
-      <c r="D116" s="7" t="s">
-        <v>420</v>
-      </c>
-      <c r="E116" s="11" t="s">
+      <c r="C116" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="D116" s="14" t="s">
+        <v>423</v>
+      </c>
+      <c r="E116" s="8"/>
+      <c r="F116" s="14" t="s">
+        <v>424</v>
+      </c>
+      <c r="G116" s="8"/>
+      <c r="H116" s="8"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="B117" s="14" t="s">
+        <v>425</v>
+      </c>
+      <c r="C117" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="D117" s="14" t="s">
+        <v>427</v>
+      </c>
+      <c r="E117" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F116" s="11"/>
-      <c r="G116" s="10"/>
-      <c r="H116" s="5"/>
-      <c r="I116" s="5"/>
-      <c r="J116" s="5"/>
-      <c r="K116" s="5"/>
-      <c r="L116" s="5"/>
-      <c r="M116" s="5"/>
-      <c r="N116" s="5"/>
-      <c r="O116" s="5"/>
-      <c r="P116" s="5"/>
-      <c r="Q116" s="5"/>
-      <c r="R116" s="5"/>
-      <c r="S116" s="5"/>
-      <c r="T116" s="5"/>
-      <c r="U116" s="5"/>
-      <c r="V116" s="5"/>
-      <c r="W116" s="5"/>
-      <c r="X116" s="5"/>
-      <c r="Y116" s="5"/>
-      <c r="Z116" s="5"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B117" s="28" t="s">
+      <c r="F117" s="8"/>
+      <c r="G117" s="8"/>
+      <c r="H117" s="8"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="B118" s="14" t="s">
+        <v>419</v>
+      </c>
+      <c r="C118" s="8"/>
+      <c r="D118" s="8"/>
+      <c r="E118" s="8"/>
+      <c r="F118" s="8"/>
+      <c r="G118" s="8"/>
+      <c r="H118" s="8"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B119" s="14" t="s">
+        <v>431</v>
+      </c>
+      <c r="C119" s="8" t="s">
         <v>421</v>
       </c>
-      <c r="C117" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="D117" s="5"/>
-      <c r="E117" s="5"/>
-      <c r="F117" s="11"/>
-      <c r="G117" s="10" t="s">
-        <v>175</v>
-      </c>
-      <c r="H117" s="5"/>
-      <c r="I117" s="5"/>
-      <c r="J117" s="5"/>
-      <c r="K117" s="5"/>
-      <c r="L117" s="5"/>
-      <c r="M117" s="5"/>
-      <c r="N117" s="5"/>
-      <c r="O117" s="5"/>
-      <c r="P117" s="5"/>
-      <c r="Q117" s="5"/>
-      <c r="R117" s="5"/>
-      <c r="S117" s="5"/>
-      <c r="T117" s="5"/>
-      <c r="U117" s="5"/>
-      <c r="V117" s="5"/>
-      <c r="W117" s="5"/>
-      <c r="X117" s="5"/>
-      <c r="Y117" s="5"/>
-      <c r="Z117" s="5"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="10" t="s">
-        <v>422</v>
-      </c>
-      <c r="B118" s="28" t="s">
+      <c r="D119" s="14" t="s">
         <v>423</v>
       </c>
-      <c r="C118" s="31" t="s">
-        <v>424</v>
-      </c>
-      <c r="D118" s="27" t="s">
-        <v>425</v>
-      </c>
-      <c r="E118" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F118" s="11"/>
-      <c r="G118" s="10"/>
-      <c r="H118" s="5"/>
-      <c r="I118" s="5"/>
-      <c r="J118" s="5"/>
-      <c r="K118" s="5"/>
-      <c r="L118" s="5"/>
-      <c r="M118" s="5"/>
-      <c r="N118" s="5"/>
-      <c r="O118" s="5"/>
-      <c r="P118" s="5"/>
-      <c r="Q118" s="5"/>
-      <c r="R118" s="5"/>
-      <c r="S118" s="5"/>
-      <c r="T118" s="5"/>
-      <c r="U118" s="5"/>
-      <c r="V118" s="5"/>
-      <c r="W118" s="5"/>
-      <c r="X118" s="5"/>
-      <c r="Y118" s="5"/>
-      <c r="Z118" s="5"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="10" t="s">
-        <v>376</v>
-      </c>
-      <c r="B119" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="C119" s="10" t="s">
-        <v>378</v>
-      </c>
-      <c r="D119" s="27" t="s">
-        <v>427</v>
-      </c>
-      <c r="E119" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F119" s="11" t="s">
-        <v>428</v>
-      </c>
-      <c r="G119" s="10"/>
-      <c r="H119" s="5"/>
-      <c r="I119" s="5"/>
-      <c r="J119" s="5"/>
-      <c r="K119" s="5"/>
-      <c r="L119" s="5"/>
-      <c r="M119" s="5"/>
-      <c r="N119" s="5"/>
-      <c r="O119" s="5"/>
-      <c r="P119" s="5"/>
-      <c r="Q119" s="5"/>
-      <c r="R119" s="5"/>
-      <c r="S119" s="5"/>
-      <c r="T119" s="5"/>
-      <c r="U119" s="5"/>
-      <c r="V119" s="5"/>
-      <c r="W119" s="5"/>
-      <c r="X119" s="5"/>
-      <c r="Y119" s="5"/>
-      <c r="Z119" s="5"/>
+      <c r="E119" s="8"/>
+      <c r="F119" s="14" t="s">
+        <v>432</v>
+      </c>
+      <c r="G119" s="8"/>
+      <c r="H119" s="8"/>
     </row>
     <row r="120">
       <c r="A120" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="B120" s="10" t="s">
-        <v>421</v>
-      </c>
-      <c r="C120" s="32"/>
-      <c r="D120" s="5"/>
-      <c r="E120" s="5"/>
+        <v>434</v>
+      </c>
+      <c r="B120" s="28" t="s">
+        <v>436</v>
+      </c>
+      <c r="C120" s="29" t="s">
+        <v>441</v>
+      </c>
+      <c r="D120" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="E120" s="11" t="s">
+        <v>17</v>
+      </c>
       <c r="F120" s="11"/>
       <c r="G120" s="10"/>
       <c r="H120" s="5"/>
@@ -4781,22 +4740,20 @@
     </row>
     <row r="121">
       <c r="A121" s="10" t="s">
-        <v>429</v>
+        <v>39</v>
       </c>
       <c r="B121" s="28" t="s">
-        <v>430</v>
-      </c>
-      <c r="C121" s="31" t="s">
-        <v>431</v>
-      </c>
-      <c r="D121" s="27" t="s">
-        <v>432</v>
-      </c>
-      <c r="E121" s="5" t="s">
-        <v>17</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="C121" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="D121" s="5"/>
+      <c r="E121" s="5"/>
       <c r="F121" s="11"/>
-      <c r="G121" s="10"/>
+      <c r="G121" s="10" t="s">
+        <v>181</v>
+      </c>
       <c r="H121" s="5"/>
       <c r="I121" s="5"/>
       <c r="J121" s="5"/>
@@ -4819,16 +4776,16 @@
     </row>
     <row r="122">
       <c r="A122" s="10" t="s">
-        <v>433</v>
+        <v>466</v>
       </c>
       <c r="B122" s="28" t="s">
-        <v>434</v>
+        <v>467</v>
       </c>
       <c r="C122" s="31" t="s">
-        <v>435</v>
+        <v>468</v>
       </c>
       <c r="D122" s="27" t="s">
-        <v>436</v>
+        <v>476</v>
       </c>
       <c r="E122" s="5" t="s">
         <v>17</v>
@@ -4857,19 +4814,23 @@
     </row>
     <row r="123">
       <c r="A123" s="10" t="s">
-        <v>433</v>
+        <v>391</v>
       </c>
       <c r="B123" s="10" t="s">
-        <v>437</v>
-      </c>
-      <c r="C123" s="33" t="s">
-        <v>438</v>
-      </c>
-      <c r="D123" s="34" t="s">
-        <v>441</v>
-      </c>
-      <c r="E123" s="5"/>
-      <c r="F123" s="11"/>
+        <v>479</v>
+      </c>
+      <c r="C123" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="D123" s="27" t="s">
+        <v>480</v>
+      </c>
+      <c r="E123" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F123" s="11" t="s">
+        <v>481</v>
+      </c>
       <c r="G123" s="10"/>
       <c r="H123" s="5"/>
       <c r="I123" s="5"/>
@@ -4893,20 +4854,16 @@
     </row>
     <row r="124">
       <c r="A124" s="10" t="s">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="B124" s="10" t="s">
-        <v>444</v>
-      </c>
-      <c r="C124" s="32" t="s">
-        <v>45</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="C124" s="32"/>
       <c r="D124" s="5"/>
       <c r="E124" s="5"/>
       <c r="F124" s="11"/>
-      <c r="G124" s="10" t="s">
-        <v>175</v>
-      </c>
+      <c r="G124" s="10"/>
       <c r="H124" s="5"/>
       <c r="I124" s="5"/>
       <c r="J124" s="5"/>
@@ -4929,16 +4886,16 @@
     </row>
     <row r="125">
       <c r="A125" s="10" t="s">
-        <v>446</v>
+        <v>503</v>
       </c>
       <c r="B125" s="28" t="s">
-        <v>447</v>
+        <v>506</v>
       </c>
       <c r="C125" s="31" t="s">
-        <v>448</v>
+        <v>507</v>
       </c>
       <c r="D125" s="27" t="s">
-        <v>450</v>
+        <v>508</v>
       </c>
       <c r="E125" s="5" t="s">
         <v>17</v>
@@ -4967,23 +4924,21 @@
     </row>
     <row r="126">
       <c r="A126" s="10" t="s">
-        <v>376</v>
-      </c>
-      <c r="B126" s="10" t="s">
-        <v>452</v>
-      </c>
-      <c r="C126" s="10" t="s">
-        <v>378</v>
+        <v>517</v>
+      </c>
+      <c r="B126" s="28" t="s">
+        <v>518</v>
+      </c>
+      <c r="C126" s="31" t="s">
+        <v>520</v>
       </c>
       <c r="D126" s="27" t="s">
-        <v>427</v>
+        <v>522</v>
       </c>
       <c r="E126" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F126" s="11" t="s">
-        <v>455</v>
-      </c>
+      <c r="F126" s="11"/>
       <c r="G126" s="10"/>
       <c r="H126" s="5"/>
       <c r="I126" s="5"/>
@@ -5007,13 +4962,17 @@
     </row>
     <row r="127">
       <c r="A127" s="10" t="s">
-        <v>82</v>
+        <v>517</v>
       </c>
       <c r="B127" s="10" t="s">
-        <v>444</v>
-      </c>
-      <c r="C127" s="10"/>
-      <c r="D127" s="5"/>
+        <v>530</v>
+      </c>
+      <c r="C127" s="33" t="s">
+        <v>531</v>
+      </c>
+      <c r="D127" s="34" t="s">
+        <v>538</v>
+      </c>
       <c r="E127" s="5"/>
       <c r="F127" s="11"/>
       <c r="G127" s="10"/>
@@ -5039,19 +4998,19 @@
     </row>
     <row r="128">
       <c r="A128" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B128" s="10" t="s">
+        <v>548</v>
+      </c>
+      <c r="C128" s="32" t="s">
         <v>41</v>
-      </c>
-      <c r="B128" s="10" t="s">
-        <v>461</v>
-      </c>
-      <c r="C128" s="10" t="s">
-        <v>45</v>
       </c>
       <c r="D128" s="5"/>
       <c r="E128" s="5"/>
       <c r="F128" s="11"/>
       <c r="G128" s="10" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="H128" s="5"/>
       <c r="I128" s="5"/>
@@ -5075,20 +5034,22 @@
     </row>
     <row r="129">
       <c r="A129" s="10" t="s">
-        <v>176</v>
-      </c>
-      <c r="B129" s="10" t="s">
-        <v>465</v>
-      </c>
-      <c r="C129" s="35" t="s">
-        <v>466</v>
-      </c>
-      <c r="D129" s="13" t="s">
-        <v>470</v>
-      </c>
-      <c r="E129" s="5"/>
+        <v>552</v>
+      </c>
+      <c r="B129" s="28" t="s">
+        <v>553</v>
+      </c>
+      <c r="C129" s="31" t="s">
+        <v>554</v>
+      </c>
+      <c r="D129" s="27" t="s">
+        <v>555</v>
+      </c>
+      <c r="E129" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="F129" s="11"/>
-      <c r="G129" s="36"/>
+      <c r="G129" s="10"/>
       <c r="H129" s="5"/>
       <c r="I129" s="5"/>
       <c r="J129" s="5"/>
@@ -5111,21 +5072,23 @@
     </row>
     <row r="130">
       <c r="A130" s="10" t="s">
-        <v>433</v>
-      </c>
-      <c r="B130" s="28" t="s">
-        <v>474</v>
-      </c>
-      <c r="C130" s="31" t="s">
-        <v>475</v>
+        <v>391</v>
+      </c>
+      <c r="B130" s="10" t="s">
+        <v>559</v>
+      </c>
+      <c r="C130" s="10" t="s">
+        <v>393</v>
       </c>
       <c r="D130" s="27" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="E130" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F130" s="11"/>
+      <c r="F130" s="11" t="s">
+        <v>563</v>
+      </c>
       <c r="G130" s="10"/>
       <c r="H130" s="5"/>
       <c r="I130" s="5"/>
@@ -5149,10 +5112,10 @@
     </row>
     <row r="131">
       <c r="A131" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B131" s="10" t="s">
-        <v>461</v>
+        <v>548</v>
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="5"/>
@@ -5181,19 +5144,19 @@
     </row>
     <row r="132">
       <c r="A132" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B132" s="10" t="s">
+        <v>570</v>
+      </c>
+      <c r="C132" s="10" t="s">
         <v>41</v>
-      </c>
-      <c r="B132" s="10" t="s">
-        <v>478</v>
-      </c>
-      <c r="C132" s="10" t="s">
-        <v>45</v>
       </c>
       <c r="D132" s="5"/>
       <c r="E132" s="5"/>
       <c r="F132" s="11"/>
       <c r="G132" s="10" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="H132" s="5"/>
       <c r="I132" s="5"/>
@@ -5217,21 +5180,19 @@
     </row>
     <row r="133">
       <c r="A133" s="10" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B133" s="10" t="s">
-        <v>479</v>
-      </c>
-      <c r="C133" s="10" t="s">
-        <v>466</v>
+        <v>574</v>
+      </c>
+      <c r="C133" s="35" t="s">
+        <v>575</v>
       </c>
       <c r="D133" s="13" t="s">
-        <v>470</v>
+        <v>579</v>
       </c>
       <c r="E133" s="5"/>
-      <c r="F133" s="11" t="s">
-        <v>480</v>
-      </c>
+      <c r="F133" s="11"/>
       <c r="G133" s="36"/>
       <c r="H133" s="5"/>
       <c r="I133" s="5"/>
@@ -5255,23 +5216,21 @@
     </row>
     <row r="134">
       <c r="A134" s="10" t="s">
-        <v>481</v>
-      </c>
-      <c r="B134" s="10" t="s">
-        <v>482</v>
-      </c>
-      <c r="C134" s="10" t="s">
-        <v>483</v>
+        <v>517</v>
+      </c>
+      <c r="B134" s="28" t="s">
+        <v>586</v>
+      </c>
+      <c r="C134" s="31" t="s">
+        <v>587</v>
       </c>
       <c r="D134" s="27" t="s">
-        <v>484</v>
+        <v>588</v>
       </c>
       <c r="E134" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F134" s="11" t="s">
-        <v>480</v>
-      </c>
+      <c r="F134" s="11"/>
       <c r="G134" s="10"/>
       <c r="H134" s="5"/>
       <c r="I134" s="5"/>
@@ -5295,10 +5254,10 @@
     </row>
     <row r="135">
       <c r="A135" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B135" s="10" t="s">
-        <v>478</v>
+        <v>570</v>
       </c>
       <c r="C135" s="10"/>
       <c r="D135" s="5"/>
@@ -5327,19 +5286,19 @@
     </row>
     <row r="136">
       <c r="A136" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B136" s="10" t="s">
+        <v>592</v>
+      </c>
+      <c r="C136" s="10" t="s">
         <v>41</v>
-      </c>
-      <c r="B136" s="10" t="s">
-        <v>485</v>
-      </c>
-      <c r="C136" s="10" t="s">
-        <v>45</v>
       </c>
       <c r="D136" s="5"/>
       <c r="E136" s="5"/>
       <c r="F136" s="11"/>
       <c r="G136" s="10" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="H136" s="5"/>
       <c r="I136" s="5"/>
@@ -5363,20 +5322,20 @@
     </row>
     <row r="137">
       <c r="A137" s="10" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B137" s="10" t="s">
-        <v>486</v>
+        <v>598</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>466</v>
+        <v>575</v>
       </c>
       <c r="D137" s="13" t="s">
-        <v>470</v>
+        <v>579</v>
       </c>
       <c r="E137" s="5"/>
       <c r="F137" s="11" t="s">
-        <v>487</v>
+        <v>600</v>
       </c>
       <c r="G137" s="36"/>
       <c r="H137" s="5"/>
@@ -5401,22 +5360,22 @@
     </row>
     <row r="138">
       <c r="A138" s="10" t="s">
-        <v>433</v>
+        <v>602</v>
       </c>
       <c r="B138" s="10" t="s">
-        <v>488</v>
-      </c>
-      <c r="C138" s="37" t="s">
-        <v>489</v>
-      </c>
-      <c r="D138" s="38" t="s">
-        <v>490</v>
+        <v>604</v>
+      </c>
+      <c r="C138" s="10" t="s">
+        <v>606</v>
+      </c>
+      <c r="D138" s="27" t="s">
+        <v>607</v>
       </c>
       <c r="E138" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F138" s="11" t="s">
-        <v>487</v>
+        <v>600</v>
       </c>
       <c r="G138" s="10"/>
       <c r="H138" s="5"/>
@@ -5441,10 +5400,10 @@
     </row>
     <row r="139">
       <c r="A139" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B139" s="10" t="s">
-        <v>485</v>
+        <v>592</v>
       </c>
       <c r="C139" s="10"/>
       <c r="D139" s="5"/>
@@ -5473,19 +5432,19 @@
     </row>
     <row r="140">
       <c r="A140" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B140" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="C140" s="10" t="s">
         <v>41</v>
-      </c>
-      <c r="B140" s="10" t="s">
-        <v>491</v>
-      </c>
-      <c r="C140" s="10" t="s">
-        <v>45</v>
       </c>
       <c r="D140" s="5"/>
       <c r="E140" s="5"/>
       <c r="F140" s="11"/>
       <c r="G140" s="10" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="H140" s="5"/>
       <c r="I140" s="5"/>
@@ -5509,30 +5468,26 @@
     </row>
     <row r="141">
       <c r="A141" s="10" t="s">
-        <v>492</v>
+        <v>182</v>
       </c>
       <c r="B141" s="10" t="s">
-        <v>493</v>
+        <v>616</v>
       </c>
       <c r="C141" s="10" t="s">
-        <v>494</v>
-      </c>
-      <c r="D141" s="7" t="s">
-        <v>495</v>
+        <v>575</v>
+      </c>
+      <c r="D141" s="13" t="s">
+        <v>579</v>
       </c>
       <c r="E141" s="5"/>
       <c r="F141" s="11" t="s">
-        <v>487</v>
-      </c>
-      <c r="G141" s="10"/>
+        <v>617</v>
+      </c>
+      <c r="G141" s="36"/>
       <c r="H141" s="5"/>
-      <c r="I141" s="5" t="s">
-        <v>496</v>
-      </c>
-      <c r="J141" s="13" t="s">
-        <v>497</v>
-      </c>
-      <c r="K141" s="18"/>
+      <c r="I141" s="5"/>
+      <c r="J141" s="5"/>
+      <c r="K141" s="5"/>
       <c r="L141" s="5"/>
       <c r="M141" s="5"/>
       <c r="N141" s="5"/>
@@ -5551,22 +5506,22 @@
     </row>
     <row r="142">
       <c r="A142" s="10" t="s">
-        <v>501</v>
+        <v>517</v>
       </c>
       <c r="B142" s="10" t="s">
-        <v>502</v>
+        <v>621</v>
       </c>
       <c r="C142" s="37" t="s">
-        <v>503</v>
-      </c>
-      <c r="D142" s="27" t="s">
-        <v>504</v>
+        <v>623</v>
+      </c>
+      <c r="D142" s="38" t="s">
+        <v>630</v>
       </c>
       <c r="E142" s="5" t="s">
         <v>17</v>
       </c>
       <c r="F142" s="11" t="s">
-        <v>487</v>
+        <v>617</v>
       </c>
       <c r="G142" s="10"/>
       <c r="H142" s="5"/>
@@ -5591,10 +5546,10 @@
     </row>
     <row r="143">
       <c r="A143" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B143" s="10" t="s">
-        <v>493</v>
+        <v>612</v>
       </c>
       <c r="C143" s="10"/>
       <c r="D143" s="5"/>
@@ -5623,19 +5578,19 @@
     </row>
     <row r="144">
       <c r="A144" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B144" s="10" t="s">
+        <v>640</v>
+      </c>
+      <c r="C144" s="10" t="s">
         <v>41</v>
-      </c>
-      <c r="B144" s="10" t="s">
-        <v>511</v>
-      </c>
-      <c r="C144" s="10" t="s">
-        <v>45</v>
       </c>
       <c r="D144" s="5"/>
       <c r="E144" s="5"/>
       <c r="F144" s="11"/>
       <c r="G144" s="10" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="H144" s="5"/>
       <c r="I144" s="5"/>
@@ -5659,28 +5614,30 @@
     </row>
     <row r="145">
       <c r="A145" s="10" t="s">
-        <v>433</v>
+        <v>642</v>
       </c>
       <c r="B145" s="10" t="s">
-        <v>515</v>
-      </c>
-      <c r="C145" s="37" t="s">
-        <v>516</v>
+        <v>643</v>
+      </c>
+      <c r="C145" s="10" t="s">
+        <v>644</v>
       </c>
       <c r="D145" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="E145" s="5" t="s">
-        <v>17</v>
-      </c>
+        <v>645</v>
+      </c>
+      <c r="E145" s="5"/>
       <c r="F145" s="11" t="s">
-        <v>487</v>
+        <v>617</v>
       </c>
       <c r="G145" s="10"/>
       <c r="H145" s="5"/>
-      <c r="I145" s="5"/>
-      <c r="J145" s="5"/>
-      <c r="K145" s="5"/>
+      <c r="I145" s="5" t="s">
+        <v>648</v>
+      </c>
+      <c r="J145" s="13" t="s">
+        <v>649</v>
+      </c>
+      <c r="K145" s="18"/>
       <c r="L145" s="5"/>
       <c r="M145" s="5"/>
       <c r="N145" s="5"/>
@@ -5699,30 +5656,28 @@
     </row>
     <row r="146">
       <c r="A146" s="10" t="s">
-        <v>492</v>
+        <v>650</v>
       </c>
       <c r="B146" s="10" t="s">
-        <v>521</v>
+        <v>646</v>
       </c>
       <c r="C146" s="37" t="s">
-        <v>522</v>
-      </c>
-      <c r="D146" s="7" t="s">
-        <v>523</v>
-      </c>
-      <c r="E146" s="5"/>
+        <v>652</v>
+      </c>
+      <c r="D146" s="27" t="s">
+        <v>653</v>
+      </c>
+      <c r="E146" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="F146" s="11" t="s">
-        <v>525</v>
+        <v>617</v>
       </c>
       <c r="G146" s="10"/>
       <c r="H146" s="5"/>
-      <c r="I146" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="J146" s="13" t="s">
-        <v>529</v>
-      </c>
-      <c r="K146" s="18"/>
+      <c r="I146" s="5"/>
+      <c r="J146" s="5"/>
+      <c r="K146" s="5"/>
       <c r="L146" s="5"/>
       <c r="M146" s="5"/>
       <c r="N146" s="5"/>
@@ -5741,15 +5696,15 @@
     </row>
     <row r="147">
       <c r="A147" s="10" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B147" s="10" t="s">
-        <v>511</v>
+        <v>643</v>
       </c>
       <c r="C147" s="10"/>
       <c r="D147" s="5"/>
       <c r="E147" s="5"/>
-      <c r="F147" s="10"/>
+      <c r="F147" s="11"/>
       <c r="G147" s="10"/>
       <c r="H147" s="5"/>
       <c r="I147" s="5"/>
@@ -5772,172 +5727,310 @@
       <c r="Z147" s="5"/>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="s">
-        <v>82</v>
+      <c r="A148" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="B148" s="10" t="s">
-        <v>415</v>
-      </c>
-      <c r="C148" s="2"/>
-      <c r="F148" s="22"/>
-      <c r="G148" s="2"/>
+        <v>655</v>
+      </c>
+      <c r="C148" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D148" s="5"/>
+      <c r="E148" s="5"/>
+      <c r="F148" s="11"/>
+      <c r="G148" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="H148" s="5"/>
+      <c r="I148" s="5"/>
+      <c r="J148" s="5"/>
+      <c r="K148" s="5"/>
+      <c r="L148" s="5"/>
+      <c r="M148" s="5"/>
+      <c r="N148" s="5"/>
+      <c r="O148" s="5"/>
+      <c r="P148" s="5"/>
+      <c r="Q148" s="5"/>
+      <c r="R148" s="5"/>
+      <c r="S148" s="5"/>
+      <c r="T148" s="5"/>
+      <c r="U148" s="5"/>
+      <c r="V148" s="5"/>
+      <c r="W148" s="5"/>
+      <c r="X148" s="5"/>
+      <c r="Y148" s="5"/>
+      <c r="Z148" s="5"/>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B149" s="25" t="s">
-        <v>532</v>
-      </c>
-      <c r="L149" s="2" t="s">
-        <v>535</v>
-      </c>
+      <c r="A149" s="10" t="s">
+        <v>517</v>
+      </c>
+      <c r="B149" s="10" t="s">
+        <v>657</v>
+      </c>
+      <c r="C149" s="37" t="s">
+        <v>658</v>
+      </c>
+      <c r="D149" s="7" t="s">
+        <v>659</v>
+      </c>
+      <c r="E149" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F149" s="11" t="s">
+        <v>617</v>
+      </c>
+      <c r="G149" s="10"/>
+      <c r="H149" s="5"/>
+      <c r="I149" s="5"/>
+      <c r="J149" s="5"/>
+      <c r="K149" s="5"/>
+      <c r="L149" s="5"/>
+      <c r="M149" s="5"/>
+      <c r="N149" s="5"/>
+      <c r="O149" s="5"/>
+      <c r="P149" s="5"/>
+      <c r="Q149" s="5"/>
+      <c r="R149" s="5"/>
+      <c r="S149" s="5"/>
+      <c r="T149" s="5"/>
+      <c r="U149" s="5"/>
+      <c r="V149" s="5"/>
+      <c r="W149" s="5"/>
+      <c r="X149" s="5"/>
+      <c r="Y149" s="5"/>
+      <c r="Z149" s="5"/>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B150" s="25" t="s">
-        <v>537</v>
-      </c>
-      <c r="L150" s="2" t="s">
-        <v>540</v>
-      </c>
+      <c r="A150" s="10" t="s">
+        <v>642</v>
+      </c>
+      <c r="B150" s="10" t="s">
+        <v>661</v>
+      </c>
+      <c r="C150" s="37" t="s">
+        <v>663</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="E150" s="5"/>
+      <c r="F150" s="11" t="s">
+        <v>665</v>
+      </c>
+      <c r="G150" s="10"/>
+      <c r="H150" s="5"/>
+      <c r="I150" s="5" t="s">
+        <v>666</v>
+      </c>
+      <c r="J150" s="13" t="s">
+        <v>667</v>
+      </c>
+      <c r="K150" s="18"/>
+      <c r="L150" s="5"/>
+      <c r="M150" s="5"/>
+      <c r="N150" s="5"/>
+      <c r="O150" s="5"/>
+      <c r="P150" s="5"/>
+      <c r="Q150" s="5"/>
+      <c r="R150" s="5"/>
+      <c r="S150" s="5"/>
+      <c r="T150" s="5"/>
+      <c r="U150" s="5"/>
+      <c r="V150" s="5"/>
+      <c r="W150" s="5"/>
+      <c r="X150" s="5"/>
+      <c r="Y150" s="5"/>
+      <c r="Z150" s="5"/>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B151" s="25" t="s">
-        <v>542</v>
-      </c>
-      <c r="L151" s="2" t="s">
-        <v>544</v>
-      </c>
+      <c r="A151" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B151" s="10" t="s">
+        <v>655</v>
+      </c>
+      <c r="C151" s="10"/>
+      <c r="D151" s="5"/>
+      <c r="E151" s="5"/>
+      <c r="F151" s="10"/>
+      <c r="G151" s="10"/>
+      <c r="H151" s="5"/>
+      <c r="I151" s="5"/>
+      <c r="J151" s="5"/>
+      <c r="K151" s="5"/>
+      <c r="L151" s="5"/>
+      <c r="M151" s="5"/>
+      <c r="N151" s="5"/>
+      <c r="O151" s="5"/>
+      <c r="P151" s="5"/>
+      <c r="Q151" s="5"/>
+      <c r="R151" s="5"/>
+      <c r="S151" s="5"/>
+      <c r="T151" s="5"/>
+      <c r="U151" s="5"/>
+      <c r="V151" s="5"/>
+      <c r="W151" s="5"/>
+      <c r="X151" s="5"/>
+      <c r="Y151" s="5"/>
+      <c r="Z151" s="5"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B152" s="39" t="s">
-        <v>547</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="D152" s="4" t="s">
-        <v>555</v>
-      </c>
-      <c r="G152" s="2" t="s">
-        <v>175</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="B152" s="10" t="s">
+        <v>431</v>
+      </c>
+      <c r="C152" s="2"/>
+      <c r="F152" s="22"/>
+      <c r="G152" s="2"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="B153" s="39" t="s">
-        <v>556</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="D153" s="4" t="s">
-        <v>558</v>
-      </c>
-      <c r="F153" s="2" t="s">
-        <v>559</v>
+        <v>102</v>
+      </c>
+      <c r="B153" s="25" t="s">
+        <v>671</v>
+      </c>
+      <c r="L153" s="2" t="s">
+        <v>673</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>560</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="D154" s="4" t="s">
-        <v>563</v>
-      </c>
-      <c r="F154" s="2" t="s">
-        <v>566</v>
+        <v>102</v>
+      </c>
+      <c r="B154" s="25" t="s">
+        <v>674</v>
+      </c>
+      <c r="L154" s="2" t="s">
+        <v>675</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="B155" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="D155" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="F155" s="2" t="s">
-        <v>573</v>
+        <v>102</v>
+      </c>
+      <c r="B155" s="25" t="s">
+        <v>676</v>
+      </c>
+      <c r="L155" s="2" t="s">
+        <v>677</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>574</v>
+        <v>39</v>
+      </c>
+      <c r="B156" s="39" t="s">
+        <v>678</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>576</v>
+        <v>680</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>577</v>
-      </c>
-      <c r="F156" s="2" t="s">
-        <v>581</v>
+        <v>681</v>
+      </c>
+      <c r="G156" s="2" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B157" s="2" t="s">
-        <v>547</v>
+        <v>182</v>
+      </c>
+      <c r="B157" s="39" t="s">
+        <v>682</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="D157" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="F157" s="2" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="D158" s="4" t="s">
+        <v>688</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="D159" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>693</v>
       </c>
     </row>
     <row r="160">
-      <c r="B160" s="40"/>
-    </row>
-    <row r="163">
-      <c r="C163" s="25"/>
+      <c r="A160" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="D160" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>678</v>
+      </c>
     </row>
     <row r="164">
       <c r="B164" s="40"/>
-      <c r="C164" s="25"/>
-    </row>
-    <row r="166">
-      <c r="B166" s="40"/>
     </row>
     <row r="167">
-      <c r="B167" s="39"/>
+      <c r="C167" s="25"/>
     </row>
     <row r="168">
       <c r="B168" s="40"/>
-    </row>
-    <row r="169">
-      <c r="B169" s="40"/>
+      <c r="C168" s="25"/>
     </row>
     <row r="170">
-      <c r="B170" s="39"/>
+      <c r="B170" s="40"/>
     </row>
     <row r="171">
-      <c r="B171" s="40"/>
+      <c r="B171" s="39"/>
     </row>
     <row r="172">
-      <c r="B172" s="39"/>
+      <c r="B172" s="40"/>
     </row>
     <row r="173">
       <c r="B173" s="40"/>
@@ -5951,24 +6044,36 @@
     <row r="176">
       <c r="B176" s="39"/>
     </row>
+    <row r="177">
+      <c r="B177" s="40"/>
+    </row>
     <row r="178">
-      <c r="C178" s="40"/>
+      <c r="B178" s="39"/>
     </row>
     <row r="179">
-      <c r="B179" s="39"/>
+      <c r="B179" s="40"/>
     </row>
     <row r="180">
       <c r="B180" s="39"/>
     </row>
     <row r="182">
-      <c r="B182" s="25"/>
+      <c r="C182" s="40"/>
     </row>
     <row r="183">
-      <c r="B183" s="40"/>
+      <c r="B183" s="39"/>
+    </row>
+    <row r="184">
+      <c r="B184" s="39"/>
+    </row>
+    <row r="186">
+      <c r="B186" s="25"/>
+    </row>
+    <row r="187">
+      <c r="B187" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="L29:Q29"/>
+    <mergeCell ref="L30:Q30"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -5988,19 +6093,19 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2">
@@ -6050,18 +6155,18 @@
         <v>23</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>46</v>
@@ -6097,7 +6202,7 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>48</v>
@@ -6133,7 +6238,7 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>50</v>
@@ -6178,7 +6283,7 @@
         <v>61</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>46</v>
@@ -6248,13 +6353,13 @@
         <v>59</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>46</v>
@@ -6286,13 +6391,13 @@
         <v>59</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>46</v>
@@ -6324,13 +6429,13 @@
         <v>59</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>46</v>
@@ -6362,13 +6467,13 @@
         <v>59</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>46</v>
@@ -6400,13 +6505,13 @@
         <v>59</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>46</v>
@@ -6438,13 +6543,13 @@
         <v>59</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>48</v>
@@ -6476,13 +6581,13 @@
         <v>59</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>48</v>
@@ -6514,13 +6619,13 @@
         <v>59</v>
       </c>
       <c r="B18" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>100</v>
-      </c>
       <c r="D18" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>48</v>
@@ -6552,13 +6657,13 @@
         <v>59</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>48</v>
@@ -6587,20 +6692,20 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B20" s="5" t="str">
         <f t="shared" ref="B20:B83" si="1">lower(substitute(C20," ",""))</f>
         <v>chakechakedistricthospital</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
@@ -6626,20 +6731,20 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B21" s="5" t="str">
         <f t="shared" si="1"/>
         <v>pujiniphcu+</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
@@ -6665,20 +6770,20 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B22" s="5" t="str">
         <f t="shared" si="1"/>
         <v>tundauwaphcu+</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
@@ -6704,20 +6809,20 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B23" s="5" t="str">
         <f t="shared" si="1"/>
         <v>vitongojiphcc</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
@@ -6743,20 +6848,20 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B24" s="5" t="str">
         <f t="shared" si="1"/>
         <v>weshaphcu+</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
@@ -6782,7 +6887,7 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B25" s="5" t="str">
         <f t="shared" si="1"/>
@@ -6795,7 +6900,7 @@
         <v>126</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
@@ -6821,20 +6926,20 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B26" s="5" t="str">
         <f t="shared" si="1"/>
         <v>makangalephcu+</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
@@ -6860,7 +6965,7 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B27" s="5" t="str">
         <f t="shared" si="1"/>
@@ -6873,7 +6978,7 @@
         <v>129</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
@@ -6899,20 +7004,20 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B28" s="5" t="str">
         <f t="shared" si="1"/>
         <v>micheweniphcc</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
@@ -6938,7 +7043,7 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B29" s="5" t="str">
         <f t="shared" si="1"/>
@@ -6951,7 +7056,7 @@
         <v>136</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
@@ -6977,7 +7082,7 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B30" s="5" t="str">
         <f t="shared" si="1"/>
@@ -6990,7 +7095,7 @@
         <v>138</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
@@ -7016,20 +7121,20 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B31" s="5" t="str">
         <f t="shared" si="1"/>
         <v>bogoaphcu+</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
@@ -7055,7 +7160,7 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B32" s="5" t="str">
         <f t="shared" si="1"/>
@@ -7068,7 +7173,7 @@
         <v>143</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
@@ -7094,20 +7199,20 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B33" s="5" t="str">
         <f t="shared" si="1"/>
         <v>abdallahmzeedistricthospital</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
@@ -7133,20 +7238,20 @@
     </row>
     <row r="34">
       <c r="A34" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B34" s="5" t="str">
         <f t="shared" si="1"/>
         <v>michenzaniphcu+</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D34" s="13" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
@@ -7172,20 +7277,20 @@
     </row>
     <row r="35">
       <c r="A35" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B35" s="5" t="str">
         <f t="shared" si="1"/>
         <v>fundophcu+</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
@@ -7211,20 +7316,20 @@
     </row>
     <row r="36">
       <c r="A36" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B36" s="5" t="str">
         <f t="shared" si="1"/>
         <v>kojaniphcu+</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
@@ -7250,20 +7355,20 @@
     </row>
     <row r="37">
       <c r="A37" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B37" s="5" t="str">
         <f t="shared" si="1"/>
         <v>makongeniphcu+</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
@@ -7289,20 +7394,20 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B38" s="5" t="str">
         <f t="shared" si="1"/>
         <v>wetedistricthospital</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
@@ -7328,20 +7433,20 @@
     </row>
     <row r="39">
       <c r="A39" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B39" s="5" t="str">
         <f t="shared" si="1"/>
         <v>mzambarauniphcu+</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D39" s="13" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
@@ -7367,20 +7472,20 @@
     </row>
     <row r="40">
       <c r="A40" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B40" s="5" t="str">
         <f t="shared" si="1"/>
         <v>junguniphcu+</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
@@ -7406,20 +7511,20 @@
     </row>
     <row r="41">
       <c r="A41" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B41" s="5" t="str">
         <f t="shared" si="1"/>
         <v>ukunjwiphcu+</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
@@ -7445,20 +7550,20 @@
     </row>
     <row r="42">
       <c r="A42" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B42" s="5" t="str">
         <f t="shared" si="1"/>
         <v>uondwephcu+</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
@@ -7484,20 +7589,20 @@
     </row>
     <row r="43">
       <c r="A43" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B43" s="5" t="str">
         <f t="shared" si="1"/>
         <v>chwakaphcu+</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
@@ -7523,20 +7628,20 @@
     </row>
     <row r="44">
       <c r="A44" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B44" s="5" t="str">
         <f t="shared" si="1"/>
         <v>mweraphcu+</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>190</v>
+        <v>174</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
@@ -7562,20 +7667,20 @@
     </row>
     <row r="45">
       <c r="A45" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B45" s="5" t="str">
         <f t="shared" si="1"/>
         <v>ungujaukuuphcu+</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
@@ -7601,20 +7706,20 @@
     </row>
     <row r="46">
       <c r="A46" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B46" s="5" t="str">
         <f t="shared" si="1"/>
         <v>uziniphcu+</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
@@ -7640,20 +7745,20 @@
     </row>
     <row r="47">
       <c r="A47" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B47" s="5" t="str">
         <f t="shared" si="1"/>
         <v>uroaphcu+</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
@@ -7679,17 +7784,17 @@
     </row>
     <row r="48">
       <c r="A48" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B48" s="5" t="str">
         <f t="shared" si="1"/>
         <v>kivungedistricthospital</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>221</v>
+        <v>198</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>60</v>
@@ -7718,17 +7823,17 @@
     </row>
     <row r="49">
       <c r="A49" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B49" s="5" t="str">
         <f t="shared" si="1"/>
         <v>matemwephcu+</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>60</v>
@@ -7757,17 +7862,17 @@
     </row>
     <row r="50">
       <c r="A50" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B50" s="5" t="str">
         <f t="shared" si="1"/>
         <v>nungwiphcu+</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>235</v>
+        <v>208</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>235</v>
+        <v>208</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>60</v>
@@ -7796,17 +7901,17 @@
     </row>
     <row r="51">
       <c r="A51" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B51" s="5" t="str">
         <f t="shared" si="1"/>
         <v>pwanimchanganiphcu+</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>242</v>
+        <v>215</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>242</v>
+        <v>215</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>60</v>
@@ -7835,17 +7940,17 @@
     </row>
     <row r="52">
       <c r="A52" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B52" s="5" t="str">
         <f t="shared" si="1"/>
         <v>tumbatugomaniphcu+</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>251</v>
+        <v>224</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>251</v>
+        <v>224</v>
       </c>
       <c r="E52" s="5" t="s">
         <v>60</v>
@@ -7874,17 +7979,17 @@
     </row>
     <row r="53">
       <c r="A53" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B53" s="5" t="str">
         <f t="shared" si="1"/>
         <v>kendwaphcu+</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>259</v>
+        <v>229</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>259</v>
+        <v>229</v>
       </c>
       <c r="E53" s="5" t="s">
         <v>60</v>
@@ -7913,17 +8018,17 @@
     </row>
     <row r="54">
       <c r="A54" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B54" s="5" t="str">
         <f t="shared" si="1"/>
         <v>bumbwinimisufiniphcu+</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>271</v>
+        <v>233</v>
       </c>
       <c r="D54" s="13" t="s">
-        <v>271</v>
+        <v>233</v>
       </c>
       <c r="E54" s="5" t="s">
         <v>64</v>
@@ -7952,17 +8057,17 @@
     </row>
     <row r="55">
       <c r="A55" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B55" s="5" t="str">
         <f t="shared" si="1"/>
         <v>dongevijibweniphcu+</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>279</v>
+        <v>243</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>279</v>
+        <v>243</v>
       </c>
       <c r="E55" s="5" t="s">
         <v>64</v>
@@ -7991,17 +8096,17 @@
     </row>
     <row r="56">
       <c r="A56" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B56" s="5" t="str">
         <f t="shared" si="1"/>
         <v>kiongwephcu</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>290</v>
+        <v>249</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>290</v>
+        <v>249</v>
       </c>
       <c r="E56" s="5" t="s">
         <v>64</v>
@@ -8030,17 +8135,17 @@
     </row>
     <row r="57">
       <c r="A57" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B57" s="5" t="str">
         <f t="shared" si="1"/>
         <v>kitopephcu</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>297</v>
+        <v>256</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>297</v>
+        <v>256</v>
       </c>
       <c r="E57" s="5" t="s">
         <v>64</v>
@@ -8069,17 +8174,17 @@
     </row>
     <row r="58">
       <c r="A58" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B58" s="5" t="str">
         <f t="shared" si="1"/>
         <v>mahondaphcu+</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>305</v>
+        <v>265</v>
       </c>
       <c r="D58" s="13" t="s">
-        <v>305</v>
+        <v>265</v>
       </c>
       <c r="E58" s="5" t="s">
         <v>64</v>
@@ -8108,20 +8213,20 @@
     </row>
     <row r="59">
       <c r="A59" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B59" s="5" t="str">
         <f t="shared" si="1"/>
         <v>jambianiphcu+</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>312</v>
+        <v>273</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>312</v>
+        <v>273</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F59" s="5"/>
       <c r="G59" s="5"/>
@@ -8147,20 +8252,20 @@
     </row>
     <row r="60">
       <c r="A60" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B60" s="5" t="str">
         <f t="shared" si="1"/>
         <v>makunduchidistricthospital</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>321</v>
+        <v>283</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>322</v>
+        <v>284</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
@@ -8186,20 +8291,20 @@
     </row>
     <row r="61">
       <c r="A61" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B61" s="5" t="str">
         <f t="shared" si="1"/>
         <v>muyuniphcu+</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>328</v>
+        <v>286</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>328</v>
+        <v>286</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="5"/>
@@ -8225,20 +8330,20 @@
     </row>
     <row r="62">
       <c r="A62" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B62" s="5" t="str">
         <f t="shared" si="1"/>
         <v>bwejuuphcu+</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>337</v>
+        <v>292</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>337</v>
+        <v>292</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="5"/>
@@ -8264,20 +8369,20 @@
     </row>
     <row r="63">
       <c r="A63" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B63" s="5" t="str">
         <f t="shared" si="1"/>
         <v>chumbuniphcu+</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>345</v>
+        <v>299</v>
       </c>
       <c r="D63" s="13" t="s">
-        <v>345</v>
+        <v>299</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F63" s="5"/>
       <c r="G63" s="5"/>
@@ -8303,20 +8408,20 @@
     </row>
     <row r="64">
       <c r="A64" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B64" s="5" t="str">
         <f t="shared" si="1"/>
         <v>mnazimmojahospital</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>352</v>
+        <v>307</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>354</v>
+        <v>309</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="5"/>
@@ -8342,20 +8447,20 @@
     </row>
     <row r="65">
       <c r="A65" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B65" s="5" t="str">
         <f t="shared" si="1"/>
         <v>mwembeladumchclinic</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>359</v>
+        <v>315</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>359</v>
+        <v>315</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F65" s="5"/>
       <c r="G65" s="5"/>
@@ -8381,20 +8486,20 @@
     </row>
     <row r="66">
       <c r="A66" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B66" s="5" t="str">
         <f t="shared" si="1"/>
         <v>sebleniphcu+</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>360</v>
+        <v>322</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>360</v>
+        <v>322</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="5"/>
@@ -8420,20 +8525,20 @@
     </row>
     <row r="67">
       <c r="A67" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B67" s="5" t="str">
         <f t="shared" si="1"/>
         <v>chukwaniphcu+</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>366</v>
+        <v>331</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>366</v>
+        <v>331</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="5"/>
@@ -8459,20 +8564,20 @@
     </row>
     <row r="68">
       <c r="A68" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B68" s="5" t="str">
         <f t="shared" si="1"/>
         <v>fuoniphcu+</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>370</v>
+        <v>341</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>370</v>
+        <v>341</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="5"/>
@@ -8498,20 +8603,20 @@
     </row>
     <row r="69">
       <c r="A69" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B69" s="5" t="str">
         <f t="shared" si="1"/>
         <v>kombeniphcu+</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>375</v>
+        <v>345</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>375</v>
+        <v>345</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
@@ -8537,20 +8642,20 @@
     </row>
     <row r="70">
       <c r="A70" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B70" s="5" t="str">
         <f t="shared" si="1"/>
         <v>mtofaaniphcu+(kinuni)</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>385</v>
+        <v>353</v>
       </c>
       <c r="D70" s="13" t="s">
-        <v>385</v>
+        <v>353</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="5"/>
@@ -8576,20 +8681,20 @@
     </row>
     <row r="71">
       <c r="A71" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B71" s="5" t="str">
         <f t="shared" si="1"/>
         <v>bumbwisudiphcu+</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>391</v>
+        <v>359</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>391</v>
+        <v>359</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F71" s="5"/>
       <c r="G71" s="5"/>
@@ -8615,20 +8720,20 @@
     </row>
     <row r="72">
       <c r="A72" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B72" s="5" t="str">
         <f t="shared" si="1"/>
         <v>selemphcu+</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>403</v>
+        <v>367</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>403</v>
+        <v>367</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F72" s="5"/>
       <c r="G72" s="5"/>
@@ -8654,7 +8759,7 @@
     </row>
     <row r="73">
       <c r="A73" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B73" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8664,10 +8769,10 @@
         <v>51</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>413</v>
+        <v>372</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F73" s="5"/>
       <c r="G73" s="5"/>
@@ -8693,7 +8798,7 @@
     </row>
     <row r="74">
       <c r="A74" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B74" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8703,10 +8808,10 @@
         <v>51</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>413</v>
+        <v>372</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F74" s="5"/>
       <c r="G74" s="5"/>
@@ -8732,7 +8837,7 @@
     </row>
     <row r="75">
       <c r="A75" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B75" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8742,10 +8847,10 @@
         <v>51</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>413</v>
+        <v>372</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F75" s="5"/>
       <c r="G75" s="5"/>
@@ -8771,7 +8876,7 @@
     </row>
     <row r="76">
       <c r="A76" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B76" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8781,10 +8886,10 @@
         <v>51</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>413</v>
+        <v>372</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F76" s="5"/>
       <c r="G76" s="5"/>
@@ -8810,7 +8915,7 @@
     </row>
     <row r="77">
       <c r="A77" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B77" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8820,10 +8925,10 @@
         <v>51</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>413</v>
+        <v>372</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F77" s="5"/>
       <c r="G77" s="5"/>
@@ -8849,7 +8954,7 @@
     </row>
     <row r="78">
       <c r="A78" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B78" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8859,7 +8964,7 @@
         <v>51</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>413</v>
+        <v>372</v>
       </c>
       <c r="E78" s="5" t="s">
         <v>60</v>
@@ -8888,7 +8993,7 @@
     </row>
     <row r="79">
       <c r="A79" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B79" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8898,7 +9003,7 @@
         <v>51</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>413</v>
+        <v>372</v>
       </c>
       <c r="E79" s="5" t="s">
         <v>64</v>
@@ -8927,7 +9032,7 @@
     </row>
     <row r="80">
       <c r="A80" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B80" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8937,10 +9042,10 @@
         <v>51</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>413</v>
+        <v>372</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F80" s="5"/>
       <c r="G80" s="5"/>
@@ -8966,7 +9071,7 @@
     </row>
     <row r="81">
       <c r="A81" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B81" s="5" t="str">
         <f t="shared" si="1"/>
@@ -8976,10 +9081,10 @@
         <v>51</v>
       </c>
       <c r="D81" s="7" t="s">
-        <v>413</v>
+        <v>372</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F81" s="5"/>
       <c r="G81" s="5"/>
@@ -9005,7 +9110,7 @@
     </row>
     <row r="82">
       <c r="A82" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B82" s="5" t="str">
         <f t="shared" si="1"/>
@@ -9015,10 +9120,10 @@
         <v>51</v>
       </c>
       <c r="D82" s="7" t="s">
-        <v>413</v>
+        <v>372</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F82" s="5"/>
       <c r="G82" s="5"/>
@@ -9044,7 +9149,7 @@
     </row>
     <row r="83">
       <c r="A83" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B83" s="5" t="str">
         <f t="shared" si="1"/>
@@ -9054,10 +9159,10 @@
         <v>51</v>
       </c>
       <c r="D83" s="7" t="s">
-        <v>413</v>
+        <v>372</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F83" s="5"/>
       <c r="G83" s="5"/>
@@ -9083,16 +9188,16 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="s">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>439</v>
+        <v>420</v>
       </c>
       <c r="D84" s="27" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="E84" s="5"/>
       <c r="F84" s="5"/>
@@ -9119,16 +9224,16 @@
     </row>
     <row r="85">
       <c r="A85" s="5" t="s">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>442</v>
+        <v>428</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>443</v>
+        <v>429</v>
       </c>
       <c r="D85" s="27" t="s">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="E85" s="18"/>
       <c r="F85" s="18"/>
@@ -9155,16 +9260,16 @@
     </row>
     <row r="86">
       <c r="A86" s="5" t="s">
-        <v>382</v>
+        <v>397</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>449</v>
+        <v>433</v>
       </c>
       <c r="D86" s="27" t="s">
-        <v>451</v>
+        <v>435</v>
       </c>
       <c r="E86" s="5"/>
       <c r="F86" s="5"/>
@@ -9191,16 +9296,16 @@
     </row>
     <row r="87">
       <c r="A87" s="5" t="s">
-        <v>453</v>
+        <v>437</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>454</v>
+        <v>438</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>456</v>
+        <v>439</v>
       </c>
       <c r="D87" s="27" t="s">
-        <v>457</v>
+        <v>440</v>
       </c>
       <c r="E87" s="5"/>
       <c r="F87" s="5"/>
@@ -9227,16 +9332,16 @@
     </row>
     <row r="88">
       <c r="A88" s="5" t="s">
-        <v>453</v>
+        <v>437</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>458</v>
+        <v>442</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="D88" s="27" t="s">
-        <v>460</v>
+        <v>444</v>
       </c>
       <c r="E88" s="5"/>
       <c r="F88" s="5"/>
@@ -9263,16 +9368,16 @@
     </row>
     <row r="89">
       <c r="A89" s="5" t="s">
-        <v>453</v>
+        <v>437</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>462</v>
+        <v>445</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>463</v>
+        <v>446</v>
       </c>
       <c r="D89" s="27" t="s">
-        <v>464</v>
+        <v>447</v>
       </c>
       <c r="E89" s="5"/>
       <c r="F89" s="5"/>
@@ -9299,16 +9404,16 @@
     </row>
     <row r="90">
       <c r="A90" s="5" t="s">
-        <v>453</v>
+        <v>437</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>467</v>
+        <v>448</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>468</v>
+        <v>449</v>
       </c>
       <c r="D90" s="27" t="s">
-        <v>469</v>
+        <v>450</v>
       </c>
       <c r="E90" s="18"/>
       <c r="F90" s="5"/>
@@ -9335,16 +9440,16 @@
     </row>
     <row r="91">
       <c r="A91" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="C91" s="5" t="s">
         <v>453</v>
       </c>
-      <c r="B91" s="5" t="s">
-        <v>471</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>472</v>
-      </c>
       <c r="D91" s="27" t="s">
-        <v>473</v>
+        <v>454</v>
       </c>
       <c r="E91" s="5"/>
       <c r="F91" s="5"/>
@@ -9371,7 +9476,7 @@
     </row>
     <row r="92">
       <c r="A92" s="5" t="s">
-        <v>453</v>
+        <v>437</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>50</v>
@@ -9380,7 +9485,7 @@
         <v>51</v>
       </c>
       <c r="D92" s="27" t="s">
-        <v>476</v>
+        <v>455</v>
       </c>
       <c r="E92" s="5"/>
       <c r="F92" s="5"/>
@@ -9407,16 +9512,16 @@
     </row>
     <row r="93">
       <c r="A93" s="5" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>498</v>
+        <v>457</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>499</v>
+        <v>458</v>
       </c>
       <c r="D93" s="27" t="s">
-        <v>500</v>
+        <v>459</v>
       </c>
       <c r="E93" s="5"/>
       <c r="F93" s="5"/>
@@ -9443,16 +9548,16 @@
     </row>
     <row r="94">
       <c r="A94" s="5" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>505</v>
+        <v>460</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>506</v>
+        <v>461</v>
       </c>
       <c r="D94" s="27" t="s">
-        <v>507</v>
+        <v>462</v>
       </c>
       <c r="E94" s="5"/>
       <c r="F94" s="5"/>
@@ -9479,16 +9584,16 @@
     </row>
     <row r="95">
       <c r="A95" s="5" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>508</v>
+        <v>463</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>509</v>
+        <v>464</v>
       </c>
       <c r="D95" s="27" t="s">
-        <v>510</v>
+        <v>465</v>
       </c>
       <c r="E95" s="5"/>
       <c r="F95" s="5"/>
@@ -9515,16 +9620,16 @@
     </row>
     <row r="96">
       <c r="A96" s="5" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>512</v>
+        <v>469</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>513</v>
+        <v>470</v>
       </c>
       <c r="D96" s="27" t="s">
-        <v>514</v>
+        <v>471</v>
       </c>
       <c r="E96" s="5"/>
       <c r="F96" s="5"/>
@@ -9551,16 +9656,16 @@
     </row>
     <row r="97">
       <c r="A97" s="5" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>518</v>
+        <v>472</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>519</v>
+        <v>473</v>
       </c>
       <c r="D97" s="27" t="s">
-        <v>520</v>
+        <v>474</v>
       </c>
       <c r="E97" s="5"/>
       <c r="F97" s="5"/>
@@ -9587,16 +9692,16 @@
     </row>
     <row r="98">
       <c r="A98" s="5" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>524</v>
+        <v>475</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>526</v>
+        <v>477</v>
       </c>
       <c r="D98" s="27" t="s">
-        <v>527</v>
+        <v>478</v>
       </c>
       <c r="E98" s="5"/>
       <c r="F98" s="5"/>
@@ -9623,7 +9728,7 @@
     </row>
     <row r="99">
       <c r="A99" s="5" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>50</v>
@@ -9632,7 +9737,7 @@
         <v>51</v>
       </c>
       <c r="D99" s="27" t="s">
-        <v>476</v>
+        <v>455</v>
       </c>
       <c r="E99" s="5"/>
       <c r="F99" s="5"/>
@@ -9659,119 +9764,119 @@
     </row>
     <row r="100">
       <c r="A100" s="5" t="s">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>530</v>
+        <v>482</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>531</v>
+        <v>483</v>
       </c>
       <c r="D100" s="27" t="s">
-        <v>507</v>
+        <v>462</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="s">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>533</v>
+        <v>484</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>534</v>
+        <v>485</v>
       </c>
       <c r="D101" s="27" t="s">
-        <v>536</v>
+        <v>486</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="s">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>538</v>
+        <v>487</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>539</v>
+        <v>488</v>
       </c>
       <c r="D102" s="27" t="s">
-        <v>541</v>
+        <v>489</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="s">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>543</v>
+        <v>490</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>545</v>
+        <v>491</v>
       </c>
       <c r="D103" s="27" t="s">
-        <v>546</v>
+        <v>492</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="s">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>548</v>
+        <v>493</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>549</v>
+        <v>494</v>
       </c>
       <c r="D104" s="27" t="s">
-        <v>550</v>
+        <v>495</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="s">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>551</v>
+        <v>496</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>552</v>
+        <v>497</v>
       </c>
       <c r="D105" s="27" t="s">
-        <v>553</v>
+        <v>498</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="s">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>561</v>
+        <v>499</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>564</v>
+        <v>500</v>
       </c>
       <c r="D106" s="27" t="s">
-        <v>565</v>
+        <v>501</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="s">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>568</v>
+        <v>502</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>570</v>
+        <v>504</v>
       </c>
       <c r="D107" s="27" t="s">
-        <v>572</v>
+        <v>505</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="s">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>50</v>
@@ -9780,82 +9885,82 @@
         <v>51</v>
       </c>
       <c r="D108" s="27" t="s">
-        <v>575</v>
+        <v>509</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="s">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>578</v>
+        <v>510</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>579</v>
+        <v>511</v>
       </c>
       <c r="D109" s="27" t="s">
-        <v>580</v>
+        <v>512</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="s">
-        <v>582</v>
+        <v>513</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>583</v>
+        <v>514</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>584</v>
+        <v>515</v>
       </c>
       <c r="D110" s="27" t="s">
-        <v>585</v>
+        <v>516</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="s">
-        <v>582</v>
+        <v>513</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>586</v>
+        <v>519</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>587</v>
+        <v>521</v>
       </c>
       <c r="D111" s="27" t="s">
-        <v>588</v>
+        <v>523</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="s">
-        <v>582</v>
+        <v>513</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>589</v>
+        <v>524</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>590</v>
+        <v>525</v>
       </c>
       <c r="D112" s="27" t="s">
-        <v>591</v>
+        <v>526</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="s">
-        <v>582</v>
+        <v>513</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>592</v>
+        <v>527</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>593</v>
+        <v>528</v>
       </c>
       <c r="D113" s="27" t="s">
-        <v>594</v>
+        <v>529</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="s">
-        <v>582</v>
+        <v>513</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>50</v>
@@ -9864,35 +9969,35 @@
         <v>51</v>
       </c>
       <c r="D114" s="27" t="s">
-        <v>476</v>
+        <v>455</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="s">
-        <v>582</v>
+        <v>513</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>578</v>
+        <v>510</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>579</v>
+        <v>511</v>
       </c>
       <c r="D115" s="27" t="s">
-        <v>580</v>
+        <v>512</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>595</v>
+        <v>532</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>596</v>
+        <v>533</v>
       </c>
       <c r="D116" s="27" t="s">
-        <v>597</v>
+        <v>534</v>
       </c>
       <c r="E116" s="5"/>
       <c r="F116" s="5"/>
@@ -9919,16 +10024,16 @@
     </row>
     <row r="117">
       <c r="A117" s="5" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>598</v>
+        <v>535</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>599</v>
+        <v>536</v>
       </c>
       <c r="D117" s="27" t="s">
-        <v>600</v>
+        <v>537</v>
       </c>
       <c r="E117" s="5"/>
       <c r="F117" s="5"/>
@@ -9955,16 +10060,16 @@
     </row>
     <row r="118">
       <c r="A118" s="5" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>601</v>
+        <v>539</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>602</v>
+        <v>540</v>
       </c>
       <c r="D118" s="27" t="s">
-        <v>603</v>
+        <v>541</v>
       </c>
       <c r="E118" s="5"/>
       <c r="F118" s="5"/>
@@ -9991,16 +10096,16 @@
     </row>
     <row r="119">
       <c r="A119" s="5" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>604</v>
+        <v>542</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>605</v>
+        <v>543</v>
       </c>
       <c r="D119" s="7" t="s">
-        <v>606</v>
+        <v>544</v>
       </c>
       <c r="E119" s="5"/>
       <c r="F119" s="5"/>
@@ -10027,16 +10132,16 @@
     </row>
     <row r="120">
       <c r="A120" s="5" t="s">
-        <v>423</v>
+        <v>467</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>607</v>
+        <v>545</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>608</v>
+        <v>546</v>
       </c>
       <c r="D120" s="27" t="s">
-        <v>609</v>
+        <v>547</v>
       </c>
       <c r="E120" s="5"/>
       <c r="F120" s="5"/>
@@ -10063,16 +10168,16 @@
     </row>
     <row r="121">
       <c r="A121" s="5" t="s">
-        <v>423</v>
+        <v>467</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>610</v>
+        <v>549</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>611</v>
+        <v>550</v>
       </c>
       <c r="D121" s="27" t="s">
-        <v>612</v>
+        <v>551</v>
       </c>
       <c r="E121" s="5"/>
       <c r="F121" s="5"/>
@@ -10099,16 +10204,16 @@
     </row>
     <row r="122">
       <c r="A122" s="5" t="s">
-        <v>423</v>
+        <v>467</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>613</v>
+        <v>556</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>614</v>
+        <v>557</v>
       </c>
       <c r="D122" s="27" t="s">
-        <v>615</v>
+        <v>558</v>
       </c>
       <c r="E122" s="5"/>
       <c r="F122" s="5"/>
@@ -10135,16 +10240,16 @@
     </row>
     <row r="123">
       <c r="A123" s="5" t="s">
-        <v>423</v>
+        <v>467</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>616</v>
+        <v>560</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>617</v>
+        <v>561</v>
       </c>
       <c r="D123" s="27" t="s">
-        <v>618</v>
+        <v>562</v>
       </c>
       <c r="E123" s="5"/>
       <c r="F123" s="5"/>
@@ -10171,16 +10276,16 @@
     </row>
     <row r="124">
       <c r="A124" s="5" t="s">
-        <v>423</v>
+        <v>467</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>619</v>
+        <v>564</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>620</v>
+        <v>565</v>
       </c>
       <c r="D124" s="27" t="s">
-        <v>621</v>
+        <v>566</v>
       </c>
       <c r="E124" s="5"/>
       <c r="F124" s="5"/>
@@ -10207,16 +10312,16 @@
     </row>
     <row r="125">
       <c r="A125" s="5" t="s">
-        <v>423</v>
+        <v>467</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>622</v>
+        <v>567</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>623</v>
+        <v>568</v>
       </c>
       <c r="D125" s="27" t="s">
-        <v>624</v>
+        <v>569</v>
       </c>
       <c r="E125" s="5"/>
       <c r="F125" s="5"/>
@@ -10243,16 +10348,16 @@
     </row>
     <row r="126">
       <c r="A126" s="5" t="s">
-        <v>423</v>
+        <v>467</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>625</v>
+        <v>571</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>626</v>
+        <v>572</v>
       </c>
       <c r="D126" s="27" t="s">
-        <v>627</v>
+        <v>573</v>
       </c>
       <c r="E126" s="5"/>
       <c r="F126" s="5"/>
@@ -10279,16 +10384,16 @@
     </row>
     <row r="127">
       <c r="A127" s="5" t="s">
-        <v>423</v>
+        <v>467</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>628</v>
+        <v>576</v>
       </c>
       <c r="D127" s="27" t="s">
-        <v>476</v>
+        <v>455</v>
       </c>
       <c r="E127" s="5"/>
       <c r="F127" s="5"/>
@@ -10315,16 +10420,16 @@
     </row>
     <row r="128">
       <c r="A128" s="5" t="s">
-        <v>423</v>
+        <v>467</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>629</v>
+        <v>577</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>630</v>
+        <v>578</v>
       </c>
       <c r="D128" s="7" t="s">
-        <v>606</v>
+        <v>544</v>
       </c>
       <c r="E128" s="5"/>
       <c r="F128" s="5"/>
@@ -10351,16 +10456,16 @@
     </row>
     <row r="129">
       <c r="A129" s="5" t="s">
-        <v>430</v>
+        <v>506</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>631</v>
+        <v>580</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>632</v>
+        <v>581</v>
       </c>
       <c r="D129" s="27" t="s">
-        <v>633</v>
+        <v>582</v>
       </c>
       <c r="E129" s="5"/>
       <c r="F129" s="5"/>
@@ -10387,16 +10492,16 @@
     </row>
     <row r="130">
       <c r="A130" s="5" t="s">
-        <v>430</v>
+        <v>506</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>634</v>
+        <v>583</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>635</v>
+        <v>584</v>
       </c>
       <c r="D130" s="27" t="s">
-        <v>636</v>
+        <v>585</v>
       </c>
       <c r="E130" s="5"/>
       <c r="F130" s="5"/>
@@ -10423,16 +10528,16 @@
     </row>
     <row r="131">
       <c r="A131" s="5" t="s">
-        <v>430</v>
+        <v>506</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>637</v>
+        <v>589</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>638</v>
+        <v>590</v>
       </c>
       <c r="D131" s="27" t="s">
-        <v>639</v>
+        <v>591</v>
       </c>
       <c r="E131" s="5"/>
       <c r="F131" s="5"/>
@@ -10459,16 +10564,16 @@
     </row>
     <row r="132">
       <c r="A132" s="5" t="s">
-        <v>430</v>
+        <v>506</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>640</v>
+        <v>593</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>641</v>
+        <v>594</v>
       </c>
       <c r="D132" s="27" t="s">
-        <v>642</v>
+        <v>595</v>
       </c>
       <c r="E132" s="5"/>
       <c r="F132" s="5"/>
@@ -10495,16 +10600,16 @@
     </row>
     <row r="133">
       <c r="A133" s="5" t="s">
-        <v>430</v>
+        <v>506</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>643</v>
+        <v>596</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>644</v>
+        <v>597</v>
       </c>
       <c r="D133" s="27" t="s">
-        <v>645</v>
+        <v>599</v>
       </c>
       <c r="E133" s="5"/>
       <c r="F133" s="5"/>
@@ -10531,16 +10636,16 @@
     </row>
     <row r="134">
       <c r="A134" s="5" t="s">
-        <v>430</v>
+        <v>506</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>646</v>
+        <v>601</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>647</v>
+        <v>603</v>
       </c>
       <c r="D134" s="27" t="s">
-        <v>648</v>
+        <v>605</v>
       </c>
       <c r="E134" s="5"/>
       <c r="F134" s="5"/>
@@ -10567,16 +10672,16 @@
     </row>
     <row r="135">
       <c r="A135" s="5" t="s">
-        <v>430</v>
+        <v>506</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>649</v>
+        <v>608</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>650</v>
+        <v>609</v>
       </c>
       <c r="D135" s="27" t="s">
-        <v>651</v>
+        <v>610</v>
       </c>
       <c r="E135" s="5"/>
       <c r="F135" s="5"/>
@@ -10603,16 +10708,16 @@
     </row>
     <row r="136">
       <c r="A136" s="5" t="s">
-        <v>430</v>
+        <v>506</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>652</v>
+        <v>611</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>630</v>
+        <v>578</v>
       </c>
       <c r="D136" s="7" t="s">
-        <v>606</v>
+        <v>544</v>
       </c>
       <c r="E136" s="5"/>
       <c r="F136" s="5"/>
@@ -10639,16 +10744,16 @@
     </row>
     <row r="137">
       <c r="A137" s="5" t="s">
-        <v>447</v>
+        <v>553</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>653</v>
+        <v>613</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>654</v>
+        <v>614</v>
       </c>
       <c r="D137" s="7" t="s">
-        <v>655</v>
+        <v>615</v>
       </c>
       <c r="E137" s="5"/>
       <c r="F137" s="5"/>
@@ -10675,16 +10780,16 @@
     </row>
     <row r="138">
       <c r="A138" s="5" t="s">
-        <v>447</v>
+        <v>553</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>656</v>
+        <v>618</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>657</v>
+        <v>619</v>
       </c>
       <c r="D138" s="7" t="s">
-        <v>658</v>
+        <v>620</v>
       </c>
       <c r="E138" s="5"/>
       <c r="F138" s="5"/>
@@ -10711,16 +10816,16 @@
     </row>
     <row r="139">
       <c r="A139" s="5" t="s">
-        <v>447</v>
+        <v>553</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>659</v>
+        <v>622</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>660</v>
+        <v>624</v>
       </c>
       <c r="D139" s="27" t="s">
-        <v>661</v>
+        <v>625</v>
       </c>
       <c r="E139" s="18"/>
       <c r="F139" s="5"/>
@@ -10747,16 +10852,16 @@
     </row>
     <row r="140">
       <c r="A140" s="5" t="s">
-        <v>447</v>
+        <v>553</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>50</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>662</v>
+        <v>626</v>
       </c>
       <c r="D140" s="27" t="s">
-        <v>663</v>
+        <v>627</v>
       </c>
       <c r="E140" s="5"/>
       <c r="F140" s="5"/>
@@ -10783,16 +10888,16 @@
     </row>
     <row r="141">
       <c r="A141" s="5" t="s">
-        <v>447</v>
+        <v>553</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>664</v>
+        <v>628</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>665</v>
+        <v>629</v>
       </c>
       <c r="D141" s="7" t="s">
-        <v>606</v>
+        <v>544</v>
       </c>
       <c r="E141" s="5"/>
       <c r="F141" s="5"/>
@@ -10819,16 +10924,16 @@
     </row>
     <row r="142">
       <c r="A142" s="5" t="s">
-        <v>482</v>
+        <v>604</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>666</v>
+        <v>631</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>667</v>
+        <v>632</v>
       </c>
       <c r="D142" s="27" t="s">
-        <v>668</v>
+        <v>633</v>
       </c>
       <c r="E142" s="5"/>
       <c r="F142" s="5"/>
@@ -10855,16 +10960,16 @@
     </row>
     <row r="143">
       <c r="A143" s="5" t="s">
-        <v>482</v>
+        <v>604</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>669</v>
+        <v>634</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>670</v>
+        <v>635</v>
       </c>
       <c r="D143" s="27" t="s">
-        <v>671</v>
+        <v>636</v>
       </c>
       <c r="E143" s="5"/>
       <c r="F143" s="5"/>
@@ -10891,16 +10996,16 @@
     </row>
     <row r="144">
       <c r="A144" s="5" t="s">
-        <v>482</v>
+        <v>604</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>672</v>
+        <v>637</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>673</v>
+        <v>638</v>
       </c>
       <c r="D144" s="27" t="s">
-        <v>674</v>
+        <v>639</v>
       </c>
       <c r="E144" s="5"/>
       <c r="F144" s="5"/>
@@ -10927,16 +11032,16 @@
     </row>
     <row r="145">
       <c r="A145" s="5" t="s">
-        <v>482</v>
+        <v>604</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>675</v>
+        <v>641</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>630</v>
+        <v>578</v>
       </c>
       <c r="D145" s="7" t="s">
-        <v>606</v>
+        <v>544</v>
       </c>
       <c r="E145" s="5"/>
       <c r="F145" s="5"/>
@@ -10963,16 +11068,16 @@
     </row>
     <row r="146">
       <c r="A146" s="5" t="s">
-        <v>502</v>
+        <v>646</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>676</v>
+        <v>647</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>632</v>
+        <v>581</v>
       </c>
       <c r="D146" s="27" t="s">
-        <v>633</v>
+        <v>582</v>
       </c>
       <c r="E146" s="5"/>
       <c r="F146" s="5"/>
@@ -10999,16 +11104,16 @@
     </row>
     <row r="147">
       <c r="A147" s="5" t="s">
-        <v>502</v>
+        <v>646</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>677</v>
+        <v>651</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>635</v>
+        <v>584</v>
       </c>
       <c r="D147" s="27" t="s">
-        <v>636</v>
+        <v>585</v>
       </c>
       <c r="E147" s="5"/>
       <c r="F147" s="5"/>
@@ -11035,16 +11140,16 @@
     </row>
     <row r="148">
       <c r="A148" s="5" t="s">
-        <v>502</v>
+        <v>646</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>678</v>
+        <v>654</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>638</v>
+        <v>590</v>
       </c>
       <c r="D148" s="27" t="s">
-        <v>639</v>
+        <v>591</v>
       </c>
       <c r="E148" s="5"/>
       <c r="F148" s="5"/>
@@ -11071,16 +11176,16 @@
     </row>
     <row r="149">
       <c r="A149" s="5" t="s">
-        <v>502</v>
+        <v>646</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>679</v>
+        <v>656</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>641</v>
+        <v>594</v>
       </c>
       <c r="D149" s="27" t="s">
-        <v>642</v>
+        <v>595</v>
       </c>
       <c r="E149" s="5"/>
       <c r="F149" s="5"/>
@@ -11107,16 +11212,16 @@
     </row>
     <row r="150">
       <c r="A150" s="5" t="s">
-        <v>502</v>
+        <v>646</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>680</v>
+        <v>660</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>644</v>
+        <v>597</v>
       </c>
       <c r="D150" s="27" t="s">
-        <v>645</v>
+        <v>599</v>
       </c>
       <c r="E150" s="5"/>
       <c r="F150" s="5"/>
@@ -11143,16 +11248,16 @@
     </row>
     <row r="151">
       <c r="A151" s="5" t="s">
-        <v>502</v>
+        <v>646</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>681</v>
+        <v>662</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>647</v>
+        <v>603</v>
       </c>
       <c r="D151" s="27" t="s">
-        <v>648</v>
+        <v>605</v>
       </c>
       <c r="E151" s="5"/>
       <c r="F151" s="5"/>
@@ -11179,16 +11284,16 @@
     </row>
     <row r="152">
       <c r="A152" s="5" t="s">
-        <v>502</v>
+        <v>646</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>682</v>
+        <v>668</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>650</v>
+        <v>609</v>
       </c>
       <c r="D152" s="27" t="s">
-        <v>651</v>
+        <v>610</v>
       </c>
       <c r="E152" s="5"/>
       <c r="F152" s="5"/>
@@ -11215,16 +11320,16 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="s">
-        <v>502</v>
+        <v>646</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>683</v>
+        <v>669</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>665</v>
+        <v>629</v>
       </c>
       <c r="D153" s="7" t="s">
-        <v>606</v>
+        <v>544</v>
       </c>
       <c r="E153" s="5"/>
       <c r="F153" s="5"/>
@@ -11251,7 +11356,7 @@
     </row>
     <row r="154">
       <c r="A154" s="5" t="s">
-        <v>684</v>
+        <v>670</v>
       </c>
       <c r="B154" s="5" t="s">
         <v>17</v>
@@ -11260,7 +11365,7 @@
         <v>18</v>
       </c>
       <c r="D154" s="27" t="s">
-        <v>685</v>
+        <v>672</v>
       </c>
       <c r="E154" s="5"/>
       <c r="F154" s="5"/>
@@ -11287,7 +11392,7 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="s">
-        <v>684</v>
+        <v>670</v>
       </c>
       <c r="B155" s="5" t="s">
         <v>20</v>
@@ -11323,16 +11428,16 @@
     </row>
     <row r="156">
       <c r="A156" s="5" t="s">
-        <v>684</v>
+        <v>670</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>686</v>
+        <v>679</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>665</v>
+        <v>629</v>
       </c>
       <c r="D156" s="7" t="s">
-        <v>606</v>
+        <v>544</v>
       </c>
       <c r="E156" s="5"/>
       <c r="F156" s="5"/>
@@ -11476,22 +11581,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2">

--- a/forms/app/postpartum.xlsx
+++ b/forms/app/postpartum.xlsx
@@ -1,14 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D-tree\config-dtree-newrepo\config-dtree\forms\app\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6325"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="survey" sheetId="1" r:id="rId3"/>
-    <sheet state="visible" name="choices" sheetId="2" r:id="rId4"/>
-    <sheet state="visible" name="settings" sheetId="3" r:id="rId5"/>
+    <sheet name="survey" sheetId="1" r:id="rId1"/>
+    <sheet name="choices" sheetId="2" r:id="rId2"/>
+    <sheet name="settings" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="162913" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
@@ -405,12 +413,6 @@
   </si>
   <si>
     <t>postpartum_danger_signs_note</t>
-  </si>
-  <si>
-    <t>First, I'm going to check for any postpartum danger signs.</t>
-  </si>
-  <si>
-    <t>Kwanza kabisa nitakuchunguza kam unadalili za hatari baada ya kujifungua</t>
   </si>
   <si>
     <t>postpartum_emergency_danger_signs</t>
@@ -2293,43 +2295,57 @@
   <si>
     <t>data</t>
   </si>
+  <si>
+    <t>First, I'm going to check for any postpartum danger signs.  If you have any of the following danger signs, I shall refer you to a nearest health facility so that you can receive the appropriate medical attention.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kwanza kabisa nitakuchunguza kam unadalili za hatari baada ya kujifungua.  Iwapo utaonesha una dalili za hatari, utapatiwa rufaa (kwenda kituo cha afya) na kuunganishwa na mtoa huduma kwenye kituo kilicho karibu yako. </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="9">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
-    <font/>
     <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Sans"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Roboto"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF1D1C1D"/>
       <name val="Slack-Lato"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Cambria"/>
     </font>
@@ -2339,7 +2355,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -2355,16 +2371,31 @@
     </fill>
   </fills>
   <borders count="7">
-    <border/>
     <border>
+      <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FFBFBFBF"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right/>
       <top style="thin">
         <color rgb="FFBFBFBF"/>
@@ -2372,209 +2403,398 @@
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FFBFBFBF"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4472C4"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
+  <dimension ref="A1:Z185"/>
+  <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="19.86"/>
-    <col customWidth="1" min="2" max="2" width="42.71"/>
-    <col customWidth="1" min="3" max="3" width="49.57"/>
-    <col customWidth="1" min="4" max="4" width="278.86"/>
+    <col min="1" max="1" width="19.86328125" customWidth="1"/>
+    <col min="2" max="2" width="42.6796875" customWidth="1"/>
+    <col min="3" max="3" width="49.54296875" customWidth="1"/>
+    <col min="4" max="4" width="278.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:26" ht="13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2627,7 +2847,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:26" ht="13">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
@@ -2642,7 +2862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:26" ht="13">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
@@ -2653,7 +2873,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:26" ht="13">
       <c r="A4" s="1" t="s">
         <v>22</v>
       </c>
@@ -2664,7 +2884,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:26" ht="13">
       <c r="A5" s="1" t="s">
         <v>22</v>
       </c>
@@ -2675,7 +2895,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:26" ht="13">
       <c r="A6" s="1" t="s">
         <v>22</v>
       </c>
@@ -2686,7 +2906,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:26" ht="13">
       <c r="A7" s="4" t="s">
         <v>22</v>
       </c>
@@ -2720,7 +2940,7 @@
       <c r="Y7" s="5"/>
       <c r="Z7" s="5"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:26" ht="13">
       <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
@@ -2731,7 +2951,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:26" ht="13">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -2742,7 +2962,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:26" ht="13">
       <c r="A10" s="6" t="s">
         <v>22</v>
       </c>
@@ -2753,7 +2973,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:26" ht="13">
       <c r="A11" s="7" t="s">
         <v>22</v>
       </c>
@@ -2764,7 +2984,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:26" ht="13">
       <c r="A12" s="7" t="s">
         <v>22</v>
       </c>
@@ -2775,7 +2995,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:26" ht="13">
       <c r="A13" s="7" t="s">
         <v>34</v>
       </c>
@@ -2784,7 +3004,7 @@
       </c>
       <c r="C13" s="7"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:26" ht="13">
       <c r="A14" s="8" t="s">
         <v>17</v>
       </c>
@@ -2795,7 +3015,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:26" ht="13">
       <c r="A15" s="8" t="s">
         <v>36</v>
       </c>
@@ -2806,7 +3026,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:26" ht="13">
       <c r="A16" s="8" t="s">
         <v>22</v>
       </c>
@@ -2817,7 +3037,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:26" ht="13">
       <c r="A17" s="9" t="s">
         <v>22</v>
       </c>
@@ -2828,7 +3048,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:26" ht="13">
       <c r="A18" s="8" t="s">
         <v>34</v>
       </c>
@@ -2837,7 +3057,7 @@
       </c>
       <c r="C18" s="5"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:26" ht="13">
       <c r="A19" s="7" t="s">
         <v>34</v>
       </c>
@@ -2846,7 +3066,7 @@
       </c>
       <c r="C19" s="2"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:26" ht="13">
       <c r="A20" s="8" t="s">
         <v>39</v>
       </c>
@@ -2880,7 +3100,7 @@
       <c r="Y20" s="5"/>
       <c r="Z20" s="5"/>
     </row>
-    <row r="21">
+    <row r="21" spans="1:26" ht="13">
       <c r="A21" s="1" t="s">
         <v>39</v>
       </c>
@@ -2905,7 +3125,7 @@
       <c r="P21" s="5"/>
       <c r="Q21" s="5"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:26" ht="13">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -2932,7 +3152,7 @@
       <c r="P22" s="5"/>
       <c r="Q22" s="5"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:26" ht="13">
       <c r="A23" s="1" t="s">
         <v>39</v>
       </c>
@@ -2959,7 +3179,7 @@
       <c r="P23" s="5"/>
       <c r="Q23" s="5"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:26" ht="13">
       <c r="A24" s="1" t="s">
         <v>39</v>
       </c>
@@ -2986,7 +3206,7 @@
       <c r="P24" s="5"/>
       <c r="Q24" s="5"/>
     </row>
-    <row r="25">
+    <row r="25" spans="1:26" ht="13">
       <c r="A25" s="1" t="s">
         <v>39</v>
       </c>
@@ -3011,7 +3231,7 @@
       <c r="P25" s="5"/>
       <c r="Q25" s="5"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:26" ht="13">
       <c r="A26" s="1" t="s">
         <v>39</v>
       </c>
@@ -3036,7 +3256,7 @@
       <c r="P26" s="5"/>
       <c r="Q26" s="5"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:26" ht="13">
       <c r="A27" s="1" t="s">
         <v>39</v>
       </c>
@@ -3061,7 +3281,7 @@
       <c r="P27" s="5"/>
       <c r="Q27" s="5"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:26" ht="13">
       <c r="A28" s="1" t="s">
         <v>39</v>
       </c>
@@ -3086,7 +3306,7 @@
       <c r="P28" s="5"/>
       <c r="Q28" s="5"/>
     </row>
-    <row r="29">
+    <row r="29" spans="1:26" ht="13">
       <c r="A29" s="1" t="s">
         <v>39</v>
       </c>
@@ -3111,7 +3331,7 @@
       <c r="P29" s="5"/>
       <c r="Q29" s="5"/>
     </row>
-    <row r="30">
+    <row r="30" spans="1:26" ht="13">
       <c r="A30" s="1" t="s">
         <v>39</v>
       </c>
@@ -3127,11 +3347,16 @@
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
       <c r="K30" s="5"/>
-      <c r="L30" s="16" t="s">
+      <c r="L30" s="47" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="31">
+      <c r="M30" s="48"/>
+      <c r="N30" s="48"/>
+      <c r="O30" s="48"/>
+      <c r="P30" s="48"/>
+      <c r="Q30" s="48"/>
+    </row>
+    <row r="31" spans="1:26" ht="13">
       <c r="A31" s="1" t="s">
         <v>39</v>
       </c>
@@ -3156,7 +3381,7 @@
       <c r="P31" s="5"/>
       <c r="Q31" s="5"/>
     </row>
-    <row r="32">
+    <row r="32" spans="1:26" ht="13">
       <c r="A32" s="1" t="s">
         <v>39</v>
       </c>
@@ -3172,8 +3397,8 @@
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
-      <c r="L32" s="17">
-        <v>7.0</v>
+      <c r="L32" s="16">
+        <v>7</v>
       </c>
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
@@ -3181,7 +3406,7 @@
       <c r="P32" s="5"/>
       <c r="Q32" s="5"/>
     </row>
-    <row r="33">
+    <row r="33" spans="1:26" ht="13">
       <c r="A33" s="1" t="s">
         <v>39</v>
       </c>
@@ -3197,8 +3422,8 @@
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
-      <c r="L33" s="17">
-        <v>30.0</v>
+      <c r="L33" s="16">
+        <v>30</v>
       </c>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
@@ -3206,7 +3431,7 @@
       <c r="P33" s="5"/>
       <c r="Q33" s="5"/>
     </row>
-    <row r="34">
+    <row r="34" spans="1:26" ht="13">
       <c r="A34" s="1" t="s">
         <v>39</v>
       </c>
@@ -3222,7 +3447,7 @@
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
-      <c r="L34" s="18" t="s">
+      <c r="L34" s="17" t="s">
         <v>68</v>
       </c>
       <c r="M34" s="15"/>
@@ -3231,7 +3456,7 @@
       <c r="P34" s="5"/>
       <c r="Q34" s="5"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:26" ht="13">
       <c r="A35" s="1" t="s">
         <v>39</v>
       </c>
@@ -3247,7 +3472,7 @@
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
-      <c r="L35" s="18" t="s">
+      <c r="L35" s="17" t="s">
         <v>70</v>
       </c>
       <c r="M35" s="15"/>
@@ -3256,7 +3481,7 @@
       <c r="P35" s="5"/>
       <c r="Q35" s="5"/>
     </row>
-    <row r="36">
+    <row r="36" spans="1:26" ht="13">
       <c r="A36" s="1" t="s">
         <v>39</v>
       </c>
@@ -3272,7 +3497,7 @@
       <c r="I36" s="5"/>
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
-      <c r="L36" s="18" t="s">
+      <c r="L36" s="17" t="s">
         <v>72</v>
       </c>
       <c r="M36" s="15"/>
@@ -3281,7 +3506,7 @@
       <c r="P36" s="5"/>
       <c r="Q36" s="5"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:26" ht="13">
       <c r="A37" s="1" t="s">
         <v>39</v>
       </c>
@@ -3297,7 +3522,7 @@
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
-      <c r="L37" s="18" t="s">
+      <c r="L37" s="17" t="s">
         <v>74</v>
       </c>
       <c r="M37" s="15"/>
@@ -3306,11 +3531,11 @@
       <c r="P37" s="5"/>
       <c r="Q37" s="5"/>
     </row>
-    <row r="38">
+    <row r="38" spans="1:26" ht="13">
       <c r="A38" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="19" t="s">
+      <c r="B38" s="18" t="s">
         <v>24</v>
       </c>
       <c r="C38" s="5"/>
@@ -3331,7 +3556,7 @@
       <c r="P38" s="5"/>
       <c r="Q38" s="5"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:26" ht="13">
       <c r="A39" s="1" t="s">
         <v>39</v>
       </c>
@@ -3356,33 +3581,33 @@
       <c r="P39" s="5"/>
       <c r="Q39" s="5"/>
     </row>
-    <row r="40">
-      <c r="A40" s="19" t="s">
+    <row r="40" spans="1:26" ht="13">
+      <c r="A40" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="19" t="s">
+      <c r="B40" s="18" t="s">
         <v>78</v>
       </c>
       <c r="C40" s="5"/>
       <c r="G40" s="1"/>
-      <c r="L40" s="20" t="s">
+      <c r="L40" s="19" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="19" t="s">
+    <row r="41" spans="1:26" ht="13">
+      <c r="A41" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="19" t="s">
+      <c r="B41" s="18" t="s">
         <v>80</v>
       </c>
       <c r="C41" s="5"/>
       <c r="G41" s="1"/>
-      <c r="L41" s="20" t="s">
+      <c r="L41" s="19" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:26" ht="13">
       <c r="A42" s="8" t="s">
         <v>39</v>
       </c>
@@ -3392,7 +3617,7 @@
       <c r="C42" s="5"/>
       <c r="D42" s="8"/>
       <c r="E42" s="5"/>
-      <c r="F42" s="21"/>
+      <c r="F42" s="20"/>
       <c r="G42" s="8"/>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
@@ -3416,168 +3641,168 @@
       <c r="Y42" s="5"/>
       <c r="Z42" s="5"/>
     </row>
-    <row r="43">
-      <c r="A43" s="19" t="s">
+    <row r="43" spans="1:26" ht="13">
+      <c r="A43" s="18" t="s">
         <v>39</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>83</v>
       </c>
       <c r="C43" s="5"/>
-      <c r="D43" s="22"/>
+      <c r="D43" s="21"/>
       <c r="G43" s="1"/>
-      <c r="L43" s="20" t="s">
+      <c r="L43" s="19" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:26" ht="13">
       <c r="A44" s="4" t="s">
         <v>85</v>
       </c>
       <c r="B44" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="C44" s="23"/>
-      <c r="D44" s="24"/>
-      <c r="E44" s="23"/>
-      <c r="F44" s="23"/>
-      <c r="G44" s="24"/>
-      <c r="H44" s="23"/>
-      <c r="I44" s="23"/>
-      <c r="J44" s="23"/>
-      <c r="K44" s="23"/>
-      <c r="L44" s="25"/>
-      <c r="M44" s="23"/>
-      <c r="N44" s="23"/>
-      <c r="O44" s="23"/>
-      <c r="P44" s="23"/>
-      <c r="Q44" s="23"/>
-      <c r="R44" s="23"/>
-      <c r="S44" s="23"/>
-      <c r="T44" s="23"/>
-      <c r="U44" s="23"/>
-      <c r="V44" s="23"/>
-      <c r="W44" s="23"/>
-      <c r="X44" s="23"/>
-      <c r="Y44" s="23"/>
-      <c r="Z44" s="23"/>
-    </row>
-    <row r="45">
+      <c r="C44" s="22"/>
+      <c r="D44" s="23"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="23"/>
+      <c r="H44" s="22"/>
+      <c r="I44" s="22"/>
+      <c r="J44" s="22"/>
+      <c r="K44" s="22"/>
+      <c r="L44" s="24"/>
+      <c r="M44" s="22"/>
+      <c r="N44" s="22"/>
+      <c r="O44" s="22"/>
+      <c r="P44" s="22"/>
+      <c r="Q44" s="22"/>
+      <c r="R44" s="22"/>
+      <c r="S44" s="22"/>
+      <c r="T44" s="22"/>
+      <c r="U44" s="22"/>
+      <c r="V44" s="22"/>
+      <c r="W44" s="22"/>
+      <c r="X44" s="22"/>
+      <c r="Y44" s="22"/>
+      <c r="Z44" s="22"/>
+    </row>
+    <row r="45" spans="1:26" ht="13">
       <c r="A45" s="4" t="s">
         <v>86</v>
       </c>
       <c r="B45" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="C45" s="23"/>
-      <c r="D45" s="24"/>
-      <c r="E45" s="23"/>
-      <c r="F45" s="23"/>
-      <c r="G45" s="24"/>
-      <c r="H45" s="23"/>
-      <c r="I45" s="23"/>
-      <c r="J45" s="23"/>
-      <c r="K45" s="23"/>
-      <c r="L45" s="25"/>
-      <c r="M45" s="23"/>
-      <c r="N45" s="23"/>
-      <c r="O45" s="23"/>
-      <c r="P45" s="23"/>
-      <c r="Q45" s="23"/>
-      <c r="R45" s="23"/>
-      <c r="S45" s="23"/>
-      <c r="T45" s="23"/>
-      <c r="U45" s="23"/>
-      <c r="V45" s="23"/>
-      <c r="W45" s="23"/>
-      <c r="X45" s="23"/>
-      <c r="Y45" s="23"/>
-      <c r="Z45" s="23"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="24" t="s">
+      <c r="C45" s="22"/>
+      <c r="D45" s="23"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="22"/>
+      <c r="G45" s="23"/>
+      <c r="H45" s="22"/>
+      <c r="I45" s="22"/>
+      <c r="J45" s="22"/>
+      <c r="K45" s="22"/>
+      <c r="L45" s="24"/>
+      <c r="M45" s="22"/>
+      <c r="N45" s="22"/>
+      <c r="O45" s="22"/>
+      <c r="P45" s="22"/>
+      <c r="Q45" s="22"/>
+      <c r="R45" s="22"/>
+      <c r="S45" s="22"/>
+      <c r="T45" s="22"/>
+      <c r="U45" s="22"/>
+      <c r="V45" s="22"/>
+      <c r="W45" s="22"/>
+      <c r="X45" s="22"/>
+      <c r="Y45" s="22"/>
+      <c r="Z45" s="22"/>
+    </row>
+    <row r="46" spans="1:26" ht="13">
+      <c r="A46" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="B46" s="23" t="s">
+      <c r="B46" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="C46" s="23" t="s">
+      <c r="C46" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="D46" s="26" t="s">
+      <c r="D46" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="E46" s="23"/>
-      <c r="F46" s="23"/>
-      <c r="G46" s="24"/>
-      <c r="H46" s="23"/>
-      <c r="I46" s="23"/>
-      <c r="J46" s="23"/>
-      <c r="K46" s="23"/>
-      <c r="L46" s="23"/>
-      <c r="M46" s="23"/>
-      <c r="N46" s="23"/>
-      <c r="O46" s="23"/>
-      <c r="P46" s="23"/>
-      <c r="Q46" s="23"/>
-      <c r="R46" s="23"/>
-      <c r="S46" s="23"/>
-    </row>
-    <row r="47" ht="17.25" customHeight="1">
-      <c r="A47" s="24" t="s">
+      <c r="E46" s="22"/>
+      <c r="F46" s="22"/>
+      <c r="G46" s="23"/>
+      <c r="H46" s="22"/>
+      <c r="I46" s="22"/>
+      <c r="J46" s="22"/>
+      <c r="K46" s="22"/>
+      <c r="L46" s="22"/>
+      <c r="M46" s="22"/>
+      <c r="N46" s="22"/>
+      <c r="O46" s="22"/>
+      <c r="P46" s="22"/>
+      <c r="Q46" s="22"/>
+      <c r="R46" s="22"/>
+      <c r="S46" s="22"/>
+    </row>
+    <row r="47" spans="1:26" ht="17.25" customHeight="1">
+      <c r="A47" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="B47" s="23" t="s">
+      <c r="B47" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="C47" s="27" t="s">
+      <c r="C47" s="26" t="s">
         <v>93</v>
       </c>
-      <c r="D47" s="27" t="s">
+      <c r="D47" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="E47" s="23"/>
-      <c r="F47" s="23"/>
-      <c r="G47" s="24"/>
-      <c r="H47" s="23"/>
-      <c r="I47" s="23"/>
-      <c r="J47" s="23"/>
-      <c r="K47" s="23"/>
-      <c r="L47" s="23"/>
-      <c r="M47" s="23"/>
-      <c r="N47" s="23"/>
-      <c r="O47" s="23"/>
-      <c r="P47" s="23"/>
-      <c r="Q47" s="23"/>
-      <c r="R47" s="23"/>
-      <c r="S47" s="23"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="24" t="s">
+      <c r="E47" s="22"/>
+      <c r="F47" s="22"/>
+      <c r="G47" s="23"/>
+      <c r="H47" s="22"/>
+      <c r="I47" s="22"/>
+      <c r="J47" s="22"/>
+      <c r="K47" s="22"/>
+      <c r="L47" s="22"/>
+      <c r="M47" s="22"/>
+      <c r="N47" s="22"/>
+      <c r="O47" s="22"/>
+      <c r="P47" s="22"/>
+      <c r="Q47" s="22"/>
+      <c r="R47" s="22"/>
+      <c r="S47" s="22"/>
+    </row>
+    <row r="48" spans="1:26" ht="13">
+      <c r="A48" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="B48" s="23" t="s">
+      <c r="B48" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="C48" s="23"/>
-      <c r="D48" s="24"/>
-      <c r="E48" s="23"/>
-      <c r="F48" s="23"/>
-      <c r="G48" s="24"/>
-      <c r="H48" s="23"/>
-      <c r="I48" s="23"/>
-      <c r="J48" s="23"/>
-      <c r="K48" s="23"/>
-      <c r="L48" s="23"/>
-      <c r="M48" s="23"/>
-      <c r="N48" s="23"/>
-      <c r="O48" s="23"/>
-      <c r="P48" s="23"/>
-      <c r="Q48" s="23"/>
-      <c r="R48" s="23"/>
-      <c r="S48" s="23"/>
-    </row>
-    <row r="49">
+      <c r="C48" s="22"/>
+      <c r="D48" s="23"/>
+      <c r="E48" s="22"/>
+      <c r="F48" s="22"/>
+      <c r="G48" s="23"/>
+      <c r="H48" s="22"/>
+      <c r="I48" s="22"/>
+      <c r="J48" s="22"/>
+      <c r="K48" s="22"/>
+      <c r="L48" s="22"/>
+      <c r="M48" s="22"/>
+      <c r="N48" s="22"/>
+      <c r="O48" s="22"/>
+      <c r="P48" s="22"/>
+      <c r="Q48" s="22"/>
+      <c r="R48" s="22"/>
+      <c r="S48" s="22"/>
+    </row>
+    <row r="49" spans="1:7" ht="13">
       <c r="A49" s="8" t="s">
         <v>17</v>
       </c>
@@ -3587,28 +3812,28 @@
       <c r="C49" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D49" s="22" t="s">
+      <c r="D49" s="21" t="s">
         <v>98</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:7" ht="13">
       <c r="A50" s="8" t="s">
         <v>91</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C50" s="19" t="s">
+      <c r="C50" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="D50" s="20" t="s">
+      <c r="D50" s="19" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:7" ht="13">
       <c r="A51" s="8" t="s">
         <v>91</v>
       </c>
@@ -3622,7 +3847,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:7" ht="13">
       <c r="A52" s="8" t="s">
         <v>91</v>
       </c>
@@ -3636,7 +3861,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:7" ht="13">
       <c r="A53" s="8" t="s">
         <v>91</v>
       </c>
@@ -3646,23 +3871,23 @@
       <c r="C53" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D53" s="19" t="s">
+      <c r="D53" s="18" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:7" ht="14.25">
       <c r="A54" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B54" s="28" t="s">
+      <c r="B54" s="27" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:7" ht="14.25">
       <c r="A55" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B55" s="28" t="s">
+      <c r="B55" s="27" t="s">
         <v>112</v>
       </c>
       <c r="C55" s="1" t="s">
@@ -3672,11 +3897,11 @@
         <v>114</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:7" ht="14.25">
       <c r="A56" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B56" s="28" t="s">
+      <c r="B56" s="27" t="s">
         <v>115</v>
       </c>
       <c r="C56" s="1" t="s">
@@ -3686,19 +3911,19 @@
         <v>117</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:7" ht="14.25">
       <c r="A57" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B57" s="28" t="s">
+      <c r="B57" s="27" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:7" ht="14.25">
       <c r="A58" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B58" s="28" t="s">
+      <c r="B58" s="27" t="s">
         <v>118</v>
       </c>
       <c r="C58" s="1" t="s">
@@ -3708,26 +3933,26 @@
         <v>120</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:7" ht="14.25">
       <c r="A59" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B59" s="28" t="s">
+      <c r="B59" s="27" t="s">
         <v>121</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="D59" s="29" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="60">
+        <v>724</v>
+      </c>
+      <c r="D59" s="28" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="14.25">
       <c r="A60" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B60" s="28" t="s">
-        <v>124</v>
+      <c r="B60" s="27" t="s">
+        <v>122</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>19</v>
@@ -3736,759 +3961,759 @@
         <v>99</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:7" ht="14.25">
       <c r="A61" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B61" s="28" t="s">
+      <c r="B61" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C61" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="62">
+    </row>
+    <row r="62" spans="1:7" ht="14.25">
       <c r="A62" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B62" s="28" t="s">
+      <c r="B62" s="27" t="s">
+        <v>126</v>
+      </c>
+      <c r="C62" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C62" s="30" t="s">
-        <v>129</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="G62" s="1"/>
     </row>
-    <row r="63">
+    <row r="63" spans="1:7" ht="14.25">
       <c r="A63" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B63" s="28" t="s">
-        <v>131</v>
+      <c r="B63" s="27" t="s">
+        <v>129</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G63" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="14.25">
+      <c r="A64" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B64" s="27" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="s">
+      <c r="C64" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B64" s="28" t="s">
+      <c r="D64" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="E64" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D64" s="29" t="s">
+    </row>
+    <row r="65" spans="1:7" ht="14.25">
+      <c r="A65" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B65" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="C65" s="1" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B65" s="28" t="s">
+      <c r="D65" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="E65" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="14.25">
+      <c r="A66" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B66" s="27" t="s">
         <v>139</v>
       </c>
-      <c r="D65" s="31" t="s">
+      <c r="C66" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E65" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B66" s="28" t="s">
+      <c r="D66" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="D66" s="29" t="s">
-        <v>143</v>
-      </c>
       <c r="E66" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="67">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="14.25">
       <c r="A67" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B67" s="28" t="s">
+      <c r="B67" s="27" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="14.25">
+      <c r="A68" s="1" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B68" s="28" t="s">
+      <c r="B68" s="27" t="s">
+        <v>142</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D68" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="E68" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F68" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D68" s="29" t="s">
-        <v>146</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="69">
+    </row>
+    <row r="69" spans="1:7" ht="14.25">
       <c r="A69" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B69" s="28" t="s">
+      <c r="B69" s="27" t="s">
+        <v>146</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D69" s="28" t="s">
         <v>148</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="F69" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="D69" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="70" ht="15.75" customHeight="1">
+    </row>
+    <row r="70" spans="1:7" ht="15.75" customHeight="1">
       <c r="A70" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B70" s="28" t="s">
+      <c r="B70" s="27" t="s">
+        <v>150</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D70" s="28" t="s">
         <v>152</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="F70" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D70" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="71">
+    </row>
+    <row r="71" spans="1:7" ht="14.25">
       <c r="A71" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B71" s="28" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="72">
+      <c r="B71" s="27" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="14.25">
       <c r="A72" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B72" s="28" t="s">
+      <c r="B72" s="27" t="s">
         <v>118</v>
       </c>
       <c r="C72" s="1"/>
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
     </row>
-    <row r="73">
+    <row r="73" spans="1:7" ht="14.25">
       <c r="A73" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B73" s="28" t="s">
+      <c r="B73" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D73" s="28" t="s">
         <v>156</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="F73" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="D73" s="29" t="s">
-        <v>158</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>159</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:7" ht="14.25">
       <c r="A74" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B74" s="28" t="s">
+      <c r="B74" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C74" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="75">
+    </row>
+    <row r="75" spans="1:7" ht="14.25">
       <c r="A75" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B75" s="28" t="s">
-        <v>163</v>
+      <c r="B75" s="27" t="s">
+        <v>161</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="76">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="14.25">
       <c r="A76" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B76" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="B76" s="27" t="s">
+        <v>162</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D76" s="28" t="s">
         <v>164</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="E76" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="14.25">
+      <c r="A77" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B77" s="27" t="s">
         <v>165</v>
       </c>
-      <c r="D76" s="29" t="s">
+      <c r="C77" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E76" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B77" s="28" t="s">
+      <c r="D77" s="28" t="s">
         <v>167</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="E77" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="14.25">
+      <c r="A78" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B78" s="27" t="s">
         <v>168</v>
       </c>
-      <c r="D77" s="29" t="s">
+      <c r="C78" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E77" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B78" s="28" t="s">
+      <c r="D78" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="E78" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="14.25">
+      <c r="A79" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B79" s="27" t="s">
         <v>171</v>
       </c>
-      <c r="D78" s="29" t="s">
+      <c r="C79" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="E78" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B79" s="28" t="s">
+      <c r="D79" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="E79" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="14.25">
+      <c r="A80" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B80" s="27" t="s">
         <v>174</v>
       </c>
-      <c r="D79" s="29" t="s">
+      <c r="C80" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E79" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B80" s="28" t="s">
+      <c r="D80" s="28" t="s">
         <v>176</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="E80" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="14.25">
+      <c r="A81" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B81" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="D80" s="29" t="s">
+      <c r="C81" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="E80" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B81" s="28" t="s">
+      <c r="D81" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="E81" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="14.25">
+      <c r="A82" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B82" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="D81" s="1" t="s">
+      <c r="C82" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="E81" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B82" s="28" t="s">
+      <c r="D82" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="E82" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="14.25">
+      <c r="A83" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B83" s="27" t="s">
         <v>183</v>
       </c>
-      <c r="D82" s="29" t="s">
+      <c r="C83" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="E82" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B83" s="28" t="s">
+      <c r="D83" s="28" t="s">
         <v>185</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="E83" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="14.25">
+      <c r="A84" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B84" s="27" t="s">
         <v>186</v>
       </c>
-      <c r="D83" s="29" t="s">
+      <c r="C84" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="E83" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B84" s="28" t="s">
+      <c r="D84" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="E84" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="14.25">
+      <c r="A85" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B85" s="27" t="s">
         <v>189</v>
       </c>
-      <c r="D84" s="1" t="s">
+      <c r="C85" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E84" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B85" s="28" t="s">
+      <c r="D85" s="28" t="s">
         <v>191</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="E85" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="14.25">
+      <c r="A86" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B86" s="27" t="s">
         <v>192</v>
       </c>
-      <c r="D85" s="29" t="s">
+      <c r="C86" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="E85" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B86" s="28" t="s">
+      <c r="D86" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="E86" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="14.25">
+      <c r="A87" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B87" s="27" t="s">
         <v>195</v>
       </c>
-      <c r="D86" s="29" t="s">
+      <c r="C87" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E86" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B87" s="28" t="s">
+      <c r="D87" s="28" t="s">
         <v>197</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="E87" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="14.25">
+      <c r="A88" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B88" s="27" t="s">
         <v>198</v>
       </c>
-      <c r="D87" s="29" t="s">
+      <c r="C88" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="E87" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B88" s="28" t="s">
+      <c r="D88" s="28" t="s">
         <v>200</v>
       </c>
-      <c r="C88" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="D88" s="29" t="s">
-        <v>202</v>
-      </c>
       <c r="E88" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="89">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="14.25">
       <c r="A89" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B89" s="28" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="90">
+      <c r="B89" s="27" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="14.25">
       <c r="A90" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B90" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="C90" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B90" s="28" t="s">
+      <c r="D90" s="28" t="s">
         <v>204</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="E90" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F90" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="D90" s="29" t="s">
+    </row>
+    <row r="91" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A91" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B91" s="27" t="s">
         <v>206</v>
       </c>
-      <c r="E90" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="F90" s="1" t="s">
+      <c r="C91" s="1" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B91" s="28" t="s">
+      <c r="D91" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="E91" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F91" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="D91" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="92" ht="15.75" customHeight="1">
+    </row>
+    <row r="92" spans="1:6" ht="15.75" customHeight="1">
       <c r="A92" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B92" s="28" t="s">
+      <c r="B92" s="27" t="s">
+        <v>210</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="F92" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="D92" s="1" t="s">
+    </row>
+    <row r="93" spans="1:6" ht="14.25">
+      <c r="A93" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B93" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="F92" s="1" t="s">
+      <c r="C93" s="1" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B93" s="28" t="s">
+      <c r="D93" s="28" t="s">
         <v>216</v>
       </c>
-      <c r="C93" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="D93" s="29" t="s">
-        <v>218</v>
-      </c>
       <c r="E93" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="94" ht="15.75" customHeight="1">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="15.75" customHeight="1">
       <c r="A94" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B94" s="28" t="s">
+      <c r="B94" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D94" s="28" t="s">
         <v>219</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="F94" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="D94" s="29" t="s">
-        <v>221</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="95">
+    </row>
+    <row r="95" spans="1:6" ht="14.25">
       <c r="A95" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B95" s="28" t="s">
+      <c r="B95" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D95" s="28" t="s">
         <v>223</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="F95" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="D95" s="29" t="s">
-        <v>225</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="96" ht="15.75" customHeight="1">
+    </row>
+    <row r="96" spans="1:6" ht="15.75" customHeight="1">
       <c r="A96" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B96" s="28" t="s">
+      <c r="B96" s="27" t="s">
+        <v>225</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="D96" s="28" t="s">
         <v>227</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="F96" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="D96" s="29" t="s">
-        <v>229</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="97">
+    </row>
+    <row r="97" spans="1:26" ht="14.25">
       <c r="A97" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B97" s="28" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="98">
+      <c r="B97" s="27" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="98" spans="1:26" ht="14.25">
       <c r="A98" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B98" s="28" t="s">
+      <c r="B98" s="27" t="s">
+        <v>229</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="E98" s="1"/>
+      <c r="F98" s="19" t="s">
         <v>232</v>
       </c>
-      <c r="D98" s="1" t="s">
+      <c r="G98" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="E98" s="1"/>
-      <c r="F98" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="G98" s="1" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="99">
+    </row>
+    <row r="99" spans="1:26" ht="14.25">
       <c r="A99" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B99" s="28" t="s">
+      <c r="B99" s="27" t="s">
+        <v>234</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>238</v>
       </c>
       <c r="F99" s="1"/>
       <c r="G99" s="1"/>
     </row>
-    <row r="100">
+    <row r="100" spans="1:26" ht="14.25">
       <c r="A100" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B100" s="28" t="s">
-        <v>231</v>
+      <c r="B100" s="27" t="s">
+        <v>229</v>
       </c>
       <c r="C100" s="1"/>
-      <c r="D100" s="29"/>
+      <c r="D100" s="28"/>
       <c r="F100" s="1"/>
       <c r="G100" s="1"/>
     </row>
-    <row r="101">
+    <row r="101" spans="1:26" ht="14.25">
       <c r="A101" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B101" s="28" t="s">
+      <c r="B101" s="27" t="s">
+        <v>237</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D101" s="28" t="s">
         <v>239</v>
       </c>
-      <c r="C101" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="D101" s="29" t="s">
-        <v>241</v>
-      </c>
       <c r="F101" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G101" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:26" ht="14.25">
       <c r="A102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B102" s="28" t="s">
+      <c r="B102" s="27" t="s">
+        <v>240</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="C102" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>244</v>
-      </c>
       <c r="G102" s="1"/>
     </row>
-    <row r="103">
+    <row r="103" spans="1:26" ht="14.25">
       <c r="A103" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B103" s="28" t="s">
+      <c r="B103" s="27" t="s">
+        <v>243</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C103" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="G103" s="1"/>
     </row>
-    <row r="104">
+    <row r="104" spans="1:26" ht="14.25">
       <c r="A104" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B104" s="28" t="s">
-        <v>239</v>
+      <c r="B104" s="27" t="s">
+        <v>237</v>
       </c>
       <c r="C104" s="1"/>
       <c r="G104" s="1"/>
     </row>
-    <row r="105">
+    <row r="105" spans="1:26" ht="14.25">
       <c r="A105" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B105" s="28" t="s">
+      <c r="B105" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="F105" s="1" t="s">
         <v>249</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>251</v>
       </c>
       <c r="G105" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:26" ht="14.25">
       <c r="A106" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B106" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="B106" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="D106" s="28" t="s">
         <v>252</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="E106" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G106" s="1"/>
+    </row>
+    <row r="107" spans="1:26" ht="13">
+      <c r="A107" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="D106" s="29" t="s">
+      <c r="B107" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="E106" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="G106" s="1"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="6" t="s">
+      <c r="C107" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="B107" s="6" t="s">
+      <c r="D107" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="C107" s="6" t="s">
+      <c r="E107" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="F107" s="31" t="s">
         <v>257</v>
-      </c>
-      <c r="D107" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="E107" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="F107" s="32" t="s">
-        <v>259</v>
       </c>
       <c r="G107" s="8"/>
       <c r="H107" s="5"/>
@@ -4511,70 +4736,70 @@
       <c r="Y107" s="5"/>
       <c r="Z107" s="5"/>
     </row>
-    <row r="108">
+    <row r="108" spans="1:26" ht="14.25">
       <c r="A108" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B108" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="B108" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D108" s="28" t="s">
         <v>260</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="F108" s="19" t="s">
         <v>261</v>
       </c>
-      <c r="D108" s="29" t="s">
-        <v>262</v>
-      </c>
-      <c r="F108" s="20" t="s">
-        <v>263</v>
-      </c>
       <c r="G108" s="1"/>
     </row>
-    <row r="109">
+    <row r="109" spans="1:26" ht="14.25">
       <c r="A109" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B109" s="28" t="s">
-        <v>248</v>
+      <c r="B109" s="27" t="s">
+        <v>246</v>
       </c>
       <c r="C109" s="1"/>
-      <c r="F109" s="20"/>
+      <c r="F109" s="19"/>
       <c r="G109" s="1"/>
     </row>
-    <row r="110">
+    <row r="110" spans="1:26" ht="14.25">
       <c r="A110" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B110" s="28" t="s">
+      <c r="B110" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D110" s="28" t="s">
         <v>264</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="F110" s="19" t="s">
         <v>265</v>
-      </c>
-      <c r="D110" s="29" t="s">
-        <v>266</v>
-      </c>
-      <c r="F110" s="20" t="s">
-        <v>267</v>
       </c>
       <c r="G110" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:26" ht="13">
       <c r="A111" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="C111" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="B111" s="4" t="s">
+      <c r="D111" s="18" t="s">
         <v>269</v>
       </c>
-      <c r="C111" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="D111" s="19" t="s">
-        <v>271</v>
-      </c>
       <c r="E111" s="12" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F111" s="4"/>
       <c r="G111" s="8"/>
@@ -4598,24 +4823,24 @@
       <c r="Y111" s="5"/>
       <c r="Z111" s="5"/>
     </row>
-    <row r="112">
+    <row r="112" spans="1:26" ht="13">
       <c r="A112" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="C112" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="B112" s="4" t="s">
+      <c r="D112" s="32" t="s">
         <v>273</v>
       </c>
-      <c r="C112" s="4" t="s">
+      <c r="E112" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="F112" s="4" t="s">
         <v>274</v>
-      </c>
-      <c r="D112" s="33" t="s">
-        <v>275</v>
-      </c>
-      <c r="E112" s="12" t="s">
-        <v>137</v>
-      </c>
-      <c r="F112" s="4" t="s">
-        <v>276</v>
       </c>
       <c r="G112" s="8"/>
       <c r="H112" s="5"/>
@@ -4624,7 +4849,7 @@
       <c r="K112" s="5"/>
       <c r="L112" s="5"/>
       <c r="M112" s="11" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="N112" s="5"/>
       <c r="O112" s="5"/>
@@ -4640,12 +4865,12 @@
       <c r="Y112" s="5"/>
       <c r="Z112" s="5"/>
     </row>
-    <row r="113">
+    <row r="113" spans="1:26" ht="13">
       <c r="A113" s="4" t="s">
         <v>17</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>19</v>
@@ -4676,24 +4901,24 @@
       <c r="Y113" s="5"/>
       <c r="Z113" s="5"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1">
+    <row r="114" spans="1:26" ht="15.75" customHeight="1">
       <c r="A114" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C114" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="B114" s="4" t="s">
+      <c r="D114" s="18" t="s">
         <v>280</v>
       </c>
-      <c r="C114" s="4" t="s">
+      <c r="E114" s="12" t="s">
         <v>281</v>
       </c>
-      <c r="D114" s="19" t="s">
+      <c r="F114" s="4" t="s">
         <v>282</v>
-      </c>
-      <c r="E114" s="12" t="s">
-        <v>283</v>
-      </c>
-      <c r="F114" s="4" t="s">
-        <v>284</v>
       </c>
       <c r="G114" s="8"/>
       <c r="H114" s="5"/>
@@ -4702,7 +4927,7 @@
       <c r="K114" s="5"/>
       <c r="L114" s="5"/>
       <c r="M114" s="11" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="N114" s="5"/>
       <c r="O114" s="5"/>
@@ -4718,24 +4943,24 @@
       <c r="Y114" s="5"/>
       <c r="Z114" s="5"/>
     </row>
-    <row r="115">
+    <row r="115" spans="1:26" ht="13">
       <c r="A115" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="C115" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="B115" s="4" t="s">
+      <c r="D115" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="C115" s="4" t="s">
+      <c r="E115" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F115" s="4" t="s">
         <v>288</v>
-      </c>
-      <c r="D115" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="E115" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="F115" s="4" t="s">
-        <v>290</v>
       </c>
       <c r="G115" s="4"/>
       <c r="H115" s="4"/>
@@ -4758,12 +4983,12 @@
       <c r="Y115" s="5"/>
       <c r="Z115" s="5"/>
     </row>
-    <row r="116">
+    <row r="116" spans="1:26" ht="13">
       <c r="A116" s="4" t="s">
         <v>34</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C116" s="4"/>
       <c r="D116" s="4"/>
@@ -4790,21 +5015,21 @@
       <c r="Y116" s="5"/>
       <c r="Z116" s="5"/>
     </row>
-    <row r="117">
+    <row r="117" spans="1:26" ht="13">
       <c r="A117" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B117" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C117" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="B117" s="4" t="s">
+      <c r="D117" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="C117" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="D117" s="6" t="s">
-        <v>294</v>
-      </c>
       <c r="E117" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F117" s="4"/>
       <c r="G117" s="4"/>
@@ -4828,24 +5053,24 @@
       <c r="Y117" s="5"/>
       <c r="Z117" s="5"/>
     </row>
-    <row r="118">
+    <row r="118" spans="1:26" ht="13">
       <c r="A118" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="B118" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="C118" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="B118" s="4" t="s">
+      <c r="D118" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="C118" s="4" t="s">
+      <c r="E118" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F118" s="4" t="s">
         <v>297</v>
-      </c>
-      <c r="D118" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="E118" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="F118" s="4" t="s">
-        <v>299</v>
       </c>
       <c r="G118" s="4"/>
       <c r="H118" s="4"/>
@@ -4868,24 +5093,24 @@
       <c r="Y118" s="5"/>
       <c r="Z118" s="5"/>
     </row>
-    <row r="119">
+    <row r="119" spans="1:26" ht="13">
       <c r="A119" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="C119" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="B119" s="4" t="s">
+      <c r="D119" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="C119" s="4" t="s">
+      <c r="E119" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F119" s="4" t="s">
         <v>302</v>
-      </c>
-      <c r="D119" s="6" t="s">
-        <v>303</v>
-      </c>
-      <c r="E119" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="F119" s="4" t="s">
-        <v>304</v>
       </c>
       <c r="G119" s="4"/>
       <c r="H119" s="4"/>
@@ -4908,72 +5133,72 @@
       <c r="Y119" s="5"/>
       <c r="Z119" s="5"/>
     </row>
-    <row r="120">
+    <row r="120" spans="1:26" ht="13">
       <c r="A120" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="C120" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="B120" s="4" t="s">
+      <c r="D120" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="C120" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="D120" s="6" t="s">
-        <v>308</v>
-      </c>
       <c r="E120" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F120" s="4"/>
       <c r="G120" s="4"/>
       <c r="H120" s="4"/>
       <c r="I120" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="J120" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="K120" s="33" t="s">
         <v>309</v>
       </c>
-      <c r="J120" s="10" t="s">
+    </row>
+    <row r="121" spans="1:26" ht="13">
+      <c r="A121" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="K120" s="34" t="s">
+      <c r="B121" s="4" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="4" t="s">
+      <c r="C121" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="B121" s="4" t="s">
+      <c r="D121" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="C121" s="4" t="s">
+      <c r="E121" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F121" s="6" t="s">
         <v>314</v>
-      </c>
-      <c r="D121" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="E121" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="F121" s="6" t="s">
-        <v>316</v>
       </c>
       <c r="G121" s="4"/>
       <c r="H121" s="4"/>
       <c r="I121" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="J121" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="K121" s="33" t="s">
         <v>309</v>
       </c>
-      <c r="J121" s="10" t="s">
-        <v>310</v>
-      </c>
-      <c r="K121" s="34" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="122">
+    </row>
+    <row r="122" spans="1:26" ht="13">
       <c r="A122" s="4" t="s">
         <v>34</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C122" s="4"/>
       <c r="D122" s="4"/>
@@ -4982,52 +5207,52 @@
       <c r="G122" s="4"/>
       <c r="H122" s="4"/>
     </row>
-    <row r="123">
+    <row r="123" spans="1:26" ht="13">
       <c r="A123" s="4" t="s">
         <v>87</v>
       </c>
       <c r="B123" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="D123" s="6" t="s">
         <v>317</v>
-      </c>
-      <c r="C123" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="D123" s="6" t="s">
-        <v>319</v>
       </c>
       <c r="E123" s="4"/>
       <c r="F123" s="6" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="G123" s="4"/>
       <c r="H123" s="4"/>
     </row>
-    <row r="124">
+    <row r="124" spans="1:26" ht="13">
       <c r="A124" s="6" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B124" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="D124" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="C124" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="D124" s="6" t="s">
-        <v>323</v>
-      </c>
       <c r="E124" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F124" s="4"/>
       <c r="G124" s="4"/>
       <c r="H124" s="4"/>
     </row>
-    <row r="125">
+    <row r="125" spans="1:26" ht="13">
       <c r="A125" s="6" t="s">
         <v>34</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C125" s="4"/>
       <c r="D125" s="4"/>
@@ -5036,41 +5261,41 @@
       <c r="G125" s="4"/>
       <c r="H125" s="4"/>
     </row>
-    <row r="126">
+    <row r="126" spans="1:26" ht="13">
       <c r="A126" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E126" s="4"/>
       <c r="F126" s="6" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G126" s="4"/>
       <c r="H126" s="4"/>
     </row>
-    <row r="127">
+    <row r="127" spans="1:26" ht="13">
       <c r="A127" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="B127" s="34" t="s">
+        <v>325</v>
+      </c>
+      <c r="C127" s="35" t="s">
         <v>326</v>
       </c>
-      <c r="B127" s="35" t="s">
+      <c r="D127" s="18" t="s">
         <v>327</v>
       </c>
-      <c r="C127" s="36" t="s">
-        <v>328</v>
-      </c>
-      <c r="D127" s="19" t="s">
-        <v>329</v>
-      </c>
       <c r="E127" s="9" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F127" s="9"/>
       <c r="G127" s="8"/>
@@ -5094,14 +5319,14 @@
       <c r="Y127" s="5"/>
       <c r="Z127" s="5"/>
     </row>
-    <row r="128">
+    <row r="128" spans="1:26" ht="13">
       <c r="A128" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B128" s="35" t="s">
-        <v>330</v>
-      </c>
-      <c r="C128" s="37" t="s">
+      <c r="B128" s="34" t="s">
+        <v>328</v>
+      </c>
+      <c r="C128" s="36" t="s">
         <v>19</v>
       </c>
       <c r="D128" s="5"/>
@@ -5130,21 +5355,21 @@
       <c r="Y128" s="5"/>
       <c r="Z128" s="5"/>
     </row>
-    <row r="129">
+    <row r="129" spans="1:26" ht="13">
       <c r="A129" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="B129" s="34" t="s">
+        <v>330</v>
+      </c>
+      <c r="C129" s="37" t="s">
         <v>331</v>
       </c>
-      <c r="B129" s="35" t="s">
+      <c r="D129" s="32" t="s">
         <v>332</v>
       </c>
-      <c r="C129" s="38" t="s">
-        <v>333</v>
-      </c>
-      <c r="D129" s="33" t="s">
-        <v>334</v>
-      </c>
       <c r="E129" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F129" s="9"/>
       <c r="G129" s="8"/>
@@ -5168,24 +5393,24 @@
       <c r="Y129" s="5"/>
       <c r="Z129" s="5"/>
     </row>
-    <row r="130">
+    <row r="130" spans="1:26" ht="13">
       <c r="A130" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="B130" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="C130" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="B130" s="8" t="s">
+      <c r="D130" s="32" t="s">
+        <v>334</v>
+      </c>
+      <c r="E130" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F130" s="9" t="s">
         <v>335</v>
-      </c>
-      <c r="C130" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="D130" s="33" t="s">
-        <v>336</v>
-      </c>
-      <c r="E130" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="F130" s="9" t="s">
-        <v>337</v>
       </c>
       <c r="G130" s="8"/>
       <c r="H130" s="5"/>
@@ -5208,14 +5433,14 @@
       <c r="Y130" s="5"/>
       <c r="Z130" s="5"/>
     </row>
-    <row r="131">
+    <row r="131" spans="1:26" ht="13">
       <c r="A131" s="8" t="s">
         <v>34</v>
       </c>
       <c r="B131" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="C131" s="39"/>
+        <v>328</v>
+      </c>
+      <c r="C131" s="38"/>
       <c r="D131" s="5"/>
       <c r="E131" s="5"/>
       <c r="F131" s="9"/>
@@ -5240,14 +5465,14 @@
       <c r="Y131" s="5"/>
       <c r="Z131" s="5"/>
     </row>
-    <row r="132">
+    <row r="132" spans="1:26" ht="13">
       <c r="A132" s="8" t="s">
         <v>17</v>
       </c>
       <c r="B132" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="C132" s="39" t="s">
+        <v>336</v>
+      </c>
+      <c r="C132" s="38" t="s">
         <v>19</v>
       </c>
       <c r="D132" s="5"/>
@@ -5276,21 +5501,21 @@
       <c r="Y132" s="5"/>
       <c r="Z132" s="5"/>
     </row>
-    <row r="133">
+    <row r="133" spans="1:26" ht="13">
       <c r="A133" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="B133" s="34" t="s">
+        <v>338</v>
+      </c>
+      <c r="C133" s="37" t="s">
         <v>339</v>
       </c>
-      <c r="B133" s="35" t="s">
+      <c r="D133" s="32" t="s">
         <v>340</v>
       </c>
-      <c r="C133" s="38" t="s">
-        <v>341</v>
-      </c>
-      <c r="D133" s="33" t="s">
-        <v>342</v>
-      </c>
       <c r="E133" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F133" s="9"/>
       <c r="G133" s="8"/>
@@ -5314,24 +5539,24 @@
       <c r="Y133" s="5"/>
       <c r="Z133" s="5"/>
     </row>
-    <row r="134">
+    <row r="134" spans="1:26" ht="13">
       <c r="A134" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="B134" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="C134" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="B134" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="C134" s="8" t="s">
-        <v>288</v>
-      </c>
-      <c r="D134" s="33" t="s">
-        <v>336</v>
+      <c r="D134" s="32" t="s">
+        <v>334</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F134" s="9" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G134" s="8"/>
       <c r="H134" s="5"/>
@@ -5354,12 +5579,12 @@
       <c r="Y134" s="5"/>
       <c r="Z134" s="5"/>
     </row>
-    <row r="135">
+    <row r="135" spans="1:26" ht="13">
       <c r="A135" s="8" t="s">
         <v>34</v>
       </c>
       <c r="B135" s="8" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C135" s="8"/>
       <c r="D135" s="5"/>
@@ -5386,12 +5611,12 @@
       <c r="Y135" s="5"/>
       <c r="Z135" s="5"/>
     </row>
-    <row r="136">
+    <row r="136" spans="1:26" ht="13">
       <c r="A136" s="8" t="s">
         <v>17</v>
       </c>
       <c r="B136" s="8" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C136" s="8" t="s">
         <v>19</v>
@@ -5422,21 +5647,21 @@
       <c r="Y136" s="5"/>
       <c r="Z136" s="5"/>
     </row>
-    <row r="137">
+    <row r="137" spans="1:26" ht="13">
       <c r="A137" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="B137" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="C137" s="18" t="s">
         <v>346</v>
       </c>
-      <c r="B137" s="8" t="s">
+      <c r="D137" s="18" t="s">
         <v>347</v>
       </c>
-      <c r="C137" s="19" t="s">
-        <v>348</v>
-      </c>
-      <c r="D137" s="19" t="s">
-        <v>349</v>
-      </c>
       <c r="E137" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F137" s="9"/>
       <c r="G137" s="8"/>
@@ -5460,12 +5685,12 @@
       <c r="Y137" s="5"/>
       <c r="Z137" s="5"/>
     </row>
-    <row r="138">
+    <row r="138" spans="1:26" ht="13">
       <c r="A138" s="8" t="s">
         <v>34</v>
       </c>
       <c r="B138" s="8" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C138" s="8"/>
       <c r="D138" s="5"/>
@@ -5492,12 +5717,12 @@
       <c r="Y138" s="5"/>
       <c r="Z138" s="5"/>
     </row>
-    <row r="139">
+    <row r="139" spans="1:26" ht="13">
       <c r="A139" s="8" t="s">
         <v>17</v>
       </c>
       <c r="B139" s="8" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C139" s="8" t="s">
         <v>19</v>
@@ -5528,24 +5753,24 @@
       <c r="Y139" s="5"/>
       <c r="Z139" s="5"/>
     </row>
-    <row r="140">
+    <row r="140" spans="1:26" ht="13">
       <c r="A140" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="B140" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="C140" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="B140" s="8" t="s">
+      <c r="D140" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="C140" s="8" t="s">
+      <c r="E140" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F140" s="9" t="s">
         <v>353</v>
-      </c>
-      <c r="D140" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="E140" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="F140" s="9" t="s">
-        <v>355</v>
       </c>
       <c r="G140" s="8"/>
       <c r="H140" s="5"/>
@@ -5568,12 +5793,12 @@
       <c r="Y140" s="5"/>
       <c r="Z140" s="5"/>
     </row>
-    <row r="141">
+    <row r="141" spans="1:26" ht="13">
       <c r="A141" s="8" t="s">
         <v>34</v>
       </c>
       <c r="B141" s="8" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C141" s="8"/>
       <c r="D141" s="5"/>
@@ -5600,12 +5825,12 @@
       <c r="Y141" s="5"/>
       <c r="Z141" s="5"/>
     </row>
-    <row r="142">
+    <row r="142" spans="1:26" ht="13">
       <c r="A142" s="8" t="s">
         <v>17</v>
       </c>
       <c r="B142" s="8" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C142" s="8" t="s">
         <v>19</v>
@@ -5636,30 +5861,30 @@
       <c r="Y142" s="5"/>
       <c r="Z142" s="5"/>
     </row>
-    <row r="143">
+    <row r="143" spans="1:26" ht="13">
       <c r="A143" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="B143" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="C143" s="8" t="s">
         <v>357</v>
       </c>
-      <c r="B143" s="8" t="s">
+      <c r="D143" s="18" t="s">
         <v>358</v>
-      </c>
-      <c r="C143" s="8" t="s">
-        <v>359</v>
-      </c>
-      <c r="D143" s="19" t="s">
-        <v>360</v>
       </c>
       <c r="E143" s="5"/>
       <c r="F143" s="9" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G143" s="8"/>
       <c r="H143" s="5"/>
       <c r="I143" s="5" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J143" s="11" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="K143" s="15"/>
       <c r="L143" s="5"/>
@@ -5678,24 +5903,24 @@
       <c r="Y143" s="5"/>
       <c r="Z143" s="5"/>
     </row>
-    <row r="144">
+    <row r="144" spans="1:26" ht="13">
       <c r="A144" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="B144" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="C144" s="39" t="s">
         <v>363</v>
       </c>
-      <c r="B144" s="8" t="s">
+      <c r="D144" s="32" t="s">
         <v>364</v>
       </c>
-      <c r="C144" s="40" t="s">
-        <v>365</v>
-      </c>
-      <c r="D144" s="33" t="s">
-        <v>366</v>
-      </c>
       <c r="E144" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F144" s="9" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G144" s="8"/>
       <c r="H144" s="5"/>
@@ -5718,12 +5943,12 @@
       <c r="Y144" s="5"/>
       <c r="Z144" s="5"/>
     </row>
-    <row r="145">
+    <row r="145" spans="1:26" ht="13">
       <c r="A145" s="8" t="s">
         <v>34</v>
       </c>
       <c r="B145" s="8" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C145" s="8"/>
       <c r="D145" s="5"/>
@@ -5750,12 +5975,12 @@
       <c r="Y145" s="5"/>
       <c r="Z145" s="5"/>
     </row>
-    <row r="146">
+    <row r="146" spans="1:26" ht="13">
       <c r="A146" s="8" t="s">
         <v>17</v>
       </c>
       <c r="B146" s="8" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C146" s="8" t="s">
         <v>19</v>
@@ -5786,24 +6011,24 @@
       <c r="Y146" s="5"/>
       <c r="Z146" s="5"/>
     </row>
-    <row r="147">
+    <row r="147" spans="1:26" ht="13">
       <c r="A147" s="8" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B147" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="C147" s="39" t="s">
+        <v>367</v>
+      </c>
+      <c r="D147" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="C147" s="40" t="s">
-        <v>369</v>
-      </c>
-      <c r="D147" s="19" t="s">
-        <v>370</v>
-      </c>
       <c r="E147" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F147" s="9" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G147" s="8"/>
       <c r="H147" s="5"/>
@@ -5826,30 +6051,30 @@
       <c r="Y147" s="5"/>
       <c r="Z147" s="5"/>
     </row>
-    <row r="148">
+    <row r="148" spans="1:26" ht="13">
       <c r="A148" s="8" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B148" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="C148" s="39" t="s">
+        <v>370</v>
+      </c>
+      <c r="D148" s="18" t="s">
         <v>371</v>
-      </c>
-      <c r="C148" s="40" t="s">
-        <v>372</v>
-      </c>
-      <c r="D148" s="19" t="s">
-        <v>373</v>
       </c>
       <c r="E148" s="5"/>
       <c r="F148" s="9" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="G148" s="8"/>
       <c r="H148" s="5"/>
       <c r="I148" s="5" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="J148" s="11" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="K148" s="15"/>
       <c r="L148" s="5"/>
@@ -5868,12 +6093,12 @@
       <c r="Y148" s="5"/>
       <c r="Z148" s="5"/>
     </row>
-    <row r="149">
+    <row r="149" spans="1:26" ht="13">
       <c r="A149" s="8" t="s">
         <v>34</v>
       </c>
       <c r="B149" s="8" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C149" s="8"/>
       <c r="D149" s="5"/>
@@ -5900,346 +6125,347 @@
       <c r="Y149" s="5"/>
       <c r="Z149" s="5"/>
     </row>
-    <row r="150">
+    <row r="150" spans="1:26" ht="13">
       <c r="A150" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B150" s="8" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C150" s="1"/>
-      <c r="F150" s="20"/>
+      <c r="F150" s="19"/>
       <c r="G150" s="1"/>
     </row>
-    <row r="151">
+    <row r="151" spans="1:26" ht="13">
       <c r="A151" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B151" s="41" t="s">
+      <c r="B151" s="40" t="s">
+        <v>375</v>
+      </c>
+      <c r="C151" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="D151" s="18" t="s">
         <v>377</v>
-      </c>
-      <c r="C151" s="19" t="s">
-        <v>378</v>
-      </c>
-      <c r="D151" s="19" t="s">
-        <v>379</v>
       </c>
       <c r="G151" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" spans="1:26" ht="13">
       <c r="A152" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B152" s="41" t="s">
+      <c r="B152" s="40" t="s">
+        <v>378</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="C152" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>382</v>
-      </c>
       <c r="G152" s="1"/>
     </row>
-    <row r="153">
+    <row r="153" spans="1:26" ht="13">
       <c r="A153" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B153" s="41" t="s">
-        <v>377</v>
+      <c r="B153" s="40" t="s">
+        <v>375</v>
       </c>
       <c r="C153" s="1"/>
-      <c r="D153" s="29"/>
+      <c r="D153" s="28"/>
       <c r="G153" s="1"/>
     </row>
-    <row r="154">
+    <row r="154" spans="1:26" ht="13">
       <c r="A154" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B154" s="41" t="s">
+      <c r="B154" s="40" t="s">
+        <v>381</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D154" s="28" t="s">
         <v>383</v>
-      </c>
-      <c r="C154" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="D154" s="29" t="s">
-        <v>385</v>
       </c>
       <c r="G154" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" spans="1:26" ht="13">
       <c r="A155" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B155" s="41" t="s">
+      <c r="B155" s="40" t="s">
+        <v>384</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="D155" s="28" t="s">
         <v>386</v>
       </c>
-      <c r="C155" s="1" t="s">
+      <c r="F155" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="D155" s="29" t="s">
-        <v>388</v>
-      </c>
-      <c r="F155" s="1" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="156">
+    </row>
+    <row r="156" spans="1:26" ht="13">
       <c r="A156" s="1" t="s">
         <v>91</v>
       </c>
       <c r="B156" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="D156" s="28" t="s">
         <v>390</v>
       </c>
-      <c r="C156" s="1" t="s">
+      <c r="F156" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="D156" s="29" t="s">
-        <v>392</v>
-      </c>
-      <c r="F156" s="1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="157">
+    </row>
+    <row r="157" spans="1:26" ht="13">
       <c r="A157" s="1" t="s">
         <v>91</v>
       </c>
       <c r="B157" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="D157" s="28" t="s">
         <v>394</v>
       </c>
-      <c r="C157" s="1" t="s">
+      <c r="F157" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="D157" s="29" t="s">
-        <v>396</v>
-      </c>
-      <c r="F157" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="158">
+    </row>
+    <row r="158" spans="1:26" ht="13">
       <c r="A158" s="1" t="s">
         <v>91</v>
       </c>
       <c r="B158" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="D158" s="28" t="s">
         <v>398</v>
       </c>
-      <c r="C158" s="1" t="s">
+      <c r="F158" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="D158" s="29" t="s">
-        <v>400</v>
-      </c>
-      <c r="F158" s="1" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="159">
+    </row>
+    <row r="159" spans="1:26" ht="13">
       <c r="A159" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="160">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="160" spans="1:26" ht="14.25">
       <c r="A160" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B160" s="28" t="s">
-        <v>402</v>
+      <c r="B160" s="27" t="s">
+        <v>400</v>
       </c>
       <c r="L160" s="1" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="161">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" ht="14.25">
       <c r="A161" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B161" s="28" t="s">
-        <v>404</v>
+      <c r="B161" s="27" t="s">
+        <v>402</v>
       </c>
       <c r="L161" s="1" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="162">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" ht="14.25">
       <c r="A162" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B162" s="28" t="s">
-        <v>406</v>
+      <c r="B162" s="27" t="s">
+        <v>404</v>
       </c>
       <c r="L162" s="1" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="C165" s="28"/>
-    </row>
-    <row r="166">
-      <c r="B166" s="42"/>
-      <c r="C166" s="28"/>
-    </row>
-    <row r="168">
-      <c r="B168" s="42"/>
-    </row>
-    <row r="169">
-      <c r="B169" s="41"/>
-    </row>
-    <row r="170">
-      <c r="B170" s="42"/>
-    </row>
-    <row r="171">
-      <c r="B171" s="42"/>
-    </row>
-    <row r="172">
-      <c r="B172" s="41"/>
-    </row>
-    <row r="173">
-      <c r="B173" s="42"/>
-    </row>
-    <row r="174">
-      <c r="B174" s="41"/>
-    </row>
-    <row r="175">
-      <c r="B175" s="42"/>
-    </row>
-    <row r="176">
-      <c r="B176" s="41"/>
-    </row>
-    <row r="177">
-      <c r="B177" s="42"/>
-    </row>
-    <row r="178">
-      <c r="B178" s="41"/>
-    </row>
-    <row r="180">
-      <c r="C180" s="42"/>
-    </row>
-    <row r="181">
-      <c r="B181" s="41"/>
-    </row>
-    <row r="182">
-      <c r="B182" s="41"/>
-    </row>
-    <row r="184">
-      <c r="B184" s="28"/>
-    </row>
-    <row r="185">
-      <c r="B185" s="42"/>
+        <v>405</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" ht="14.25">
+      <c r="C165" s="27"/>
+    </row>
+    <row r="166" spans="1:12" ht="14.25">
+      <c r="B166" s="41"/>
+      <c r="C166" s="27"/>
+    </row>
+    <row r="168" spans="1:12" ht="14.25">
+      <c r="B168" s="41"/>
+    </row>
+    <row r="169" spans="1:12" ht="13">
+      <c r="B169" s="40"/>
+    </row>
+    <row r="170" spans="1:12" ht="14.25">
+      <c r="B170" s="41"/>
+    </row>
+    <row r="171" spans="1:12" ht="14.25">
+      <c r="B171" s="41"/>
+    </row>
+    <row r="172" spans="1:12" ht="13">
+      <c r="B172" s="40"/>
+    </row>
+    <row r="173" spans="1:12" ht="14.25">
+      <c r="B173" s="41"/>
+    </row>
+    <row r="174" spans="1:12" ht="13">
+      <c r="B174" s="40"/>
+    </row>
+    <row r="175" spans="1:12" ht="14.25">
+      <c r="B175" s="41"/>
+    </row>
+    <row r="176" spans="1:12" ht="13">
+      <c r="B176" s="40"/>
+    </row>
+    <row r="177" spans="2:3" ht="14.25">
+      <c r="B177" s="41"/>
+    </row>
+    <row r="178" spans="2:3" ht="13">
+      <c r="B178" s="40"/>
+    </row>
+    <row r="180" spans="2:3" ht="14.25">
+      <c r="C180" s="41"/>
+    </row>
+    <row r="181" spans="2:3" ht="13">
+      <c r="B181" s="40"/>
+    </row>
+    <row r="182" spans="2:3" ht="13">
+      <c r="B182" s="40"/>
+    </row>
+    <row r="184" spans="2:3" ht="14.25">
+      <c r="B184" s="27"/>
+    </row>
+    <row r="185" spans="2:3" ht="14.25">
+      <c r="B185" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="L30:Q30"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
+  <dimension ref="A1:Z173"/>
+  <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="25.71"/>
-    <col customWidth="1" min="2" max="2" width="24.29"/>
-    <col customWidth="1" min="3" max="3" width="31.0"/>
+    <col min="1" max="1" width="25.6796875" customWidth="1"/>
+    <col min="2" max="2" width="24.26953125" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="43" t="s">
-        <v>408</v>
-      </c>
-      <c r="B1" s="43" t="s">
+    <row r="1" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A1" s="42" t="s">
+        <v>406</v>
+      </c>
+      <c r="B1" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="C1" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="42" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:26" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="C3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="D4" s="28" t="s">
         <v>415</v>
       </c>
-      <c r="C4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="C5" s="1" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="C5" s="1" t="s">
+    </row>
+    <row r="6" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A6" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="C6" s="5" t="s">
         <v>420</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>421</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>422</v>
-      </c>
       <c r="D6" s="5" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -6264,18 +6490,18 @@
       <c r="Y6" s="5"/>
       <c r="Z6" s="5"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:26" ht="15.75" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -6300,18 +6526,18 @@
       <c r="Y7" s="5"/>
       <c r="Z7" s="5"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:26" ht="15.75" customHeight="1">
       <c r="A8" s="5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="D8" s="18" t="s">
         <v>425</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>427</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
@@ -6336,21 +6562,21 @@
       <c r="Y8" s="5"/>
       <c r="Z8" s="5"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:26" ht="15.75" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="D9" s="18" t="s">
         <v>428</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>430</v>
-      </c>
       <c r="E9" s="5" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
@@ -6374,21 +6600,21 @@
       <c r="Y9" s="5"/>
       <c r="Z9" s="5"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:26" ht="15.75" customHeight="1">
       <c r="A10" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="D10" s="18" t="s">
         <v>431</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>432</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>433</v>
-      </c>
       <c r="E10" s="5" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
@@ -6412,21 +6638,21 @@
       <c r="Y10" s="5"/>
       <c r="Z10" s="5"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:26" ht="15.75" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B11" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="D11" s="18" t="s">
         <v>434</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>436</v>
-      </c>
       <c r="E11" s="5" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
@@ -6450,21 +6676,21 @@
       <c r="Y11" s="5"/>
       <c r="Z11" s="5"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:26" ht="15.75" customHeight="1">
       <c r="A12" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B12" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="D12" s="18" t="s">
         <v>437</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>438</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>439</v>
-      </c>
       <c r="E12" s="5" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
@@ -6488,21 +6714,21 @@
       <c r="Y12" s="5"/>
       <c r="Z12" s="5"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:26" ht="15.75" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="D13" s="18" t="s">
         <v>440</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>442</v>
-      </c>
       <c r="E13" s="5" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
@@ -6526,21 +6752,21 @@
       <c r="Y13" s="5"/>
       <c r="Z13" s="5"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:26" ht="15.75" customHeight="1">
       <c r="A14" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B14" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="D14" s="18" t="s">
         <v>443</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>444</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>445</v>
-      </c>
       <c r="E14" s="5" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
@@ -6564,21 +6790,21 @@
       <c r="Y14" s="5"/>
       <c r="Z14" s="5"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:26" ht="15.75" customHeight="1">
       <c r="A15" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B15" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="D15" s="18" t="s">
         <v>446</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>448</v>
-      </c>
       <c r="E15" s="5" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
@@ -6602,21 +6828,21 @@
       <c r="Y15" s="5"/>
       <c r="Z15" s="5"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:26" ht="15.75" customHeight="1">
       <c r="A16" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
@@ -6640,21 +6866,21 @@
       <c r="Y16" s="5"/>
       <c r="Z16" s="5"/>
     </row>
-    <row r="17">
+    <row r="17" spans="1:26" ht="15.75" customHeight="1">
       <c r="A17" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -6678,21 +6904,21 @@
       <c r="Y17" s="5"/>
       <c r="Z17" s="5"/>
     </row>
-    <row r="18">
+    <row r="18" spans="1:26" ht="15.75" customHeight="1">
       <c r="A18" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
@@ -6716,21 +6942,21 @@
       <c r="Y18" s="5"/>
       <c r="Z18" s="5"/>
     </row>
-    <row r="19">
+    <row r="19" spans="1:26" ht="13">
       <c r="A19" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
@@ -6754,22 +6980,22 @@
       <c r="Y19" s="5"/>
       <c r="Z19" s="5"/>
     </row>
-    <row r="20">
+    <row r="20" spans="1:26" ht="13">
       <c r="A20" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B20" s="5" t="str">
-        <f t="shared" ref="B20:B83" si="1">lower(substitute(C20," ",""))</f>
+        <f t="shared" ref="B20:B83" si="0">LOWER(SUBSTITUTE(C20," ",""))</f>
         <v>chakechakedistricthospital</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>457</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>458</v>
+        <v>455</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>456</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
@@ -6793,22 +7019,22 @@
       <c r="Y20" s="5"/>
       <c r="Z20" s="5"/>
     </row>
-    <row r="21">
+    <row r="21" spans="1:26" ht="13">
       <c r="A21" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B21" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>pujiniphcu+</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
@@ -6832,22 +7058,22 @@
       <c r="Y21" s="5"/>
       <c r="Z21" s="5"/>
     </row>
-    <row r="22">
+    <row r="22" spans="1:26" ht="13">
       <c r="A22" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B22" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>tundauwaphcu+</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
@@ -6871,22 +7097,22 @@
       <c r="Y22" s="5"/>
       <c r="Z22" s="5"/>
     </row>
-    <row r="23">
+    <row r="23" spans="1:26" ht="13">
       <c r="A23" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B23" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>vitongojiphcc</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
@@ -6910,22 +7136,22 @@
       <c r="Y23" s="5"/>
       <c r="Z23" s="5"/>
     </row>
-    <row r="24">
+    <row r="24" spans="1:26" ht="13">
       <c r="A24" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B24" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>weshaphcu+</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
@@ -6949,22 +7175,22 @@
       <c r="Y24" s="5"/>
       <c r="Z24" s="5"/>
     </row>
-    <row r="25">
+    <row r="25" spans="1:26" ht="13">
       <c r="A25" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B25" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>kondephcu+</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
@@ -6988,22 +7214,22 @@
       <c r="Y25" s="5"/>
       <c r="Z25" s="5"/>
     </row>
-    <row r="26">
+    <row r="26" spans="1:26" ht="13">
       <c r="A26" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B26" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>makangalephcu+</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
@@ -7027,22 +7253,22 @@
       <c r="Y26" s="5"/>
       <c r="Z26" s="5"/>
     </row>
-    <row r="27">
+    <row r="27" spans="1:26" ht="13">
       <c r="A27" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B27" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>maziwangombephcu+</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
@@ -7066,22 +7292,22 @@
       <c r="Y27" s="5"/>
       <c r="Z27" s="5"/>
     </row>
-    <row r="28">
+    <row r="28" spans="1:26" ht="13">
       <c r="A28" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B28" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>micheweniphcc</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
@@ -7105,22 +7331,22 @@
       <c r="Y28" s="5"/>
       <c r="Z28" s="5"/>
     </row>
-    <row r="29">
+    <row r="29" spans="1:26" ht="13">
       <c r="A29" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B29" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>wingwiphcu+</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
@@ -7144,22 +7370,22 @@
       <c r="Y29" s="5"/>
       <c r="Z29" s="5"/>
     </row>
-    <row r="30">
+    <row r="30" spans="1:26" ht="13">
       <c r="A30" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B30" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>kiuyumbuyuniphcu+</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
@@ -7183,22 +7409,22 @@
       <c r="Y30" s="5"/>
       <c r="Z30" s="5"/>
     </row>
-    <row r="31">
+    <row r="31" spans="1:26" ht="13">
       <c r="A31" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B31" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>bogoaphcu+</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
@@ -7222,22 +7448,22 @@
       <c r="Y31" s="5"/>
       <c r="Z31" s="5"/>
     </row>
-    <row r="32">
+    <row r="32" spans="1:26" ht="13">
       <c r="A32" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B32" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>kengejaphcu+</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
@@ -7261,22 +7487,22 @@
       <c r="Y32" s="5"/>
       <c r="Z32" s="5"/>
     </row>
-    <row r="33">
+    <row r="33" spans="1:26" ht="13">
       <c r="A33" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B33" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>abdallahmzeedistricthospital</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>471</v>
-      </c>
-      <c r="D33" s="19" t="s">
-        <v>472</v>
+        <v>469</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>470</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
@@ -7300,22 +7526,22 @@
       <c r="Y33" s="5"/>
       <c r="Z33" s="5"/>
     </row>
-    <row r="34">
+    <row r="34" spans="1:26" ht="13">
       <c r="A34" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B34" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>michenzaniphcu+</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
@@ -7339,22 +7565,22 @@
       <c r="Y34" s="5"/>
       <c r="Z34" s="5"/>
     </row>
-    <row r="35">
+    <row r="35" spans="1:26" ht="13">
       <c r="A35" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B35" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>fundophcu+</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
@@ -7378,22 +7604,22 @@
       <c r="Y35" s="5"/>
       <c r="Z35" s="5"/>
     </row>
-    <row r="36">
+    <row r="36" spans="1:26" ht="13">
       <c r="A36" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B36" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>kojaniphcu+</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
@@ -7417,22 +7643,22 @@
       <c r="Y36" s="5"/>
       <c r="Z36" s="5"/>
     </row>
-    <row r="37">
+    <row r="37" spans="1:26" ht="13">
       <c r="A37" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B37" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>makongeniphcu+</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
@@ -7456,22 +7682,22 @@
       <c r="Y37" s="5"/>
       <c r="Z37" s="5"/>
     </row>
-    <row r="38">
+    <row r="38" spans="1:26" ht="13">
       <c r="A38" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B38" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>wetedistricthospital</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>477</v>
-      </c>
-      <c r="D38" s="19" t="s">
-        <v>478</v>
+        <v>475</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>476</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
@@ -7495,22 +7721,22 @@
       <c r="Y38" s="5"/>
       <c r="Z38" s="5"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:26" ht="13">
       <c r="A39" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B39" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>mzambarauniphcu+</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
@@ -7534,22 +7760,22 @@
       <c r="Y39" s="5"/>
       <c r="Z39" s="5"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:26" ht="13">
       <c r="A40" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B40" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>junguniphcu+</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
@@ -7573,22 +7799,22 @@
       <c r="Y40" s="5"/>
       <c r="Z40" s="5"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:26" ht="13">
       <c r="A41" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B41" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>ukunjwiphcu+</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
@@ -7612,22 +7838,22 @@
       <c r="Y41" s="5"/>
       <c r="Z41" s="5"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:26" ht="13">
       <c r="A42" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B42" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>uondwephcu+</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
@@ -7651,22 +7877,22 @@
       <c r="Y42" s="5"/>
       <c r="Z42" s="5"/>
     </row>
-    <row r="43">
+    <row r="43" spans="1:26" ht="13">
       <c r="A43" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B43" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>chwakaphcu+</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
@@ -7690,22 +7916,22 @@
       <c r="Y43" s="5"/>
       <c r="Z43" s="5"/>
     </row>
-    <row r="44">
+    <row r="44" spans="1:26" ht="13">
       <c r="A44" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B44" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>mweraphcu+</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
@@ -7729,22 +7955,22 @@
       <c r="Y44" s="5"/>
       <c r="Z44" s="5"/>
     </row>
-    <row r="45">
+    <row r="45" spans="1:26" ht="13">
       <c r="A45" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B45" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>ungujaukuuphcu+</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
@@ -7768,22 +7994,22 @@
       <c r="Y45" s="5"/>
       <c r="Z45" s="5"/>
     </row>
-    <row r="46">
+    <row r="46" spans="1:26" ht="13">
       <c r="A46" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B46" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>uziniphcu+</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
@@ -7807,22 +8033,22 @@
       <c r="Y46" s="5"/>
       <c r="Z46" s="5"/>
     </row>
-    <row r="47">
+    <row r="47" spans="1:26" ht="13">
       <c r="A47" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B47" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>uroaphcu+</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
@@ -7846,22 +8072,22 @@
       <c r="Y47" s="5"/>
       <c r="Z47" s="5"/>
     </row>
-    <row r="48">
+    <row r="48" spans="1:26" ht="13">
       <c r="A48" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B48" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>kivungedistricthospital</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>488</v>
-      </c>
-      <c r="D48" s="19" t="s">
-        <v>489</v>
+        <v>486</v>
+      </c>
+      <c r="D48" s="18" t="s">
+        <v>487</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
@@ -7885,22 +8111,22 @@
       <c r="Y48" s="5"/>
       <c r="Z48" s="5"/>
     </row>
-    <row r="49">
+    <row r="49" spans="1:26" ht="13">
       <c r="A49" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B49" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>matemwephcu+</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
@@ -7924,22 +8150,22 @@
       <c r="Y49" s="5"/>
       <c r="Z49" s="5"/>
     </row>
-    <row r="50">
+    <row r="50" spans="1:26" ht="13">
       <c r="A50" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B50" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>nungwiphcu+</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
@@ -7963,22 +8189,22 @@
       <c r="Y50" s="5"/>
       <c r="Z50" s="5"/>
     </row>
-    <row r="51">
+    <row r="51" spans="1:26" ht="13">
       <c r="A51" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B51" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>pwanimchanganiphcu+</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
@@ -8002,22 +8228,22 @@
       <c r="Y51" s="5"/>
       <c r="Z51" s="5"/>
     </row>
-    <row r="52">
+    <row r="52" spans="1:26" ht="13">
       <c r="A52" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B52" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>tumbatugomaniphcu+</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
@@ -8041,22 +8267,22 @@
       <c r="Y52" s="5"/>
       <c r="Z52" s="5"/>
     </row>
-    <row r="53">
+    <row r="53" spans="1:26" ht="13">
       <c r="A53" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B53" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>kendwaphcu+</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
@@ -8080,22 +8306,22 @@
       <c r="Y53" s="5"/>
       <c r="Z53" s="5"/>
     </row>
-    <row r="54">
+    <row r="54" spans="1:26" ht="13">
       <c r="A54" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B54" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>bumbwinimisufiniphcu+</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
@@ -8119,22 +8345,22 @@
       <c r="Y54" s="5"/>
       <c r="Z54" s="5"/>
     </row>
-    <row r="55">
+    <row r="55" spans="1:26" ht="13">
       <c r="A55" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B55" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>dongevijibweniphcu+</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
@@ -8158,22 +8384,22 @@
       <c r="Y55" s="5"/>
       <c r="Z55" s="5"/>
     </row>
-    <row r="56">
+    <row r="56" spans="1:26" ht="13">
       <c r="A56" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B56" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>kiongwephcu</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
@@ -8197,22 +8423,22 @@
       <c r="Y56" s="5"/>
       <c r="Z56" s="5"/>
     </row>
-    <row r="57">
+    <row r="57" spans="1:26" ht="13">
       <c r="A57" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B57" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>kitopephcu</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
@@ -8236,22 +8462,22 @@
       <c r="Y57" s="5"/>
       <c r="Z57" s="5"/>
     </row>
-    <row r="58">
+    <row r="58" spans="1:26" ht="13">
       <c r="A58" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B58" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>mahondaphcu+</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
@@ -8275,22 +8501,22 @@
       <c r="Y58" s="5"/>
       <c r="Z58" s="5"/>
     </row>
-    <row r="59">
+    <row r="59" spans="1:26" ht="13">
       <c r="A59" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B59" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>jambianiphcu+</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F59" s="5"/>
       <c r="G59" s="5"/>
@@ -8314,22 +8540,22 @@
       <c r="Y59" s="5"/>
       <c r="Z59" s="5"/>
     </row>
-    <row r="60">
+    <row r="60" spans="1:26" ht="13">
       <c r="A60" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B60" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>makunduchidistricthospital</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>501</v>
-      </c>
-      <c r="D60" s="19" t="s">
-        <v>502</v>
+        <v>499</v>
+      </c>
+      <c r="D60" s="18" t="s">
+        <v>500</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
@@ -8353,22 +8579,22 @@
       <c r="Y60" s="5"/>
       <c r="Z60" s="5"/>
     </row>
-    <row r="61">
+    <row r="61" spans="1:26" ht="13">
       <c r="A61" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B61" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>muyuniphcu+</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="5"/>
@@ -8392,22 +8618,22 @@
       <c r="Y61" s="5"/>
       <c r="Z61" s="5"/>
     </row>
-    <row r="62">
+    <row r="62" spans="1:26" ht="13">
       <c r="A62" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B62" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>bwejuuphcu+</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="5"/>
@@ -8431,22 +8657,22 @@
       <c r="Y62" s="5"/>
       <c r="Z62" s="5"/>
     </row>
-    <row r="63">
+    <row r="63" spans="1:26" ht="13">
       <c r="A63" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B63" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>chumbuniphcu+</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="F63" s="5"/>
       <c r="G63" s="5"/>
@@ -8470,22 +8696,22 @@
       <c r="Y63" s="5"/>
       <c r="Z63" s="5"/>
     </row>
-    <row r="64">
+    <row r="64" spans="1:26" ht="13">
       <c r="A64" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B64" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>mnazimmojahospital</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>506</v>
-      </c>
-      <c r="D64" s="19" t="s">
-        <v>507</v>
+        <v>504</v>
+      </c>
+      <c r="D64" s="18" t="s">
+        <v>505</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="5"/>
@@ -8509,22 +8735,22 @@
       <c r="Y64" s="5"/>
       <c r="Z64" s="5"/>
     </row>
-    <row r="65">
+    <row r="65" spans="1:26" ht="13">
       <c r="A65" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B65" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>mwembeladumchclinic</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="F65" s="5"/>
       <c r="G65" s="5"/>
@@ -8548,22 +8774,22 @@
       <c r="Y65" s="5"/>
       <c r="Z65" s="5"/>
     </row>
-    <row r="66">
+    <row r="66" spans="1:26" ht="13">
       <c r="A66" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B66" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>sebleniphcu+</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="5"/>
@@ -8587,22 +8813,22 @@
       <c r="Y66" s="5"/>
       <c r="Z66" s="5"/>
     </row>
-    <row r="67">
+    <row r="67" spans="1:26" ht="13">
       <c r="A67" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B67" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>chukwaniphcu+</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="5"/>
@@ -8626,22 +8852,22 @@
       <c r="Y67" s="5"/>
       <c r="Z67" s="5"/>
     </row>
-    <row r="68">
+    <row r="68" spans="1:26" ht="13">
       <c r="A68" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B68" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>fuoniphcu+</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="5"/>
@@ -8665,22 +8891,22 @@
       <c r="Y68" s="5"/>
       <c r="Z68" s="5"/>
     </row>
-    <row r="69">
+    <row r="69" spans="1:26" ht="13">
       <c r="A69" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B69" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>kombeniphcu+</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
@@ -8704,22 +8930,22 @@
       <c r="Y69" s="5"/>
       <c r="Z69" s="5"/>
     </row>
-    <row r="70">
+    <row r="70" spans="1:26" ht="13">
       <c r="A70" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B70" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>mtofaaniphcu+(kinuni)</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="5"/>
@@ -8743,22 +8969,22 @@
       <c r="Y70" s="5"/>
       <c r="Z70" s="5"/>
     </row>
-    <row r="71">
+    <row r="71" spans="1:26" ht="13">
       <c r="A71" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B71" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>bumbwisudiphcu+</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F71" s="5"/>
       <c r="G71" s="5"/>
@@ -8782,22 +9008,22 @@
       <c r="Y71" s="5"/>
       <c r="Z71" s="5"/>
     </row>
-    <row r="72">
+    <row r="72" spans="1:26" ht="13">
       <c r="A72" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B72" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>selemphcu+</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F72" s="5"/>
       <c r="G72" s="5"/>
@@ -8821,22 +9047,22 @@
       <c r="Y72" s="5"/>
       <c r="Z72" s="5"/>
     </row>
-    <row r="73">
+    <row r="73" spans="1:26" ht="13">
       <c r="A73" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B73" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="D73" s="19" t="s">
-        <v>516</v>
+        <v>424</v>
+      </c>
+      <c r="D73" s="18" t="s">
+        <v>514</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F73" s="5"/>
       <c r="G73" s="5"/>
@@ -8860,22 +9086,22 @@
       <c r="Y73" s="5"/>
       <c r="Z73" s="5"/>
     </row>
-    <row r="74">
+    <row r="74" spans="1:26" ht="13">
       <c r="A74" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B74" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="D74" s="19" t="s">
-        <v>516</v>
+        <v>424</v>
+      </c>
+      <c r="D74" s="18" t="s">
+        <v>514</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F74" s="5"/>
       <c r="G74" s="5"/>
@@ -8899,22 +9125,22 @@
       <c r="Y74" s="5"/>
       <c r="Z74" s="5"/>
     </row>
-    <row r="75">
+    <row r="75" spans="1:26" ht="13">
       <c r="A75" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B75" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="D75" s="19" t="s">
-        <v>516</v>
+        <v>424</v>
+      </c>
+      <c r="D75" s="18" t="s">
+        <v>514</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F75" s="5"/>
       <c r="G75" s="5"/>
@@ -8938,22 +9164,22 @@
       <c r="Y75" s="5"/>
       <c r="Z75" s="5"/>
     </row>
-    <row r="76">
+    <row r="76" spans="1:26" ht="13">
       <c r="A76" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B76" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="D76" s="19" t="s">
-        <v>516</v>
+        <v>424</v>
+      </c>
+      <c r="D76" s="18" t="s">
+        <v>514</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F76" s="5"/>
       <c r="G76" s="5"/>
@@ -8977,22 +9203,22 @@
       <c r="Y76" s="5"/>
       <c r="Z76" s="5"/>
     </row>
-    <row r="77">
+    <row r="77" spans="1:26" ht="13">
       <c r="A77" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B77" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="D77" s="19" t="s">
-        <v>516</v>
+        <v>424</v>
+      </c>
+      <c r="D77" s="18" t="s">
+        <v>514</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F77" s="5"/>
       <c r="G77" s="5"/>
@@ -9016,22 +9242,22 @@
       <c r="Y77" s="5"/>
       <c r="Z77" s="5"/>
     </row>
-    <row r="78">
+    <row r="78" spans="1:26" ht="13">
       <c r="A78" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B78" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C78" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="D78" s="18" t="s">
+        <v>514</v>
+      </c>
+      <c r="E78" s="5" t="s">
         <v>426</v>
-      </c>
-      <c r="D78" s="19" t="s">
-        <v>516</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>428</v>
       </c>
       <c r="F78" s="5"/>
       <c r="G78" s="5"/>
@@ -9055,22 +9281,22 @@
       <c r="Y78" s="5"/>
       <c r="Z78" s="5"/>
     </row>
-    <row r="79">
+    <row r="79" spans="1:26" ht="13">
       <c r="A79" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B79" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="D79" s="19" t="s">
-        <v>516</v>
+        <v>424</v>
+      </c>
+      <c r="D79" s="18" t="s">
+        <v>514</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F79" s="5"/>
       <c r="G79" s="5"/>
@@ -9094,22 +9320,22 @@
       <c r="Y79" s="5"/>
       <c r="Z79" s="5"/>
     </row>
-    <row r="80">
+    <row r="80" spans="1:26" ht="13">
       <c r="A80" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B80" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="D80" s="19" t="s">
-        <v>516</v>
+        <v>424</v>
+      </c>
+      <c r="D80" s="18" t="s">
+        <v>514</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F80" s="5"/>
       <c r="G80" s="5"/>
@@ -9133,22 +9359,22 @@
       <c r="Y80" s="5"/>
       <c r="Z80" s="5"/>
     </row>
-    <row r="81">
+    <row r="81" spans="1:26" ht="13">
       <c r="A81" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B81" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="D81" s="19" t="s">
-        <v>516</v>
+        <v>424</v>
+      </c>
+      <c r="D81" s="18" t="s">
+        <v>514</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="F81" s="5"/>
       <c r="G81" s="5"/>
@@ -9172,22 +9398,22 @@
       <c r="Y81" s="5"/>
       <c r="Z81" s="5"/>
     </row>
-    <row r="82">
+    <row r="82" spans="1:26" ht="13">
       <c r="A82" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B82" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="D82" s="19" t="s">
-        <v>516</v>
+        <v>424</v>
+      </c>
+      <c r="D82" s="18" t="s">
+        <v>514</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F82" s="5"/>
       <c r="G82" s="5"/>
@@ -9211,22 +9437,22 @@
       <c r="Y82" s="5"/>
       <c r="Z82" s="5"/>
     </row>
-    <row r="83">
+    <row r="83" spans="1:26" ht="13">
       <c r="A83" s="5" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B83" s="5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>other</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="D83" s="19" t="s">
-        <v>516</v>
+        <v>424</v>
+      </c>
+      <c r="D83" s="18" t="s">
+        <v>514</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="F83" s="5"/>
       <c r="G83" s="5"/>
@@ -9250,18 +9476,18 @@
       <c r="Y83" s="5"/>
       <c r="Z83" s="5"/>
     </row>
-    <row r="84">
+    <row r="84" spans="1:26" ht="13">
       <c r="A84" s="5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>517</v>
-      </c>
-      <c r="D84" s="33" t="s">
-        <v>518</v>
+        <v>515</v>
+      </c>
+      <c r="D84" s="32" t="s">
+        <v>516</v>
       </c>
       <c r="E84" s="5"/>
       <c r="F84" s="5"/>
@@ -9286,18 +9512,18 @@
       <c r="Y84" s="5"/>
       <c r="Z84" s="5"/>
     </row>
-    <row r="85">
+    <row r="85" spans="1:26" ht="13">
       <c r="A85" s="5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B85" s="5" t="s">
+        <v>517</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="D85" s="32" t="s">
         <v>519</v>
-      </c>
-      <c r="C85" s="5" t="s">
-        <v>520</v>
-      </c>
-      <c r="D85" s="33" t="s">
-        <v>521</v>
       </c>
       <c r="E85" s="15"/>
       <c r="F85" s="15"/>
@@ -9322,18 +9548,18 @@
       <c r="Y85" s="5"/>
       <c r="Z85" s="5"/>
     </row>
-    <row r="86">
+    <row r="86" spans="1:26" ht="13">
       <c r="A86" s="5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>522</v>
-      </c>
-      <c r="D86" s="33" t="s">
-        <v>523</v>
+        <v>520</v>
+      </c>
+      <c r="D86" s="32" t="s">
+        <v>521</v>
       </c>
       <c r="E86" s="5"/>
       <c r="F86" s="5"/>
@@ -9358,18 +9584,18 @@
       <c r="Y86" s="5"/>
       <c r="Z86" s="5"/>
     </row>
-    <row r="87">
+    <row r="87" spans="1:26" ht="13">
       <c r="A87" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="C87" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="B87" s="5" t="s">
+      <c r="D87" s="32" t="s">
         <v>525</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>526</v>
-      </c>
-      <c r="D87" s="33" t="s">
-        <v>527</v>
       </c>
       <c r="E87" s="5"/>
       <c r="F87" s="5"/>
@@ -9394,18 +9620,18 @@
       <c r="Y87" s="5"/>
       <c r="Z87" s="5"/>
     </row>
-    <row r="88">
+    <row r="88" spans="1:26" ht="13">
       <c r="A88" s="5" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B88" s="5" t="s">
+        <v>526</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="D88" s="32" t="s">
         <v>528</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>529</v>
-      </c>
-      <c r="D88" s="33" t="s">
-        <v>530</v>
       </c>
       <c r="E88" s="5"/>
       <c r="F88" s="5"/>
@@ -9430,18 +9656,18 @@
       <c r="Y88" s="5"/>
       <c r="Z88" s="5"/>
     </row>
-    <row r="89">
+    <row r="89" spans="1:26" ht="13">
       <c r="A89" s="5" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B89" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="D89" s="32" t="s">
         <v>531</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="D89" s="33" t="s">
-        <v>533</v>
       </c>
       <c r="E89" s="5"/>
       <c r="F89" s="5"/>
@@ -9466,18 +9692,18 @@
       <c r="Y89" s="5"/>
       <c r="Z89" s="5"/>
     </row>
-    <row r="90">
+    <row r="90" spans="1:26" ht="13">
       <c r="A90" s="5" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B90" s="5" t="s">
+        <v>532</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="D90" s="32" t="s">
         <v>534</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>535</v>
-      </c>
-      <c r="D90" s="33" t="s">
-        <v>536</v>
       </c>
       <c r="E90" s="15"/>
       <c r="F90" s="5"/>
@@ -9502,18 +9728,18 @@
       <c r="Y90" s="5"/>
       <c r="Z90" s="5"/>
     </row>
-    <row r="91">
+    <row r="91" spans="1:26" ht="13">
       <c r="A91" s="5" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B91" s="5" t="s">
+        <v>535</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>536</v>
+      </c>
+      <c r="D91" s="32" t="s">
         <v>537</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>538</v>
-      </c>
-      <c r="D91" s="33" t="s">
-        <v>539</v>
       </c>
       <c r="E91" s="5"/>
       <c r="F91" s="5"/>
@@ -9538,18 +9764,18 @@
       <c r="Y91" s="5"/>
       <c r="Z91" s="5"/>
     </row>
-    <row r="92">
+    <row r="92" spans="1:26" ht="13">
       <c r="A92" s="5" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="D92" s="33" t="s">
-        <v>540</v>
+        <v>424</v>
+      </c>
+      <c r="D92" s="32" t="s">
+        <v>538</v>
       </c>
       <c r="E92" s="5"/>
       <c r="F92" s="5"/>
@@ -9574,18 +9800,18 @@
       <c r="Y92" s="5"/>
       <c r="Z92" s="5"/>
     </row>
-    <row r="93">
+    <row r="93" spans="1:26" ht="13">
       <c r="A93" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B93" s="5" t="s">
+        <v>539</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>540</v>
+      </c>
+      <c r="D93" s="32" t="s">
         <v>541</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>542</v>
-      </c>
-      <c r="D93" s="33" t="s">
-        <v>543</v>
       </c>
       <c r="E93" s="5"/>
       <c r="F93" s="5"/>
@@ -9610,18 +9836,18 @@
       <c r="Y93" s="5"/>
       <c r="Z93" s="5"/>
     </row>
-    <row r="94">
+    <row r="94" spans="1:26" ht="13">
       <c r="A94" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B94" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="D94" s="32" t="s">
         <v>544</v>
-      </c>
-      <c r="C94" s="5" t="s">
-        <v>545</v>
-      </c>
-      <c r="D94" s="33" t="s">
-        <v>546</v>
       </c>
       <c r="E94" s="5"/>
       <c r="F94" s="5"/>
@@ -9646,18 +9872,18 @@
       <c r="Y94" s="5"/>
       <c r="Z94" s="5"/>
     </row>
-    <row r="95">
+    <row r="95" spans="1:26" ht="13">
       <c r="A95" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B95" s="5" t="s">
+        <v>545</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="D95" s="32" t="s">
         <v>547</v>
-      </c>
-      <c r="C95" s="5" t="s">
-        <v>548</v>
-      </c>
-      <c r="D95" s="33" t="s">
-        <v>549</v>
       </c>
       <c r="E95" s="5"/>
       <c r="F95" s="5"/>
@@ -9682,18 +9908,18 @@
       <c r="Y95" s="5"/>
       <c r="Z95" s="5"/>
     </row>
-    <row r="96">
+    <row r="96" spans="1:26" ht="13">
       <c r="A96" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B96" s="5" t="s">
+        <v>548</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>549</v>
+      </c>
+      <c r="D96" s="32" t="s">
         <v>550</v>
-      </c>
-      <c r="C96" s="5" t="s">
-        <v>551</v>
-      </c>
-      <c r="D96" s="33" t="s">
-        <v>552</v>
       </c>
       <c r="E96" s="5"/>
       <c r="F96" s="5"/>
@@ -9718,18 +9944,18 @@
       <c r="Y96" s="5"/>
       <c r="Z96" s="5"/>
     </row>
-    <row r="97">
+    <row r="97" spans="1:26" ht="13">
       <c r="A97" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B97" s="5" t="s">
+        <v>551</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>552</v>
+      </c>
+      <c r="D97" s="32" t="s">
         <v>553</v>
-      </c>
-      <c r="C97" s="5" t="s">
-        <v>554</v>
-      </c>
-      <c r="D97" s="33" t="s">
-        <v>555</v>
       </c>
       <c r="E97" s="5"/>
       <c r="F97" s="5"/>
@@ -9754,18 +9980,18 @@
       <c r="Y97" s="5"/>
       <c r="Z97" s="5"/>
     </row>
-    <row r="98">
+    <row r="98" spans="1:26" ht="13">
       <c r="A98" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B98" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>555</v>
+      </c>
+      <c r="D98" s="32" t="s">
         <v>556</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>557</v>
-      </c>
-      <c r="D98" s="33" t="s">
-        <v>558</v>
       </c>
       <c r="E98" s="5"/>
       <c r="F98" s="5"/>
@@ -9790,18 +10016,18 @@
       <c r="Y98" s="5"/>
       <c r="Z98" s="5"/>
     </row>
-    <row r="99">
+    <row r="99" spans="1:26" ht="13">
       <c r="A99" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="D99" s="33" t="s">
-        <v>540</v>
+        <v>424</v>
+      </c>
+      <c r="D99" s="32" t="s">
+        <v>538</v>
       </c>
       <c r="E99" s="5"/>
       <c r="F99" s="5"/>
@@ -9826,242 +10052,242 @@
       <c r="Y99" s="5"/>
       <c r="Z99" s="5"/>
     </row>
-    <row r="100">
+    <row r="100" spans="1:26" ht="13">
       <c r="A100" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B100" s="5" t="s">
+        <v>557</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>558</v>
+      </c>
+      <c r="D100" s="32" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="101" spans="1:26" ht="13">
+      <c r="A101" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="B101" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="C100" s="5" t="s">
+      <c r="C101" s="5" t="s">
         <v>560</v>
       </c>
-      <c r="D100" s="33" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="B101" s="5" t="s">
+      <c r="D101" s="32" t="s">
         <v>561</v>
       </c>
-      <c r="C101" s="5" t="s">
+    </row>
+    <row r="102" spans="1:26" ht="13">
+      <c r="A102" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="B102" s="5" t="s">
         <v>562</v>
       </c>
-      <c r="D101" s="33" t="s">
+      <c r="C102" s="5" t="s">
         <v>563</v>
       </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="B102" s="5" t="s">
+      <c r="D102" s="32" t="s">
         <v>564</v>
       </c>
-      <c r="C102" s="5" t="s">
+    </row>
+    <row r="103" spans="1:26" ht="13">
+      <c r="A103" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="B103" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="D102" s="33" t="s">
+      <c r="C103" s="5" t="s">
         <v>566</v>
       </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="B103" s="5" t="s">
+      <c r="D103" s="32" t="s">
         <v>567</v>
       </c>
-      <c r="C103" s="5" t="s">
+    </row>
+    <row r="104" spans="1:26" ht="13">
+      <c r="A104" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="B104" s="5" t="s">
         <v>568</v>
       </c>
-      <c r="D103" s="33" t="s">
+      <c r="C104" s="5" t="s">
         <v>569</v>
       </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="B104" s="5" t="s">
+      <c r="D104" s="32" t="s">
         <v>570</v>
       </c>
-      <c r="C104" s="5" t="s">
+    </row>
+    <row r="105" spans="1:26" ht="13">
+      <c r="A105" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="B105" s="5" t="s">
         <v>571</v>
       </c>
-      <c r="D104" s="33" t="s">
+      <c r="C105" s="5" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="B105" s="5" t="s">
+      <c r="D105" s="32" t="s">
         <v>573</v>
       </c>
-      <c r="C105" s="5" t="s">
+    </row>
+    <row r="106" spans="1:26" ht="13">
+      <c r="A106" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="B106" s="5" t="s">
         <v>574</v>
       </c>
-      <c r="D105" s="33" t="s">
+      <c r="C106" s="5" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="B106" s="5" t="s">
+      <c r="D106" s="32" t="s">
         <v>576</v>
       </c>
-      <c r="C106" s="5" t="s">
+    </row>
+    <row r="107" spans="1:26" ht="13">
+      <c r="A107" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="B107" s="5" t="s">
         <v>577</v>
       </c>
-      <c r="D106" s="33" t="s">
+      <c r="C107" s="5" t="s">
         <v>578</v>
       </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="B107" s="5" t="s">
+      <c r="D107" s="32" t="s">
         <v>579</v>
       </c>
-      <c r="C107" s="5" t="s">
+    </row>
+    <row r="108" spans="1:26" ht="13">
+      <c r="A108" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="D108" s="32" t="s">
         <v>580</v>
       </c>
-      <c r="D107" s="33" t="s">
+    </row>
+    <row r="109" spans="1:26" ht="13">
+      <c r="A109" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="B109" s="5" t="s">
         <v>581</v>
       </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="B108" s="5" t="s">
-        <v>425</v>
-      </c>
-      <c r="C108" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="D108" s="33" t="s">
+      <c r="C109" s="5" t="s">
         <v>582</v>
       </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="B109" s="5" t="s">
+      <c r="D109" s="32" t="s">
         <v>583</v>
       </c>
-      <c r="C109" s="5" t="s">
+    </row>
+    <row r="110" spans="1:26" ht="13">
+      <c r="A110" s="5" t="s">
         <v>584</v>
       </c>
-      <c r="D109" s="33" t="s">
+      <c r="B110" s="5" t="s">
         <v>585</v>
       </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="5" t="s">
+      <c r="C110" s="5" t="s">
         <v>586</v>
       </c>
-      <c r="B110" s="5" t="s">
+      <c r="D110" s="32" t="s">
         <v>587</v>
       </c>
-      <c r="C110" s="5" t="s">
+    </row>
+    <row r="111" spans="1:26" ht="13">
+      <c r="A111" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="B111" s="5" t="s">
         <v>588</v>
       </c>
-      <c r="D110" s="33" t="s">
+      <c r="C111" s="5" t="s">
         <v>589</v>
       </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="5" t="s">
-        <v>586</v>
-      </c>
-      <c r="B111" s="5" t="s">
+      <c r="D111" s="32" t="s">
         <v>590</v>
       </c>
-      <c r="C111" s="5" t="s">
+    </row>
+    <row r="112" spans="1:26" ht="13">
+      <c r="A112" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="B112" s="5" t="s">
         <v>591</v>
       </c>
-      <c r="D111" s="33" t="s">
+      <c r="C112" s="5" t="s">
         <v>592</v>
       </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="5" t="s">
-        <v>586</v>
-      </c>
-      <c r="B112" s="5" t="s">
+      <c r="D112" s="32" t="s">
         <v>593</v>
       </c>
-      <c r="C112" s="5" t="s">
+    </row>
+    <row r="113" spans="1:26" ht="13">
+      <c r="A113" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="B113" s="5" t="s">
         <v>594</v>
       </c>
-      <c r="D112" s="33" t="s">
+      <c r="C113" s="5" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="5" t="s">
-        <v>586</v>
-      </c>
-      <c r="B113" s="5" t="s">
+      <c r="D113" s="32" t="s">
         <v>596</v>
       </c>
-      <c r="C113" s="5" t="s">
+    </row>
+    <row r="114" spans="1:26" ht="13">
+      <c r="A114" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="D114" s="32" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="115" spans="1:26" ht="13">
+      <c r="A115" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>581</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>582</v>
+      </c>
+      <c r="D115" s="32" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="116" spans="1:26" ht="13">
+      <c r="A116" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="B116" s="5" t="s">
         <v>597</v>
       </c>
-      <c r="D113" s="33" t="s">
+      <c r="C116" s="5" t="s">
         <v>598</v>
       </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="5" t="s">
-        <v>586</v>
-      </c>
-      <c r="B114" s="5" t="s">
-        <v>425</v>
-      </c>
-      <c r="C114" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="D114" s="33" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="5" t="s">
-        <v>586</v>
-      </c>
-      <c r="B115" s="5" t="s">
-        <v>583</v>
-      </c>
-      <c r="C115" s="5" t="s">
-        <v>584</v>
-      </c>
-      <c r="D115" s="33" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="B116" s="5" t="s">
+      <c r="D116" s="32" t="s">
         <v>599</v>
-      </c>
-      <c r="C116" s="5" t="s">
-        <v>600</v>
-      </c>
-      <c r="D116" s="33" t="s">
-        <v>601</v>
       </c>
       <c r="E116" s="5"/>
       <c r="F116" s="5"/>
@@ -10086,18 +10312,18 @@
       <c r="Y116" s="5"/>
       <c r="Z116" s="5"/>
     </row>
-    <row r="117">
+    <row r="117" spans="1:26" ht="13">
       <c r="A117" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B117" s="5" t="s">
+        <v>600</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="D117" s="32" t="s">
         <v>602</v>
-      </c>
-      <c r="C117" s="5" t="s">
-        <v>603</v>
-      </c>
-      <c r="D117" s="33" t="s">
-        <v>604</v>
       </c>
       <c r="E117" s="5"/>
       <c r="F117" s="5"/>
@@ -10122,18 +10348,18 @@
       <c r="Y117" s="5"/>
       <c r="Z117" s="5"/>
     </row>
-    <row r="118">
+    <row r="118" spans="1:26" ht="13">
       <c r="A118" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B118" s="5" t="s">
+        <v>603</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="D118" s="32" t="s">
         <v>605</v>
-      </c>
-      <c r="C118" s="5" t="s">
-        <v>606</v>
-      </c>
-      <c r="D118" s="33" t="s">
-        <v>607</v>
       </c>
       <c r="E118" s="5"/>
       <c r="F118" s="5"/>
@@ -10158,18 +10384,18 @@
       <c r="Y118" s="5"/>
       <c r="Z118" s="5"/>
     </row>
-    <row r="119">
+    <row r="119" spans="1:26" ht="13">
       <c r="A119" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B119" s="5" t="s">
+        <v>606</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="D119" s="18" t="s">
         <v>608</v>
-      </c>
-      <c r="C119" s="5" t="s">
-        <v>609</v>
-      </c>
-      <c r="D119" s="19" t="s">
-        <v>610</v>
       </c>
       <c r="E119" s="5"/>
       <c r="F119" s="5"/>
@@ -10194,18 +10420,18 @@
       <c r="Y119" s="5"/>
       <c r="Z119" s="5"/>
     </row>
-    <row r="120">
+    <row r="120" spans="1:26" ht="13">
       <c r="A120" s="5" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B120" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>610</v>
+      </c>
+      <c r="D120" s="32" t="s">
         <v>611</v>
-      </c>
-      <c r="C120" s="5" t="s">
-        <v>612</v>
-      </c>
-      <c r="D120" s="33" t="s">
-        <v>613</v>
       </c>
       <c r="E120" s="5"/>
       <c r="F120" s="5"/>
@@ -10230,18 +10456,18 @@
       <c r="Y120" s="5"/>
       <c r="Z120" s="5"/>
     </row>
-    <row r="121">
+    <row r="121" spans="1:26" ht="13">
       <c r="A121" s="5" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B121" s="5" t="s">
+        <v>612</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="D121" s="32" t="s">
         <v>614</v>
-      </c>
-      <c r="C121" s="5" t="s">
-        <v>615</v>
-      </c>
-      <c r="D121" s="33" t="s">
-        <v>616</v>
       </c>
       <c r="E121" s="5"/>
       <c r="F121" s="5"/>
@@ -10266,18 +10492,18 @@
       <c r="Y121" s="5"/>
       <c r="Z121" s="5"/>
     </row>
-    <row r="122">
+    <row r="122" spans="1:26" ht="13">
       <c r="A122" s="5" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B122" s="5" t="s">
+        <v>615</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="D122" s="32" t="s">
         <v>617</v>
-      </c>
-      <c r="C122" s="5" t="s">
-        <v>618</v>
-      </c>
-      <c r="D122" s="33" t="s">
-        <v>619</v>
       </c>
       <c r="E122" s="5"/>
       <c r="F122" s="5"/>
@@ -10302,18 +10528,18 @@
       <c r="Y122" s="5"/>
       <c r="Z122" s="5"/>
     </row>
-    <row r="123">
+    <row r="123" spans="1:26" ht="13">
       <c r="A123" s="5" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B123" s="5" t="s">
+        <v>618</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>619</v>
+      </c>
+      <c r="D123" s="32" t="s">
         <v>620</v>
-      </c>
-      <c r="C123" s="5" t="s">
-        <v>621</v>
-      </c>
-      <c r="D123" s="33" t="s">
-        <v>622</v>
       </c>
       <c r="E123" s="5"/>
       <c r="F123" s="5"/>
@@ -10338,18 +10564,18 @@
       <c r="Y123" s="5"/>
       <c r="Z123" s="5"/>
     </row>
-    <row r="124">
+    <row r="124" spans="1:26" ht="13">
       <c r="A124" s="5" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B124" s="5" t="s">
+        <v>621</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>622</v>
+      </c>
+      <c r="D124" s="32" t="s">
         <v>623</v>
-      </c>
-      <c r="C124" s="5" t="s">
-        <v>624</v>
-      </c>
-      <c r="D124" s="33" t="s">
-        <v>625</v>
       </c>
       <c r="E124" s="5"/>
       <c r="F124" s="5"/>
@@ -10374,18 +10600,18 @@
       <c r="Y124" s="5"/>
       <c r="Z124" s="5"/>
     </row>
-    <row r="125">
+    <row r="125" spans="1:26" ht="13">
       <c r="A125" s="5" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B125" s="5" t="s">
+        <v>624</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>625</v>
+      </c>
+      <c r="D125" s="32" t="s">
         <v>626</v>
-      </c>
-      <c r="C125" s="5" t="s">
-        <v>627</v>
-      </c>
-      <c r="D125" s="33" t="s">
-        <v>628</v>
       </c>
       <c r="E125" s="5"/>
       <c r="F125" s="5"/>
@@ -10410,18 +10636,18 @@
       <c r="Y125" s="5"/>
       <c r="Z125" s="5"/>
     </row>
-    <row r="126">
+    <row r="126" spans="1:26" ht="13">
       <c r="A126" s="5" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B126" s="5" t="s">
+        <v>627</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>628</v>
+      </c>
+      <c r="D126" s="32" t="s">
         <v>629</v>
-      </c>
-      <c r="C126" s="5" t="s">
-        <v>630</v>
-      </c>
-      <c r="D126" s="33" t="s">
-        <v>631</v>
       </c>
       <c r="E126" s="5"/>
       <c r="F126" s="5"/>
@@ -10446,18 +10672,18 @@
       <c r="Y126" s="5"/>
       <c r="Z126" s="5"/>
     </row>
-    <row r="127">
+    <row r="127" spans="1:26" ht="13">
       <c r="A127" s="5" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>632</v>
-      </c>
-      <c r="D127" s="33" t="s">
-        <v>540</v>
+        <v>630</v>
+      </c>
+      <c r="D127" s="32" t="s">
+        <v>538</v>
       </c>
       <c r="E127" s="5"/>
       <c r="F127" s="5"/>
@@ -10482,18 +10708,18 @@
       <c r="Y127" s="5"/>
       <c r="Z127" s="5"/>
     </row>
-    <row r="128">
+    <row r="128" spans="1:26" ht="13">
       <c r="A128" s="5" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>634</v>
-      </c>
-      <c r="D128" s="19" t="s">
-        <v>610</v>
+        <v>632</v>
+      </c>
+      <c r="D128" s="18" t="s">
+        <v>608</v>
       </c>
       <c r="E128" s="5"/>
       <c r="F128" s="5"/>
@@ -10518,18 +10744,18 @@
       <c r="Y128" s="5"/>
       <c r="Z128" s="5"/>
     </row>
-    <row r="129">
+    <row r="129" spans="1:26" ht="13">
       <c r="A129" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>634</v>
+      </c>
+      <c r="C129" s="5" t="s">
         <v>635</v>
       </c>
-      <c r="B129" s="5" t="s">
+      <c r="D129" s="32" t="s">
         <v>636</v>
-      </c>
-      <c r="C129" s="5" t="s">
-        <v>637</v>
-      </c>
-      <c r="D129" s="33" t="s">
-        <v>638</v>
       </c>
       <c r="E129" s="5"/>
       <c r="F129" s="5"/>
@@ -10554,18 +10780,18 @@
       <c r="Y129" s="5"/>
       <c r="Z129" s="5"/>
     </row>
-    <row r="130">
+    <row r="130" spans="1:26" ht="13">
       <c r="A130" s="5" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B130" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>638</v>
+      </c>
+      <c r="D130" s="32" t="s">
         <v>639</v>
-      </c>
-      <c r="C130" s="5" t="s">
-        <v>640</v>
-      </c>
-      <c r="D130" s="33" t="s">
-        <v>641</v>
       </c>
       <c r="E130" s="5"/>
       <c r="F130" s="5"/>
@@ -10590,18 +10816,18 @@
       <c r="Y130" s="5"/>
       <c r="Z130" s="5"/>
     </row>
-    <row r="131">
+    <row r="131" spans="1:26" ht="13">
       <c r="A131" s="5" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B131" s="5" t="s">
+        <v>640</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="D131" s="32" t="s">
         <v>642</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="D131" s="33" t="s">
-        <v>644</v>
       </c>
       <c r="E131" s="5"/>
       <c r="F131" s="5"/>
@@ -10626,18 +10852,18 @@
       <c r="Y131" s="5"/>
       <c r="Z131" s="5"/>
     </row>
-    <row r="132">
+    <row r="132" spans="1:26" ht="13">
       <c r="A132" s="5" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B132" s="5" t="s">
+        <v>643</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>644</v>
+      </c>
+      <c r="D132" s="32" t="s">
         <v>645</v>
-      </c>
-      <c r="C132" s="5" t="s">
-        <v>646</v>
-      </c>
-      <c r="D132" s="33" t="s">
-        <v>647</v>
       </c>
       <c r="E132" s="5"/>
       <c r="F132" s="5"/>
@@ -10662,18 +10888,18 @@
       <c r="Y132" s="5"/>
       <c r="Z132" s="5"/>
     </row>
-    <row r="133">
+    <row r="133" spans="1:26" ht="13">
       <c r="A133" s="5" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B133" s="5" t="s">
+        <v>646</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>647</v>
+      </c>
+      <c r="D133" s="32" t="s">
         <v>648</v>
-      </c>
-      <c r="C133" s="5" t="s">
-        <v>649</v>
-      </c>
-      <c r="D133" s="33" t="s">
-        <v>650</v>
       </c>
       <c r="E133" s="5"/>
       <c r="F133" s="5"/>
@@ -10698,18 +10924,18 @@
       <c r="Y133" s="5"/>
       <c r="Z133" s="5"/>
     </row>
-    <row r="134">
+    <row r="134" spans="1:26" ht="13">
       <c r="A134" s="5" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B134" s="5" t="s">
+        <v>649</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>650</v>
+      </c>
+      <c r="D134" s="32" t="s">
         <v>651</v>
-      </c>
-      <c r="C134" s="5" t="s">
-        <v>652</v>
-      </c>
-      <c r="D134" s="33" t="s">
-        <v>653</v>
       </c>
       <c r="E134" s="5"/>
       <c r="F134" s="5"/>
@@ -10734,18 +10960,18 @@
       <c r="Y134" s="5"/>
       <c r="Z134" s="5"/>
     </row>
-    <row r="135">
+    <row r="135" spans="1:26" ht="13">
       <c r="A135" s="5" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B135" s="5" t="s">
+        <v>652</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>653</v>
+      </c>
+      <c r="D135" s="32" t="s">
         <v>654</v>
-      </c>
-      <c r="C135" s="5" t="s">
-        <v>655</v>
-      </c>
-      <c r="D135" s="33" t="s">
-        <v>656</v>
       </c>
       <c r="E135" s="5"/>
       <c r="F135" s="5"/>
@@ -10770,18 +10996,18 @@
       <c r="Y135" s="5"/>
       <c r="Z135" s="5"/>
     </row>
-    <row r="136">
+    <row r="136" spans="1:26" ht="13">
       <c r="A136" s="5" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>634</v>
-      </c>
-      <c r="D136" s="19" t="s">
-        <v>610</v>
+        <v>632</v>
+      </c>
+      <c r="D136" s="18" t="s">
+        <v>608</v>
       </c>
       <c r="E136" s="5"/>
       <c r="F136" s="5"/>
@@ -10806,18 +11032,18 @@
       <c r="Y136" s="5"/>
       <c r="Z136" s="5"/>
     </row>
-    <row r="137">
+    <row r="137" spans="1:26" ht="13">
       <c r="A137" s="5" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B137" s="5" t="s">
+        <v>656</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>657</v>
+      </c>
+      <c r="D137" s="18" t="s">
         <v>658</v>
-      </c>
-      <c r="C137" s="5" t="s">
-        <v>659</v>
-      </c>
-      <c r="D137" s="19" t="s">
-        <v>660</v>
       </c>
       <c r="E137" s="5"/>
       <c r="F137" s="5"/>
@@ -10842,18 +11068,18 @@
       <c r="Y137" s="5"/>
       <c r="Z137" s="5"/>
     </row>
-    <row r="138">
+    <row r="138" spans="1:26" ht="13">
       <c r="A138" s="5" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B138" s="5" t="s">
+        <v>659</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="D138" s="18" t="s">
         <v>661</v>
-      </c>
-      <c r="C138" s="5" t="s">
-        <v>662</v>
-      </c>
-      <c r="D138" s="19" t="s">
-        <v>663</v>
       </c>
       <c r="E138" s="5"/>
       <c r="F138" s="5"/>
@@ -10878,18 +11104,18 @@
       <c r="Y138" s="5"/>
       <c r="Z138" s="5"/>
     </row>
-    <row r="139">
+    <row r="139" spans="1:26" ht="13">
       <c r="A139" s="5" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B139" s="5" t="s">
+        <v>662</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>663</v>
+      </c>
+      <c r="D139" s="32" t="s">
         <v>664</v>
-      </c>
-      <c r="C139" s="5" t="s">
-        <v>665</v>
-      </c>
-      <c r="D139" s="33" t="s">
-        <v>666</v>
       </c>
       <c r="E139" s="15"/>
       <c r="F139" s="5"/>
@@ -10914,18 +11140,18 @@
       <c r="Y139" s="5"/>
       <c r="Z139" s="5"/>
     </row>
-    <row r="140">
+    <row r="140" spans="1:26" ht="13">
       <c r="A140" s="5" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>667</v>
-      </c>
-      <c r="D140" s="33" t="s">
-        <v>668</v>
+        <v>665</v>
+      </c>
+      <c r="D140" s="32" t="s">
+        <v>666</v>
       </c>
       <c r="E140" s="5"/>
       <c r="F140" s="5"/>
@@ -10950,18 +11176,18 @@
       <c r="Y140" s="5"/>
       <c r="Z140" s="5"/>
     </row>
-    <row r="141">
+    <row r="141" spans="1:26" ht="13">
       <c r="A141" s="5" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>670</v>
-      </c>
-      <c r="D141" s="19" t="s">
-        <v>610</v>
+        <v>668</v>
+      </c>
+      <c r="D141" s="18" t="s">
+        <v>608</v>
       </c>
       <c r="E141" s="5"/>
       <c r="F141" s="5"/>
@@ -10986,18 +11212,18 @@
       <c r="Y141" s="5"/>
       <c r="Z141" s="5"/>
     </row>
-    <row r="142">
+    <row r="142" spans="1:26" ht="13">
       <c r="A142" s="5" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B142" s="5" t="s">
+        <v>669</v>
+      </c>
+      <c r="C142" s="43" t="s">
+        <v>670</v>
+      </c>
+      <c r="D142" s="5" t="s">
         <v>671</v>
-      </c>
-      <c r="C142" s="44" t="s">
-        <v>672</v>
-      </c>
-      <c r="D142" s="5" t="s">
-        <v>673</v>
       </c>
       <c r="E142" s="5"/>
       <c r="F142" s="5"/>
@@ -11022,18 +11248,18 @@
       <c r="Y142" s="5"/>
       <c r="Z142" s="5"/>
     </row>
-    <row r="143">
+    <row r="143" spans="1:26" ht="13">
       <c r="A143" s="5" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B143" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>673</v>
+      </c>
+      <c r="D143" s="32" t="s">
         <v>674</v>
-      </c>
-      <c r="C143" s="5" t="s">
-        <v>675</v>
-      </c>
-      <c r="D143" s="33" t="s">
-        <v>676</v>
       </c>
       <c r="E143" s="5"/>
       <c r="F143" s="5"/>
@@ -11058,18 +11284,18 @@
       <c r="Y143" s="5"/>
       <c r="Z143" s="5"/>
     </row>
-    <row r="144">
+    <row r="144" spans="1:26" ht="13">
       <c r="A144" s="5" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B144" s="5" t="s">
+        <v>675</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>676</v>
+      </c>
+      <c r="D144" s="32" t="s">
         <v>677</v>
-      </c>
-      <c r="C144" s="5" t="s">
-        <v>678</v>
-      </c>
-      <c r="D144" s="33" t="s">
-        <v>679</v>
       </c>
       <c r="E144" s="5"/>
       <c r="F144" s="5"/>
@@ -11094,18 +11320,18 @@
       <c r="Y144" s="5"/>
       <c r="Z144" s="5"/>
     </row>
-    <row r="145">
+    <row r="145" spans="1:26" ht="13">
       <c r="A145" s="5" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B145" s="5" t="s">
+        <v>678</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>679</v>
+      </c>
+      <c r="D145" s="32" t="s">
         <v>680</v>
-      </c>
-      <c r="C145" s="5" t="s">
-        <v>681</v>
-      </c>
-      <c r="D145" s="33" t="s">
-        <v>682</v>
       </c>
       <c r="E145" s="5"/>
       <c r="F145" s="5"/>
@@ -11130,18 +11356,18 @@
       <c r="Y145" s="5"/>
       <c r="Z145" s="5"/>
     </row>
-    <row r="146">
+    <row r="146" spans="1:26" ht="13">
       <c r="A146" s="5" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>634</v>
-      </c>
-      <c r="D146" s="19" t="s">
-        <v>610</v>
+        <v>632</v>
+      </c>
+      <c r="D146" s="18" t="s">
+        <v>608</v>
       </c>
       <c r="E146" s="5"/>
       <c r="F146" s="5"/>
@@ -11166,18 +11392,18 @@
       <c r="Y146" s="5"/>
       <c r="Z146" s="5"/>
     </row>
-    <row r="147">
+    <row r="147" spans="1:26" ht="13">
       <c r="A147" s="5" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>637</v>
-      </c>
-      <c r="D147" s="33" t="s">
-        <v>638</v>
+        <v>635</v>
+      </c>
+      <c r="D147" s="32" t="s">
+        <v>636</v>
       </c>
       <c r="E147" s="5"/>
       <c r="F147" s="5"/>
@@ -11202,18 +11428,18 @@
       <c r="Y147" s="5"/>
       <c r="Z147" s="5"/>
     </row>
-    <row r="148">
+    <row r="148" spans="1:26" ht="13">
       <c r="A148" s="5" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>640</v>
-      </c>
-      <c r="D148" s="33" t="s">
-        <v>641</v>
+        <v>638</v>
+      </c>
+      <c r="D148" s="32" t="s">
+        <v>639</v>
       </c>
       <c r="E148" s="5"/>
       <c r="F148" s="5"/>
@@ -11238,18 +11464,18 @@
       <c r="Y148" s="5"/>
       <c r="Z148" s="5"/>
     </row>
-    <row r="149">
+    <row r="149" spans="1:26" ht="13">
       <c r="A149" s="5" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="D149" s="33" t="s">
-        <v>644</v>
+        <v>641</v>
+      </c>
+      <c r="D149" s="32" t="s">
+        <v>642</v>
       </c>
       <c r="E149" s="5"/>
       <c r="F149" s="5"/>
@@ -11274,18 +11500,18 @@
       <c r="Y149" s="5"/>
       <c r="Z149" s="5"/>
     </row>
-    <row r="150">
+    <row r="150" spans="1:26" ht="13">
       <c r="A150" s="5" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>646</v>
-      </c>
-      <c r="D150" s="33" t="s">
-        <v>647</v>
+        <v>644</v>
+      </c>
+      <c r="D150" s="32" t="s">
+        <v>645</v>
       </c>
       <c r="E150" s="5"/>
       <c r="F150" s="5"/>
@@ -11310,18 +11536,18 @@
       <c r="Y150" s="5"/>
       <c r="Z150" s="5"/>
     </row>
-    <row r="151">
+    <row r="151" spans="1:26" ht="13">
       <c r="A151" s="5" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>649</v>
-      </c>
-      <c r="D151" s="33" t="s">
-        <v>650</v>
+        <v>647</v>
+      </c>
+      <c r="D151" s="32" t="s">
+        <v>648</v>
       </c>
       <c r="E151" s="5"/>
       <c r="F151" s="5"/>
@@ -11346,18 +11572,18 @@
       <c r="Y151" s="5"/>
       <c r="Z151" s="5"/>
     </row>
-    <row r="152">
+    <row r="152" spans="1:26" ht="13">
       <c r="A152" s="5" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>652</v>
-      </c>
-      <c r="D152" s="33" t="s">
-        <v>653</v>
+        <v>650</v>
+      </c>
+      <c r="D152" s="32" t="s">
+        <v>651</v>
       </c>
       <c r="E152" s="5"/>
       <c r="F152" s="5"/>
@@ -11382,18 +11608,18 @@
       <c r="Y152" s="5"/>
       <c r="Z152" s="5"/>
     </row>
-    <row r="153">
+    <row r="153" spans="1:26" ht="13">
       <c r="A153" s="5" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>655</v>
-      </c>
-      <c r="D153" s="33" t="s">
-        <v>656</v>
+        <v>653</v>
+      </c>
+      <c r="D153" s="32" t="s">
+        <v>654</v>
       </c>
       <c r="E153" s="5"/>
       <c r="F153" s="5"/>
@@ -11418,18 +11644,18 @@
       <c r="Y153" s="5"/>
       <c r="Z153" s="5"/>
     </row>
-    <row r="154">
+    <row r="154" spans="1:26" ht="13">
       <c r="A154" s="5" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>670</v>
-      </c>
-      <c r="D154" s="19" t="s">
-        <v>610</v>
+        <v>668</v>
+      </c>
+      <c r="D154" s="18" t="s">
+        <v>608</v>
       </c>
       <c r="E154" s="5"/>
       <c r="F154" s="5"/>
@@ -11454,18 +11680,18 @@
       <c r="Y154" s="5"/>
       <c r="Z154" s="5"/>
     </row>
-    <row r="155">
+    <row r="155" spans="1:26" ht="13">
       <c r="A155" s="5" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="D155" s="33" t="s">
-        <v>693</v>
+        <v>408</v>
+      </c>
+      <c r="D155" s="32" t="s">
+        <v>691</v>
       </c>
       <c r="E155" s="5"/>
       <c r="F155" s="5"/>
@@ -11490,18 +11716,18 @@
       <c r="Y155" s="5"/>
       <c r="Z155" s="5"/>
     </row>
-    <row r="156">
+    <row r="156" spans="1:26" ht="13">
       <c r="A156" s="5" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B156" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="C156" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="D156" s="32" t="s">
         <v>412</v>
-      </c>
-      <c r="C156" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="D156" s="33" t="s">
-        <v>414</v>
       </c>
       <c r="E156" s="5"/>
       <c r="F156" s="5"/>
@@ -11526,18 +11752,18 @@
       <c r="Y156" s="5"/>
       <c r="Z156" s="5"/>
     </row>
-    <row r="157">
+    <row r="157" spans="1:26" ht="13">
       <c r="A157" s="5" t="s">
+        <v>690</v>
+      </c>
+      <c r="B157" s="5" t="s">
         <v>692</v>
       </c>
-      <c r="B157" s="5" t="s">
-        <v>694</v>
-      </c>
       <c r="C157" s="5" t="s">
-        <v>670</v>
-      </c>
-      <c r="D157" s="19" t="s">
-        <v>610</v>
+        <v>668</v>
+      </c>
+      <c r="D157" s="18" t="s">
+        <v>608</v>
       </c>
       <c r="E157" s="5"/>
       <c r="F157" s="5"/>
@@ -11562,18 +11788,18 @@
       <c r="Y157" s="5"/>
       <c r="Z157" s="5"/>
     </row>
-    <row r="158">
+    <row r="158" spans="1:26" ht="13">
       <c r="A158" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B158" s="10" t="s">
+        <v>693</v>
+      </c>
+      <c r="C158" s="10" t="s">
+        <v>694</v>
+      </c>
+      <c r="D158" s="33" t="s">
         <v>695</v>
-      </c>
-      <c r="C158" s="10" t="s">
-        <v>696</v>
-      </c>
-      <c r="D158" s="34" t="s">
-        <v>697</v>
       </c>
       <c r="E158" s="5"/>
       <c r="F158" s="5"/>
@@ -11598,18 +11824,18 @@
       <c r="Y158" s="5"/>
       <c r="Z158" s="5"/>
     </row>
-    <row r="159">
+    <row r="159" spans="1:26" ht="13">
       <c r="A159" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B159" s="10" t="s">
+        <v>696</v>
+      </c>
+      <c r="C159" s="44" t="s">
+        <v>697</v>
+      </c>
+      <c r="D159" s="33" t="s">
         <v>698</v>
-      </c>
-      <c r="C159" s="45" t="s">
-        <v>699</v>
-      </c>
-      <c r="D159" s="34" t="s">
-        <v>700</v>
       </c>
       <c r="E159" s="15"/>
       <c r="F159" s="15"/>
@@ -11634,18 +11860,18 @@
       <c r="Y159" s="5"/>
       <c r="Z159" s="5"/>
     </row>
-    <row r="160">
+    <row r="160" spans="1:26" ht="13">
       <c r="A160" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B160" s="10" t="s">
+        <v>699</v>
+      </c>
+      <c r="C160" s="45" t="s">
+        <v>700</v>
+      </c>
+      <c r="D160" s="46" t="s">
         <v>701</v>
-      </c>
-      <c r="C160" s="46" t="s">
-        <v>702</v>
-      </c>
-      <c r="D160" s="47" t="s">
-        <v>703</v>
       </c>
       <c r="E160" s="15"/>
       <c r="F160" s="15"/>
@@ -11670,18 +11896,18 @@
       <c r="Y160" s="5"/>
       <c r="Z160" s="5"/>
     </row>
-    <row r="161">
+    <row r="161" spans="1:26" ht="13">
       <c r="A161" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B161" s="10" t="s">
+        <v>702</v>
+      </c>
+      <c r="C161" s="10" t="s">
+        <v>703</v>
+      </c>
+      <c r="D161" s="10" t="s">
         <v>704</v>
-      </c>
-      <c r="C161" s="10" t="s">
-        <v>705</v>
-      </c>
-      <c r="D161" s="10" t="s">
-        <v>706</v>
       </c>
       <c r="E161" s="5"/>
       <c r="F161" s="5"/>
@@ -11706,18 +11932,18 @@
       <c r="Y161" s="5"/>
       <c r="Z161" s="5"/>
     </row>
-    <row r="162">
+    <row r="162" spans="1:26" ht="13">
       <c r="A162" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B162" s="10" t="s">
+        <v>705</v>
+      </c>
+      <c r="C162" s="44" t="s">
+        <v>706</v>
+      </c>
+      <c r="D162" s="33" t="s">
         <v>707</v>
-      </c>
-      <c r="C162" s="45" t="s">
-        <v>708</v>
-      </c>
-      <c r="D162" s="34" t="s">
-        <v>709</v>
       </c>
       <c r="E162" s="15"/>
       <c r="F162" s="15"/>
@@ -11742,18 +11968,18 @@
       <c r="Y162" s="5"/>
       <c r="Z162" s="5"/>
     </row>
-    <row r="163">
+    <row r="163" spans="1:26" ht="13">
       <c r="A163" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B163" s="10" t="s">
+        <v>708</v>
+      </c>
+      <c r="C163" s="44" t="s">
+        <v>709</v>
+      </c>
+      <c r="D163" s="33" t="s">
         <v>710</v>
-      </c>
-      <c r="C163" s="45" t="s">
-        <v>711</v>
-      </c>
-      <c r="D163" s="34" t="s">
-        <v>712</v>
       </c>
       <c r="E163" s="15"/>
       <c r="F163" s="15"/>
@@ -11778,18 +12004,18 @@
       <c r="Y163" s="5"/>
       <c r="Z163" s="5"/>
     </row>
-    <row r="164">
+    <row r="164" spans="1:26" ht="13">
       <c r="A164" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B164" s="10" t="s">
+        <v>711</v>
+      </c>
+      <c r="C164" s="10" t="s">
+        <v>712</v>
+      </c>
+      <c r="D164" s="10" t="s">
         <v>713</v>
-      </c>
-      <c r="C164" s="10" t="s">
-        <v>714</v>
-      </c>
-      <c r="D164" s="10" t="s">
-        <v>715</v>
       </c>
       <c r="E164" s="5"/>
       <c r="F164" s="5"/>
@@ -11814,110 +12040,111 @@
       <c r="Y164" s="5"/>
       <c r="Z164" s="5"/>
     </row>
-    <row r="165">
+    <row r="165" spans="1:26" ht="13">
       <c r="A165" s="5"/>
       <c r="B165" s="5"/>
       <c r="C165" s="5"/>
       <c r="D165" s="5"/>
     </row>
-    <row r="166">
+    <row r="166" spans="1:26" ht="13">
       <c r="A166" s="5"/>
       <c r="B166" s="5"/>
       <c r="C166" s="5"/>
       <c r="D166" s="5"/>
     </row>
-    <row r="167">
+    <row r="167" spans="1:26" ht="13">
       <c r="A167" s="5"/>
       <c r="B167" s="5"/>
       <c r="C167" s="5"/>
       <c r="D167" s="5"/>
     </row>
-    <row r="168">
+    <row r="168" spans="1:26" ht="13">
       <c r="A168" s="5"/>
       <c r="B168" s="5"/>
       <c r="C168" s="5"/>
       <c r="D168" s="5"/>
     </row>
-    <row r="169">
+    <row r="169" spans="1:26" ht="13">
       <c r="A169" s="5"/>
       <c r="B169" s="5"/>
       <c r="C169" s="5"/>
       <c r="D169" s="5"/>
     </row>
-    <row r="170">
+    <row r="170" spans="1:26" ht="13">
       <c r="A170" s="5"/>
       <c r="B170" s="5"/>
       <c r="C170" s="5"/>
       <c r="D170" s="5"/>
     </row>
-    <row r="171">
+    <row r="171" spans="1:26" ht="13">
       <c r="A171" s="5"/>
       <c r="B171" s="5"/>
       <c r="C171" s="5"/>
       <c r="D171" s="5"/>
     </row>
-    <row r="172">
+    <row r="172" spans="1:26" ht="13">
       <c r="A172" s="5"/>
       <c r="B172" s="5"/>
       <c r="C172" s="5"/>
       <c r="D172" s="5"/>
     </row>
-    <row r="173">
+    <row r="173" spans="1:26" ht="13">
       <c r="A173" s="5"/>
       <c r="B173" s="5"/>
       <c r="C173" s="5"/>
       <c r="D173" s="5"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="26.43"/>
+    <col min="1" max="1" width="26.40625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A1" s="42" t="s">
+        <v>714</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>715</v>
+      </c>
+      <c r="C1" s="42" t="s">
         <v>716</v>
       </c>
-      <c r="B1" s="43" t="s">
+      <c r="D1" s="42" t="s">
         <v>717</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="E1" s="42" t="s">
         <v>718</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="F1" s="42" t="s">
         <v>719</v>
       </c>
-      <c r="E1" s="43" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="F1" s="43" t="s">
+      <c r="B2" s="1" t="s">
         <v>721</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>724</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>725</v>
-      </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/forms/app/postpartum.xlsx
+++ b/forms/app/postpartum.xlsx
@@ -1,27 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20374"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D-tree\config-dtree-newrepo\config-dtree\forms\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E740E93-4250-4D32-BDEE-F7DA658BF6CD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6325"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
     <sheet name="choices" sheetId="2" r:id="rId2"/>
     <sheet name="settings" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1339" uniqueCount="726">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1455" uniqueCount="788">
   <si>
     <t>type</t>
   </si>
@@ -2301,12 +2302,265 @@
   <si>
     <t xml:space="preserve">Kwanza kabisa nitakuchunguza kam unadalili za hatari baada ya kujifungua.  Iwapo utaonesha una dalili za hatari, utapatiwa rufaa (kwenda kituo cha afya) na kuunganishwa na mtoa huduma kwenye kituo kilicho karibu yako. </t>
   </si>
+  <si>
+    <t>wash</t>
+  </si>
+  <si>
+    <t>subgroup_cholera</t>
+  </si>
+  <si>
+    <t>ask_familiy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;strong&gt;Kuelewa Kipindupindu&lt;/strong&gt; 
+Waulize wana familia: 
+• Unafahamu/mnafahamu chochote kuhusu kipindupindu?
+• Dalili za kipindupindu
+• Jinsi kinavyoenea 
+• Nani yupo katika hatari ya kupata kipindupindu?
+• Na vipi utajikinga na kipindupindu?
+&lt;span style="color:#f58a1f"&gt;Kulingana na majibu hapo juu tumia kitini rejea umuelezee zaidi kuhusu kipindupindu (Kipindupindu ni nini, Jinsi kinavyo enezwa na jinsi ya kuzuia kipindupindu)&lt;/span&gt;
+</t>
+  </si>
+  <si>
+    <t>important_note_cholera</t>
+  </si>
+  <si>
+    <t>&lt;strong&gt;Ujumbe Muhumi&lt;/strong&gt;
+Kipindupindu kinapatikana kwa kunywa au kula chakula chenye maambukizi ya kipindupindu. Kipindupindu kinaepukika ikiwa  watu watazingatia usafi wa mikono, chakula, maji na matumizi sahihi ya vyoo.</t>
+  </si>
+  <si>
+    <t>cholera_signs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">subgroup_ors </t>
+  </si>
+  <si>
+    <t>ors_uses</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>subgroup_health_concerns</t>
+  </si>
+  <si>
+    <t>health_concerns_note_to_chv</t>
+  </si>
+  <si>
+    <t>&lt;span style="color:#f58a1f"&gt;CHV chunguza na dadisi hali hatarishi zinahusu usafi kwenye nyumba hii na uchague  ni sehemu gani ya ushauri inahitajika zaidi. Unaweza kuchagua zaidi ya eneo moja kulingana na uhitaji. &lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>select_multiple health_concerns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">health_concerns </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ningependa tuongelee zaidi kuhusu: </t>
+  </si>
+  <si>
+    <t>subgroup_cleanliness</t>
+  </si>
+  <si>
+    <t>selected(${health_concerns},"cleanliness")</t>
+  </si>
+  <si>
+    <t>hand_cleanliness_note</t>
+  </si>
+  <si>
+    <t>&lt;span style="color:#337ab7;font-weight: bold;text-align:center"&gt;Usafi &lt;/span&gt;
+&lt;strong&gt;Usafi wa mikono kwajili ya kujikinga na kipindupindu.&lt;/strong&gt;</t>
+  </si>
+  <si>
+    <t>hand_wash_importance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Je unafahamu umuhimu wa kunawa mikono? 
+</t>
+  </si>
+  <si>
+    <t>note_to_chv_kitini_rejea</t>
+  </si>
+  <si>
+    <t>&lt;span style="color:#f58a1f"&gt;Kama hapana tumia kitini rejea kuelimisha wana familia.&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>hand_wash_timings</t>
+  </si>
+  <si>
+    <t>Nyakati muhimu unazo takiwa kunawa mikono ni: 
+• Kabla ya kula au kuandaa chakula 
+• Kabla ya kumlisha mtoto
+• Kabla ya kuaanda juice za matunda
+• Baada ya kutumia choo
+• Baada ya kumsafisha mtoto akimaliza kujisaidia, ama baada ya kumbadilisha nepi
+• Baada ya kumhudia mgonjwa wa kipindupindu</t>
+  </si>
+  <si>
+    <t>hand_wash_steps</t>
+  </si>
+  <si>
+    <t>hand_wash_steps_pic</t>
+  </si>
+  <si>
+    <t>handwashsteps.png</t>
+  </si>
+  <si>
+    <t>subgroup_water</t>
+  </si>
+  <si>
+    <t>selected(${health_concerns},"water")</t>
+  </si>
+  <si>
+    <t>safe_water</t>
+  </si>
+  <si>
+    <t>cleanwater_audio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jinsi ya kuandaa na kuhifadhi maji safi na salama </t>
+  </si>
+  <si>
+    <t>majisafi.mp3</t>
+  </si>
+  <si>
+    <t>subgroup_environment</t>
+  </si>
+  <si>
+    <t>selected(${health_concerns},"environment")</t>
+  </si>
+  <si>
+    <t>environment_cleanliness</t>
+  </si>
+  <si>
+    <t>show_wash_protocol</t>
+  </si>
+  <si>
+    <t>show_wash_protocol_c</t>
+  </si>
+  <si>
+    <t>../inputs/show_wash_protocol</t>
+  </si>
+  <si>
+    <t>${refer_postpartum_emergency_danger_sign_flag}=0 and ${show_wash_protocol_c} = 1</t>
+  </si>
+  <si>
+    <t>health_concerns</t>
+  </si>
+  <si>
+    <t>cleanliness</t>
+  </si>
+  <si>
+    <t>Cleanliness</t>
+  </si>
+  <si>
+    <t>Usafi</t>
+  </si>
+  <si>
+    <t>water</t>
+  </si>
+  <si>
+    <t>Water</t>
+  </si>
+  <si>
+    <t>Maji</t>
+  </si>
+  <si>
+    <t>environment</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>Mazingira</t>
+  </si>
+  <si>
+    <t>media::image::en</t>
+  </si>
+  <si>
+    <t>media::image::sw</t>
+  </si>
+  <si>
+    <t>media::audio::en</t>
+  </si>
+  <si>
+    <t>media::audio::sw</t>
+  </si>
+  <si>
+    <t>cholera_note</t>
+  </si>
+  <si>
+    <t>&lt;strong&gt;Huduma ya kwanza kwa mtu alieanza kuonesha dalili za kipindupindu&lt;/strong&gt; 
+Sasa ningependa kuzungmza na nyie kuhusu hatua za kuchukua ikiwa wewe au kuna mwanafamilia  mnahisi ana dalili za kipindupindu 
+• Kuharisha au kuharisha kinyesi kinachofanana na maji ya mchele
+• Kutapika
+• Je Ufanye nini ukiona una dalili za kipindupindu?
+• Nenda haraka kwenye kituo cha afya cha karibu 
+• Kunywa maji au ORS kama inapatikana mara kwa mara huku ukielekea kwenye kituo cha kutolea huduma za afya
+• Iwapo ni mtoto mdogo aliepata maambukizi, endelea kumnyonyesha hata kama anaharisha mnapoelekea kwenye kituo cha kutolea huduma za afya kupata matibabu
+• Watoto wakubwa na watu wazima waendelee kula chakula mara kwa mara</t>
+  </si>
+  <si>
+    <t>&lt;strong&gt; Matumizi ya ORS &lt;/strong&gt; 
+&lt;strong&gt; Kuna mtu yoyote anaeweza kunieleza ORS ni nini?&lt;/strong&gt;
+         • ORS (Oral Rehydration Solution) ni kinywaji kinachotumika kurudisha maji na chumvichumvi iliyopotea wakati wa kuharisha au kutapika.
+&lt;strong&gt; Jinsi ya kutengeneza ORS kwa kutumia ORS ya kwenye pakiti&lt;/strong&gt;
+        • Nawa mikono kwa maji safi ya mtiririko na sabuni 
+        • Weka lita moja ya drop ya maji salama ya kunywa kwenye chombo kisafi 
+&lt;strong&gt;Angalizo&lt;/strong&gt; 
+Wakati wa kutengeneza ORS, tumia kiwango sahihi cha maji. Ukitumia maji kidogo, ORS itafanya kuharisha kuendelee. Ukitumia maji mengi, ORS haitafanya kazi yake. Usiongeze vinywaji vingine kwenye mchanganyiko wa ORS mfano maziwa, supu, juisi n.k.
+        • Safisha kijiko na chombo cha kuwekea maji kwa sabuni na maji salama 
+        • Weka ORS kutoka kwenye pakiti kwenye maji salama huku ukikoroga 
+        • Kunywa maji kidogo kidogo mara kwa mara</t>
+  </si>
+  <si>
+    <t>&lt;span style="color:#f58a1f"&gt;Muombe akuoneshe jinsi ya kunawa mikono kwa maji tiririka na sabuni(zingatia hatua)&lt;/span&gt;
+• Vua urembo wowote, mfano pete au saa ya mkononi
+• Rowesha mikono kwa maji
+• Paka sabuni sehemu zote za mikono na viganja
+• Sugua viganja vya mikono
+• Sugua sehemu ya nyuma ya kiganja cha mkono na kwenye pachikwa za vidole
+• Sugua sehemu za viganja sawa sawa 
+• Sugua vidole gumba
+• Sugua ncha za vidole
+• Suuza mikono kwa kutumia maji tiririka
+• Funga mfereji
+• Kausha mikono</t>
+  </si>
+  <si>
+    <t>&lt;span style="color:#337ab7;font-weight: bold;text-align:center"&gt;Maji &lt;/span&gt;
+&lt;strong&gt;Maji safi na salama &lt;/strong&gt; 
+ Waulize wanafamilia wakuelezee maji safi na salama ni yepi?      
+  Maji salama ni: 
+         • Yale ambayo yako kwenye chupa yenye mfuniko ambao haujavunjika
+         • Yamechemshwa au
+         • Yamewekewa kitakasa maji
+Umuhimu wa kunywa maji safi na salama
+         • Ili kuzuia ueneaji wa  maambukizi ya vimelea vinavyoweza kusababisha maradhi mbalimbali ikiwemo kipindupindu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span style="color:#337ab7;font-weight: bold;text-align:center"&gt;Mazingira &lt;/span&gt;
+&lt;strong&gt; Matumizi ya choo &lt;/strong&gt; 
+• Nielezee madhara wana Jamii wanayo weza kupata ikiwa hawana vyoo au havitumiwi kwa usahihi?
+         • Wasikilize wana Jamii, tumia kitini rejea ukurasa wa 19 umuelezee choo bora, aina ya vyoo, jinsi ya kutumia choo vizuri na kujisaidia kusiko sahihi
+&lt;strong&gt; Usafi wa mwili na mavazi&lt;/strong&gt; 
+Sasa ningependa tuzungumze  kuhusu usafi wa mwili na mavazi ili kuzuia kuenea kwa vijidudu vikiwemo vimelea vya kipindupindu
+• Unaweza kunielezea umuhimu wa usafi wa mwili na mavazi kwa familia yako hususan watoto na athari zinazoweza kupatika ikiwa usafi wa mwili na mavazi ukikosekana
+&lt;span style="color:#f58a1f"&gt;Msiiklize mama na wanafamilia ,halafu tumia kitini rejea kuwaelimisha zaidi faida za usafi wa mwili na mavazi katika kuzuia kuenea kwa vijidudu vinavyoweza sababisha maambukizi ya maradhi. &lt;/span&gt;
+&lt;strong&gt; Usafi wa mazingira &lt;/strong&gt; 
+Sasa ningependa tuzungumze kuhusu umuhimu wa usafi wa mazingira ili tuwe na mazingira safi na kuzuia kuzaliana kwa vijidudu vinavyoweza kusababisha maambukizi ya magonjwa mbalimbali ikiwemo kipindupindu
+• Unaweza kunielezea usafi wa mazingira ni nini?
+Msikilize/wasikilize wana familia na kisha tumia kitini rejea uwafahamishe zaidi juu kuhusu
+     • Kuelewa maana ya usafi wa mazingira,  umuhimu wa usafi wa mazingira na  jinsi ya kuweka mazingira safi
+    </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="14">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2315,6 +2569,7 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2325,10 +2580,12 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2343,14 +2600,45 @@
     <font>
       <sz val="11"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Sans"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Roboto"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2366,6 +2654,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF8F8F8"/>
+        <bgColor rgb="FFF8F8F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFF8F8F8"/>
       </patternFill>
     </fill>
@@ -2438,7 +2732,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -2500,8 +2794,27 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2781,11 +3094,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z185"/>
+  <dimension ref="A1:Z218"/>
   <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.86328125" customWidth="1"/>
@@ -2845,6 +3158,18 @@
       </c>
       <c r="Q1" s="2" t="s">
         <v>16</v>
+      </c>
+      <c r="R1" s="54" t="s">
+        <v>778</v>
+      </c>
+      <c r="S1" s="54" t="s">
+        <v>779</v>
+      </c>
+      <c r="T1" s="51" t="s">
+        <v>780</v>
+      </c>
+      <c r="U1" s="51" t="s">
+        <v>781</v>
       </c>
     </row>
     <row r="2" spans="1:26" ht="13">
@@ -2951,37 +3276,51 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="13">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:26" s="50" customFormat="1" ht="13">
+      <c r="A9" s="51" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="51" t="s">
+        <v>764</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="51"/>
+      <c r="K9" s="51"/>
+      <c r="L9" s="51"/>
+      <c r="M9" s="51"/>
+      <c r="N9" s="51"/>
+      <c r="O9" s="51"/>
+      <c r="P9" s="51"/>
+      <c r="Q9" s="51"/>
+    </row>
+    <row r="10" spans="1:26" ht="13">
+      <c r="A10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="13">
-      <c r="A10" s="6" t="s">
+    <row r="11" spans="1:26" ht="13">
+      <c r="A11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B11" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C11" s="7" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" ht="13">
-      <c r="A11" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="13">
@@ -2989,38 +3328,38 @@
         <v>22</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="13">
       <c r="A13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" ht="13">
+      <c r="A14" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B14" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="7"/>
-    </row>
-    <row r="14" spans="1:26" ht="13">
-      <c r="A14" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>19</v>
-      </c>
+      <c r="C14" s="7"/>
     </row>
     <row r="15" spans="1:26" ht="13">
       <c r="A15" s="8" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>19</v>
@@ -3028,84 +3367,61 @@
     </row>
     <row r="16" spans="1:26" ht="13">
       <c r="A16" s="8" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:26" ht="13">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" ht="13">
+      <c r="A18" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C18" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:26" ht="13">
-      <c r="A18" s="8" t="s">
+    <row r="19" spans="1:26" ht="13">
+      <c r="A19" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B19" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="5"/>
-    </row>
-    <row r="19" spans="1:26" ht="13">
-      <c r="A19" s="7" t="s">
+      <c r="C19" s="5"/>
+    </row>
+    <row r="20" spans="1:26" ht="13">
+      <c r="A20" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B20" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:26" ht="13">
-      <c r="A20" s="8" t="s">
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:26" ht="13">
+      <c r="A21" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B21" s="8" t="s">
         <v>40</v>
-      </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
-      <c r="Q20" s="5"/>
-      <c r="R20" s="5"/>
-      <c r="S20" s="5"/>
-      <c r="T20" s="5"/>
-      <c r="U20" s="5"/>
-      <c r="V20" s="5"/>
-      <c r="W20" s="5"/>
-      <c r="X20" s="5"/>
-      <c r="Y20" s="5"/>
-      <c r="Z20" s="5"/>
-    </row>
-    <row r="21" spans="1:26" ht="13">
-      <c r="A21" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>42</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
@@ -3117,34 +3433,41 @@
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
       <c r="L21" s="11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M21" s="5"/>
       <c r="N21" s="5"/>
       <c r="O21" s="5"/>
       <c r="P21" s="5"/>
       <c r="Q21" s="5"/>
+      <c r="R21" s="5"/>
+      <c r="S21" s="5"/>
+      <c r="T21" s="5"/>
+      <c r="U21" s="5"/>
+      <c r="V21" s="5"/>
+      <c r="W21" s="5"/>
+      <c r="X21" s="5"/>
+      <c r="Y21" s="5"/>
+      <c r="Z21" s="5"/>
     </row>
     <row r="22" spans="1:26" ht="13">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>44</v>
+      <c r="B22" s="8" t="s">
+        <v>42</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
-      <c r="G22" s="5" t="s">
-        <v>45</v>
-      </c>
+      <c r="G22" s="5"/>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
       <c r="L22" s="11" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
@@ -3156,8 +3479,8 @@
       <c r="A23" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>47</v>
+      <c r="B23" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
@@ -3171,7 +3494,7 @@
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
       <c r="L23" s="11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M23" s="5"/>
       <c r="N23" s="5"/>
@@ -3184,7 +3507,7 @@
         <v>39</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
@@ -3198,7 +3521,7 @@
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
       <c r="L24" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
@@ -3210,20 +3533,22 @@
       <c r="A25" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C25" s="12"/>
+      <c r="B25" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="5"/>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
+      <c r="G25" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
-      <c r="L25" s="13" t="s">
-        <v>52</v>
+      <c r="L25" s="11" t="s">
+        <v>50</v>
       </c>
       <c r="M25" s="5"/>
       <c r="N25" s="5"/>
@@ -3235,8 +3560,8 @@
       <c r="A26" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>53</v>
+      <c r="B26" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="C26" s="12"/>
       <c r="D26" s="5"/>
@@ -3247,8 +3572,8 @@
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
-      <c r="L26" s="11" t="s">
-        <v>54</v>
+      <c r="L26" s="13" t="s">
+        <v>52</v>
       </c>
       <c r="M26" s="5"/>
       <c r="N26" s="5"/>
@@ -3260,10 +3585,10 @@
       <c r="A27" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C27" s="5"/>
+      <c r="B27" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="12"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -3272,11 +3597,11 @@
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
-      <c r="L27" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="M27" s="15"/>
-      <c r="N27" s="15"/>
+      <c r="L27" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
       <c r="O27" s="5"/>
       <c r="P27" s="5"/>
       <c r="Q27" s="5"/>
@@ -3285,8 +3610,8 @@
       <c r="A28" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="9" t="s">
-        <v>57</v>
+      <c r="B28" s="8" t="s">
+        <v>55</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
@@ -3297,8 +3622,8 @@
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
-      <c r="L28" s="11" t="s">
-        <v>58</v>
+      <c r="L28" s="14" t="s">
+        <v>56</v>
       </c>
       <c r="M28" s="15"/>
       <c r="N28" s="15"/>
@@ -3311,7 +3636,7 @@
         <v>39</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
@@ -3323,10 +3648,10 @@
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
       <c r="L29" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="M29" s="5"/>
-      <c r="N29" s="5"/>
+        <v>58</v>
+      </c>
+      <c r="M29" s="15"/>
+      <c r="N29" s="15"/>
       <c r="O29" s="5"/>
       <c r="P29" s="5"/>
       <c r="Q29" s="5"/>
@@ -3336,7 +3661,7 @@
         <v>39</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
@@ -3347,21 +3672,21 @@
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
       <c r="K30" s="5"/>
-      <c r="L30" s="47" t="s">
-        <v>62</v>
-      </c>
-      <c r="M30" s="48"/>
-      <c r="N30" s="48"/>
-      <c r="O30" s="48"/>
-      <c r="P30" s="48"/>
-      <c r="Q30" s="48"/>
+      <c r="L30" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="5"/>
     </row>
     <row r="31" spans="1:26" ht="13">
       <c r="A31" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
@@ -3372,21 +3697,21 @@
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
-      <c r="L31" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="M31" s="15"/>
-      <c r="N31" s="15"/>
-      <c r="O31" s="5"/>
-      <c r="P31" s="5"/>
-      <c r="Q31" s="5"/>
+      <c r="L31" s="55" t="s">
+        <v>62</v>
+      </c>
+      <c r="M31" s="56"/>
+      <c r="N31" s="56"/>
+      <c r="O31" s="56"/>
+      <c r="P31" s="56"/>
+      <c r="Q31" s="56"/>
     </row>
     <row r="32" spans="1:26" ht="13">
       <c r="A32" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="8" t="s">
-        <v>65</v>
+      <c r="B32" s="9" t="s">
+        <v>63</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -3397,11 +3722,11 @@
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
-      <c r="L32" s="16">
-        <v>7</v>
-      </c>
-      <c r="M32" s="5"/>
-      <c r="N32" s="5"/>
+      <c r="L32" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="M32" s="15"/>
+      <c r="N32" s="15"/>
       <c r="O32" s="5"/>
       <c r="P32" s="5"/>
       <c r="Q32" s="5"/>
@@ -3411,7 +3736,7 @@
         <v>39</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
@@ -3423,7 +3748,7 @@
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
       <c r="L33" s="16">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
@@ -3435,8 +3760,8 @@
       <c r="A34" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>67</v>
+      <c r="B34" s="8" t="s">
+        <v>66</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
@@ -3447,11 +3772,11 @@
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
-      <c r="L34" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="M34" s="15"/>
-      <c r="N34" s="15"/>
+      <c r="L34" s="16">
+        <v>30</v>
+      </c>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
       <c r="O34" s="5"/>
       <c r="P34" s="5"/>
       <c r="Q34" s="5"/>
@@ -3461,7 +3786,7 @@
         <v>39</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
@@ -3473,7 +3798,7 @@
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
       <c r="L35" s="17" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="M35" s="15"/>
       <c r="N35" s="15"/>
@@ -3486,7 +3811,7 @@
         <v>39</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
@@ -3498,10 +3823,10 @@
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
       <c r="L36" s="17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="M36" s="15"/>
-      <c r="N36" s="5"/>
+      <c r="N36" s="15"/>
       <c r="O36" s="5"/>
       <c r="P36" s="5"/>
       <c r="Q36" s="5"/>
@@ -3511,7 +3836,7 @@
         <v>39</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
@@ -3523,7 +3848,7 @@
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
       <c r="L37" s="17" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M37" s="15"/>
       <c r="N37" s="5"/>
@@ -3535,8 +3860,8 @@
       <c r="A38" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="18" t="s">
-        <v>24</v>
+      <c r="B38" s="4" t="s">
+        <v>73</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
@@ -3547,8 +3872,8 @@
       <c r="I38" s="5"/>
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
-      <c r="L38" s="13" t="s">
-        <v>75</v>
+      <c r="L38" s="17" t="s">
+        <v>74</v>
       </c>
       <c r="M38" s="15"/>
       <c r="N38" s="5"/>
@@ -3560,8 +3885,8 @@
       <c r="A39" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="8" t="s">
-        <v>76</v>
+      <c r="B39" s="18" t="s">
+        <v>24</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
@@ -3572,8 +3897,8 @@
       <c r="I39" s="5"/>
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
-      <c r="L39" s="11" t="s">
-        <v>77</v>
+      <c r="L39" s="13" t="s">
+        <v>75</v>
       </c>
       <c r="M39" s="15"/>
       <c r="N39" s="5"/>
@@ -3582,156 +3907,138 @@
       <c r="Q39" s="5"/>
     </row>
     <row r="40" spans="1:26" ht="13">
-      <c r="A40" s="18" t="s">
+      <c r="A40" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="18" t="s">
-        <v>78</v>
+      <c r="B40" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="C40" s="5"/>
-      <c r="G40" s="1"/>
-      <c r="L40" s="19" t="s">
-        <v>79</v>
-      </c>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="M40" s="15"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5"/>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="5"/>
     </row>
     <row r="41" spans="1:26" ht="13">
       <c r="A41" s="18" t="s">
         <v>39</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C41" s="5"/>
       <c r="G41" s="1"/>
       <c r="L41" s="19" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:26" ht="13">
+      <c r="A42" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B42" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="C42" s="5"/>
+      <c r="G42" s="1"/>
+      <c r="L42" s="19" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="42" spans="1:26" ht="13">
-      <c r="A42" s="8" t="s">
+    <row r="43" spans="1:26" ht="13">
+      <c r="A43" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B43" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C42" s="5"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="20"/>
-      <c r="G42" s="8"/>
-      <c r="H42" s="5"/>
-      <c r="I42" s="5"/>
-      <c r="J42" s="5"/>
-      <c r="K42" s="5"/>
-      <c r="L42" s="11" t="s">
+      <c r="C43" s="5"/>
+      <c r="D43" s="8"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="8"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="M42" s="15"/>
-      <c r="N42" s="15"/>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="5"/>
-      <c r="R42" s="5"/>
-      <c r="S42" s="5"/>
-      <c r="T42" s="5"/>
-      <c r="U42" s="5"/>
-      <c r="V42" s="5"/>
-      <c r="W42" s="5"/>
-      <c r="X42" s="5"/>
-      <c r="Y42" s="5"/>
-      <c r="Z42" s="5"/>
-    </row>
-    <row r="43" spans="1:26" ht="13">
-      <c r="A43" s="18" t="s">
+      <c r="M43" s="15"/>
+      <c r="N43" s="15"/>
+      <c r="O43" s="5"/>
+      <c r="P43" s="5"/>
+      <c r="Q43" s="5"/>
+      <c r="R43" s="5"/>
+      <c r="S43" s="5"/>
+      <c r="T43" s="5"/>
+      <c r="U43" s="5"/>
+      <c r="V43" s="5"/>
+      <c r="W43" s="5"/>
+      <c r="X43" s="5"/>
+      <c r="Y43" s="5"/>
+      <c r="Z43" s="5"/>
+    </row>
+    <row r="44" spans="1:26" ht="13">
+      <c r="A44" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B44" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C43" s="5"/>
-      <c r="D43" s="21"/>
-      <c r="G43" s="1"/>
-      <c r="L43" s="19" t="s">
+      <c r="C44" s="5"/>
+      <c r="D44" s="21"/>
+      <c r="G44" s="1"/>
+      <c r="L44" s="19" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="1:26" ht="13">
-      <c r="A44" s="4" t="s">
+    <row r="45" spans="1:26" s="50" customFormat="1" ht="13">
+      <c r="A45" s="51" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="51" t="s">
+        <v>765</v>
+      </c>
+      <c r="C45" s="51"/>
+      <c r="D45" s="51"/>
+      <c r="E45" s="51"/>
+      <c r="F45" s="51"/>
+      <c r="G45" s="51"/>
+      <c r="H45" s="51"/>
+      <c r="I45" s="51"/>
+      <c r="J45" s="51"/>
+      <c r="K45" s="51"/>
+      <c r="L45" s="53" t="s">
+        <v>766</v>
+      </c>
+      <c r="M45" s="51"/>
+      <c r="N45" s="51"/>
+      <c r="O45" s="51"/>
+      <c r="P45" s="51"/>
+      <c r="Q45" s="51"/>
+    </row>
+    <row r="46" spans="1:26" ht="13">
+      <c r="A46" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B44" s="12" t="s">
+      <c r="B46" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="C44" s="22"/>
-      <c r="D44" s="23"/>
-      <c r="E44" s="22"/>
-      <c r="F44" s="22"/>
-      <c r="G44" s="23"/>
-      <c r="H44" s="22"/>
-      <c r="I44" s="22"/>
-      <c r="J44" s="22"/>
-      <c r="K44" s="22"/>
-      <c r="L44" s="24"/>
-      <c r="M44" s="22"/>
-      <c r="N44" s="22"/>
-      <c r="O44" s="22"/>
-      <c r="P44" s="22"/>
-      <c r="Q44" s="22"/>
-      <c r="R44" s="22"/>
-      <c r="S44" s="22"/>
-      <c r="T44" s="22"/>
-      <c r="U44" s="22"/>
-      <c r="V44" s="22"/>
-      <c r="W44" s="22"/>
-      <c r="X44" s="22"/>
-      <c r="Y44" s="22"/>
-      <c r="Z44" s="22"/>
-    </row>
-    <row r="45" spans="1:26" ht="13">
-      <c r="A45" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="C45" s="22"/>
-      <c r="D45" s="23"/>
-      <c r="E45" s="22"/>
-      <c r="F45" s="22"/>
-      <c r="G45" s="23"/>
-      <c r="H45" s="22"/>
-      <c r="I45" s="22"/>
-      <c r="J45" s="22"/>
-      <c r="K45" s="22"/>
-      <c r="L45" s="24"/>
-      <c r="M45" s="22"/>
-      <c r="N45" s="22"/>
-      <c r="O45" s="22"/>
-      <c r="P45" s="22"/>
-      <c r="Q45" s="22"/>
-      <c r="R45" s="22"/>
-      <c r="S45" s="22"/>
-      <c r="T45" s="22"/>
-      <c r="U45" s="22"/>
-      <c r="V45" s="22"/>
-      <c r="W45" s="22"/>
-      <c r="X45" s="22"/>
-      <c r="Y45" s="22"/>
-      <c r="Z45" s="22"/>
-    </row>
-    <row r="46" spans="1:26" ht="13">
-      <c r="A46" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="B46" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="C46" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="D46" s="25" t="s">
-        <v>90</v>
-      </c>
+      <c r="C46" s="22"/>
+      <c r="D46" s="23"/>
       <c r="E46" s="22"/>
       <c r="F46" s="22"/>
       <c r="G46" s="23"/>
@@ -3739,7 +4046,7 @@
       <c r="I46" s="22"/>
       <c r="J46" s="22"/>
       <c r="K46" s="22"/>
-      <c r="L46" s="22"/>
+      <c r="L46" s="24"/>
       <c r="M46" s="22"/>
       <c r="N46" s="22"/>
       <c r="O46" s="22"/>
@@ -3747,20 +4054,23 @@
       <c r="Q46" s="22"/>
       <c r="R46" s="22"/>
       <c r="S46" s="22"/>
-    </row>
-    <row r="47" spans="1:26" ht="17.25" customHeight="1">
-      <c r="A47" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="B47" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="C47" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="D47" s="26" t="s">
-        <v>94</v>
-      </c>
+      <c r="T46" s="22"/>
+      <c r="U46" s="22"/>
+      <c r="V46" s="22"/>
+      <c r="W46" s="22"/>
+      <c r="X46" s="22"/>
+      <c r="Y46" s="22"/>
+      <c r="Z46" s="22"/>
+    </row>
+    <row r="47" spans="1:26" ht="13">
+      <c r="A47" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C47" s="22"/>
+      <c r="D47" s="23"/>
       <c r="E47" s="22"/>
       <c r="F47" s="22"/>
       <c r="G47" s="23"/>
@@ -3768,7 +4078,7 @@
       <c r="I47" s="22"/>
       <c r="J47" s="22"/>
       <c r="K47" s="22"/>
-      <c r="L47" s="22"/>
+      <c r="L47" s="24"/>
       <c r="M47" s="22"/>
       <c r="N47" s="22"/>
       <c r="O47" s="22"/>
@@ -3776,16 +4086,27 @@
       <c r="Q47" s="22"/>
       <c r="R47" s="22"/>
       <c r="S47" s="22"/>
+      <c r="T47" s="22"/>
+      <c r="U47" s="22"/>
+      <c r="V47" s="22"/>
+      <c r="W47" s="22"/>
+      <c r="X47" s="22"/>
+      <c r="Y47" s="22"/>
+      <c r="Z47" s="22"/>
     </row>
     <row r="48" spans="1:26" ht="13">
       <c r="A48" s="23" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B48" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="C48" s="22"/>
-      <c r="D48" s="23"/>
+      <c r="C48" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D48" s="25" t="s">
+        <v>90</v>
+      </c>
       <c r="E48" s="22"/>
       <c r="F48" s="22"/>
       <c r="G48" s="23"/>
@@ -3802,240 +4123,260 @@
       <c r="R48" s="22"/>
       <c r="S48" s="22"/>
     </row>
-    <row r="49" spans="1:7" ht="13">
-      <c r="A49" s="8" t="s">
+    <row r="49" spans="1:19" ht="17.25" customHeight="1">
+      <c r="A49" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="B49" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="C49" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="D49" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="E49" s="22"/>
+      <c r="F49" s="22"/>
+      <c r="G49" s="23"/>
+      <c r="H49" s="22"/>
+      <c r="I49" s="22"/>
+      <c r="J49" s="22"/>
+      <c r="K49" s="22"/>
+      <c r="L49" s="22"/>
+      <c r="M49" s="22"/>
+      <c r="N49" s="22"/>
+      <c r="O49" s="22"/>
+      <c r="P49" s="22"/>
+      <c r="Q49" s="22"/>
+      <c r="R49" s="22"/>
+      <c r="S49" s="22"/>
+    </row>
+    <row r="50" spans="1:19" ht="13">
+      <c r="A50" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="B50" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C50" s="22"/>
+      <c r="D50" s="23"/>
+      <c r="E50" s="22"/>
+      <c r="F50" s="22"/>
+      <c r="G50" s="23"/>
+      <c r="H50" s="22"/>
+      <c r="I50" s="22"/>
+      <c r="J50" s="22"/>
+      <c r="K50" s="22"/>
+      <c r="L50" s="22"/>
+      <c r="M50" s="22"/>
+      <c r="N50" s="22"/>
+      <c r="O50" s="22"/>
+      <c r="P50" s="22"/>
+      <c r="Q50" s="22"/>
+      <c r="R50" s="22"/>
+      <c r="S50" s="22"/>
+    </row>
+    <row r="51" spans="1:19" ht="13">
+      <c r="A51" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B51" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C51" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D49" s="21" t="s">
+      <c r="D51" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="G49" s="1" t="s">
+      <c r="G51" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="13">
-      <c r="A50" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C50" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="D50" s="19" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="13">
-      <c r="A51" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C51" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D51" s="13" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="13">
+    <row r="52" spans="1:19" ht="13">
       <c r="A52" s="8" t="s">
         <v>91</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D52" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="13">
+        <v>100</v>
+      </c>
+      <c r="C52" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D52" s="19" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" ht="13">
       <c r="A53" s="8" t="s">
         <v>91</v>
       </c>
       <c r="B53" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D53" s="13" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" ht="13">
+      <c r="A54" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" ht="13">
+      <c r="A55" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B55" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="C55" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D53" s="18" t="s">
+      <c r="D55" s="18" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="14.25">
-      <c r="A54" s="1" t="s">
+    <row r="56" spans="1:19" ht="14.25">
+      <c r="A56" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B54" s="27" t="s">
+      <c r="B56" s="27" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="14.25">
-      <c r="A55" s="1" t="s">
+    <row r="57" spans="1:19" ht="14.25">
+      <c r="A57" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B55" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="14.25">
-      <c r="A56" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B56" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="14.25">
-      <c r="A57" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="B57" s="27" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" ht="14.25">
+      <c r="C57" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" ht="14.25">
       <c r="A58" s="1" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="B58" s="27" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="14.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" ht="14.25">
       <c r="A59" s="1" t="s">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>121</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>724</v>
-      </c>
-      <c r="D59" s="28" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="14.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" ht="14.25">
       <c r="A60" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B60" s="27" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="14.25">
+        <v>119</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" ht="14.25">
       <c r="A61" s="1" t="s">
         <v>91</v>
       </c>
       <c r="B61" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="D61" s="28" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" ht="14.25">
+      <c r="A62" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B62" s="27" t="s">
+        <v>122</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" ht="14.25">
+      <c r="A63" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B63" s="27" t="s">
         <v>123</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C63" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D63" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="14.25">
-      <c r="A62" s="1" t="s">
+    <row r="64" spans="1:19" ht="14.25">
+      <c r="A64" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B62" s="27" t="s">
+      <c r="B64" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="C62" s="29" t="s">
+      <c r="C64" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="D64" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="G62" s="1"/>
-    </row>
-    <row r="63" spans="1:7" ht="14.25">
-      <c r="A63" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B63" s="27" t="s">
-        <v>129</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="14.25">
-      <c r="A64" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B64" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="D64" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>135</v>
-      </c>
+      <c r="G64" s="1"/>
     </row>
     <row r="65" spans="1:7" ht="14.25">
       <c r="A65" s="1" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="B65" s="27" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D65" s="30" t="s">
-        <v>138</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>135</v>
+        <v>19</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="14.25">
@@ -4043,13 +4384,13 @@
         <v>131</v>
       </c>
       <c r="B66" s="27" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="D66" s="28" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>135</v>
@@ -4057,10 +4398,19 @@
     </row>
     <row r="67" spans="1:7" ht="14.25">
       <c r="A67" s="1" t="s">
-        <v>34</v>
+        <v>131</v>
       </c>
       <c r="B67" s="27" t="s">
-        <v>129</v>
+        <v>136</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D67" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="14.25">
@@ -4068,154 +4418,145 @@
         <v>131</v>
       </c>
       <c r="B68" s="27" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D68" s="28" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="F68" s="1" t="s">
-        <v>145</v>
-      </c>
     </row>
     <row r="69" spans="1:7" ht="14.25">
       <c r="A69" s="1" t="s">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="B69" s="27" t="s">
-        <v>146</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D69" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="15.75" customHeight="1">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="14.25">
       <c r="A70" s="1" t="s">
-        <v>91</v>
+        <v>131</v>
       </c>
       <c r="B70" s="27" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="D70" s="28" t="s">
-        <v>152</v>
+        <v>144</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="14.25">
       <c r="A71" s="1" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="B71" s="27" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="14.25">
+        <v>146</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D71" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="15.75" customHeight="1">
       <c r="A72" s="1" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="B72" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="C72" s="1"/>
-      <c r="F72" s="1"/>
-      <c r="G72" s="1"/>
+        <v>150</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D72" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="73" spans="1:7" ht="14.25">
       <c r="A73" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="B73" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="D73" s="28" t="s">
-        <v>156</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="14.25">
       <c r="A74" s="1" t="s">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="B74" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>160</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="C74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
     </row>
     <row r="75" spans="1:7" ht="14.25">
       <c r="A75" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B75" s="27" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>19</v>
+        <v>155</v>
+      </c>
+      <c r="D75" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>157</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>130</v>
+        <v>99</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="14.25">
       <c r="A76" s="1" t="s">
-        <v>131</v>
+        <v>91</v>
       </c>
       <c r="B76" s="27" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="D76" s="28" t="s">
-        <v>164</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>135</v>
+        <v>159</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="14.25">
       <c r="A77" s="1" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="B77" s="27" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D77" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>135</v>
+        <v>19</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="14.25">
@@ -4223,13 +4564,13 @@
         <v>131</v>
       </c>
       <c r="B78" s="27" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="D78" s="28" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>135</v>
@@ -4240,13 +4581,13 @@
         <v>131</v>
       </c>
       <c r="B79" s="27" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D79" s="28" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>135</v>
@@ -4257,13 +4598,13 @@
         <v>131</v>
       </c>
       <c r="B80" s="27" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D80" s="28" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>135</v>
@@ -4274,13 +4615,13 @@
         <v>131</v>
       </c>
       <c r="B81" s="27" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>179</v>
+        <v>172</v>
+      </c>
+      <c r="D81" s="28" t="s">
+        <v>173</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>135</v>
@@ -4291,13 +4632,13 @@
         <v>131</v>
       </c>
       <c r="B82" s="27" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D82" s="28" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>135</v>
@@ -4308,13 +4649,13 @@
         <v>131</v>
       </c>
       <c r="B83" s="27" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="D83" s="28" t="s">
-        <v>185</v>
+        <v>178</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>179</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>135</v>
@@ -4325,13 +4666,13 @@
         <v>131</v>
       </c>
       <c r="B84" s="27" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>188</v>
+        <v>181</v>
+      </c>
+      <c r="D84" s="28" t="s">
+        <v>182</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>135</v>
@@ -4342,13 +4683,13 @@
         <v>131</v>
       </c>
       <c r="B85" s="27" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D85" s="28" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>135</v>
@@ -4359,13 +4700,13 @@
         <v>131</v>
       </c>
       <c r="B86" s="27" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="D86" s="28" t="s">
-        <v>194</v>
+        <v>187</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>188</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>135</v>
@@ -4376,13 +4717,13 @@
         <v>131</v>
       </c>
       <c r="B87" s="27" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D87" s="28" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>135</v>
@@ -4393,13 +4734,13 @@
         <v>131</v>
       </c>
       <c r="B88" s="27" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D88" s="28" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>135</v>
@@ -4407,87 +4748,84 @@
     </row>
     <row r="89" spans="1:6" ht="14.25">
       <c r="A89" s="1" t="s">
-        <v>34</v>
+        <v>131</v>
       </c>
       <c r="B89" s="27" t="s">
-        <v>161</v>
+        <v>195</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D89" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="90" spans="1:6" ht="14.25">
       <c r="A90" s="1" t="s">
-        <v>201</v>
+        <v>131</v>
       </c>
       <c r="B90" s="27" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D90" s="28" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="F90" s="1" t="s">
+    </row>
+    <row r="91" spans="1:6" ht="14.25">
+      <c r="A91" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B91" s="27" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="14.25">
+      <c r="A92" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B92" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D92" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F92" s="1" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A91" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B91" s="27" t="s">
-        <v>206</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="D91" s="28" t="s">
-        <v>208</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A92" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B92" s="27" t="s">
-        <v>210</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" ht="14.25">
+    <row r="93" spans="1:6" ht="15.75" customHeight="1">
       <c r="A93" s="1" t="s">
         <v>131</v>
       </c>
       <c r="B93" s="27" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D93" s="28" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>135</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="94" spans="1:6" ht="15.75" customHeight="1">
@@ -4495,33 +4833,36 @@
         <v>91</v>
       </c>
       <c r="B94" s="27" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="D94" s="28" t="s">
-        <v>219</v>
+        <v>211</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>212</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="14.25">
       <c r="A95" s="1" t="s">
-        <v>91</v>
+        <v>131</v>
       </c>
       <c r="B95" s="27" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="D95" s="28" t="s">
-        <v>223</v>
+        <v>216</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="15.75" customHeight="1">
@@ -4529,1248 +4870,1012 @@
         <v>91</v>
       </c>
       <c r="B96" s="27" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="D96" s="28" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
     </row>
     <row r="97" spans="1:26" ht="14.25">
       <c r="A97" s="1" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="B97" s="27" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="98" spans="1:26" ht="14.25">
+        <v>221</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D97" s="28" t="s">
+        <v>223</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="98" spans="1:26" ht="15.75" customHeight="1">
       <c r="A98" s="1" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="B98" s="27" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="E98" s="1"/>
-      <c r="F98" s="19" t="s">
-        <v>232</v>
-      </c>
-      <c r="G98" s="1" t="s">
-        <v>233</v>
+        <v>226</v>
+      </c>
+      <c r="D98" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="99" spans="1:26" ht="14.25">
       <c r="A99" s="1" t="s">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="B99" s="27" t="s">
-        <v>234</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="F99" s="1"/>
-      <c r="G99" s="1"/>
+        <v>154</v>
+      </c>
     </row>
     <row r="100" spans="1:26" ht="14.25">
       <c r="A100" s="1" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B100" s="27" t="s">
         <v>229</v>
       </c>
-      <c r="C100" s="1"/>
-      <c r="D100" s="28"/>
-      <c r="F100" s="1"/>
-      <c r="G100" s="1"/>
+      <c r="C100" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E100" s="1"/>
+      <c r="F100" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="101" spans="1:26" ht="14.25">
       <c r="A101" s="1" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="B101" s="27" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="D101" s="28" t="s">
-        <v>239</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="G101" s="1" t="s">
-        <v>99</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F101" s="1"/>
+      <c r="G101" s="1"/>
     </row>
     <row r="102" spans="1:26" ht="14.25">
       <c r="A102" s="1" t="s">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="B102" s="27" t="s">
-        <v>240</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>242</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="C102" s="1"/>
+      <c r="D102" s="28"/>
+      <c r="F102" s="1"/>
       <c r="G102" s="1"/>
     </row>
     <row r="103" spans="1:26" ht="14.25">
       <c r="A103" s="1" t="s">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="B103" s="27" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="G103" s="1"/>
+        <v>238</v>
+      </c>
+      <c r="D103" s="28" t="s">
+        <v>239</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="104" spans="1:26" ht="14.25">
       <c r="A104" s="1" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="B104" s="27" t="s">
-        <v>237</v>
-      </c>
-      <c r="C104" s="1"/>
+        <v>240</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>242</v>
+      </c>
       <c r="G104" s="1"/>
     </row>
     <row r="105" spans="1:26" ht="14.25">
       <c r="A105" s="1" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="B105" s="27" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="G105" s="1" t="s">
-        <v>99</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="G105" s="1"/>
     </row>
     <row r="106" spans="1:26" ht="14.25">
       <c r="A106" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B106" s="27" t="s">
+        <v>237</v>
+      </c>
+      <c r="C106" s="1"/>
+      <c r="G106" s="1"/>
+    </row>
+    <row r="107" spans="1:26" s="50" customFormat="1" ht="13">
+      <c r="A107" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="B107" s="47" t="s">
+        <v>726</v>
+      </c>
+      <c r="C107" s="48"/>
+      <c r="D107" s="48"/>
+      <c r="E107" s="48"/>
+      <c r="F107" s="28" t="s">
+        <v>767</v>
+      </c>
+      <c r="G107" s="48"/>
+      <c r="H107" s="48"/>
+      <c r="I107" s="48"/>
+      <c r="J107" s="48"/>
+      <c r="K107" s="48"/>
+      <c r="L107" s="49"/>
+      <c r="M107" s="48"/>
+      <c r="N107" s="48"/>
+      <c r="O107" s="48"/>
+      <c r="P107" s="48"/>
+      <c r="Q107" s="48"/>
+      <c r="R107" s="48"/>
+      <c r="S107" s="48"/>
+      <c r="T107" s="48"/>
+      <c r="U107" s="48"/>
+      <c r="V107" s="48"/>
+      <c r="W107" s="48"/>
+      <c r="X107" s="48"/>
+      <c r="Y107" s="48"/>
+      <c r="Z107" s="48"/>
+    </row>
+    <row r="108" spans="1:26" s="50" customFormat="1" ht="36" customHeight="1">
+      <c r="A108" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B108" s="28" t="s">
+        <v>727</v>
+      </c>
+      <c r="C108" s="28"/>
+      <c r="D108" s="28"/>
+      <c r="E108" s="28"/>
+      <c r="G108" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="H108" s="28"/>
+      <c r="I108" s="28"/>
+      <c r="J108" s="28"/>
+      <c r="K108" s="28"/>
+      <c r="L108" s="28"/>
+      <c r="M108" s="28"/>
+      <c r="N108" s="28"/>
+      <c r="O108" s="28"/>
+      <c r="P108" s="28"/>
+      <c r="Q108" s="28"/>
+    </row>
+    <row r="109" spans="1:26" s="50" customFormat="1" ht="36" customHeight="1">
+      <c r="A109" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="B109" s="28" t="s">
+        <v>728</v>
+      </c>
+      <c r="C109" s="28"/>
+      <c r="D109" s="57" t="s">
+        <v>729</v>
+      </c>
+      <c r="E109" s="28"/>
+      <c r="F109" s="28"/>
+      <c r="G109" s="28"/>
+      <c r="H109" s="28"/>
+      <c r="I109" s="28"/>
+      <c r="J109" s="28"/>
+      <c r="K109" s="28"/>
+      <c r="L109" s="28"/>
+      <c r="M109" s="28"/>
+      <c r="N109" s="28"/>
+      <c r="O109" s="28"/>
+      <c r="P109" s="28"/>
+      <c r="Q109" s="28"/>
+    </row>
+    <row r="110" spans="1:26" s="50" customFormat="1" ht="36" customHeight="1">
+      <c r="A110" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="B110" s="28" t="s">
+        <v>727</v>
+      </c>
+      <c r="C110" s="28"/>
+      <c r="D110" s="57"/>
+      <c r="E110" s="28"/>
+      <c r="F110" s="28"/>
+      <c r="G110" s="28"/>
+      <c r="H110" s="28"/>
+      <c r="I110" s="28"/>
+      <c r="J110" s="28"/>
+      <c r="K110" s="28"/>
+      <c r="L110" s="28"/>
+      <c r="M110" s="28"/>
+      <c r="N110" s="28"/>
+      <c r="O110" s="28"/>
+      <c r="P110" s="28"/>
+      <c r="Q110" s="28"/>
+    </row>
+    <row r="111" spans="1:26" s="50" customFormat="1" ht="36" customHeight="1">
+      <c r="A111" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="B111" s="28" t="s">
+        <v>782</v>
+      </c>
+      <c r="C111" s="28"/>
+      <c r="D111" s="57"/>
+      <c r="E111" s="28"/>
+      <c r="F111" s="28"/>
+      <c r="G111" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="H111" s="28"/>
+      <c r="I111" s="28"/>
+      <c r="J111" s="28"/>
+      <c r="K111" s="28"/>
+      <c r="L111" s="28"/>
+      <c r="M111" s="28"/>
+      <c r="N111" s="28"/>
+      <c r="O111" s="28"/>
+      <c r="P111" s="28"/>
+      <c r="Q111" s="28"/>
+    </row>
+    <row r="112" spans="1:26" s="50" customFormat="1" ht="36" customHeight="1">
+      <c r="A112" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="B112" s="28" t="s">
+        <v>730</v>
+      </c>
+      <c r="C112" s="28"/>
+      <c r="D112" s="58" t="s">
+        <v>731</v>
+      </c>
+      <c r="E112" s="28"/>
+      <c r="F112" s="28"/>
+      <c r="G112" s="28"/>
+      <c r="H112" s="28"/>
+      <c r="I112" s="28"/>
+      <c r="J112" s="28"/>
+      <c r="K112" s="28"/>
+      <c r="L112" s="28"/>
+      <c r="M112" s="28"/>
+      <c r="N112" s="28"/>
+      <c r="O112" s="28"/>
+      <c r="P112" s="28"/>
+      <c r="Q112" s="28"/>
+    </row>
+    <row r="113" spans="1:19" s="50" customFormat="1" ht="36" customHeight="1">
+      <c r="A113" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="B113" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="C113" s="28"/>
+      <c r="D113" s="58" t="s">
+        <v>783</v>
+      </c>
+      <c r="E113" s="28"/>
+      <c r="F113" s="28"/>
+      <c r="G113" s="28"/>
+      <c r="H113" s="28"/>
+      <c r="I113" s="28"/>
+      <c r="J113" s="28"/>
+      <c r="K113" s="28"/>
+      <c r="L113" s="28"/>
+      <c r="M113" s="28"/>
+      <c r="N113" s="28"/>
+      <c r="O113" s="28"/>
+      <c r="P113" s="28"/>
+      <c r="Q113" s="28"/>
+    </row>
+    <row r="114" spans="1:19" s="50" customFormat="1" ht="36" customHeight="1">
+      <c r="A114" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="B114" s="28" t="s">
+        <v>782</v>
+      </c>
+      <c r="C114" s="28"/>
+      <c r="D114" s="58"/>
+      <c r="E114" s="28"/>
+      <c r="F114" s="28"/>
+      <c r="G114" s="28"/>
+      <c r="H114" s="28"/>
+      <c r="I114" s="28"/>
+      <c r="J114" s="28"/>
+      <c r="K114" s="28"/>
+      <c r="L114" s="28"/>
+      <c r="M114" s="28"/>
+      <c r="N114" s="28"/>
+      <c r="O114" s="28"/>
+      <c r="P114" s="28"/>
+      <c r="Q114" s="28"/>
+    </row>
+    <row r="115" spans="1:19" s="50" customFormat="1" ht="36" customHeight="1">
+      <c r="A115" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="B115" s="28" t="s">
+        <v>733</v>
+      </c>
+      <c r="C115" s="28"/>
+      <c r="D115" s="58"/>
+      <c r="E115" s="28"/>
+      <c r="F115" s="28"/>
+      <c r="G115" s="28" t="s">
+        <v>233</v>
+      </c>
+      <c r="H115" s="28"/>
+      <c r="I115" s="28"/>
+      <c r="J115" s="28"/>
+      <c r="K115" s="28"/>
+      <c r="L115" s="28"/>
+      <c r="M115" s="28"/>
+      <c r="N115" s="28"/>
+      <c r="O115" s="28"/>
+      <c r="P115" s="28"/>
+      <c r="Q115" s="28"/>
+    </row>
+    <row r="116" spans="1:19" s="50" customFormat="1" ht="36" customHeight="1">
+      <c r="A116" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="B116" s="28" t="s">
+        <v>734</v>
+      </c>
+      <c r="C116" s="28"/>
+      <c r="D116" s="58" t="s">
+        <v>784</v>
+      </c>
+      <c r="E116" s="28" t="s">
+        <v>735</v>
+      </c>
+      <c r="F116" s="28"/>
+      <c r="G116" s="28"/>
+      <c r="H116" s="28"/>
+      <c r="I116" s="28"/>
+      <c r="J116" s="28"/>
+      <c r="K116" s="28"/>
+      <c r="L116" s="28"/>
+      <c r="M116" s="28"/>
+      <c r="N116" s="28"/>
+      <c r="O116" s="28"/>
+      <c r="P116" s="28"/>
+      <c r="Q116" s="28"/>
+    </row>
+    <row r="117" spans="1:19" s="50" customFormat="1" ht="36" customHeight="1">
+      <c r="A117" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="B117" s="28" t="s">
+        <v>733</v>
+      </c>
+      <c r="C117" s="28"/>
+      <c r="D117" s="58"/>
+      <c r="E117" s="28"/>
+      <c r="F117" s="28"/>
+      <c r="G117" s="28"/>
+      <c r="H117" s="28"/>
+      <c r="I117" s="28"/>
+      <c r="J117" s="28"/>
+      <c r="K117" s="28"/>
+      <c r="L117" s="28"/>
+      <c r="M117" s="28"/>
+      <c r="N117" s="28"/>
+      <c r="O117" s="28"/>
+      <c r="P117" s="28"/>
+      <c r="Q117" s="28"/>
+    </row>
+    <row r="118" spans="1:19" s="50" customFormat="1" ht="36" customHeight="1">
+      <c r="A118" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B118" s="28" t="s">
+        <v>736</v>
+      </c>
+      <c r="C118" s="28"/>
+      <c r="D118" s="58"/>
+      <c r="E118" s="28"/>
+      <c r="F118" s="28"/>
+      <c r="G118" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="H118" s="28"/>
+      <c r="I118" s="28"/>
+      <c r="J118" s="28"/>
+      <c r="K118" s="28"/>
+      <c r="L118" s="28"/>
+      <c r="M118" s="28"/>
+      <c r="N118" s="28"/>
+      <c r="O118" s="28"/>
+      <c r="P118" s="28"/>
+      <c r="Q118" s="28"/>
+    </row>
+    <row r="119" spans="1:19" s="50" customFormat="1" ht="36" customHeight="1">
+      <c r="A119" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="B119" s="28" t="s">
+        <v>737</v>
+      </c>
+      <c r="C119" s="28"/>
+      <c r="D119" s="58" t="s">
+        <v>738</v>
+      </c>
+      <c r="E119" s="28"/>
+      <c r="F119" s="28"/>
+      <c r="G119" s="28"/>
+      <c r="H119" s="28"/>
+      <c r="I119" s="28"/>
+      <c r="J119" s="28"/>
+      <c r="K119" s="28"/>
+      <c r="L119" s="28"/>
+      <c r="M119" s="28"/>
+      <c r="N119" s="28"/>
+      <c r="O119" s="28"/>
+      <c r="P119" s="28"/>
+      <c r="Q119" s="28"/>
+    </row>
+    <row r="120" spans="1:19" s="50" customFormat="1" ht="36" customHeight="1">
+      <c r="A120" s="28" t="s">
+        <v>739</v>
+      </c>
+      <c r="B120" s="28" t="s">
+        <v>740</v>
+      </c>
+      <c r="C120" s="28"/>
+      <c r="D120" s="58" t="s">
+        <v>741</v>
+      </c>
+      <c r="E120" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="F120" s="28"/>
+      <c r="G120" s="28"/>
+      <c r="H120" s="28"/>
+      <c r="I120" s="28"/>
+      <c r="J120" s="28"/>
+      <c r="K120" s="28"/>
+      <c r="L120" s="28"/>
+      <c r="M120" s="28"/>
+      <c r="N120" s="28"/>
+      <c r="O120" s="28"/>
+      <c r="P120" s="28"/>
+      <c r="Q120" s="28"/>
+    </row>
+    <row r="121" spans="1:19" s="50" customFormat="1" ht="36" customHeight="1">
+      <c r="A121" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="B121" s="28" t="s">
+        <v>736</v>
+      </c>
+      <c r="C121" s="28"/>
+      <c r="D121" s="58"/>
+      <c r="E121" s="28"/>
+      <c r="F121" s="28"/>
+      <c r="G121" s="28"/>
+      <c r="H121" s="28"/>
+      <c r="I121" s="28"/>
+      <c r="J121" s="28"/>
+      <c r="K121" s="28"/>
+      <c r="L121" s="28"/>
+      <c r="M121" s="28"/>
+      <c r="N121" s="28"/>
+      <c r="O121" s="28"/>
+      <c r="P121" s="28"/>
+      <c r="Q121" s="28"/>
+    </row>
+    <row r="122" spans="1:19" s="50" customFormat="1" ht="36" customHeight="1">
+      <c r="A122" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B122" s="28" t="s">
+        <v>742</v>
+      </c>
+      <c r="C122" s="28"/>
+      <c r="D122" s="58"/>
+      <c r="E122" s="28"/>
+      <c r="F122" s="59" t="s">
+        <v>743</v>
+      </c>
+      <c r="G122" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="H122" s="28"/>
+      <c r="I122" s="28"/>
+      <c r="J122" s="28"/>
+      <c r="K122" s="28"/>
+      <c r="L122" s="28"/>
+      <c r="M122" s="28"/>
+      <c r="N122" s="28"/>
+      <c r="O122" s="28"/>
+      <c r="P122" s="28"/>
+      <c r="Q122" s="28"/>
+    </row>
+    <row r="123" spans="1:19" s="50" customFormat="1" ht="36" customHeight="1">
+      <c r="A123" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="B123" s="28" t="s">
+        <v>744</v>
+      </c>
+      <c r="C123" s="28"/>
+      <c r="D123" s="58" t="s">
+        <v>745</v>
+      </c>
+      <c r="E123" s="28"/>
+      <c r="F123" s="28"/>
+      <c r="G123" s="28"/>
+      <c r="H123" s="28"/>
+      <c r="I123" s="28"/>
+      <c r="J123" s="28"/>
+      <c r="K123" s="28"/>
+      <c r="L123" s="28"/>
+      <c r="M123" s="28"/>
+      <c r="N123" s="28"/>
+      <c r="O123" s="28"/>
+      <c r="P123" s="28"/>
+      <c r="Q123" s="28"/>
+    </row>
+    <row r="124" spans="1:19" s="50" customFormat="1" ht="36" customHeight="1">
+      <c r="A124" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="B106" s="27" t="s">
+      <c r="B124" s="28" t="s">
+        <v>746</v>
+      </c>
+      <c r="C124" s="28"/>
+      <c r="D124" s="58" t="s">
+        <v>747</v>
+      </c>
+      <c r="E124" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="F124" s="28"/>
+      <c r="G124" s="28"/>
+      <c r="H124" s="28"/>
+      <c r="I124" s="28"/>
+      <c r="J124" s="28"/>
+      <c r="K124" s="28"/>
+      <c r="L124" s="28"/>
+      <c r="M124" s="28"/>
+      <c r="N124" s="28"/>
+      <c r="O124" s="28"/>
+      <c r="P124" s="28"/>
+      <c r="Q124" s="28"/>
+    </row>
+    <row r="125" spans="1:19" s="50" customFormat="1" ht="36" customHeight="1">
+      <c r="A125" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="B125" s="28" t="s">
+        <v>748</v>
+      </c>
+      <c r="C125" s="28"/>
+      <c r="D125" s="58" t="s">
+        <v>749</v>
+      </c>
+      <c r="E125" s="28"/>
+      <c r="F125" s="28"/>
+      <c r="G125" s="28"/>
+      <c r="H125" s="28"/>
+      <c r="I125" s="28"/>
+      <c r="J125" s="28"/>
+      <c r="K125" s="28"/>
+      <c r="L125" s="28"/>
+      <c r="M125" s="28"/>
+      <c r="N125" s="28"/>
+      <c r="O125" s="28"/>
+      <c r="P125" s="28"/>
+      <c r="Q125" s="28"/>
+    </row>
+    <row r="126" spans="1:19" s="50" customFormat="1" ht="36" customHeight="1">
+      <c r="A126" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="B126" s="28" t="s">
+        <v>750</v>
+      </c>
+      <c r="C126" s="28"/>
+      <c r="D126" s="58" t="s">
+        <v>751</v>
+      </c>
+      <c r="E126" s="28"/>
+      <c r="F126" s="28"/>
+      <c r="G126" s="28"/>
+      <c r="H126" s="28"/>
+      <c r="I126" s="28"/>
+      <c r="J126" s="28"/>
+      <c r="K126" s="28"/>
+      <c r="L126" s="28"/>
+      <c r="M126" s="28"/>
+      <c r="N126" s="28"/>
+      <c r="O126" s="28"/>
+      <c r="P126" s="28"/>
+      <c r="Q126" s="28"/>
+    </row>
+    <row r="127" spans="1:19" s="50" customFormat="1" ht="36" customHeight="1">
+      <c r="A127" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="B127" s="28" t="s">
+        <v>752</v>
+      </c>
+      <c r="C127" s="28"/>
+      <c r="D127" s="58" t="s">
+        <v>785</v>
+      </c>
+      <c r="E127" s="28"/>
+      <c r="F127" s="28"/>
+      <c r="G127" s="28"/>
+      <c r="H127" s="28"/>
+      <c r="I127" s="28"/>
+      <c r="J127" s="28"/>
+      <c r="K127" s="28"/>
+      <c r="L127" s="28"/>
+      <c r="M127" s="28"/>
+      <c r="N127" s="28"/>
+      <c r="O127" s="28"/>
+      <c r="P127" s="28"/>
+      <c r="Q127" s="28"/>
+    </row>
+    <row r="128" spans="1:19" s="50" customFormat="1" ht="36" customHeight="1">
+      <c r="A128" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="B128" s="28" t="s">
+        <v>753</v>
+      </c>
+      <c r="C128" s="59"/>
+      <c r="D128" s="28"/>
+      <c r="E128" s="28"/>
+      <c r="F128" s="59"/>
+      <c r="G128" s="59"/>
+      <c r="H128" s="28"/>
+      <c r="I128" s="28"/>
+      <c r="J128" s="28"/>
+      <c r="K128" s="28"/>
+      <c r="L128" s="28"/>
+      <c r="M128" s="28"/>
+      <c r="N128" s="28"/>
+      <c r="O128" s="28"/>
+      <c r="P128" s="28"/>
+      <c r="Q128" s="28"/>
+      <c r="R128" s="28" t="s">
+        <v>754</v>
+      </c>
+      <c r="S128" s="49" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="129" spans="1:26" s="50" customFormat="1" ht="36" customHeight="1">
+      <c r="A129" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="B129" s="28" t="s">
+        <v>742</v>
+      </c>
+      <c r="C129" s="28"/>
+      <c r="D129" s="58"/>
+      <c r="E129" s="28"/>
+      <c r="F129" s="28"/>
+      <c r="G129" s="28"/>
+      <c r="H129" s="28"/>
+      <c r="I129" s="28"/>
+      <c r="J129" s="28"/>
+      <c r="K129" s="28"/>
+      <c r="L129" s="28"/>
+      <c r="M129" s="28"/>
+      <c r="N129" s="28"/>
+      <c r="O129" s="28"/>
+      <c r="P129" s="28"/>
+      <c r="Q129" s="28"/>
+    </row>
+    <row r="130" spans="1:26" s="50" customFormat="1" ht="36" customHeight="1">
+      <c r="A130" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B130" s="28" t="s">
+        <v>755</v>
+      </c>
+      <c r="C130" s="28"/>
+      <c r="D130" s="58"/>
+      <c r="E130" s="28"/>
+      <c r="F130" s="59" t="s">
+        <v>756</v>
+      </c>
+      <c r="G130" s="28" t="s">
+        <v>99</v>
+      </c>
+      <c r="H130" s="28"/>
+      <c r="I130" s="28"/>
+      <c r="J130" s="28"/>
+      <c r="K130" s="28"/>
+      <c r="L130" s="28"/>
+      <c r="M130" s="28"/>
+      <c r="N130" s="28"/>
+      <c r="O130" s="28"/>
+      <c r="P130" s="28"/>
+      <c r="Q130" s="28"/>
+    </row>
+    <row r="131" spans="1:26" s="50" customFormat="1" ht="36" customHeight="1">
+      <c r="A131" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="B131" s="28" t="s">
+        <v>757</v>
+      </c>
+      <c r="C131" s="28"/>
+      <c r="D131" s="58" t="s">
+        <v>786</v>
+      </c>
+      <c r="E131" s="28"/>
+      <c r="F131" s="28"/>
+      <c r="G131" s="28"/>
+      <c r="H131" s="28"/>
+      <c r="I131" s="28"/>
+      <c r="J131" s="28"/>
+      <c r="K131" s="28"/>
+      <c r="L131" s="28"/>
+      <c r="M131" s="28"/>
+      <c r="N131" s="28"/>
+      <c r="O131" s="28"/>
+      <c r="P131" s="28"/>
+      <c r="Q131" s="28"/>
+    </row>
+    <row r="132" spans="1:26" s="50" customFormat="1" ht="36" customHeight="1">
+      <c r="A132" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="B132" s="28" t="s">
+        <v>758</v>
+      </c>
+      <c r="C132" s="60"/>
+      <c r="D132" s="60" t="s">
+        <v>759</v>
+      </c>
+      <c r="E132" s="28"/>
+      <c r="F132" s="59"/>
+      <c r="G132" s="28"/>
+      <c r="H132" s="28"/>
+      <c r="I132" s="28"/>
+      <c r="J132" s="28"/>
+      <c r="K132" s="28"/>
+      <c r="L132" s="28"/>
+      <c r="M132" s="28"/>
+      <c r="N132" s="28"/>
+      <c r="O132" s="28"/>
+      <c r="P132" s="28"/>
+      <c r="Q132" s="28"/>
+      <c r="T132" s="61" t="s">
+        <v>760</v>
+      </c>
+      <c r="U132" s="61" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="133" spans="1:26" s="50" customFormat="1" ht="36" customHeight="1">
+      <c r="A133" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="B133" s="28" t="s">
+        <v>755</v>
+      </c>
+      <c r="C133" s="28"/>
+      <c r="D133" s="58"/>
+      <c r="E133" s="28"/>
+      <c r="F133" s="28"/>
+      <c r="G133" s="28"/>
+      <c r="H133" s="28"/>
+      <c r="I133" s="28"/>
+      <c r="J133" s="28"/>
+      <c r="K133" s="28"/>
+      <c r="L133" s="28"/>
+      <c r="M133" s="28"/>
+      <c r="N133" s="28"/>
+      <c r="O133" s="28"/>
+      <c r="P133" s="28"/>
+      <c r="Q133" s="28"/>
+    </row>
+    <row r="134" spans="1:26" s="50" customFormat="1" ht="36" customHeight="1">
+      <c r="A134" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B134" s="28" t="s">
+        <v>761</v>
+      </c>
+      <c r="C134" s="28"/>
+      <c r="D134" s="58"/>
+      <c r="E134" s="28"/>
+      <c r="F134" s="59" t="s">
+        <v>762</v>
+      </c>
+      <c r="G134" s="28" t="s">
+        <v>233</v>
+      </c>
+      <c r="H134" s="28"/>
+      <c r="I134" s="28"/>
+      <c r="J134" s="28"/>
+      <c r="K134" s="28"/>
+      <c r="L134" s="28"/>
+      <c r="M134" s="28"/>
+      <c r="N134" s="28"/>
+      <c r="O134" s="28"/>
+      <c r="P134" s="28"/>
+      <c r="Q134" s="28"/>
+    </row>
+    <row r="135" spans="1:26" s="50" customFormat="1" ht="36" customHeight="1">
+      <c r="A135" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="B135" s="28" t="s">
+        <v>763</v>
+      </c>
+      <c r="C135" s="28"/>
+      <c r="D135" s="58" t="s">
+        <v>787</v>
+      </c>
+      <c r="E135" s="28"/>
+      <c r="F135" s="28"/>
+      <c r="G135" s="28"/>
+      <c r="H135" s="28"/>
+      <c r="I135" s="28"/>
+      <c r="J135" s="28"/>
+      <c r="K135" s="28"/>
+      <c r="L135" s="28"/>
+      <c r="M135" s="28"/>
+      <c r="N135" s="28"/>
+      <c r="O135" s="28"/>
+      <c r="P135" s="28"/>
+      <c r="Q135" s="28"/>
+    </row>
+    <row r="136" spans="1:26" s="50" customFormat="1" ht="36" customHeight="1">
+      <c r="A136" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="B136" s="28" t="s">
+        <v>761</v>
+      </c>
+      <c r="C136" s="28"/>
+      <c r="D136" s="58"/>
+      <c r="E136" s="28"/>
+      <c r="F136" s="28"/>
+      <c r="G136" s="28"/>
+      <c r="H136" s="28"/>
+      <c r="I136" s="28"/>
+      <c r="J136" s="28"/>
+      <c r="K136" s="28"/>
+      <c r="L136" s="28"/>
+      <c r="M136" s="28"/>
+      <c r="N136" s="28"/>
+      <c r="O136" s="28"/>
+      <c r="P136" s="28"/>
+      <c r="Q136" s="28"/>
+    </row>
+    <row r="137" spans="1:26" s="50" customFormat="1" ht="36" customHeight="1">
+      <c r="A137" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="B137" s="28" t="s">
+        <v>726</v>
+      </c>
+      <c r="E137" s="28"/>
+      <c r="F137" s="28"/>
+      <c r="G137" s="28"/>
+      <c r="H137" s="28"/>
+      <c r="I137" s="28"/>
+      <c r="J137" s="28"/>
+      <c r="K137" s="28"/>
+      <c r="L137" s="28"/>
+      <c r="M137" s="28"/>
+      <c r="N137" s="28"/>
+      <c r="O137" s="28"/>
+      <c r="P137" s="28"/>
+      <c r="Q137" s="28"/>
+    </row>
+    <row r="138" spans="1:26" ht="14.25">
+      <c r="A138" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B138" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="139" spans="1:26" ht="14.25">
+      <c r="A139" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B139" s="27" t="s">
         <v>250</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="C139" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="D106" s="28" t="s">
+      <c r="D139" s="28" t="s">
         <v>252</v>
       </c>
-      <c r="E106" s="1" t="s">
+      <c r="E139" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="G106" s="1"/>
-    </row>
-    <row r="107" spans="1:26" ht="13">
-      <c r="A107" s="6" t="s">
+      <c r="G139" s="1"/>
+    </row>
+    <row r="140" spans="1:26" ht="13">
+      <c r="A140" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="B107" s="6" t="s">
+      <c r="B140" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="C107" s="6" t="s">
+      <c r="C140" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="D107" s="6" t="s">
+      <c r="D140" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="E107" s="12" t="s">
+      <c r="E140" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="F107" s="31" t="s">
+      <c r="F140" s="31" t="s">
         <v>257</v>
-      </c>
-      <c r="G107" s="8"/>
-      <c r="H107" s="5"/>
-      <c r="I107" s="5"/>
-      <c r="J107" s="5"/>
-      <c r="K107" s="5"/>
-      <c r="L107" s="5"/>
-      <c r="M107" s="5"/>
-      <c r="N107" s="5"/>
-      <c r="O107" s="5"/>
-      <c r="P107" s="5"/>
-      <c r="Q107" s="5"/>
-      <c r="R107" s="5"/>
-      <c r="S107" s="5"/>
-      <c r="T107" s="5"/>
-      <c r="U107" s="5"/>
-      <c r="V107" s="5"/>
-      <c r="W107" s="5"/>
-      <c r="X107" s="5"/>
-      <c r="Y107" s="5"/>
-      <c r="Z107" s="5"/>
-    </row>
-    <row r="108" spans="1:26" ht="14.25">
-      <c r="A108" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B108" s="27" t="s">
-        <v>258</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="D108" s="28" t="s">
-        <v>260</v>
-      </c>
-      <c r="F108" s="19" t="s">
-        <v>261</v>
-      </c>
-      <c r="G108" s="1"/>
-    </row>
-    <row r="109" spans="1:26" ht="14.25">
-      <c r="A109" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B109" s="27" t="s">
-        <v>246</v>
-      </c>
-      <c r="C109" s="1"/>
-      <c r="F109" s="19"/>
-      <c r="G109" s="1"/>
-    </row>
-    <row r="110" spans="1:26" ht="14.25">
-      <c r="A110" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B110" s="27" t="s">
-        <v>262</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="D110" s="28" t="s">
-        <v>264</v>
-      </c>
-      <c r="F110" s="19" t="s">
-        <v>265</v>
-      </c>
-      <c r="G110" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="111" spans="1:26" ht="13">
-      <c r="A111" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="B111" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="C111" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="D111" s="18" t="s">
-        <v>269</v>
-      </c>
-      <c r="E111" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="F111" s="4"/>
-      <c r="G111" s="8"/>
-      <c r="H111" s="5"/>
-      <c r="I111" s="5"/>
-      <c r="J111" s="5"/>
-      <c r="K111" s="5"/>
-      <c r="L111" s="5"/>
-      <c r="M111" s="5"/>
-      <c r="N111" s="5"/>
-      <c r="O111" s="5"/>
-      <c r="P111" s="5"/>
-      <c r="Q111" s="5"/>
-      <c r="R111" s="5"/>
-      <c r="S111" s="5"/>
-      <c r="T111" s="5"/>
-      <c r="U111" s="5"/>
-      <c r="V111" s="5"/>
-      <c r="W111" s="5"/>
-      <c r="X111" s="5"/>
-      <c r="Y111" s="5"/>
-      <c r="Z111" s="5"/>
-    </row>
-    <row r="112" spans="1:26" ht="13">
-      <c r="A112" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="B112" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="C112" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="D112" s="32" t="s">
-        <v>273</v>
-      </c>
-      <c r="E112" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="F112" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="G112" s="8"/>
-      <c r="H112" s="5"/>
-      <c r="I112" s="5"/>
-      <c r="J112" s="5"/>
-      <c r="K112" s="5"/>
-      <c r="L112" s="5"/>
-      <c r="M112" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="N112" s="5"/>
-      <c r="O112" s="5"/>
-      <c r="P112" s="5"/>
-      <c r="Q112" s="5"/>
-      <c r="R112" s="5"/>
-      <c r="S112" s="5"/>
-      <c r="T112" s="5"/>
-      <c r="U112" s="5"/>
-      <c r="V112" s="5"/>
-      <c r="W112" s="5"/>
-      <c r="X112" s="5"/>
-      <c r="Y112" s="5"/>
-      <c r="Z112" s="5"/>
-    </row>
-    <row r="113" spans="1:26" ht="13">
-      <c r="A113" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B113" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="C113" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D113" s="5"/>
-      <c r="E113" s="12"/>
-      <c r="F113" s="4"/>
-      <c r="G113" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="H113" s="5"/>
-      <c r="I113" s="5"/>
-      <c r="J113" s="5"/>
-      <c r="K113" s="5"/>
-      <c r="L113" s="5"/>
-      <c r="M113" s="5"/>
-      <c r="N113" s="5"/>
-      <c r="O113" s="5"/>
-      <c r="P113" s="5"/>
-      <c r="Q113" s="5"/>
-      <c r="R113" s="5"/>
-      <c r="S113" s="5"/>
-      <c r="T113" s="5"/>
-      <c r="U113" s="5"/>
-      <c r="V113" s="5"/>
-      <c r="W113" s="5"/>
-      <c r="X113" s="5"/>
-      <c r="Y113" s="5"/>
-      <c r="Z113" s="5"/>
-    </row>
-    <row r="114" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A114" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="B114" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="C114" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="D114" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="E114" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="F114" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="G114" s="8"/>
-      <c r="H114" s="5"/>
-      <c r="I114" s="5"/>
-      <c r="J114" s="5"/>
-      <c r="K114" s="5"/>
-      <c r="L114" s="5"/>
-      <c r="M114" s="11" t="s">
-        <v>283</v>
-      </c>
-      <c r="N114" s="5"/>
-      <c r="O114" s="5"/>
-      <c r="P114" s="5"/>
-      <c r="Q114" s="5"/>
-      <c r="R114" s="5"/>
-      <c r="S114" s="5"/>
-      <c r="T114" s="5"/>
-      <c r="U114" s="5"/>
-      <c r="V114" s="5"/>
-      <c r="W114" s="5"/>
-      <c r="X114" s="5"/>
-      <c r="Y114" s="5"/>
-      <c r="Z114" s="5"/>
-    </row>
-    <row r="115" spans="1:26" ht="13">
-      <c r="A115" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="B115" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="C115" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="D115" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="E115" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="F115" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="G115" s="4"/>
-      <c r="H115" s="4"/>
-      <c r="I115" s="5"/>
-      <c r="J115" s="5"/>
-      <c r="K115" s="5"/>
-      <c r="L115" s="5"/>
-      <c r="M115" s="5"/>
-      <c r="N115" s="5"/>
-      <c r="O115" s="5"/>
-      <c r="P115" s="5"/>
-      <c r="Q115" s="5"/>
-      <c r="R115" s="5"/>
-      <c r="S115" s="5"/>
-      <c r="T115" s="5"/>
-      <c r="U115" s="5"/>
-      <c r="V115" s="5"/>
-      <c r="W115" s="5"/>
-      <c r="X115" s="5"/>
-      <c r="Y115" s="5"/>
-      <c r="Z115" s="5"/>
-    </row>
-    <row r="116" spans="1:26" ht="13">
-      <c r="A116" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B116" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="C116" s="4"/>
-      <c r="D116" s="4"/>
-      <c r="E116" s="4"/>
-      <c r="F116" s="4"/>
-      <c r="G116" s="4"/>
-      <c r="H116" s="4"/>
-      <c r="I116" s="5"/>
-      <c r="J116" s="5"/>
-      <c r="K116" s="5"/>
-      <c r="L116" s="5"/>
-      <c r="M116" s="5"/>
-      <c r="N116" s="5"/>
-      <c r="O116" s="5"/>
-      <c r="P116" s="5"/>
-      <c r="Q116" s="5"/>
-      <c r="R116" s="5"/>
-      <c r="S116" s="5"/>
-      <c r="T116" s="5"/>
-      <c r="U116" s="5"/>
-      <c r="V116" s="5"/>
-      <c r="W116" s="5"/>
-      <c r="X116" s="5"/>
-      <c r="Y116" s="5"/>
-      <c r="Z116" s="5"/>
-    </row>
-    <row r="117" spans="1:26" ht="13">
-      <c r="A117" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="B117" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="C117" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="D117" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="E117" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="F117" s="4"/>
-      <c r="G117" s="4"/>
-      <c r="H117" s="4"/>
-      <c r="I117" s="5"/>
-      <c r="J117" s="5"/>
-      <c r="K117" s="5"/>
-      <c r="L117" s="5"/>
-      <c r="M117" s="5"/>
-      <c r="N117" s="5"/>
-      <c r="O117" s="5"/>
-      <c r="P117" s="5"/>
-      <c r="Q117" s="5"/>
-      <c r="R117" s="5"/>
-      <c r="S117" s="5"/>
-      <c r="T117" s="5"/>
-      <c r="U117" s="5"/>
-      <c r="V117" s="5"/>
-      <c r="W117" s="5"/>
-      <c r="X117" s="5"/>
-      <c r="Y117" s="5"/>
-      <c r="Z117" s="5"/>
-    </row>
-    <row r="118" spans="1:26" ht="13">
-      <c r="A118" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="B118" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="C118" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="D118" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="E118" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="F118" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="G118" s="4"/>
-      <c r="H118" s="4"/>
-      <c r="I118" s="5"/>
-      <c r="J118" s="5"/>
-      <c r="K118" s="5"/>
-      <c r="L118" s="5"/>
-      <c r="M118" s="5"/>
-      <c r="N118" s="5"/>
-      <c r="O118" s="5"/>
-      <c r="P118" s="5"/>
-      <c r="Q118" s="5"/>
-      <c r="R118" s="5"/>
-      <c r="S118" s="5"/>
-      <c r="T118" s="5"/>
-      <c r="U118" s="5"/>
-      <c r="V118" s="5"/>
-      <c r="W118" s="5"/>
-      <c r="X118" s="5"/>
-      <c r="Y118" s="5"/>
-      <c r="Z118" s="5"/>
-    </row>
-    <row r="119" spans="1:26" ht="13">
-      <c r="A119" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="B119" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="C119" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="D119" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="E119" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="F119" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="G119" s="4"/>
-      <c r="H119" s="4"/>
-      <c r="I119" s="5"/>
-      <c r="J119" s="5"/>
-      <c r="K119" s="5"/>
-      <c r="L119" s="5"/>
-      <c r="M119" s="5"/>
-      <c r="N119" s="5"/>
-      <c r="O119" s="5"/>
-      <c r="P119" s="5"/>
-      <c r="Q119" s="5"/>
-      <c r="R119" s="5"/>
-      <c r="S119" s="5"/>
-      <c r="T119" s="5"/>
-      <c r="U119" s="5"/>
-      <c r="V119" s="5"/>
-      <c r="W119" s="5"/>
-      <c r="X119" s="5"/>
-      <c r="Y119" s="5"/>
-      <c r="Z119" s="5"/>
-    </row>
-    <row r="120" spans="1:26" ht="13">
-      <c r="A120" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="B120" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="C120" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="D120" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="E120" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="F120" s="4"/>
-      <c r="G120" s="4"/>
-      <c r="H120" s="4"/>
-      <c r="I120" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="J120" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="K120" s="33" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="121" spans="1:26" ht="13">
-      <c r="A121" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="B121" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="C121" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="D121" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="E121" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="F121" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="G121" s="4"/>
-      <c r="H121" s="4"/>
-      <c r="I121" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="J121" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="K121" s="33" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="122" spans="1:26" ht="13">
-      <c r="A122" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B122" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="C122" s="4"/>
-      <c r="D122" s="4"/>
-      <c r="E122" s="4"/>
-      <c r="F122" s="4"/>
-      <c r="G122" s="4"/>
-      <c r="H122" s="4"/>
-    </row>
-    <row r="123" spans="1:26" ht="13">
-      <c r="A123" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B123" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="C123" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="D123" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="E123" s="4"/>
-      <c r="F123" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="G123" s="4"/>
-      <c r="H123" s="4"/>
-    </row>
-    <row r="124" spans="1:26" ht="13">
-      <c r="A124" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="B124" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="C124" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="D124" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="E124" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="F124" s="4"/>
-      <c r="G124" s="4"/>
-      <c r="H124" s="4"/>
-    </row>
-    <row r="125" spans="1:26" ht="13">
-      <c r="A125" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B125" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="C125" s="4"/>
-      <c r="D125" s="4"/>
-      <c r="E125" s="4"/>
-      <c r="F125" s="4"/>
-      <c r="G125" s="4"/>
-      <c r="H125" s="4"/>
-    </row>
-    <row r="126" spans="1:26" ht="13">
-      <c r="A126" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B126" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="C126" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="D126" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="E126" s="4"/>
-      <c r="F126" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="G126" s="4"/>
-      <c r="H126" s="4"/>
-    </row>
-    <row r="127" spans="1:26" ht="13">
-      <c r="A127" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="B127" s="34" t="s">
-        <v>325</v>
-      </c>
-      <c r="C127" s="35" t="s">
-        <v>326</v>
-      </c>
-      <c r="D127" s="18" t="s">
-        <v>327</v>
-      </c>
-      <c r="E127" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="F127" s="9"/>
-      <c r="G127" s="8"/>
-      <c r="H127" s="5"/>
-      <c r="I127" s="5"/>
-      <c r="J127" s="5"/>
-      <c r="K127" s="5"/>
-      <c r="L127" s="5"/>
-      <c r="M127" s="5"/>
-      <c r="N127" s="5"/>
-      <c r="O127" s="5"/>
-      <c r="P127" s="5"/>
-      <c r="Q127" s="5"/>
-      <c r="R127" s="5"/>
-      <c r="S127" s="5"/>
-      <c r="T127" s="5"/>
-      <c r="U127" s="5"/>
-      <c r="V127" s="5"/>
-      <c r="W127" s="5"/>
-      <c r="X127" s="5"/>
-      <c r="Y127" s="5"/>
-      <c r="Z127" s="5"/>
-    </row>
-    <row r="128" spans="1:26" ht="13">
-      <c r="A128" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B128" s="34" t="s">
-        <v>328</v>
-      </c>
-      <c r="C128" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="D128" s="5"/>
-      <c r="E128" s="5"/>
-      <c r="F128" s="9"/>
-      <c r="G128" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="H128" s="5"/>
-      <c r="I128" s="5"/>
-      <c r="J128" s="5"/>
-      <c r="K128" s="5"/>
-      <c r="L128" s="5"/>
-      <c r="M128" s="5"/>
-      <c r="N128" s="5"/>
-      <c r="O128" s="5"/>
-      <c r="P128" s="5"/>
-      <c r="Q128" s="5"/>
-      <c r="R128" s="5"/>
-      <c r="S128" s="5"/>
-      <c r="T128" s="5"/>
-      <c r="U128" s="5"/>
-      <c r="V128" s="5"/>
-      <c r="W128" s="5"/>
-      <c r="X128" s="5"/>
-      <c r="Y128" s="5"/>
-      <c r="Z128" s="5"/>
-    </row>
-    <row r="129" spans="1:26" ht="13">
-      <c r="A129" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="B129" s="34" t="s">
-        <v>330</v>
-      </c>
-      <c r="C129" s="37" t="s">
-        <v>331</v>
-      </c>
-      <c r="D129" s="32" t="s">
-        <v>332</v>
-      </c>
-      <c r="E129" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="F129" s="9"/>
-      <c r="G129" s="8"/>
-      <c r="H129" s="5"/>
-      <c r="I129" s="5"/>
-      <c r="J129" s="5"/>
-      <c r="K129" s="5"/>
-      <c r="L129" s="5"/>
-      <c r="M129" s="5"/>
-      <c r="N129" s="5"/>
-      <c r="O129" s="5"/>
-      <c r="P129" s="5"/>
-      <c r="Q129" s="5"/>
-      <c r="R129" s="5"/>
-      <c r="S129" s="5"/>
-      <c r="T129" s="5"/>
-      <c r="U129" s="5"/>
-      <c r="V129" s="5"/>
-      <c r="W129" s="5"/>
-      <c r="X129" s="5"/>
-      <c r="Y129" s="5"/>
-      <c r="Z129" s="5"/>
-    </row>
-    <row r="130" spans="1:26" ht="13">
-      <c r="A130" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="B130" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="C130" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="D130" s="32" t="s">
-        <v>334</v>
-      </c>
-      <c r="E130" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="F130" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="G130" s="8"/>
-      <c r="H130" s="5"/>
-      <c r="I130" s="5"/>
-      <c r="J130" s="5"/>
-      <c r="K130" s="5"/>
-      <c r="L130" s="5"/>
-      <c r="M130" s="5"/>
-      <c r="N130" s="5"/>
-      <c r="O130" s="5"/>
-      <c r="P130" s="5"/>
-      <c r="Q130" s="5"/>
-      <c r="R130" s="5"/>
-      <c r="S130" s="5"/>
-      <c r="T130" s="5"/>
-      <c r="U130" s="5"/>
-      <c r="V130" s="5"/>
-      <c r="W130" s="5"/>
-      <c r="X130" s="5"/>
-      <c r="Y130" s="5"/>
-      <c r="Z130" s="5"/>
-    </row>
-    <row r="131" spans="1:26" ht="13">
-      <c r="A131" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B131" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="C131" s="38"/>
-      <c r="D131" s="5"/>
-      <c r="E131" s="5"/>
-      <c r="F131" s="9"/>
-      <c r="G131" s="8"/>
-      <c r="H131" s="5"/>
-      <c r="I131" s="5"/>
-      <c r="J131" s="5"/>
-      <c r="K131" s="5"/>
-      <c r="L131" s="5"/>
-      <c r="M131" s="5"/>
-      <c r="N131" s="5"/>
-      <c r="O131" s="5"/>
-      <c r="P131" s="5"/>
-      <c r="Q131" s="5"/>
-      <c r="R131" s="5"/>
-      <c r="S131" s="5"/>
-      <c r="T131" s="5"/>
-      <c r="U131" s="5"/>
-      <c r="V131" s="5"/>
-      <c r="W131" s="5"/>
-      <c r="X131" s="5"/>
-      <c r="Y131" s="5"/>
-      <c r="Z131" s="5"/>
-    </row>
-    <row r="132" spans="1:26" ht="13">
-      <c r="A132" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B132" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="C132" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="D132" s="5"/>
-      <c r="E132" s="5"/>
-      <c r="F132" s="9"/>
-      <c r="G132" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="H132" s="5"/>
-      <c r="I132" s="5"/>
-      <c r="J132" s="5"/>
-      <c r="K132" s="5"/>
-      <c r="L132" s="5"/>
-      <c r="M132" s="5"/>
-      <c r="N132" s="5"/>
-      <c r="O132" s="5"/>
-      <c r="P132" s="5"/>
-      <c r="Q132" s="5"/>
-      <c r="R132" s="5"/>
-      <c r="S132" s="5"/>
-      <c r="T132" s="5"/>
-      <c r="U132" s="5"/>
-      <c r="V132" s="5"/>
-      <c r="W132" s="5"/>
-      <c r="X132" s="5"/>
-      <c r="Y132" s="5"/>
-      <c r="Z132" s="5"/>
-    </row>
-    <row r="133" spans="1:26" ht="13">
-      <c r="A133" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="B133" s="34" t="s">
-        <v>338</v>
-      </c>
-      <c r="C133" s="37" t="s">
-        <v>339</v>
-      </c>
-      <c r="D133" s="32" t="s">
-        <v>340</v>
-      </c>
-      <c r="E133" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="F133" s="9"/>
-      <c r="G133" s="8"/>
-      <c r="H133" s="5"/>
-      <c r="I133" s="5"/>
-      <c r="J133" s="5"/>
-      <c r="K133" s="5"/>
-      <c r="L133" s="5"/>
-      <c r="M133" s="5"/>
-      <c r="N133" s="5"/>
-      <c r="O133" s="5"/>
-      <c r="P133" s="5"/>
-      <c r="Q133" s="5"/>
-      <c r="R133" s="5"/>
-      <c r="S133" s="5"/>
-      <c r="T133" s="5"/>
-      <c r="U133" s="5"/>
-      <c r="V133" s="5"/>
-      <c r="W133" s="5"/>
-      <c r="X133" s="5"/>
-      <c r="Y133" s="5"/>
-      <c r="Z133" s="5"/>
-    </row>
-    <row r="134" spans="1:26" ht="13">
-      <c r="A134" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="B134" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="C134" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="D134" s="32" t="s">
-        <v>334</v>
-      </c>
-      <c r="E134" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="F134" s="9" t="s">
-        <v>342</v>
-      </c>
-      <c r="G134" s="8"/>
-      <c r="H134" s="5"/>
-      <c r="I134" s="5"/>
-      <c r="J134" s="5"/>
-      <c r="K134" s="5"/>
-      <c r="L134" s="5"/>
-      <c r="M134" s="5"/>
-      <c r="N134" s="5"/>
-      <c r="O134" s="5"/>
-      <c r="P134" s="5"/>
-      <c r="Q134" s="5"/>
-      <c r="R134" s="5"/>
-      <c r="S134" s="5"/>
-      <c r="T134" s="5"/>
-      <c r="U134" s="5"/>
-      <c r="V134" s="5"/>
-      <c r="W134" s="5"/>
-      <c r="X134" s="5"/>
-      <c r="Y134" s="5"/>
-      <c r="Z134" s="5"/>
-    </row>
-    <row r="135" spans="1:26" ht="13">
-      <c r="A135" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B135" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="C135" s="8"/>
-      <c r="D135" s="5"/>
-      <c r="E135" s="5"/>
-      <c r="F135" s="9"/>
-      <c r="G135" s="8"/>
-      <c r="H135" s="5"/>
-      <c r="I135" s="5"/>
-      <c r="J135" s="5"/>
-      <c r="K135" s="5"/>
-      <c r="L135" s="5"/>
-      <c r="M135" s="5"/>
-      <c r="N135" s="5"/>
-      <c r="O135" s="5"/>
-      <c r="P135" s="5"/>
-      <c r="Q135" s="5"/>
-      <c r="R135" s="5"/>
-      <c r="S135" s="5"/>
-      <c r="T135" s="5"/>
-      <c r="U135" s="5"/>
-      <c r="V135" s="5"/>
-      <c r="W135" s="5"/>
-      <c r="X135" s="5"/>
-      <c r="Y135" s="5"/>
-      <c r="Z135" s="5"/>
-    </row>
-    <row r="136" spans="1:26" ht="13">
-      <c r="A136" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B136" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="C136" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D136" s="5"/>
-      <c r="E136" s="5"/>
-      <c r="F136" s="9"/>
-      <c r="G136" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="H136" s="5"/>
-      <c r="I136" s="5"/>
-      <c r="J136" s="5"/>
-      <c r="K136" s="5"/>
-      <c r="L136" s="5"/>
-      <c r="M136" s="5"/>
-      <c r="N136" s="5"/>
-      <c r="O136" s="5"/>
-      <c r="P136" s="5"/>
-      <c r="Q136" s="5"/>
-      <c r="R136" s="5"/>
-      <c r="S136" s="5"/>
-      <c r="T136" s="5"/>
-      <c r="U136" s="5"/>
-      <c r="V136" s="5"/>
-      <c r="W136" s="5"/>
-      <c r="X136" s="5"/>
-      <c r="Y136" s="5"/>
-      <c r="Z136" s="5"/>
-    </row>
-    <row r="137" spans="1:26" ht="13">
-      <c r="A137" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="B137" s="8" t="s">
-        <v>345</v>
-      </c>
-      <c r="C137" s="18" t="s">
-        <v>346</v>
-      </c>
-      <c r="D137" s="18" t="s">
-        <v>347</v>
-      </c>
-      <c r="E137" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="F137" s="9"/>
-      <c r="G137" s="8"/>
-      <c r="H137" s="5"/>
-      <c r="I137" s="5"/>
-      <c r="J137" s="5"/>
-      <c r="K137" s="5"/>
-      <c r="L137" s="5"/>
-      <c r="M137" s="5"/>
-      <c r="N137" s="5"/>
-      <c r="O137" s="5"/>
-      <c r="P137" s="5"/>
-      <c r="Q137" s="5"/>
-      <c r="R137" s="5"/>
-      <c r="S137" s="5"/>
-      <c r="T137" s="5"/>
-      <c r="U137" s="5"/>
-      <c r="V137" s="5"/>
-      <c r="W137" s="5"/>
-      <c r="X137" s="5"/>
-      <c r="Y137" s="5"/>
-      <c r="Z137" s="5"/>
-    </row>
-    <row r="138" spans="1:26" ht="13">
-      <c r="A138" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B138" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="C138" s="8"/>
-      <c r="D138" s="5"/>
-      <c r="E138" s="5"/>
-      <c r="F138" s="9"/>
-      <c r="G138" s="8"/>
-      <c r="H138" s="5"/>
-      <c r="I138" s="5"/>
-      <c r="J138" s="5"/>
-      <c r="K138" s="5"/>
-      <c r="L138" s="5"/>
-      <c r="M138" s="5"/>
-      <c r="N138" s="5"/>
-      <c r="O138" s="5"/>
-      <c r="P138" s="5"/>
-      <c r="Q138" s="5"/>
-      <c r="R138" s="5"/>
-      <c r="S138" s="5"/>
-      <c r="T138" s="5"/>
-      <c r="U138" s="5"/>
-      <c r="V138" s="5"/>
-      <c r="W138" s="5"/>
-      <c r="X138" s="5"/>
-      <c r="Y138" s="5"/>
-      <c r="Z138" s="5"/>
-    </row>
-    <row r="139" spans="1:26" ht="13">
-      <c r="A139" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B139" s="8" t="s">
-        <v>348</v>
-      </c>
-      <c r="C139" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D139" s="5"/>
-      <c r="E139" s="5"/>
-      <c r="F139" s="9"/>
-      <c r="G139" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="H139" s="5"/>
-      <c r="I139" s="5"/>
-      <c r="J139" s="5"/>
-      <c r="K139" s="5"/>
-      <c r="L139" s="5"/>
-      <c r="M139" s="5"/>
-      <c r="N139" s="5"/>
-      <c r="O139" s="5"/>
-      <c r="P139" s="5"/>
-      <c r="Q139" s="5"/>
-      <c r="R139" s="5"/>
-      <c r="S139" s="5"/>
-      <c r="T139" s="5"/>
-      <c r="U139" s="5"/>
-      <c r="V139" s="5"/>
-      <c r="W139" s="5"/>
-      <c r="X139" s="5"/>
-      <c r="Y139" s="5"/>
-      <c r="Z139" s="5"/>
-    </row>
-    <row r="140" spans="1:26" ht="13">
-      <c r="A140" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="B140" s="8" t="s">
-        <v>350</v>
-      </c>
-      <c r="C140" s="8" t="s">
-        <v>351</v>
-      </c>
-      <c r="D140" s="8" t="s">
-        <v>352</v>
-      </c>
-      <c r="E140" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="F140" s="9" t="s">
-        <v>353</v>
       </c>
       <c r="G140" s="8"/>
       <c r="H140" s="5"/>
@@ -5793,135 +5898,72 @@
       <c r="Y140" s="5"/>
       <c r="Z140" s="5"/>
     </row>
-    <row r="141" spans="1:26" ht="13">
-      <c r="A141" s="8" t="s">
+    <row r="141" spans="1:26" ht="14.25">
+      <c r="A141" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B141" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D141" s="28" t="s">
+        <v>260</v>
+      </c>
+      <c r="F141" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="G141" s="1"/>
+    </row>
+    <row r="142" spans="1:26" ht="14.25">
+      <c r="A142" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B141" s="8" t="s">
-        <v>348</v>
-      </c>
-      <c r="C141" s="8"/>
-      <c r="D141" s="5"/>
-      <c r="E141" s="5"/>
-      <c r="F141" s="9"/>
-      <c r="G141" s="8"/>
-      <c r="H141" s="5"/>
-      <c r="I141" s="5"/>
-      <c r="J141" s="5"/>
-      <c r="K141" s="5"/>
-      <c r="L141" s="5"/>
-      <c r="M141" s="5"/>
-      <c r="N141" s="5"/>
-      <c r="O141" s="5"/>
-      <c r="P141" s="5"/>
-      <c r="Q141" s="5"/>
-      <c r="R141" s="5"/>
-      <c r="S141" s="5"/>
-      <c r="T141" s="5"/>
-      <c r="U141" s="5"/>
-      <c r="V141" s="5"/>
-      <c r="W141" s="5"/>
-      <c r="X141" s="5"/>
-      <c r="Y141" s="5"/>
-      <c r="Z141" s="5"/>
-    </row>
-    <row r="142" spans="1:26" ht="13">
-      <c r="A142" s="8" t="s">
+      <c r="B142" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="C142" s="1"/>
+      <c r="F142" s="19"/>
+      <c r="G142" s="1"/>
+    </row>
+    <row r="143" spans="1:26" ht="14.25">
+      <c r="A143" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B142" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="C142" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D142" s="5"/>
-      <c r="E142" s="5"/>
-      <c r="F142" s="9"/>
-      <c r="G142" s="8" t="s">
+      <c r="B143" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D143" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="F143" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="G143" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="H142" s="5"/>
-      <c r="I142" s="5"/>
-      <c r="J142" s="5"/>
-      <c r="K142" s="5"/>
-      <c r="L142" s="5"/>
-      <c r="M142" s="5"/>
-      <c r="N142" s="5"/>
-      <c r="O142" s="5"/>
-      <c r="P142" s="5"/>
-      <c r="Q142" s="5"/>
-      <c r="R142" s="5"/>
-      <c r="S142" s="5"/>
-      <c r="T142" s="5"/>
-      <c r="U142" s="5"/>
-      <c r="V142" s="5"/>
-      <c r="W142" s="5"/>
-      <c r="X142" s="5"/>
-      <c r="Y142" s="5"/>
-      <c r="Z142" s="5"/>
-    </row>
-    <row r="143" spans="1:26" ht="13">
-      <c r="A143" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="B143" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="C143" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="D143" s="18" t="s">
-        <v>358</v>
-      </c>
-      <c r="E143" s="5"/>
-      <c r="F143" s="9" t="s">
-        <v>353</v>
-      </c>
-      <c r="G143" s="8"/>
-      <c r="H143" s="5"/>
-      <c r="I143" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="J143" s="11" t="s">
-        <v>360</v>
-      </c>
-      <c r="K143" s="15"/>
-      <c r="L143" s="5"/>
-      <c r="M143" s="5"/>
-      <c r="N143" s="5"/>
-      <c r="O143" s="5"/>
-      <c r="P143" s="5"/>
-      <c r="Q143" s="5"/>
-      <c r="R143" s="5"/>
-      <c r="S143" s="5"/>
-      <c r="T143" s="5"/>
-      <c r="U143" s="5"/>
-      <c r="V143" s="5"/>
-      <c r="W143" s="5"/>
-      <c r="X143" s="5"/>
-      <c r="Y143" s="5"/>
-      <c r="Z143" s="5"/>
     </row>
     <row r="144" spans="1:26" ht="13">
-      <c r="A144" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="B144" s="8" t="s">
-        <v>362</v>
-      </c>
-      <c r="C144" s="39" t="s">
-        <v>363</v>
-      </c>
-      <c r="D144" s="32" t="s">
-        <v>364</v>
-      </c>
-      <c r="E144" s="5" t="s">
+      <c r="A144" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D144" s="18" t="s">
+        <v>269</v>
+      </c>
+      <c r="E144" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="F144" s="9" t="s">
-        <v>353</v>
-      </c>
+      <c r="F144" s="4"/>
       <c r="G144" s="8"/>
       <c r="H144" s="5"/>
       <c r="I144" s="5"/>
@@ -5944,23 +5986,33 @@
       <c r="Z144" s="5"/>
     </row>
     <row r="145" spans="1:26" ht="13">
-      <c r="A145" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B145" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="C145" s="8"/>
-      <c r="D145" s="5"/>
-      <c r="E145" s="5"/>
-      <c r="F145" s="9"/>
+      <c r="A145" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="D145" s="32" t="s">
+        <v>273</v>
+      </c>
+      <c r="E145" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="F145" s="4" t="s">
+        <v>274</v>
+      </c>
       <c r="G145" s="8"/>
       <c r="H145" s="5"/>
       <c r="I145" s="5"/>
       <c r="J145" s="5"/>
       <c r="K145" s="5"/>
       <c r="L145" s="5"/>
-      <c r="M145" s="5"/>
+      <c r="M145" s="11" t="s">
+        <v>275</v>
+      </c>
       <c r="N145" s="5"/>
       <c r="O145" s="5"/>
       <c r="P145" s="5"/>
@@ -5976,19 +6028,19 @@
       <c r="Z145" s="5"/>
     </row>
     <row r="146" spans="1:26" ht="13">
-      <c r="A146" s="8" t="s">
+      <c r="A146" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B146" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="C146" s="8" t="s">
+      <c r="B146" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="C146" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D146" s="5"/>
-      <c r="E146" s="5"/>
-      <c r="F146" s="9"/>
-      <c r="G146" s="8" t="s">
+      <c r="E146" s="12"/>
+      <c r="F146" s="4"/>
+      <c r="G146" s="4" t="s">
         <v>99</v>
       </c>
       <c r="H146" s="5"/>
@@ -6011,24 +6063,24 @@
       <c r="Y146" s="5"/>
       <c r="Z146" s="5"/>
     </row>
-    <row r="147" spans="1:26" ht="13">
-      <c r="A147" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="B147" s="8" t="s">
-        <v>366</v>
-      </c>
-      <c r="C147" s="39" t="s">
-        <v>367</v>
+    <row r="147" spans="1:26" ht="15.75" customHeight="1">
+      <c r="A147" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="B147" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C147" s="4" t="s">
+        <v>279</v>
       </c>
       <c r="D147" s="18" t="s">
-        <v>368</v>
-      </c>
-      <c r="E147" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="F147" s="9" t="s">
-        <v>353</v>
+        <v>280</v>
+      </c>
+      <c r="E147" s="12" t="s">
+        <v>281</v>
+      </c>
+      <c r="F147" s="4" t="s">
+        <v>282</v>
       </c>
       <c r="G147" s="8"/>
       <c r="H147" s="5"/>
@@ -6036,7 +6088,9 @@
       <c r="J147" s="5"/>
       <c r="K147" s="5"/>
       <c r="L147" s="5"/>
-      <c r="M147" s="5"/>
+      <c r="M147" s="11" t="s">
+        <v>283</v>
+      </c>
       <c r="N147" s="5"/>
       <c r="O147" s="5"/>
       <c r="P147" s="5"/>
@@ -6052,31 +6106,29 @@
       <c r="Z147" s="5"/>
     </row>
     <row r="148" spans="1:26" ht="13">
-      <c r="A148" s="8" t="s">
-        <v>355</v>
-      </c>
-      <c r="B148" s="8" t="s">
-        <v>369</v>
-      </c>
-      <c r="C148" s="39" t="s">
-        <v>370</v>
-      </c>
-      <c r="D148" s="18" t="s">
-        <v>371</v>
-      </c>
-      <c r="E148" s="5"/>
-      <c r="F148" s="9" t="s">
-        <v>372</v>
-      </c>
-      <c r="G148" s="8"/>
-      <c r="H148" s="5"/>
-      <c r="I148" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="J148" s="11" t="s">
-        <v>374</v>
-      </c>
-      <c r="K148" s="15"/>
+      <c r="A148" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="B148" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="C148" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="D148" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="E148" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F148" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="G148" s="4"/>
+      <c r="H148" s="4"/>
+      <c r="I148" s="5"/>
+      <c r="J148" s="5"/>
+      <c r="K148" s="5"/>
       <c r="L148" s="5"/>
       <c r="M148" s="5"/>
       <c r="N148" s="5"/>
@@ -6094,18 +6146,18 @@
       <c r="Z148" s="5"/>
     </row>
     <row r="149" spans="1:26" ht="13">
-      <c r="A149" s="8" t="s">
+      <c r="A149" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B149" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="C149" s="8"/>
-      <c r="D149" s="5"/>
-      <c r="E149" s="5"/>
-      <c r="F149" s="8"/>
-      <c r="G149" s="8"/>
-      <c r="H149" s="5"/>
+      <c r="B149" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C149" s="4"/>
+      <c r="D149" s="4"/>
+      <c r="E149" s="4"/>
+      <c r="F149" s="4"/>
+      <c r="G149" s="4"/>
+      <c r="H149" s="4"/>
       <c r="I149" s="5"/>
       <c r="J149" s="5"/>
       <c r="K149" s="5"/>
@@ -6126,250 +6178,1360 @@
       <c r="Z149" s="5"/>
     </row>
     <row r="150" spans="1:26" ht="13">
-      <c r="A150" s="1" t="s">
+      <c r="A150" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B150" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="D150" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="E150" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F150" s="4"/>
+      <c r="G150" s="4"/>
+      <c r="H150" s="4"/>
+      <c r="I150" s="5"/>
+      <c r="J150" s="5"/>
+      <c r="K150" s="5"/>
+      <c r="L150" s="5"/>
+      <c r="M150" s="5"/>
+      <c r="N150" s="5"/>
+      <c r="O150" s="5"/>
+      <c r="P150" s="5"/>
+      <c r="Q150" s="5"/>
+      <c r="R150" s="5"/>
+      <c r="S150" s="5"/>
+      <c r="T150" s="5"/>
+      <c r="U150" s="5"/>
+      <c r="V150" s="5"/>
+      <c r="W150" s="5"/>
+      <c r="X150" s="5"/>
+      <c r="Y150" s="5"/>
+      <c r="Z150" s="5"/>
+    </row>
+    <row r="151" spans="1:26" ht="13">
+      <c r="A151" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="B151" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="C151" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="D151" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="E151" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F151" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="G151" s="4"/>
+      <c r="H151" s="4"/>
+      <c r="I151" s="5"/>
+      <c r="J151" s="5"/>
+      <c r="K151" s="5"/>
+      <c r="L151" s="5"/>
+      <c r="M151" s="5"/>
+      <c r="N151" s="5"/>
+      <c r="O151" s="5"/>
+      <c r="P151" s="5"/>
+      <c r="Q151" s="5"/>
+      <c r="R151" s="5"/>
+      <c r="S151" s="5"/>
+      <c r="T151" s="5"/>
+      <c r="U151" s="5"/>
+      <c r="V151" s="5"/>
+      <c r="W151" s="5"/>
+      <c r="X151" s="5"/>
+      <c r="Y151" s="5"/>
+      <c r="Z151" s="5"/>
+    </row>
+    <row r="152" spans="1:26" ht="13">
+      <c r="A152" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="B152" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="C152" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="D152" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="E152" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F152" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="G152" s="4"/>
+      <c r="H152" s="4"/>
+      <c r="I152" s="5"/>
+      <c r="J152" s="5"/>
+      <c r="K152" s="5"/>
+      <c r="L152" s="5"/>
+      <c r="M152" s="5"/>
+      <c r="N152" s="5"/>
+      <c r="O152" s="5"/>
+      <c r="P152" s="5"/>
+      <c r="Q152" s="5"/>
+      <c r="R152" s="5"/>
+      <c r="S152" s="5"/>
+      <c r="T152" s="5"/>
+      <c r="U152" s="5"/>
+      <c r="V152" s="5"/>
+      <c r="W152" s="5"/>
+      <c r="X152" s="5"/>
+      <c r="Y152" s="5"/>
+      <c r="Z152" s="5"/>
+    </row>
+    <row r="153" spans="1:26" ht="13">
+      <c r="A153" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="D153" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="E153" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F153" s="4"/>
+      <c r="G153" s="4"/>
+      <c r="H153" s="4"/>
+      <c r="I153" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="J153" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="K153" s="33" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="154" spans="1:26" ht="13">
+      <c r="A154" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D154" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="E154" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F154" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="G154" s="4"/>
+      <c r="H154" s="4"/>
+      <c r="I154" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="J154" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="K154" s="33" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="155" spans="1:26" ht="13">
+      <c r="A155" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B150" s="8" t="s">
+      <c r="B155" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C155" s="4"/>
+      <c r="D155" s="4"/>
+      <c r="E155" s="4"/>
+      <c r="F155" s="4"/>
+      <c r="G155" s="4"/>
+      <c r="H155" s="4"/>
+    </row>
+    <row r="156" spans="1:26" ht="13">
+      <c r="A156" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="D156" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="E156" s="4"/>
+      <c r="F156" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="G156" s="4"/>
+      <c r="H156" s="4"/>
+    </row>
+    <row r="157" spans="1:26" ht="13">
+      <c r="A157" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="D157" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="E157" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="F157" s="4"/>
+      <c r="G157" s="4"/>
+      <c r="H157" s="4"/>
+    </row>
+    <row r="158" spans="1:26" ht="13">
+      <c r="A158" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C158" s="4"/>
+      <c r="D158" s="4"/>
+      <c r="E158" s="4"/>
+      <c r="F158" s="4"/>
+      <c r="G158" s="4"/>
+      <c r="H158" s="4"/>
+    </row>
+    <row r="159" spans="1:26" ht="13">
+      <c r="A159" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B159" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="C150" s="1"/>
-      <c r="F150" s="19"/>
-      <c r="G150" s="1"/>
-    </row>
-    <row r="151" spans="1:26" ht="13">
-      <c r="A151" s="1" t="s">
+      <c r="C159" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="D159" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="E159" s="4"/>
+      <c r="F159" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="G159" s="4"/>
+      <c r="H159" s="4"/>
+    </row>
+    <row r="160" spans="1:26" ht="13">
+      <c r="A160" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="B160" s="34" t="s">
+        <v>325</v>
+      </c>
+      <c r="C160" s="35" t="s">
+        <v>326</v>
+      </c>
+      <c r="D160" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="E160" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="F160" s="9"/>
+      <c r="G160" s="8"/>
+      <c r="H160" s="5"/>
+      <c r="I160" s="5"/>
+      <c r="J160" s="5"/>
+      <c r="K160" s="5"/>
+      <c r="L160" s="5"/>
+      <c r="M160" s="5"/>
+      <c r="N160" s="5"/>
+      <c r="O160" s="5"/>
+      <c r="P160" s="5"/>
+      <c r="Q160" s="5"/>
+      <c r="R160" s="5"/>
+      <c r="S160" s="5"/>
+      <c r="T160" s="5"/>
+      <c r="U160" s="5"/>
+      <c r="V160" s="5"/>
+      <c r="W160" s="5"/>
+      <c r="X160" s="5"/>
+      <c r="Y160" s="5"/>
+      <c r="Z160" s="5"/>
+    </row>
+    <row r="161" spans="1:26" ht="13">
+      <c r="A161" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B151" s="40" t="s">
+      <c r="B161" s="34" t="s">
+        <v>328</v>
+      </c>
+      <c r="C161" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="D161" s="5"/>
+      <c r="E161" s="5"/>
+      <c r="F161" s="9"/>
+      <c r="G161" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="H161" s="5"/>
+      <c r="I161" s="5"/>
+      <c r="J161" s="5"/>
+      <c r="K161" s="5"/>
+      <c r="L161" s="5"/>
+      <c r="M161" s="5"/>
+      <c r="N161" s="5"/>
+      <c r="O161" s="5"/>
+      <c r="P161" s="5"/>
+      <c r="Q161" s="5"/>
+      <c r="R161" s="5"/>
+      <c r="S161" s="5"/>
+      <c r="T161" s="5"/>
+      <c r="U161" s="5"/>
+      <c r="V161" s="5"/>
+      <c r="W161" s="5"/>
+      <c r="X161" s="5"/>
+      <c r="Y161" s="5"/>
+      <c r="Z161" s="5"/>
+    </row>
+    <row r="162" spans="1:26" ht="13">
+      <c r="A162" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="B162" s="34" t="s">
+        <v>330</v>
+      </c>
+      <c r="C162" s="37" t="s">
+        <v>331</v>
+      </c>
+      <c r="D162" s="32" t="s">
+        <v>332</v>
+      </c>
+      <c r="E162" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F162" s="9"/>
+      <c r="G162" s="8"/>
+      <c r="H162" s="5"/>
+      <c r="I162" s="5"/>
+      <c r="J162" s="5"/>
+      <c r="K162" s="5"/>
+      <c r="L162" s="5"/>
+      <c r="M162" s="5"/>
+      <c r="N162" s="5"/>
+      <c r="O162" s="5"/>
+      <c r="P162" s="5"/>
+      <c r="Q162" s="5"/>
+      <c r="R162" s="5"/>
+      <c r="S162" s="5"/>
+      <c r="T162" s="5"/>
+      <c r="U162" s="5"/>
+      <c r="V162" s="5"/>
+      <c r="W162" s="5"/>
+      <c r="X162" s="5"/>
+      <c r="Y162" s="5"/>
+      <c r="Z162" s="5"/>
+    </row>
+    <row r="163" spans="1:26" ht="13">
+      <c r="A163" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="B163" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="C163" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="D163" s="32" t="s">
+        <v>334</v>
+      </c>
+      <c r="E163" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F163" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="G163" s="8"/>
+      <c r="H163" s="5"/>
+      <c r="I163" s="5"/>
+      <c r="J163" s="5"/>
+      <c r="K163" s="5"/>
+      <c r="L163" s="5"/>
+      <c r="M163" s="5"/>
+      <c r="N163" s="5"/>
+      <c r="O163" s="5"/>
+      <c r="P163" s="5"/>
+      <c r="Q163" s="5"/>
+      <c r="R163" s="5"/>
+      <c r="S163" s="5"/>
+      <c r="T163" s="5"/>
+      <c r="U163" s="5"/>
+      <c r="V163" s="5"/>
+      <c r="W163" s="5"/>
+      <c r="X163" s="5"/>
+      <c r="Y163" s="5"/>
+      <c r="Z163" s="5"/>
+    </row>
+    <row r="164" spans="1:26" ht="13">
+      <c r="A164" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B164" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="C164" s="38"/>
+      <c r="D164" s="5"/>
+      <c r="E164" s="5"/>
+      <c r="F164" s="9"/>
+      <c r="G164" s="8"/>
+      <c r="H164" s="5"/>
+      <c r="I164" s="5"/>
+      <c r="J164" s="5"/>
+      <c r="K164" s="5"/>
+      <c r="L164" s="5"/>
+      <c r="M164" s="5"/>
+      <c r="N164" s="5"/>
+      <c r="O164" s="5"/>
+      <c r="P164" s="5"/>
+      <c r="Q164" s="5"/>
+      <c r="R164" s="5"/>
+      <c r="S164" s="5"/>
+      <c r="T164" s="5"/>
+      <c r="U164" s="5"/>
+      <c r="V164" s="5"/>
+      <c r="W164" s="5"/>
+      <c r="X164" s="5"/>
+      <c r="Y164" s="5"/>
+      <c r="Z164" s="5"/>
+    </row>
+    <row r="165" spans="1:26" ht="13">
+      <c r="A165" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B165" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="C165" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="D165" s="5"/>
+      <c r="E165" s="5"/>
+      <c r="F165" s="9"/>
+      <c r="G165" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="H165" s="5"/>
+      <c r="I165" s="5"/>
+      <c r="J165" s="5"/>
+      <c r="K165" s="5"/>
+      <c r="L165" s="5"/>
+      <c r="M165" s="5"/>
+      <c r="N165" s="5"/>
+      <c r="O165" s="5"/>
+      <c r="P165" s="5"/>
+      <c r="Q165" s="5"/>
+      <c r="R165" s="5"/>
+      <c r="S165" s="5"/>
+      <c r="T165" s="5"/>
+      <c r="U165" s="5"/>
+      <c r="V165" s="5"/>
+      <c r="W165" s="5"/>
+      <c r="X165" s="5"/>
+      <c r="Y165" s="5"/>
+      <c r="Z165" s="5"/>
+    </row>
+    <row r="166" spans="1:26" ht="13">
+      <c r="A166" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="B166" s="34" t="s">
+        <v>338</v>
+      </c>
+      <c r="C166" s="37" t="s">
+        <v>339</v>
+      </c>
+      <c r="D166" s="32" t="s">
+        <v>340</v>
+      </c>
+      <c r="E166" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F166" s="9"/>
+      <c r="G166" s="8"/>
+      <c r="H166" s="5"/>
+      <c r="I166" s="5"/>
+      <c r="J166" s="5"/>
+      <c r="K166" s="5"/>
+      <c r="L166" s="5"/>
+      <c r="M166" s="5"/>
+      <c r="N166" s="5"/>
+      <c r="O166" s="5"/>
+      <c r="P166" s="5"/>
+      <c r="Q166" s="5"/>
+      <c r="R166" s="5"/>
+      <c r="S166" s="5"/>
+      <c r="T166" s="5"/>
+      <c r="U166" s="5"/>
+      <c r="V166" s="5"/>
+      <c r="W166" s="5"/>
+      <c r="X166" s="5"/>
+      <c r="Y166" s="5"/>
+      <c r="Z166" s="5"/>
+    </row>
+    <row r="167" spans="1:26" ht="13">
+      <c r="A167" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="B167" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="C167" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="D167" s="32" t="s">
+        <v>334</v>
+      </c>
+      <c r="E167" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F167" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="G167" s="8"/>
+      <c r="H167" s="5"/>
+      <c r="I167" s="5"/>
+      <c r="J167" s="5"/>
+      <c r="K167" s="5"/>
+      <c r="L167" s="5"/>
+      <c r="M167" s="5"/>
+      <c r="N167" s="5"/>
+      <c r="O167" s="5"/>
+      <c r="P167" s="5"/>
+      <c r="Q167" s="5"/>
+      <c r="R167" s="5"/>
+      <c r="S167" s="5"/>
+      <c r="T167" s="5"/>
+      <c r="U167" s="5"/>
+      <c r="V167" s="5"/>
+      <c r="W167" s="5"/>
+      <c r="X167" s="5"/>
+      <c r="Y167" s="5"/>
+      <c r="Z167" s="5"/>
+    </row>
+    <row r="168" spans="1:26" ht="13">
+      <c r="A168" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B168" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="C168" s="8"/>
+      <c r="D168" s="5"/>
+      <c r="E168" s="5"/>
+      <c r="F168" s="9"/>
+      <c r="G168" s="8"/>
+      <c r="H168" s="5"/>
+      <c r="I168" s="5"/>
+      <c r="J168" s="5"/>
+      <c r="K168" s="5"/>
+      <c r="L168" s="5"/>
+      <c r="M168" s="5"/>
+      <c r="N168" s="5"/>
+      <c r="O168" s="5"/>
+      <c r="P168" s="5"/>
+      <c r="Q168" s="5"/>
+      <c r="R168" s="5"/>
+      <c r="S168" s="5"/>
+      <c r="T168" s="5"/>
+      <c r="U168" s="5"/>
+      <c r="V168" s="5"/>
+      <c r="W168" s="5"/>
+      <c r="X168" s="5"/>
+      <c r="Y168" s="5"/>
+      <c r="Z168" s="5"/>
+    </row>
+    <row r="169" spans="1:26" ht="13">
+      <c r="A169" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B169" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="C169" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D169" s="5"/>
+      <c r="E169" s="5"/>
+      <c r="F169" s="9"/>
+      <c r="G169" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="H169" s="5"/>
+      <c r="I169" s="5"/>
+      <c r="J169" s="5"/>
+      <c r="K169" s="5"/>
+      <c r="L169" s="5"/>
+      <c r="M169" s="5"/>
+      <c r="N169" s="5"/>
+      <c r="O169" s="5"/>
+      <c r="P169" s="5"/>
+      <c r="Q169" s="5"/>
+      <c r="R169" s="5"/>
+      <c r="S169" s="5"/>
+      <c r="T169" s="5"/>
+      <c r="U169" s="5"/>
+      <c r="V169" s="5"/>
+      <c r="W169" s="5"/>
+      <c r="X169" s="5"/>
+      <c r="Y169" s="5"/>
+      <c r="Z169" s="5"/>
+    </row>
+    <row r="170" spans="1:26" ht="13">
+      <c r="A170" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="B170" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="C170" s="18" t="s">
+        <v>346</v>
+      </c>
+      <c r="D170" s="18" t="s">
+        <v>347</v>
+      </c>
+      <c r="E170" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F170" s="9"/>
+      <c r="G170" s="8"/>
+      <c r="H170" s="5"/>
+      <c r="I170" s="5"/>
+      <c r="J170" s="5"/>
+      <c r="K170" s="5"/>
+      <c r="L170" s="5"/>
+      <c r="M170" s="5"/>
+      <c r="N170" s="5"/>
+      <c r="O170" s="5"/>
+      <c r="P170" s="5"/>
+      <c r="Q170" s="5"/>
+      <c r="R170" s="5"/>
+      <c r="S170" s="5"/>
+      <c r="T170" s="5"/>
+      <c r="U170" s="5"/>
+      <c r="V170" s="5"/>
+      <c r="W170" s="5"/>
+      <c r="X170" s="5"/>
+      <c r="Y170" s="5"/>
+      <c r="Z170" s="5"/>
+    </row>
+    <row r="171" spans="1:26" ht="13">
+      <c r="A171" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B171" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="C171" s="8"/>
+      <c r="D171" s="5"/>
+      <c r="E171" s="5"/>
+      <c r="F171" s="9"/>
+      <c r="G171" s="8"/>
+      <c r="H171" s="5"/>
+      <c r="I171" s="5"/>
+      <c r="J171" s="5"/>
+      <c r="K171" s="5"/>
+      <c r="L171" s="5"/>
+      <c r="M171" s="5"/>
+      <c r="N171" s="5"/>
+      <c r="O171" s="5"/>
+      <c r="P171" s="5"/>
+      <c r="Q171" s="5"/>
+      <c r="R171" s="5"/>
+      <c r="S171" s="5"/>
+      <c r="T171" s="5"/>
+      <c r="U171" s="5"/>
+      <c r="V171" s="5"/>
+      <c r="W171" s="5"/>
+      <c r="X171" s="5"/>
+      <c r="Y171" s="5"/>
+      <c r="Z171" s="5"/>
+    </row>
+    <row r="172" spans="1:26" ht="13">
+      <c r="A172" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B172" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="C172" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D172" s="5"/>
+      <c r="E172" s="5"/>
+      <c r="F172" s="9"/>
+      <c r="G172" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="H172" s="5"/>
+      <c r="I172" s="5"/>
+      <c r="J172" s="5"/>
+      <c r="K172" s="5"/>
+      <c r="L172" s="5"/>
+      <c r="M172" s="5"/>
+      <c r="N172" s="5"/>
+      <c r="O172" s="5"/>
+      <c r="P172" s="5"/>
+      <c r="Q172" s="5"/>
+      <c r="R172" s="5"/>
+      <c r="S172" s="5"/>
+      <c r="T172" s="5"/>
+      <c r="U172" s="5"/>
+      <c r="V172" s="5"/>
+      <c r="W172" s="5"/>
+      <c r="X172" s="5"/>
+      <c r="Y172" s="5"/>
+      <c r="Z172" s="5"/>
+    </row>
+    <row r="173" spans="1:26" ht="13">
+      <c r="A173" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="B173" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="C173" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="D173" s="8" t="s">
+        <v>352</v>
+      </c>
+      <c r="E173" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F173" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="G173" s="8"/>
+      <c r="H173" s="5"/>
+      <c r="I173" s="5"/>
+      <c r="J173" s="5"/>
+      <c r="K173" s="5"/>
+      <c r="L173" s="5"/>
+      <c r="M173" s="5"/>
+      <c r="N173" s="5"/>
+      <c r="O173" s="5"/>
+      <c r="P173" s="5"/>
+      <c r="Q173" s="5"/>
+      <c r="R173" s="5"/>
+      <c r="S173" s="5"/>
+      <c r="T173" s="5"/>
+      <c r="U173" s="5"/>
+      <c r="V173" s="5"/>
+      <c r="W173" s="5"/>
+      <c r="X173" s="5"/>
+      <c r="Y173" s="5"/>
+      <c r="Z173" s="5"/>
+    </row>
+    <row r="174" spans="1:26" ht="13">
+      <c r="A174" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B174" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="C174" s="8"/>
+      <c r="D174" s="5"/>
+      <c r="E174" s="5"/>
+      <c r="F174" s="9"/>
+      <c r="G174" s="8"/>
+      <c r="H174" s="5"/>
+      <c r="I174" s="5"/>
+      <c r="J174" s="5"/>
+      <c r="K174" s="5"/>
+      <c r="L174" s="5"/>
+      <c r="M174" s="5"/>
+      <c r="N174" s="5"/>
+      <c r="O174" s="5"/>
+      <c r="P174" s="5"/>
+      <c r="Q174" s="5"/>
+      <c r="R174" s="5"/>
+      <c r="S174" s="5"/>
+      <c r="T174" s="5"/>
+      <c r="U174" s="5"/>
+      <c r="V174" s="5"/>
+      <c r="W174" s="5"/>
+      <c r="X174" s="5"/>
+      <c r="Y174" s="5"/>
+      <c r="Z174" s="5"/>
+    </row>
+    <row r="175" spans="1:26" ht="13">
+      <c r="A175" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B175" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="C175" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D175" s="5"/>
+      <c r="E175" s="5"/>
+      <c r="F175" s="9"/>
+      <c r="G175" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="H175" s="5"/>
+      <c r="I175" s="5"/>
+      <c r="J175" s="5"/>
+      <c r="K175" s="5"/>
+      <c r="L175" s="5"/>
+      <c r="M175" s="5"/>
+      <c r="N175" s="5"/>
+      <c r="O175" s="5"/>
+      <c r="P175" s="5"/>
+      <c r="Q175" s="5"/>
+      <c r="R175" s="5"/>
+      <c r="S175" s="5"/>
+      <c r="T175" s="5"/>
+      <c r="U175" s="5"/>
+      <c r="V175" s="5"/>
+      <c r="W175" s="5"/>
+      <c r="X175" s="5"/>
+      <c r="Y175" s="5"/>
+      <c r="Z175" s="5"/>
+    </row>
+    <row r="176" spans="1:26" ht="13">
+      <c r="A176" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="B176" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="C176" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="D176" s="18" t="s">
+        <v>358</v>
+      </c>
+      <c r="E176" s="5"/>
+      <c r="F176" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="G176" s="8"/>
+      <c r="H176" s="5"/>
+      <c r="I176" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="J176" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="K176" s="15"/>
+      <c r="L176" s="5"/>
+      <c r="M176" s="5"/>
+      <c r="N176" s="5"/>
+      <c r="O176" s="5"/>
+      <c r="P176" s="5"/>
+      <c r="Q176" s="5"/>
+      <c r="R176" s="5"/>
+      <c r="S176" s="5"/>
+      <c r="T176" s="5"/>
+      <c r="U176" s="5"/>
+      <c r="V176" s="5"/>
+      <c r="W176" s="5"/>
+      <c r="X176" s="5"/>
+      <c r="Y176" s="5"/>
+      <c r="Z176" s="5"/>
+    </row>
+    <row r="177" spans="1:26" ht="13">
+      <c r="A177" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="B177" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="C177" s="39" t="s">
+        <v>363</v>
+      </c>
+      <c r="D177" s="32" t="s">
+        <v>364</v>
+      </c>
+      <c r="E177" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F177" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="G177" s="8"/>
+      <c r="H177" s="5"/>
+      <c r="I177" s="5"/>
+      <c r="J177" s="5"/>
+      <c r="K177" s="5"/>
+      <c r="L177" s="5"/>
+      <c r="M177" s="5"/>
+      <c r="N177" s="5"/>
+      <c r="O177" s="5"/>
+      <c r="P177" s="5"/>
+      <c r="Q177" s="5"/>
+      <c r="R177" s="5"/>
+      <c r="S177" s="5"/>
+      <c r="T177" s="5"/>
+      <c r="U177" s="5"/>
+      <c r="V177" s="5"/>
+      <c r="W177" s="5"/>
+      <c r="X177" s="5"/>
+      <c r="Y177" s="5"/>
+      <c r="Z177" s="5"/>
+    </row>
+    <row r="178" spans="1:26" ht="13">
+      <c r="A178" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B178" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="C178" s="8"/>
+      <c r="D178" s="5"/>
+      <c r="E178" s="5"/>
+      <c r="F178" s="9"/>
+      <c r="G178" s="8"/>
+      <c r="H178" s="5"/>
+      <c r="I178" s="5"/>
+      <c r="J178" s="5"/>
+      <c r="K178" s="5"/>
+      <c r="L178" s="5"/>
+      <c r="M178" s="5"/>
+      <c r="N178" s="5"/>
+      <c r="O178" s="5"/>
+      <c r="P178" s="5"/>
+      <c r="Q178" s="5"/>
+      <c r="R178" s="5"/>
+      <c r="S178" s="5"/>
+      <c r="T178" s="5"/>
+      <c r="U178" s="5"/>
+      <c r="V178" s="5"/>
+      <c r="W178" s="5"/>
+      <c r="X178" s="5"/>
+      <c r="Y178" s="5"/>
+      <c r="Z178" s="5"/>
+    </row>
+    <row r="179" spans="1:26" ht="13">
+      <c r="A179" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B179" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="C179" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D179" s="5"/>
+      <c r="E179" s="5"/>
+      <c r="F179" s="9"/>
+      <c r="G179" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="H179" s="5"/>
+      <c r="I179" s="5"/>
+      <c r="J179" s="5"/>
+      <c r="K179" s="5"/>
+      <c r="L179" s="5"/>
+      <c r="M179" s="5"/>
+      <c r="N179" s="5"/>
+      <c r="O179" s="5"/>
+      <c r="P179" s="5"/>
+      <c r="Q179" s="5"/>
+      <c r="R179" s="5"/>
+      <c r="S179" s="5"/>
+      <c r="T179" s="5"/>
+      <c r="U179" s="5"/>
+      <c r="V179" s="5"/>
+      <c r="W179" s="5"/>
+      <c r="X179" s="5"/>
+      <c r="Y179" s="5"/>
+      <c r="Z179" s="5"/>
+    </row>
+    <row r="180" spans="1:26" ht="13">
+      <c r="A180" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="B180" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="C180" s="39" t="s">
+        <v>367</v>
+      </c>
+      <c r="D180" s="18" t="s">
+        <v>368</v>
+      </c>
+      <c r="E180" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F180" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="G180" s="8"/>
+      <c r="H180" s="5"/>
+      <c r="I180" s="5"/>
+      <c r="J180" s="5"/>
+      <c r="K180" s="5"/>
+      <c r="L180" s="5"/>
+      <c r="M180" s="5"/>
+      <c r="N180" s="5"/>
+      <c r="O180" s="5"/>
+      <c r="P180" s="5"/>
+      <c r="Q180" s="5"/>
+      <c r="R180" s="5"/>
+      <c r="S180" s="5"/>
+      <c r="T180" s="5"/>
+      <c r="U180" s="5"/>
+      <c r="V180" s="5"/>
+      <c r="W180" s="5"/>
+      <c r="X180" s="5"/>
+      <c r="Y180" s="5"/>
+      <c r="Z180" s="5"/>
+    </row>
+    <row r="181" spans="1:26" ht="13">
+      <c r="A181" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="B181" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="C181" s="39" t="s">
+        <v>370</v>
+      </c>
+      <c r="D181" s="18" t="s">
+        <v>371</v>
+      </c>
+      <c r="E181" s="5"/>
+      <c r="F181" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="G181" s="8"/>
+      <c r="H181" s="5"/>
+      <c r="I181" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="J181" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="K181" s="15"/>
+      <c r="L181" s="5"/>
+      <c r="M181" s="5"/>
+      <c r="N181" s="5"/>
+      <c r="O181" s="5"/>
+      <c r="P181" s="5"/>
+      <c r="Q181" s="5"/>
+      <c r="R181" s="5"/>
+      <c r="S181" s="5"/>
+      <c r="T181" s="5"/>
+      <c r="U181" s="5"/>
+      <c r="V181" s="5"/>
+      <c r="W181" s="5"/>
+      <c r="X181" s="5"/>
+      <c r="Y181" s="5"/>
+      <c r="Z181" s="5"/>
+    </row>
+    <row r="182" spans="1:26" ht="13">
+      <c r="A182" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B182" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="C182" s="8"/>
+      <c r="D182" s="5"/>
+      <c r="E182" s="5"/>
+      <c r="F182" s="8"/>
+      <c r="G182" s="8"/>
+      <c r="H182" s="5"/>
+      <c r="I182" s="5"/>
+      <c r="J182" s="5"/>
+      <c r="K182" s="5"/>
+      <c r="L182" s="5"/>
+      <c r="M182" s="5"/>
+      <c r="N182" s="5"/>
+      <c r="O182" s="5"/>
+      <c r="P182" s="5"/>
+      <c r="Q182" s="5"/>
+      <c r="R182" s="5"/>
+      <c r="S182" s="5"/>
+      <c r="T182" s="5"/>
+      <c r="U182" s="5"/>
+      <c r="V182" s="5"/>
+      <c r="W182" s="5"/>
+      <c r="X182" s="5"/>
+      <c r="Y182" s="5"/>
+      <c r="Z182" s="5"/>
+    </row>
+    <row r="183" spans="1:26" ht="13">
+      <c r="A183" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B183" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="C183" s="1"/>
+      <c r="F183" s="19"/>
+      <c r="G183" s="1"/>
+    </row>
+    <row r="184" spans="1:26" ht="13">
+      <c r="A184" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B184" s="40" t="s">
         <v>375</v>
       </c>
-      <c r="C151" s="18" t="s">
+      <c r="C184" s="18" t="s">
         <v>376</v>
       </c>
-      <c r="D151" s="18" t="s">
+      <c r="D184" s="18" t="s">
         <v>377</v>
       </c>
-      <c r="G151" s="1" t="s">
+      <c r="G184" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="152" spans="1:26" ht="13">
-      <c r="A152" s="1" t="s">
+    <row r="185" spans="1:26" ht="13">
+      <c r="A185" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B152" s="40" t="s">
+      <c r="B185" s="40" t="s">
         <v>378</v>
       </c>
-      <c r="C152" s="1" t="s">
+      <c r="C185" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="D152" s="1" t="s">
+      <c r="D185" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="G152" s="1"/>
-    </row>
-    <row r="153" spans="1:26" ht="13">
-      <c r="A153" s="1" t="s">
+      <c r="G185" s="1"/>
+    </row>
+    <row r="186" spans="1:26" ht="13">
+      <c r="A186" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B153" s="40" t="s">
+      <c r="B186" s="40" t="s">
         <v>375</v>
       </c>
-      <c r="C153" s="1"/>
-      <c r="D153" s="28"/>
-      <c r="G153" s="1"/>
-    </row>
-    <row r="154" spans="1:26" ht="13">
-      <c r="A154" s="1" t="s">
+      <c r="C186" s="1"/>
+      <c r="D186" s="28"/>
+      <c r="G186" s="1"/>
+    </row>
+    <row r="187" spans="1:26" ht="13">
+      <c r="A187" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B154" s="40" t="s">
+      <c r="B187" s="40" t="s">
         <v>381</v>
       </c>
-      <c r="C154" s="1" t="s">
+      <c r="C187" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="D154" s="28" t="s">
+      <c r="D187" s="28" t="s">
         <v>383</v>
       </c>
-      <c r="G154" s="1" t="s">
+      <c r="G187" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="155" spans="1:26" ht="13">
-      <c r="A155" s="1" t="s">
+    <row r="188" spans="1:26" ht="13">
+      <c r="A188" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B155" s="40" t="s">
+      <c r="B188" s="40" t="s">
         <v>384</v>
       </c>
-      <c r="C155" s="1" t="s">
+      <c r="C188" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="D155" s="28" t="s">
+      <c r="D188" s="28" t="s">
         <v>386</v>
       </c>
-      <c r="F155" s="1" t="s">
+      <c r="F188" s="1" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="156" spans="1:26" ht="13">
-      <c r="A156" s="1" t="s">
+    <row r="189" spans="1:26" ht="13">
+      <c r="A189" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B156" s="1" t="s">
+      <c r="B189" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C156" s="1" t="s">
+      <c r="C189" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="D156" s="28" t="s">
+      <c r="D189" s="28" t="s">
         <v>390</v>
       </c>
-      <c r="F156" s="1" t="s">
+      <c r="F189" s="1" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="157" spans="1:26" ht="13">
-      <c r="A157" s="1" t="s">
+    <row r="190" spans="1:26" ht="13">
+      <c r="A190" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B157" s="1" t="s">
+      <c r="B190" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="C157" s="1" t="s">
+      <c r="C190" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="D157" s="28" t="s">
+      <c r="D190" s="28" t="s">
         <v>394</v>
       </c>
-      <c r="F157" s="1" t="s">
+      <c r="F190" s="1" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="158" spans="1:26" ht="13">
-      <c r="A158" s="1" t="s">
+    <row r="191" spans="1:26" ht="13">
+      <c r="A191" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B158" s="1" t="s">
+      <c r="B191" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="C158" s="1" t="s">
+      <c r="C191" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D158" s="28" t="s">
+      <c r="D191" s="28" t="s">
         <v>398</v>
       </c>
-      <c r="F158" s="1" t="s">
+      <c r="F191" s="1" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="159" spans="1:26" ht="13">
-      <c r="A159" s="1" t="s">
+    <row r="192" spans="1:26" ht="13">
+      <c r="A192" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B159" s="1" t="s">
+      <c r="B192" s="1" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="160" spans="1:26" ht="14.25">
-      <c r="A160" s="1" t="s">
+    <row r="193" spans="1:12" ht="14.25">
+      <c r="A193" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B160" s="27" t="s">
+      <c r="B193" s="27" t="s">
         <v>400</v>
       </c>
-      <c r="L160" s="1" t="s">
+      <c r="L193" s="1" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="14.25">
-      <c r="A161" s="1" t="s">
+    <row r="194" spans="1:12" ht="14.25">
+      <c r="A194" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B161" s="27" t="s">
+      <c r="B194" s="27" t="s">
         <v>402</v>
       </c>
-      <c r="L161" s="1" t="s">
+      <c r="L194" s="1" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="162" spans="1:12" ht="14.25">
-      <c r="A162" s="1" t="s">
+    <row r="195" spans="1:12" ht="14.25">
+      <c r="A195" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B162" s="27" t="s">
+      <c r="B195" s="27" t="s">
         <v>404</v>
       </c>
-      <c r="L162" s="1" t="s">
+      <c r="L195" s="1" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="14.25">
-      <c r="C165" s="27"/>
-    </row>
-    <row r="166" spans="1:12" ht="14.25">
-      <c r="B166" s="41"/>
-      <c r="C166" s="27"/>
-    </row>
-    <row r="168" spans="1:12" ht="14.25">
-      <c r="B168" s="41"/>
-    </row>
-    <row r="169" spans="1:12" ht="13">
-      <c r="B169" s="40"/>
-    </row>
-    <row r="170" spans="1:12" ht="14.25">
-      <c r="B170" s="41"/>
-    </row>
-    <row r="171" spans="1:12" ht="14.25">
-      <c r="B171" s="41"/>
-    </row>
-    <row r="172" spans="1:12" ht="13">
-      <c r="B172" s="40"/>
-    </row>
-    <row r="173" spans="1:12" ht="14.25">
-      <c r="B173" s="41"/>
-    </row>
-    <row r="174" spans="1:12" ht="13">
-      <c r="B174" s="40"/>
-    </row>
-    <row r="175" spans="1:12" ht="14.25">
-      <c r="B175" s="41"/>
-    </row>
-    <row r="176" spans="1:12" ht="13">
-      <c r="B176" s="40"/>
-    </row>
-    <row r="177" spans="2:3" ht="14.25">
-      <c r="B177" s="41"/>
-    </row>
-    <row r="178" spans="2:3" ht="13">
-      <c r="B178" s="40"/>
-    </row>
-    <row r="180" spans="2:3" ht="14.25">
-      <c r="C180" s="41"/>
-    </row>
-    <row r="181" spans="2:3" ht="13">
-      <c r="B181" s="40"/>
-    </row>
-    <row r="182" spans="2:3" ht="13">
-      <c r="B182" s="40"/>
-    </row>
-    <row r="184" spans="2:3" ht="14.25">
-      <c r="B184" s="27"/>
-    </row>
-    <row r="185" spans="2:3" ht="14.25">
-      <c r="B185" s="41"/>
+    <row r="198" spans="1:12" ht="14.25">
+      <c r="C198" s="27"/>
+    </row>
+    <row r="199" spans="1:12" ht="14.25">
+      <c r="B199" s="41"/>
+      <c r="C199" s="27"/>
+    </row>
+    <row r="201" spans="1:12" ht="14.25">
+      <c r="B201" s="41"/>
+    </row>
+    <row r="202" spans="1:12" ht="13">
+      <c r="B202" s="40"/>
+    </row>
+    <row r="203" spans="1:12" ht="14.25">
+      <c r="B203" s="41"/>
+    </row>
+    <row r="204" spans="1:12" ht="14.25">
+      <c r="B204" s="41"/>
+    </row>
+    <row r="205" spans="1:12" ht="13">
+      <c r="B205" s="40"/>
+    </row>
+    <row r="206" spans="1:12" ht="14.25">
+      <c r="B206" s="41"/>
+    </row>
+    <row r="207" spans="1:12" ht="13">
+      <c r="B207" s="40"/>
+    </row>
+    <row r="208" spans="1:12" ht="14.25">
+      <c r="B208" s="41"/>
+    </row>
+    <row r="209" spans="2:3" ht="13">
+      <c r="B209" s="40"/>
+    </row>
+    <row r="210" spans="2:3" ht="14.25">
+      <c r="B210" s="41"/>
+    </row>
+    <row r="211" spans="2:3" ht="13">
+      <c r="B211" s="40"/>
+    </row>
+    <row r="213" spans="2:3" ht="14.25">
+      <c r="C213" s="41"/>
+    </row>
+    <row r="214" spans="2:3" ht="13">
+      <c r="B214" s="40"/>
+    </row>
+    <row r="215" spans="2:3" ht="13">
+      <c r="B215" s="40"/>
+    </row>
+    <row r="217" spans="2:3" ht="14.25">
+      <c r="B217" s="27"/>
+    </row>
+    <row r="218" spans="2:3" ht="14.25">
+      <c r="B218" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="L30:Q30"/>
+    <mergeCell ref="L31:Q31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -12040,23 +13202,47 @@
       <c r="Y164" s="5"/>
       <c r="Z164" s="5"/>
     </row>
-    <row r="165" spans="1:26" ht="13">
-      <c r="A165" s="5"/>
-      <c r="B165" s="5"/>
-      <c r="C165" s="5"/>
-      <c r="D165" s="5"/>
-    </row>
-    <row r="166" spans="1:26" ht="13">
-      <c r="A166" s="5"/>
-      <c r="B166" s="5"/>
-      <c r="C166" s="5"/>
-      <c r="D166" s="5"/>
-    </row>
-    <row r="167" spans="1:26" ht="13">
-      <c r="A167" s="5"/>
-      <c r="B167" s="5"/>
-      <c r="C167" s="5"/>
-      <c r="D167" s="5"/>
+    <row r="165" spans="1:26" s="50" customFormat="1" ht="13">
+      <c r="A165" s="52" t="s">
+        <v>768</v>
+      </c>
+      <c r="B165" s="52" t="s">
+        <v>769</v>
+      </c>
+      <c r="C165" s="52" t="s">
+        <v>770</v>
+      </c>
+      <c r="D165" s="52" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="166" spans="1:26" s="50" customFormat="1" ht="13">
+      <c r="A166" s="52" t="s">
+        <v>768</v>
+      </c>
+      <c r="B166" s="52" t="s">
+        <v>772</v>
+      </c>
+      <c r="C166" s="52" t="s">
+        <v>773</v>
+      </c>
+      <c r="D166" s="52" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="167" spans="1:26" s="50" customFormat="1" ht="13">
+      <c r="A167" s="52" t="s">
+        <v>768</v>
+      </c>
+      <c r="B167" s="52" t="s">
+        <v>775</v>
+      </c>
+      <c r="C167" s="52" t="s">
+        <v>776</v>
+      </c>
+      <c r="D167" s="52" t="s">
+        <v>777</v>
+      </c>
     </row>
     <row r="168" spans="1:26" ht="13">
       <c r="A168" s="5"/>
@@ -12100,7 +13286,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>

--- a/forms/app/postpartum.xlsx
+++ b/forms/app/postpartum.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20374"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20382"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D-tree\config-dtree-newrepo\config-dtree\forms\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E740E93-4250-4D32-BDEE-F7DA658BF6CD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{622B7188-E00A-4791-B83D-32FF6B8D0809}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6325" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1455" uniqueCount="788">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1483" uniqueCount="807">
   <si>
     <t>type</t>
   </si>
@@ -1319,9 +1319,6 @@
     <t>To address a postpartum danger sign</t>
   </si>
   <si>
-    <t>Kushughulikia dalili za hatari baada ya kujifungua.</t>
-  </si>
-  <si>
     <t>${refer_postpartum_other_danger_sign_flag}=1</t>
   </si>
   <si>
@@ -1338,9 +1335,6 @@
   </si>
   <si>
     <t>has_referral</t>
-  </si>
-  <si>
-    <t>if(${refer_postpartum_emergency_danger_sign_flag}=1 or ${refer_postpartum_other_danger_sign_flag}=1,1,0)</t>
   </si>
   <si>
     <t>list_name</t>
@@ -2554,6 +2548,69 @@
 Msikilize/wasikilize wana familia na kisha tumia kitini rejea uwafahamishe zaidi juu kuhusu
      • Kuelewa maana ya usafi wa mazingira,  umuhimu wa usafi wa mazingira na  jinsi ya kuweka mazingira safi
     </t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>facility_pnc_date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When did you visit? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ulienda lini? </t>
+  </si>
+  <si>
+    <t>delivery_date</t>
+  </si>
+  <si>
+    <t>delivery_date_c</t>
+  </si>
+  <si>
+    <t>../inputs/delivery_date</t>
+  </si>
+  <si>
+    <t>. &gt;= date-time(decimal-date-time(${delivery_date_c})) and . &lt;= date-time(decimal-date-time(today()))</t>
+  </si>
+  <si>
+    <t>Date should be between delivery date and today</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarehe iwe baina ya tarehe ya kujifungulia na leo </t>
+  </si>
+  <si>
+    <t>has_attended_facility_pnc_within_48hrs</t>
+  </si>
+  <si>
+    <t>Have you gone to the healthcare facility within 48 hours after your delivery for a postnatal care visit?</t>
+  </si>
+  <si>
+    <t>Je ulishawahi kuhudhuria kliniki ndani ya msaa 48 kwa ajili ya uchunguzi baada ya kujifungua?</t>
+  </si>
+  <si>
+    <t>selected(${has_attended_facility_pnc},"yes") and selected(${has_attended_facility_pnc_within_48hrs},"no")</t>
+  </si>
+  <si>
+    <t>needs_referral_pnc_visit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To attend clinic for healthcare facility for PNC visit </t>
+  </si>
+  <si>
+    <t>refer_postpartum_pnc_visit</t>
+  </si>
+  <si>
+    <t>if(${refer_postpartum_emergency_danger_sign_flag}=1 or ${refer_postpartum_other_danger_sign_flag}=1 or ${refer_postpartum_pnc_visit}=1,1,0)</t>
+  </si>
+  <si>
+    <t>Kuhudhuria kituo cha afya kwaajili ya uchunguzi baada ya kujifungua</t>
+  </si>
+  <si>
+    <t>if(selected(${has_attended_facility_pnc},"no"),1,0)</t>
+  </si>
+  <si>
+    <t>Kushughulikia dalili za hatari baada ya kujifungua</t>
   </si>
 </sst>
 </file>
@@ -2732,7 +2789,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -2802,7 +2859,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2815,6 +2871,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3098,7 +3157,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Z218"/>
+  <dimension ref="A1:Z224"/>
   <sheetFormatPr defaultColWidth="14.40625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="19.86328125" customWidth="1"/>
@@ -3160,16 +3219,16 @@
         <v>16</v>
       </c>
       <c r="R1" s="54" t="s">
+        <v>776</v>
+      </c>
+      <c r="S1" s="54" t="s">
+        <v>777</v>
+      </c>
+      <c r="T1" s="51" t="s">
         <v>778</v>
       </c>
-      <c r="S1" s="54" t="s">
+      <c r="U1" s="51" t="s">
         <v>779</v>
-      </c>
-      <c r="T1" s="51" t="s">
-        <v>780</v>
-      </c>
-      <c r="U1" s="51" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="2" spans="1:26" ht="13">
@@ -3231,107 +3290,107 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="13">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:26" s="55" customFormat="1" ht="13">
+      <c r="A7" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>790</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" ht="13">
+      <c r="A8" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="5"/>
-      <c r="S7" s="5"/>
-      <c r="T7" s="5"/>
-      <c r="U7" s="5"/>
-      <c r="V7" s="5"/>
-      <c r="W7" s="5"/>
-      <c r="X7" s="5"/>
-      <c r="Y7" s="5"/>
-      <c r="Z7" s="5"/>
-    </row>
-    <row r="8" spans="1:26" ht="13">
-      <c r="A8" s="1" t="s">
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="5"/>
+      <c r="R8" s="5"/>
+      <c r="S8" s="5"/>
+      <c r="T8" s="5"/>
+      <c r="U8" s="5"/>
+      <c r="V8" s="5"/>
+      <c r="W8" s="5"/>
+      <c r="X8" s="5"/>
+      <c r="Y8" s="5"/>
+      <c r="Z8" s="5"/>
+    </row>
+    <row r="9" spans="1:26" ht="13">
+      <c r="A9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:26" s="50" customFormat="1" ht="13">
-      <c r="A9" s="51" t="s">
+    <row r="10" spans="1:26" s="50" customFormat="1" ht="13">
+      <c r="A10" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="51" t="s">
-        <v>764</v>
-      </c>
-      <c r="C9" s="51" t="s">
+      <c r="B10" s="51" t="s">
+        <v>762</v>
+      </c>
+      <c r="C10" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="51"/>
-      <c r="K9" s="51"/>
-      <c r="L9" s="51"/>
-      <c r="M9" s="51"/>
-      <c r="N9" s="51"/>
-      <c r="O9" s="51"/>
-      <c r="P9" s="51"/>
-      <c r="Q9" s="51"/>
-    </row>
-    <row r="10" spans="1:26" ht="13">
-      <c r="A10" s="1" t="s">
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
+      <c r="K10" s="51"/>
+      <c r="L10" s="51"/>
+      <c r="M10" s="51"/>
+      <c r="N10" s="51"/>
+      <c r="O10" s="51"/>
+      <c r="P10" s="51"/>
+      <c r="Q10" s="51"/>
+    </row>
+    <row r="11" spans="1:26" ht="13">
+      <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="13">
-      <c r="A11" s="6" t="s">
+    <row r="12" spans="1:26" ht="13">
+      <c r="A12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B12" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C12" s="7" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" ht="13">
-      <c r="A12" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="13">
@@ -3339,38 +3398,38 @@
         <v>22</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="13">
       <c r="A14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="13">
+      <c r="A15" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B15" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="7"/>
-    </row>
-    <row r="15" spans="1:26" ht="13">
-      <c r="A15" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>19</v>
-      </c>
+      <c r="C15" s="7"/>
     </row>
     <row r="16" spans="1:26" ht="13">
       <c r="A16" s="8" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>19</v>
@@ -3378,84 +3437,61 @@
     </row>
     <row r="17" spans="1:26" ht="13">
       <c r="A17" s="8" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:26" ht="13">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" ht="13">
+      <c r="A19" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C19" s="10" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:26" ht="13">
-      <c r="A19" s="8" t="s">
+    <row r="20" spans="1:26" ht="13">
+      <c r="A20" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B20" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="5"/>
-    </row>
-    <row r="20" spans="1:26" ht="13">
-      <c r="A20" s="7" t="s">
+      <c r="C20" s="5"/>
+    </row>
+    <row r="21" spans="1:26" ht="13">
+      <c r="A21" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B21" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:26" ht="13">
-      <c r="A21" s="8" t="s">
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:26" ht="13">
+      <c r="A22" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B22" s="8" t="s">
         <v>40</v>
-      </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="M21" s="5"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
-      <c r="R21" s="5"/>
-      <c r="S21" s="5"/>
-      <c r="T21" s="5"/>
-      <c r="U21" s="5"/>
-      <c r="V21" s="5"/>
-      <c r="W21" s="5"/>
-      <c r="X21" s="5"/>
-      <c r="Y21" s="5"/>
-      <c r="Z21" s="5"/>
-    </row>
-    <row r="22" spans="1:26" ht="13">
-      <c r="A22" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>42</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="5"/>
@@ -3467,34 +3503,41 @@
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
       <c r="L22" s="11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
       <c r="O22" s="5"/>
       <c r="P22" s="5"/>
       <c r="Q22" s="5"/>
+      <c r="R22" s="5"/>
+      <c r="S22" s="5"/>
+      <c r="T22" s="5"/>
+      <c r="U22" s="5"/>
+      <c r="V22" s="5"/>
+      <c r="W22" s="5"/>
+      <c r="X22" s="5"/>
+      <c r="Y22" s="5"/>
+      <c r="Z22" s="5"/>
     </row>
     <row r="23" spans="1:26" ht="13">
       <c r="A23" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>44</v>
+      <c r="B23" s="8" t="s">
+        <v>42</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
-      <c r="G23" s="5" t="s">
-        <v>45</v>
-      </c>
+      <c r="G23" s="5"/>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
       <c r="L23" s="11" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M23" s="5"/>
       <c r="N23" s="5"/>
@@ -3506,8 +3549,8 @@
       <c r="A24" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>47</v>
+      <c r="B24" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
@@ -3521,7 +3564,7 @@
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
       <c r="L24" s="11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
@@ -3534,7 +3577,7 @@
         <v>39</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
@@ -3548,7 +3591,7 @@
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
       <c r="L25" s="11" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M25" s="5"/>
       <c r="N25" s="5"/>
@@ -3560,20 +3603,22 @@
       <c r="A26" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="12"/>
+      <c r="B26" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" s="5"/>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
+      <c r="G26" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
-      <c r="L26" s="13" t="s">
-        <v>52</v>
+      <c r="L26" s="11" t="s">
+        <v>50</v>
       </c>
       <c r="M26" s="5"/>
       <c r="N26" s="5"/>
@@ -3585,8 +3630,8 @@
       <c r="A27" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>53</v>
+      <c r="B27" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="C27" s="12"/>
       <c r="D27" s="5"/>
@@ -3597,8 +3642,8 @@
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
-      <c r="L27" s="11" t="s">
-        <v>54</v>
+      <c r="L27" s="13" t="s">
+        <v>52</v>
       </c>
       <c r="M27" s="5"/>
       <c r="N27" s="5"/>
@@ -3610,10 +3655,10 @@
       <c r="A28" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" s="5"/>
+      <c r="B28" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="12"/>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
@@ -3622,46 +3667,46 @@
       <c r="I28" s="5"/>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
-      <c r="L28" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="M28" s="15"/>
-      <c r="N28" s="15"/>
+      <c r="L28" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
       <c r="O28" s="5"/>
       <c r="P28" s="5"/>
       <c r="Q28" s="5"/>
     </row>
-    <row r="29" spans="1:26" ht="13">
-      <c r="A29" s="1" t="s">
+    <row r="29" spans="1:26" s="55" customFormat="1" ht="13">
+      <c r="A29" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
-      <c r="L29" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="M29" s="15"/>
-      <c r="N29" s="15"/>
-      <c r="O29" s="5"/>
-      <c r="P29" s="5"/>
-      <c r="Q29" s="5"/>
+      <c r="B29" s="12" t="s">
+        <v>791</v>
+      </c>
+      <c r="C29" s="12"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="40"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="40"/>
+      <c r="K29" s="40"/>
+      <c r="L29" s="58" t="s">
+        <v>792</v>
+      </c>
+      <c r="M29" s="40"/>
+      <c r="N29" s="40"/>
+      <c r="O29" s="40"/>
+      <c r="P29" s="40"/>
+      <c r="Q29" s="40"/>
     </row>
     <row r="30" spans="1:26" ht="13">
       <c r="A30" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="9" t="s">
-        <v>59</v>
+      <c r="B30" s="8" t="s">
+        <v>55</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
@@ -3672,11 +3717,11 @@
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
       <c r="K30" s="5"/>
-      <c r="L30" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="M30" s="5"/>
-      <c r="N30" s="5"/>
+      <c r="L30" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="M30" s="15"/>
+      <c r="N30" s="15"/>
       <c r="O30" s="5"/>
       <c r="P30" s="5"/>
       <c r="Q30" s="5"/>
@@ -3686,7 +3731,7 @@
         <v>39</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
@@ -3697,21 +3742,21 @@
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
-      <c r="L31" s="55" t="s">
-        <v>62</v>
-      </c>
-      <c r="M31" s="56"/>
-      <c r="N31" s="56"/>
-      <c r="O31" s="56"/>
-      <c r="P31" s="56"/>
-      <c r="Q31" s="56"/>
+      <c r="L31" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M31" s="15"/>
+      <c r="N31" s="15"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="5"/>
     </row>
     <row r="32" spans="1:26" ht="13">
       <c r="A32" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -3723,10 +3768,10 @@
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
       <c r="L32" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="M32" s="15"/>
-      <c r="N32" s="15"/>
+        <v>60</v>
+      </c>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
       <c r="O32" s="5"/>
       <c r="P32" s="5"/>
       <c r="Q32" s="5"/>
@@ -3735,8 +3780,8 @@
       <c r="A33" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="8" t="s">
-        <v>65</v>
+      <c r="B33" s="9" t="s">
+        <v>61</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
@@ -3747,21 +3792,21 @@
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
-      <c r="L33" s="16">
-        <v>7</v>
-      </c>
-      <c r="M33" s="5"/>
-      <c r="N33" s="5"/>
-      <c r="O33" s="5"/>
-      <c r="P33" s="5"/>
-      <c r="Q33" s="5"/>
+      <c r="L33" s="62" t="s">
+        <v>62</v>
+      </c>
+      <c r="M33" s="63"/>
+      <c r="N33" s="63"/>
+      <c r="O33" s="63"/>
+      <c r="P33" s="63"/>
+      <c r="Q33" s="63"/>
     </row>
     <row r="34" spans="1:26" ht="13">
       <c r="A34" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="8" t="s">
-        <v>66</v>
+      <c r="B34" s="9" t="s">
+        <v>63</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
@@ -3772,11 +3817,11 @@
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
-      <c r="L34" s="16">
-        <v>30</v>
-      </c>
-      <c r="M34" s="5"/>
-      <c r="N34" s="5"/>
+      <c r="L34" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="M34" s="15"/>
+      <c r="N34" s="15"/>
       <c r="O34" s="5"/>
       <c r="P34" s="5"/>
       <c r="Q34" s="5"/>
@@ -3785,8 +3830,8 @@
       <c r="A35" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>67</v>
+      <c r="B35" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
@@ -3797,11 +3842,11 @@
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
-      <c r="L35" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="M35" s="15"/>
-      <c r="N35" s="15"/>
+      <c r="L35" s="16">
+        <v>7</v>
+      </c>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
       <c r="O35" s="5"/>
       <c r="P35" s="5"/>
       <c r="Q35" s="5"/>
@@ -3810,8 +3855,8 @@
       <c r="A36" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>69</v>
+      <c r="B36" s="8" t="s">
+        <v>66</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
@@ -3822,11 +3867,11 @@
       <c r="I36" s="5"/>
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
-      <c r="L36" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="M36" s="15"/>
-      <c r="N36" s="15"/>
+      <c r="L36" s="16">
+        <v>30</v>
+      </c>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
       <c r="O36" s="5"/>
       <c r="P36" s="5"/>
       <c r="Q36" s="5"/>
@@ -3836,7 +3881,7 @@
         <v>39</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
@@ -3848,10 +3893,10 @@
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
       <c r="L37" s="17" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="M37" s="15"/>
-      <c r="N37" s="5"/>
+      <c r="N37" s="15"/>
       <c r="O37" s="5"/>
       <c r="P37" s="5"/>
       <c r="Q37" s="5"/>
@@ -3861,7 +3906,7 @@
         <v>39</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
@@ -3873,10 +3918,10 @@
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
       <c r="L38" s="17" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="M38" s="15"/>
-      <c r="N38" s="5"/>
+      <c r="N38" s="15"/>
       <c r="O38" s="5"/>
       <c r="P38" s="5"/>
       <c r="Q38" s="5"/>
@@ -3885,8 +3930,8 @@
       <c r="A39" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B39" s="18" t="s">
-        <v>24</v>
+      <c r="B39" s="4" t="s">
+        <v>71</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
@@ -3897,8 +3942,8 @@
       <c r="I39" s="5"/>
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
-      <c r="L39" s="13" t="s">
-        <v>75</v>
+      <c r="L39" s="17" t="s">
+        <v>72</v>
       </c>
       <c r="M39" s="15"/>
       <c r="N39" s="5"/>
@@ -3910,8 +3955,8 @@
       <c r="A40" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="8" t="s">
-        <v>76</v>
+      <c r="B40" s="4" t="s">
+        <v>73</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
@@ -3922,8 +3967,8 @@
       <c r="I40" s="5"/>
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
-      <c r="L40" s="11" t="s">
-        <v>77</v>
+      <c r="L40" s="17" t="s">
+        <v>74</v>
       </c>
       <c r="M40" s="15"/>
       <c r="N40" s="5"/>
@@ -3932,181 +3977,163 @@
       <c r="Q40" s="5"/>
     </row>
     <row r="41" spans="1:26" ht="13">
-      <c r="A41" s="18" t="s">
+      <c r="A41" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B41" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="M41" s="15"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="5"/>
+      <c r="Q41" s="5"/>
+    </row>
+    <row r="42" spans="1:26" ht="13">
+      <c r="A42" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5"/>
+      <c r="K42" s="5"/>
+      <c r="L42" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="M42" s="15"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="5"/>
+      <c r="P42" s="5"/>
+      <c r="Q42" s="5"/>
+    </row>
+    <row r="43" spans="1:26" ht="13">
+      <c r="A43" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B43" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="C41" s="5"/>
-      <c r="G41" s="1"/>
-      <c r="L41" s="19" t="s">
+      <c r="C43" s="5"/>
+      <c r="G43" s="1"/>
+      <c r="L43" s="19" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="42" spans="1:26" ht="13">
-      <c r="A42" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="B42" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="C42" s="5"/>
-      <c r="G42" s="1"/>
-      <c r="L42" s="19" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="43" spans="1:26" ht="13">
-      <c r="A43" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C43" s="5"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="20"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="5"/>
-      <c r="I43" s="5"/>
-      <c r="J43" s="5"/>
-      <c r="K43" s="5"/>
-      <c r="L43" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="M43" s="15"/>
-      <c r="N43" s="15"/>
-      <c r="O43" s="5"/>
-      <c r="P43" s="5"/>
-      <c r="Q43" s="5"/>
-      <c r="R43" s="5"/>
-      <c r="S43" s="5"/>
-      <c r="T43" s="5"/>
-      <c r="U43" s="5"/>
-      <c r="V43" s="5"/>
-      <c r="W43" s="5"/>
-      <c r="X43" s="5"/>
-      <c r="Y43" s="5"/>
-      <c r="Z43" s="5"/>
     </row>
     <row r="44" spans="1:26" ht="13">
       <c r="A44" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>83</v>
+      <c r="B44" s="18" t="s">
+        <v>80</v>
       </c>
       <c r="C44" s="5"/>
-      <c r="D44" s="21"/>
       <c r="G44" s="1"/>
       <c r="L44" s="19" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="45" spans="1:26" ht="13">
+      <c r="A45" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C45" s="5"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="M45" s="15"/>
+      <c r="N45" s="15"/>
+      <c r="O45" s="5"/>
+      <c r="P45" s="5"/>
+      <c r="Q45" s="5"/>
+      <c r="R45" s="5"/>
+      <c r="S45" s="5"/>
+      <c r="T45" s="5"/>
+      <c r="U45" s="5"/>
+      <c r="V45" s="5"/>
+      <c r="W45" s="5"/>
+      <c r="X45" s="5"/>
+      <c r="Y45" s="5"/>
+      <c r="Z45" s="5"/>
+    </row>
+    <row r="46" spans="1:26" ht="13">
+      <c r="A46" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C46" s="5"/>
+      <c r="D46" s="21"/>
+      <c r="G46" s="1"/>
+      <c r="L46" s="19" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="45" spans="1:26" s="50" customFormat="1" ht="13">
-      <c r="A45" s="51" t="s">
+    <row r="47" spans="1:26" s="50" customFormat="1" ht="13">
+      <c r="A47" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="B45" s="51" t="s">
-        <v>765</v>
-      </c>
-      <c r="C45" s="51"/>
-      <c r="D45" s="51"/>
-      <c r="E45" s="51"/>
-      <c r="F45" s="51"/>
-      <c r="G45" s="51"/>
-      <c r="H45" s="51"/>
-      <c r="I45" s="51"/>
-      <c r="J45" s="51"/>
-      <c r="K45" s="51"/>
-      <c r="L45" s="53" t="s">
-        <v>766</v>
-      </c>
-      <c r="M45" s="51"/>
-      <c r="N45" s="51"/>
-      <c r="O45" s="51"/>
-      <c r="P45" s="51"/>
-      <c r="Q45" s="51"/>
-    </row>
-    <row r="46" spans="1:26" ht="13">
-      <c r="A46" s="4" t="s">
+      <c r="B47" s="51" t="s">
+        <v>763</v>
+      </c>
+      <c r="C47" s="51"/>
+      <c r="D47" s="51"/>
+      <c r="E47" s="51"/>
+      <c r="F47" s="51"/>
+      <c r="G47" s="51"/>
+      <c r="H47" s="51"/>
+      <c r="I47" s="51"/>
+      <c r="J47" s="51"/>
+      <c r="K47" s="51"/>
+      <c r="L47" s="53" t="s">
+        <v>764</v>
+      </c>
+      <c r="M47" s="51"/>
+      <c r="N47" s="51"/>
+      <c r="O47" s="51"/>
+      <c r="P47" s="51"/>
+      <c r="Q47" s="51"/>
+    </row>
+    <row r="48" spans="1:26" ht="13">
+      <c r="A48" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B46" s="12" t="s">
+      <c r="B48" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="C46" s="22"/>
-      <c r="D46" s="23"/>
-      <c r="E46" s="22"/>
-      <c r="F46" s="22"/>
-      <c r="G46" s="23"/>
-      <c r="H46" s="22"/>
-      <c r="I46" s="22"/>
-      <c r="J46" s="22"/>
-      <c r="K46" s="22"/>
-      <c r="L46" s="24"/>
-      <c r="M46" s="22"/>
-      <c r="N46" s="22"/>
-      <c r="O46" s="22"/>
-      <c r="P46" s="22"/>
-      <c r="Q46" s="22"/>
-      <c r="R46" s="22"/>
-      <c r="S46" s="22"/>
-      <c r="T46" s="22"/>
-      <c r="U46" s="22"/>
-      <c r="V46" s="22"/>
-      <c r="W46" s="22"/>
-      <c r="X46" s="22"/>
-      <c r="Y46" s="22"/>
-      <c r="Z46" s="22"/>
-    </row>
-    <row r="47" spans="1:26" ht="13">
-      <c r="A47" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="C47" s="22"/>
-      <c r="D47" s="23"/>
-      <c r="E47" s="22"/>
-      <c r="F47" s="22"/>
-      <c r="G47" s="23"/>
-      <c r="H47" s="22"/>
-      <c r="I47" s="22"/>
-      <c r="J47" s="22"/>
-      <c r="K47" s="22"/>
-      <c r="L47" s="24"/>
-      <c r="M47" s="22"/>
-      <c r="N47" s="22"/>
-      <c r="O47" s="22"/>
-      <c r="P47" s="22"/>
-      <c r="Q47" s="22"/>
-      <c r="R47" s="22"/>
-      <c r="S47" s="22"/>
-      <c r="T47" s="22"/>
-      <c r="U47" s="22"/>
-      <c r="V47" s="22"/>
-      <c r="W47" s="22"/>
-      <c r="X47" s="22"/>
-      <c r="Y47" s="22"/>
-      <c r="Z47" s="22"/>
-    </row>
-    <row r="48" spans="1:26" ht="13">
-      <c r="A48" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="B48" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="C48" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="D48" s="25" t="s">
-        <v>90</v>
-      </c>
+      <c r="C48" s="22"/>
+      <c r="D48" s="23"/>
       <c r="E48" s="22"/>
       <c r="F48" s="22"/>
       <c r="G48" s="23"/>
@@ -4114,7 +4141,7 @@
       <c r="I48" s="22"/>
       <c r="J48" s="22"/>
       <c r="K48" s="22"/>
-      <c r="L48" s="22"/>
+      <c r="L48" s="24"/>
       <c r="M48" s="22"/>
       <c r="N48" s="22"/>
       <c r="O48" s="22"/>
@@ -4122,20 +4149,23 @@
       <c r="Q48" s="22"/>
       <c r="R48" s="22"/>
       <c r="S48" s="22"/>
-    </row>
-    <row r="49" spans="1:19" ht="17.25" customHeight="1">
-      <c r="A49" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="B49" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="C49" s="26" t="s">
-        <v>93</v>
-      </c>
-      <c r="D49" s="26" t="s">
-        <v>94</v>
-      </c>
+      <c r="T48" s="22"/>
+      <c r="U48" s="22"/>
+      <c r="V48" s="22"/>
+      <c r="W48" s="22"/>
+      <c r="X48" s="22"/>
+      <c r="Y48" s="22"/>
+      <c r="Z48" s="22"/>
+    </row>
+    <row r="49" spans="1:26" ht="13">
+      <c r="A49" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C49" s="22"/>
+      <c r="D49" s="23"/>
       <c r="E49" s="22"/>
       <c r="F49" s="22"/>
       <c r="G49" s="23"/>
@@ -4143,7 +4173,7 @@
       <c r="I49" s="22"/>
       <c r="J49" s="22"/>
       <c r="K49" s="22"/>
-      <c r="L49" s="22"/>
+      <c r="L49" s="24"/>
       <c r="M49" s="22"/>
       <c r="N49" s="22"/>
       <c r="O49" s="22"/>
@@ -4151,16 +4181,27 @@
       <c r="Q49" s="22"/>
       <c r="R49" s="22"/>
       <c r="S49" s="22"/>
-    </row>
-    <row r="50" spans="1:19" ht="13">
+      <c r="T49" s="22"/>
+      <c r="U49" s="22"/>
+      <c r="V49" s="22"/>
+      <c r="W49" s="22"/>
+      <c r="X49" s="22"/>
+      <c r="Y49" s="22"/>
+      <c r="Z49" s="22"/>
+    </row>
+    <row r="50" spans="1:26" ht="13">
       <c r="A50" s="23" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B50" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="C50" s="22"/>
-      <c r="D50" s="23"/>
+      <c r="C50" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D50" s="25" t="s">
+        <v>90</v>
+      </c>
       <c r="E50" s="22"/>
       <c r="F50" s="22"/>
       <c r="G50" s="23"/>
@@ -4177,240 +4218,260 @@
       <c r="R50" s="22"/>
       <c r="S50" s="22"/>
     </row>
-    <row r="51" spans="1:19" ht="13">
-      <c r="A51" s="8" t="s">
+    <row r="51" spans="1:26" ht="17.25" customHeight="1">
+      <c r="A51" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="B51" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="C51" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="D51" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="E51" s="22"/>
+      <c r="F51" s="22"/>
+      <c r="G51" s="23"/>
+      <c r="H51" s="22"/>
+      <c r="I51" s="22"/>
+      <c r="J51" s="22"/>
+      <c r="K51" s="22"/>
+      <c r="L51" s="22"/>
+      <c r="M51" s="22"/>
+      <c r="N51" s="22"/>
+      <c r="O51" s="22"/>
+      <c r="P51" s="22"/>
+      <c r="Q51" s="22"/>
+      <c r="R51" s="22"/>
+      <c r="S51" s="22"/>
+    </row>
+    <row r="52" spans="1:26" ht="13">
+      <c r="A52" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="B52" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C52" s="22"/>
+      <c r="D52" s="23"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="23"/>
+      <c r="H52" s="22"/>
+      <c r="I52" s="22"/>
+      <c r="J52" s="22"/>
+      <c r="K52" s="22"/>
+      <c r="L52" s="22"/>
+      <c r="M52" s="22"/>
+      <c r="N52" s="22"/>
+      <c r="O52" s="22"/>
+      <c r="P52" s="22"/>
+      <c r="Q52" s="22"/>
+      <c r="R52" s="22"/>
+      <c r="S52" s="22"/>
+    </row>
+    <row r="53" spans="1:26" ht="13">
+      <c r="A53" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B53" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C53" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D51" s="21" t="s">
+      <c r="D53" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="G51" s="1" t="s">
+      <c r="G53" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="52" spans="1:19" ht="13">
-      <c r="A52" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C52" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="D52" s="19" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="53" spans="1:19" ht="13">
-      <c r="A53" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D53" s="13" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="54" spans="1:19" ht="13">
+    <row r="54" spans="1:26" ht="13">
       <c r="A54" s="8" t="s">
         <v>91</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D54" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="55" spans="1:19" ht="13">
+        <v>100</v>
+      </c>
+      <c r="C54" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="D54" s="19" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="55" spans="1:26" ht="13">
       <c r="A55" s="8" t="s">
         <v>91</v>
       </c>
       <c r="B55" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D55" s="13" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="56" spans="1:26" ht="13">
+      <c r="A56" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="57" spans="1:26" ht="13">
+      <c r="A57" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B57" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="C57" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="D55" s="18" t="s">
+      <c r="D57" s="18" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="56" spans="1:19" ht="14.25">
-      <c r="A56" s="1" t="s">
+    <row r="58" spans="1:26" ht="14.25">
+      <c r="A58" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B56" s="27" t="s">
+      <c r="B58" s="27" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="57" spans="1:19" ht="14.25">
-      <c r="A57" s="1" t="s">
+    <row r="59" spans="1:26" ht="14.25">
+      <c r="A59" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B57" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="58" spans="1:19" ht="14.25">
-      <c r="A58" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B58" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="59" spans="1:19" ht="14.25">
-      <c r="A59" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="B59" s="27" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="60" spans="1:19" ht="14.25">
+      <c r="C59" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="60" spans="1:26" ht="14.25">
       <c r="A60" s="1" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="B60" s="27" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="61" spans="1:19" ht="14.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="61" spans="1:26" ht="14.25">
       <c r="A61" s="1" t="s">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="B61" s="27" t="s">
-        <v>121</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>724</v>
-      </c>
-      <c r="D61" s="28" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="62" spans="1:19" ht="14.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="62" spans="1:26" ht="14.25">
       <c r="A62" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B62" s="27" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="63" spans="1:19" ht="14.25">
+        <v>119</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="63" spans="1:26" ht="14.25">
       <c r="A63" s="1" t="s">
         <v>91</v>
       </c>
       <c r="B63" s="27" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19" ht="14.25">
+        <v>722</v>
+      </c>
+      <c r="D63" s="28" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="64" spans="1:26" ht="14.25">
       <c r="A64" s="1" t="s">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="B64" s="27" t="s">
-        <v>126</v>
-      </c>
-      <c r="C64" s="29" t="s">
-        <v>127</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="G64" s="1"/>
+        <v>122</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="65" spans="1:7" ht="14.25">
       <c r="A65" s="1" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="B65" s="27" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>130</v>
+        <v>124</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="14.25">
       <c r="A66" s="1" t="s">
-        <v>131</v>
+        <v>91</v>
       </c>
       <c r="B66" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="D66" s="28" t="s">
-        <v>134</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>135</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="C66" s="29" t="s">
+        <v>127</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="G66" s="1"/>
     </row>
     <row r="67" spans="1:7" ht="14.25">
       <c r="A67" s="1" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="B67" s="27" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D67" s="30" t="s">
-        <v>138</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>135</v>
+        <v>19</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="14.25">
@@ -4418,13 +4479,13 @@
         <v>131</v>
       </c>
       <c r="B68" s="27" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="D68" s="28" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>135</v>
@@ -4432,10 +4493,19 @@
     </row>
     <row r="69" spans="1:7" ht="14.25">
       <c r="A69" s="1" t="s">
-        <v>34</v>
+        <v>131</v>
       </c>
       <c r="B69" s="27" t="s">
-        <v>129</v>
+        <v>136</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D69" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="14.25">
@@ -4443,154 +4513,145 @@
         <v>131</v>
       </c>
       <c r="B70" s="27" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D70" s="28" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="F70" s="1" t="s">
-        <v>145</v>
-      </c>
     </row>
     <row r="71" spans="1:7" ht="14.25">
       <c r="A71" s="1" t="s">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="B71" s="27" t="s">
-        <v>146</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D71" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="15.75" customHeight="1">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="14.25">
       <c r="A72" s="1" t="s">
-        <v>91</v>
+        <v>131</v>
       </c>
       <c r="B72" s="27" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="D72" s="28" t="s">
-        <v>152</v>
+        <v>144</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="14.25">
       <c r="A73" s="1" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="B73" s="27" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="14.25">
+        <v>146</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D73" s="28" t="s">
+        <v>148</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="15.75" customHeight="1">
       <c r="A74" s="1" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="B74" s="27" t="s">
-        <v>118</v>
-      </c>
-      <c r="C74" s="1"/>
-      <c r="F74" s="1"/>
-      <c r="G74" s="1"/>
+        <v>150</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D74" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="75" spans="1:7" ht="14.25">
       <c r="A75" s="1" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="B75" s="27" t="s">
-        <v>154</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="D75" s="28" t="s">
-        <v>156</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="14.25">
       <c r="A76" s="1" t="s">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="B76" s="27" t="s">
-        <v>158</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>160</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="C76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
     </row>
     <row r="77" spans="1:7" ht="14.25">
       <c r="A77" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B77" s="27" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>19</v>
+        <v>155</v>
+      </c>
+      <c r="D77" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>157</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>130</v>
+        <v>99</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="14.25">
       <c r="A78" s="1" t="s">
-        <v>131</v>
+        <v>91</v>
       </c>
       <c r="B78" s="27" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="D78" s="28" t="s">
-        <v>164</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>135</v>
+        <v>159</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="14.25">
       <c r="A79" s="1" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="B79" s="27" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D79" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>135</v>
+        <v>19</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="14.25">
@@ -4598,13 +4659,13 @@
         <v>131</v>
       </c>
       <c r="B80" s="27" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="D80" s="28" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>135</v>
@@ -4615,13 +4676,13 @@
         <v>131</v>
       </c>
       <c r="B81" s="27" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="D81" s="28" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>135</v>
@@ -4632,13 +4693,13 @@
         <v>131</v>
       </c>
       <c r="B82" s="27" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="D82" s="28" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>135</v>
@@ -4649,13 +4710,13 @@
         <v>131</v>
       </c>
       <c r="B83" s="27" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>179</v>
+        <v>172</v>
+      </c>
+      <c r="D83" s="28" t="s">
+        <v>173</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>135</v>
@@ -4666,13 +4727,13 @@
         <v>131</v>
       </c>
       <c r="B84" s="27" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D84" s="28" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>135</v>
@@ -4683,13 +4744,13 @@
         <v>131</v>
       </c>
       <c r="B85" s="27" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="D85" s="28" t="s">
-        <v>185</v>
+        <v>178</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>179</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>135</v>
@@ -4700,13 +4761,13 @@
         <v>131</v>
       </c>
       <c r="B86" s="27" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>188</v>
+        <v>181</v>
+      </c>
+      <c r="D86" s="28" t="s">
+        <v>182</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>135</v>
@@ -4717,13 +4778,13 @@
         <v>131</v>
       </c>
       <c r="B87" s="27" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="D87" s="28" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>135</v>
@@ -4734,13 +4795,13 @@
         <v>131</v>
       </c>
       <c r="B88" s="27" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="D88" s="28" t="s">
-        <v>194</v>
+        <v>187</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>188</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>135</v>
@@ -4751,13 +4812,13 @@
         <v>131</v>
       </c>
       <c r="B89" s="27" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D89" s="28" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>135</v>
@@ -4768,13 +4829,13 @@
         <v>131</v>
       </c>
       <c r="B90" s="27" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D90" s="28" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>135</v>
@@ -4782,87 +4843,84 @@
     </row>
     <row r="91" spans="1:6" ht="14.25">
       <c r="A91" s="1" t="s">
-        <v>34</v>
+        <v>131</v>
       </c>
       <c r="B91" s="27" t="s">
-        <v>161</v>
+        <v>195</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D91" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="14.25">
       <c r="A92" s="1" t="s">
-        <v>201</v>
+        <v>131</v>
       </c>
       <c r="B92" s="27" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D92" s="28" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="F92" s="1" t="s">
+    </row>
+    <row r="93" spans="1:6" ht="14.25">
+      <c r="A93" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B93" s="27" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="14.25">
+      <c r="A94" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B94" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D94" s="28" t="s">
+        <v>204</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F94" s="1" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A93" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B93" s="27" t="s">
-        <v>206</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="D93" s="28" t="s">
-        <v>208</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A94" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B94" s="27" t="s">
-        <v>210</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" ht="14.25">
+    <row r="95" spans="1:6" ht="15.75" customHeight="1">
       <c r="A95" s="1" t="s">
         <v>131</v>
       </c>
       <c r="B95" s="27" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D95" s="28" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>135</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="96" spans="1:6" ht="15.75" customHeight="1">
@@ -4870,33 +4928,36 @@
         <v>91</v>
       </c>
       <c r="B96" s="27" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="D96" s="28" t="s">
-        <v>219</v>
+        <v>211</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>212</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
     </row>
     <row r="97" spans="1:26" ht="14.25">
       <c r="A97" s="1" t="s">
-        <v>91</v>
+        <v>131</v>
       </c>
       <c r="B97" s="27" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="D97" s="28" t="s">
-        <v>223</v>
+        <v>216</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
     </row>
     <row r="98" spans="1:26" ht="15.75" customHeight="1">
@@ -4904,230 +4965,216 @@
         <v>91</v>
       </c>
       <c r="B98" s="27" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="D98" s="28" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
     </row>
     <row r="99" spans="1:26" ht="14.25">
       <c r="A99" s="1" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="B99" s="27" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="100" spans="1:26" ht="14.25">
+        <v>221</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D99" s="28" t="s">
+        <v>223</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="100" spans="1:26" ht="15.75" customHeight="1">
       <c r="A100" s="1" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="B100" s="27" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="E100" s="1"/>
-      <c r="F100" s="19" t="s">
-        <v>232</v>
-      </c>
-      <c r="G100" s="1" t="s">
-        <v>233</v>
+        <v>226</v>
+      </c>
+      <c r="D100" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="101" spans="1:26" ht="14.25">
       <c r="A101" s="1" t="s">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="B101" s="27" t="s">
-        <v>234</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="F101" s="1"/>
-      <c r="G101" s="1"/>
+        <v>154</v>
+      </c>
     </row>
     <row r="102" spans="1:26" ht="14.25">
       <c r="A102" s="1" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B102" s="27" t="s">
         <v>229</v>
       </c>
-      <c r="C102" s="1"/>
-      <c r="D102" s="28"/>
-      <c r="F102" s="1"/>
-      <c r="G102" s="1"/>
+      <c r="C102" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="E102" s="1"/>
+      <c r="F102" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="103" spans="1:26" ht="14.25">
       <c r="A103" s="1" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="B103" s="27" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="D103" s="28" t="s">
-        <v>239</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="G103" s="1" t="s">
-        <v>99</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F103" s="1"/>
+      <c r="G103" s="1"/>
     </row>
     <row r="104" spans="1:26" ht="14.25">
       <c r="A104" s="1" t="s">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="B104" s="27" t="s">
-        <v>240</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>242</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="C104" s="1"/>
+      <c r="D104" s="28"/>
+      <c r="F104" s="1"/>
       <c r="G104" s="1"/>
     </row>
     <row r="105" spans="1:26" ht="14.25">
       <c r="A105" s="1" t="s">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="B105" s="27" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="G105" s="1"/>
+        <v>238</v>
+      </c>
+      <c r="D105" s="28" t="s">
+        <v>239</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="106" spans="1:26" ht="14.25">
       <c r="A106" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B106" s="27" t="s">
+        <v>240</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="G106" s="1"/>
+    </row>
+    <row r="107" spans="1:26" ht="14.25">
+      <c r="A107" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B107" s="27" t="s">
+        <v>243</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="G107" s="1"/>
+    </row>
+    <row r="108" spans="1:26" ht="14.25">
+      <c r="A108" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B106" s="27" t="s">
+      <c r="B108" s="27" t="s">
         <v>237</v>
       </c>
-      <c r="C106" s="1"/>
-      <c r="G106" s="1"/>
-    </row>
-    <row r="107" spans="1:26" s="50" customFormat="1" ht="13">
-      <c r="A107" s="47" t="s">
+      <c r="C108" s="1"/>
+      <c r="G108" s="1"/>
+    </row>
+    <row r="109" spans="1:26" s="50" customFormat="1" ht="13">
+      <c r="A109" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="B107" s="47" t="s">
-        <v>726</v>
-      </c>
-      <c r="C107" s="48"/>
-      <c r="D107" s="48"/>
-      <c r="E107" s="48"/>
-      <c r="F107" s="28" t="s">
-        <v>767</v>
-      </c>
-      <c r="G107" s="48"/>
-      <c r="H107" s="48"/>
-      <c r="I107" s="48"/>
-      <c r="J107" s="48"/>
-      <c r="K107" s="48"/>
-      <c r="L107" s="49"/>
-      <c r="M107" s="48"/>
-      <c r="N107" s="48"/>
-      <c r="O107" s="48"/>
-      <c r="P107" s="48"/>
-      <c r="Q107" s="48"/>
-      <c r="R107" s="48"/>
-      <c r="S107" s="48"/>
-      <c r="T107" s="48"/>
-      <c r="U107" s="48"/>
-      <c r="V107" s="48"/>
-      <c r="W107" s="48"/>
-      <c r="X107" s="48"/>
-      <c r="Y107" s="48"/>
-      <c r="Z107" s="48"/>
-    </row>
-    <row r="108" spans="1:26" s="50" customFormat="1" ht="36" customHeight="1">
-      <c r="A108" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="B108" s="28" t="s">
-        <v>727</v>
-      </c>
-      <c r="C108" s="28"/>
-      <c r="D108" s="28"/>
-      <c r="E108" s="28"/>
-      <c r="G108" s="28" t="s">
-        <v>99</v>
-      </c>
-      <c r="H108" s="28"/>
-      <c r="I108" s="28"/>
-      <c r="J108" s="28"/>
-      <c r="K108" s="28"/>
-      <c r="L108" s="28"/>
-      <c r="M108" s="28"/>
-      <c r="N108" s="28"/>
-      <c r="O108" s="28"/>
-      <c r="P108" s="28"/>
-      <c r="Q108" s="28"/>
-    </row>
-    <row r="109" spans="1:26" s="50" customFormat="1" ht="36" customHeight="1">
-      <c r="A109" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="B109" s="28" t="s">
-        <v>728</v>
-      </c>
-      <c r="C109" s="28"/>
-      <c r="D109" s="57" t="s">
-        <v>729</v>
-      </c>
-      <c r="E109" s="28"/>
-      <c r="F109" s="28"/>
-      <c r="G109" s="28"/>
-      <c r="H109" s="28"/>
-      <c r="I109" s="28"/>
-      <c r="J109" s="28"/>
-      <c r="K109" s="28"/>
-      <c r="L109" s="28"/>
-      <c r="M109" s="28"/>
-      <c r="N109" s="28"/>
-      <c r="O109" s="28"/>
-      <c r="P109" s="28"/>
-      <c r="Q109" s="28"/>
+      <c r="B109" s="47" t="s">
+        <v>724</v>
+      </c>
+      <c r="C109" s="48"/>
+      <c r="D109" s="48"/>
+      <c r="E109" s="48"/>
+      <c r="F109" s="28" t="s">
+        <v>765</v>
+      </c>
+      <c r="G109" s="48"/>
+      <c r="H109" s="48"/>
+      <c r="I109" s="48"/>
+      <c r="J109" s="48"/>
+      <c r="K109" s="48"/>
+      <c r="L109" s="49"/>
+      <c r="M109" s="48"/>
+      <c r="N109" s="48"/>
+      <c r="O109" s="48"/>
+      <c r="P109" s="48"/>
+      <c r="Q109" s="48"/>
+      <c r="R109" s="48"/>
+      <c r="S109" s="48"/>
+      <c r="T109" s="48"/>
+      <c r="U109" s="48"/>
+      <c r="V109" s="48"/>
+      <c r="W109" s="48"/>
+      <c r="X109" s="48"/>
+      <c r="Y109" s="48"/>
+      <c r="Z109" s="48"/>
     </row>
     <row r="110" spans="1:26" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="A110" s="28" t="s">
-        <v>95</v>
+        <v>17</v>
       </c>
       <c r="B110" s="28" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C110" s="28"/>
-      <c r="D110" s="57"/>
+      <c r="D110" s="28"/>
       <c r="E110" s="28"/>
-      <c r="F110" s="28"/>
-      <c r="G110" s="28"/>
+      <c r="G110" s="28" t="s">
+        <v>99</v>
+      </c>
       <c r="H110" s="28"/>
       <c r="I110" s="28"/>
       <c r="J110" s="28"/>
@@ -5141,18 +5188,18 @@
     </row>
     <row r="111" spans="1:26" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="A111" s="28" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B111" s="28" t="s">
-        <v>782</v>
+        <v>726</v>
       </c>
       <c r="C111" s="28"/>
-      <c r="D111" s="57"/>
+      <c r="D111" s="56" t="s">
+        <v>727</v>
+      </c>
       <c r="E111" s="28"/>
       <c r="F111" s="28"/>
-      <c r="G111" s="28" t="s">
-        <v>99</v>
-      </c>
+      <c r="G111" s="28"/>
       <c r="H111" s="28"/>
       <c r="I111" s="28"/>
       <c r="J111" s="28"/>
@@ -5166,15 +5213,13 @@
     </row>
     <row r="112" spans="1:26" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="A112" s="28" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B112" s="28" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="C112" s="28"/>
-      <c r="D112" s="58" t="s">
-        <v>731</v>
-      </c>
+      <c r="D112" s="56"/>
       <c r="E112" s="28"/>
       <c r="F112" s="28"/>
       <c r="G112" s="28"/>
@@ -5189,20 +5234,20 @@
       <c r="P112" s="28"/>
       <c r="Q112" s="28"/>
     </row>
-    <row r="113" spans="1:19" s="50" customFormat="1" ht="36" customHeight="1">
+    <row r="113" spans="1:17" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="A113" s="28" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B113" s="28" t="s">
-        <v>732</v>
+        <v>780</v>
       </c>
       <c r="C113" s="28"/>
-      <c r="D113" s="58" t="s">
-        <v>783</v>
-      </c>
+      <c r="D113" s="56"/>
       <c r="E113" s="28"/>
       <c r="F113" s="28"/>
-      <c r="G113" s="28"/>
+      <c r="G113" s="28" t="s">
+        <v>99</v>
+      </c>
       <c r="H113" s="28"/>
       <c r="I113" s="28"/>
       <c r="J113" s="28"/>
@@ -5214,15 +5259,17 @@
       <c r="P113" s="28"/>
       <c r="Q113" s="28"/>
     </row>
-    <row r="114" spans="1:19" s="50" customFormat="1" ht="36" customHeight="1">
+    <row r="114" spans="1:17" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="A114" s="28" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="B114" s="28" t="s">
-        <v>782</v>
+        <v>728</v>
       </c>
       <c r="C114" s="28"/>
-      <c r="D114" s="58"/>
+      <c r="D114" s="57" t="s">
+        <v>729</v>
+      </c>
       <c r="E114" s="28"/>
       <c r="F114" s="28"/>
       <c r="G114" s="28"/>
@@ -5237,20 +5284,20 @@
       <c r="P114" s="28"/>
       <c r="Q114" s="28"/>
     </row>
-    <row r="115" spans="1:19" s="50" customFormat="1" ht="36" customHeight="1">
+    <row r="115" spans="1:17" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="A115" s="28" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B115" s="28" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="C115" s="28"/>
-      <c r="D115" s="58"/>
+      <c r="D115" s="57" t="s">
+        <v>781</v>
+      </c>
       <c r="E115" s="28"/>
       <c r="F115" s="28"/>
-      <c r="G115" s="28" t="s">
-        <v>233</v>
-      </c>
+      <c r="G115" s="28"/>
       <c r="H115" s="28"/>
       <c r="I115" s="28"/>
       <c r="J115" s="28"/>
@@ -5262,20 +5309,16 @@
       <c r="P115" s="28"/>
       <c r="Q115" s="28"/>
     </row>
-    <row r="116" spans="1:19" s="50" customFormat="1" ht="36" customHeight="1">
+    <row r="116" spans="1:17" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="A116" s="28" t="s">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="B116" s="28" t="s">
-        <v>734</v>
+        <v>780</v>
       </c>
       <c r="C116" s="28"/>
-      <c r="D116" s="58" t="s">
-        <v>784</v>
-      </c>
-      <c r="E116" s="28" t="s">
-        <v>735</v>
-      </c>
+      <c r="D116" s="57"/>
+      <c r="E116" s="28"/>
       <c r="F116" s="28"/>
       <c r="G116" s="28"/>
       <c r="H116" s="28"/>
@@ -5289,18 +5332,20 @@
       <c r="P116" s="28"/>
       <c r="Q116" s="28"/>
     </row>
-    <row r="117" spans="1:19" s="50" customFormat="1" ht="36" customHeight="1">
+    <row r="117" spans="1:17" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="A117" s="28" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B117" s="28" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C117" s="28"/>
-      <c r="D117" s="58"/>
+      <c r="D117" s="57"/>
       <c r="E117" s="28"/>
       <c r="F117" s="28"/>
-      <c r="G117" s="28"/>
+      <c r="G117" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="H117" s="28"/>
       <c r="I117" s="28"/>
       <c r="J117" s="28"/>
@@ -5312,20 +5357,22 @@
       <c r="P117" s="28"/>
       <c r="Q117" s="28"/>
     </row>
-    <row r="118" spans="1:19" s="50" customFormat="1" ht="36" customHeight="1">
+    <row r="118" spans="1:17" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="A118" s="28" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="B118" s="28" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="C118" s="28"/>
-      <c r="D118" s="58"/>
-      <c r="E118" s="28"/>
+      <c r="D118" s="57" t="s">
+        <v>782</v>
+      </c>
+      <c r="E118" s="28" t="s">
+        <v>733</v>
+      </c>
       <c r="F118" s="28"/>
-      <c r="G118" s="28" t="s">
-        <v>99</v>
-      </c>
+      <c r="G118" s="28"/>
       <c r="H118" s="28"/>
       <c r="I118" s="28"/>
       <c r="J118" s="28"/>
@@ -5337,17 +5384,15 @@
       <c r="P118" s="28"/>
       <c r="Q118" s="28"/>
     </row>
-    <row r="119" spans="1:19" s="50" customFormat="1" ht="36" customHeight="1">
+    <row r="119" spans="1:17" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="A119" s="28" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B119" s="28" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="C119" s="28"/>
-      <c r="D119" s="58" t="s">
-        <v>738</v>
-      </c>
+      <c r="D119" s="57"/>
       <c r="E119" s="28"/>
       <c r="F119" s="28"/>
       <c r="G119" s="28"/>
@@ -5362,22 +5407,20 @@
       <c r="P119" s="28"/>
       <c r="Q119" s="28"/>
     </row>
-    <row r="120" spans="1:19" s="50" customFormat="1" ht="36" customHeight="1">
+    <row r="120" spans="1:17" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="A120" s="28" t="s">
-        <v>739</v>
+        <v>17</v>
       </c>
       <c r="B120" s="28" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="C120" s="28"/>
-      <c r="D120" s="58" t="s">
-        <v>741</v>
-      </c>
-      <c r="E120" s="28" t="s">
-        <v>135</v>
-      </c>
+      <c r="D120" s="57"/>
+      <c r="E120" s="28"/>
       <c r="F120" s="28"/>
-      <c r="G120" s="28"/>
+      <c r="G120" s="28" t="s">
+        <v>99</v>
+      </c>
       <c r="H120" s="28"/>
       <c r="I120" s="28"/>
       <c r="J120" s="28"/>
@@ -5389,15 +5432,17 @@
       <c r="P120" s="28"/>
       <c r="Q120" s="28"/>
     </row>
-    <row r="121" spans="1:19" s="50" customFormat="1" ht="36" customHeight="1">
+    <row r="121" spans="1:17" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="A121" s="28" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="B121" s="28" t="s">
+        <v>735</v>
+      </c>
+      <c r="C121" s="28"/>
+      <c r="D121" s="57" t="s">
         <v>736</v>
       </c>
-      <c r="C121" s="28"/>
-      <c r="D121" s="58"/>
       <c r="E121" s="28"/>
       <c r="F121" s="28"/>
       <c r="G121" s="28"/>
@@ -5412,22 +5457,22 @@
       <c r="P121" s="28"/>
       <c r="Q121" s="28"/>
     </row>
-    <row r="122" spans="1:19" s="50" customFormat="1" ht="36" customHeight="1">
+    <row r="122" spans="1:17" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="A122" s="28" t="s">
-        <v>17</v>
+        <v>737</v>
       </c>
       <c r="B122" s="28" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="C122" s="28"/>
-      <c r="D122" s="58"/>
-      <c r="E122" s="28"/>
-      <c r="F122" s="59" t="s">
-        <v>743</v>
-      </c>
-      <c r="G122" s="28" t="s">
-        <v>99</v>
-      </c>
+      <c r="D122" s="57" t="s">
+        <v>739</v>
+      </c>
+      <c r="E122" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="F122" s="28"/>
+      <c r="G122" s="28"/>
       <c r="H122" s="28"/>
       <c r="I122" s="28"/>
       <c r="J122" s="28"/>
@@ -5439,17 +5484,15 @@
       <c r="P122" s="28"/>
       <c r="Q122" s="28"/>
     </row>
-    <row r="123" spans="1:19" s="50" customFormat="1" ht="36" customHeight="1">
+    <row r="123" spans="1:17" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="A123" s="28" t="s">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="B123" s="28" t="s">
-        <v>744</v>
+        <v>734</v>
       </c>
       <c r="C123" s="28"/>
-      <c r="D123" s="58" t="s">
-        <v>745</v>
-      </c>
+      <c r="D123" s="57"/>
       <c r="E123" s="28"/>
       <c r="F123" s="28"/>
       <c r="G123" s="28"/>
@@ -5464,22 +5507,22 @@
       <c r="P123" s="28"/>
       <c r="Q123" s="28"/>
     </row>
-    <row r="124" spans="1:19" s="50" customFormat="1" ht="36" customHeight="1">
+    <row r="124" spans="1:17" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="A124" s="28" t="s">
-        <v>131</v>
+        <v>17</v>
       </c>
       <c r="B124" s="28" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="C124" s="28"/>
-      <c r="D124" s="58" t="s">
-        <v>747</v>
-      </c>
-      <c r="E124" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="F124" s="28"/>
-      <c r="G124" s="28"/>
+      <c r="D124" s="57"/>
+      <c r="E124" s="28"/>
+      <c r="F124" s="58" t="s">
+        <v>741</v>
+      </c>
+      <c r="G124" s="28" t="s">
+        <v>99</v>
+      </c>
       <c r="H124" s="28"/>
       <c r="I124" s="28"/>
       <c r="J124" s="28"/>
@@ -5491,16 +5534,16 @@
       <c r="P124" s="28"/>
       <c r="Q124" s="28"/>
     </row>
-    <row r="125" spans="1:19" s="50" customFormat="1" ht="36" customHeight="1">
+    <row r="125" spans="1:17" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="A125" s="28" t="s">
         <v>91</v>
       </c>
       <c r="B125" s="28" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="C125" s="28"/>
-      <c r="D125" s="58" t="s">
-        <v>749</v>
+      <c r="D125" s="57" t="s">
+        <v>743</v>
       </c>
       <c r="E125" s="28"/>
       <c r="F125" s="28"/>
@@ -5516,18 +5559,20 @@
       <c r="P125" s="28"/>
       <c r="Q125" s="28"/>
     </row>
-    <row r="126" spans="1:19" s="50" customFormat="1" ht="36" customHeight="1">
+    <row r="126" spans="1:17" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="A126" s="28" t="s">
-        <v>91</v>
+        <v>131</v>
       </c>
       <c r="B126" s="28" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="C126" s="28"/>
-      <c r="D126" s="58" t="s">
-        <v>751</v>
-      </c>
-      <c r="E126" s="28"/>
+      <c r="D126" s="57" t="s">
+        <v>745</v>
+      </c>
+      <c r="E126" s="28" t="s">
+        <v>135</v>
+      </c>
       <c r="F126" s="28"/>
       <c r="G126" s="28"/>
       <c r="H126" s="28"/>
@@ -5541,16 +5586,16 @@
       <c r="P126" s="28"/>
       <c r="Q126" s="28"/>
     </row>
-    <row r="127" spans="1:19" s="50" customFormat="1" ht="36" customHeight="1">
+    <row r="127" spans="1:17" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="A127" s="28" t="s">
         <v>91</v>
       </c>
       <c r="B127" s="28" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="C127" s="28"/>
-      <c r="D127" s="58" t="s">
-        <v>785</v>
+      <c r="D127" s="57" t="s">
+        <v>747</v>
       </c>
       <c r="E127" s="28"/>
       <c r="F127" s="28"/>
@@ -5566,18 +5611,20 @@
       <c r="P127" s="28"/>
       <c r="Q127" s="28"/>
     </row>
-    <row r="128" spans="1:19" s="50" customFormat="1" ht="36" customHeight="1">
+    <row r="128" spans="1:17" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="A128" s="28" t="s">
         <v>91</v>
       </c>
       <c r="B128" s="28" t="s">
-        <v>753</v>
-      </c>
-      <c r="C128" s="59"/>
-      <c r="D128" s="28"/>
+        <v>748</v>
+      </c>
+      <c r="C128" s="28"/>
+      <c r="D128" s="57" t="s">
+        <v>749</v>
+      </c>
       <c r="E128" s="28"/>
-      <c r="F128" s="59"/>
-      <c r="G128" s="59"/>
+      <c r="F128" s="28"/>
+      <c r="G128" s="28"/>
       <c r="H128" s="28"/>
       <c r="I128" s="28"/>
       <c r="J128" s="28"/>
@@ -5588,22 +5635,18 @@
       <c r="O128" s="28"/>
       <c r="P128" s="28"/>
       <c r="Q128" s="28"/>
-      <c r="R128" s="28" t="s">
-        <v>754</v>
-      </c>
-      <c r="S128" s="49" t="s">
-        <v>754</v>
-      </c>
     </row>
     <row r="129" spans="1:26" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="A129" s="28" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="B129" s="28" t="s">
-        <v>742</v>
+        <v>750</v>
       </c>
       <c r="C129" s="28"/>
-      <c r="D129" s="58"/>
+      <c r="D129" s="57" t="s">
+        <v>783</v>
+      </c>
       <c r="E129" s="28"/>
       <c r="F129" s="28"/>
       <c r="G129" s="28"/>
@@ -5620,20 +5663,16 @@
     </row>
     <row r="130" spans="1:26" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="A130" s="28" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="B130" s="28" t="s">
-        <v>755</v>
-      </c>
-      <c r="C130" s="28"/>
-      <c r="D130" s="58"/>
+        <v>751</v>
+      </c>
+      <c r="C130" s="58"/>
+      <c r="D130" s="28"/>
       <c r="E130" s="28"/>
-      <c r="F130" s="59" t="s">
-        <v>756</v>
-      </c>
-      <c r="G130" s="28" t="s">
-        <v>99</v>
-      </c>
+      <c r="F130" s="58"/>
+      <c r="G130" s="58"/>
       <c r="H130" s="28"/>
       <c r="I130" s="28"/>
       <c r="J130" s="28"/>
@@ -5644,18 +5683,22 @@
       <c r="O130" s="28"/>
       <c r="P130" s="28"/>
       <c r="Q130" s="28"/>
+      <c r="R130" s="28" t="s">
+        <v>752</v>
+      </c>
+      <c r="S130" s="49" t="s">
+        <v>752</v>
+      </c>
     </row>
     <row r="131" spans="1:26" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="A131" s="28" t="s">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="B131" s="28" t="s">
-        <v>757</v>
+        <v>740</v>
       </c>
       <c r="C131" s="28"/>
-      <c r="D131" s="58" t="s">
-        <v>786</v>
-      </c>
+      <c r="D131" s="57"/>
       <c r="E131" s="28"/>
       <c r="F131" s="28"/>
       <c r="G131" s="28"/>
@@ -5672,18 +5715,20 @@
     </row>
     <row r="132" spans="1:26" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="A132" s="28" t="s">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="B132" s="28" t="s">
-        <v>758</v>
-      </c>
-      <c r="C132" s="60"/>
-      <c r="D132" s="60" t="s">
-        <v>759</v>
-      </c>
+        <v>753</v>
+      </c>
+      <c r="C132" s="28"/>
+      <c r="D132" s="57"/>
       <c r="E132" s="28"/>
-      <c r="F132" s="59"/>
-      <c r="G132" s="28"/>
+      <c r="F132" s="58" t="s">
+        <v>754</v>
+      </c>
+      <c r="G132" s="28" t="s">
+        <v>99</v>
+      </c>
       <c r="H132" s="28"/>
       <c r="I132" s="28"/>
       <c r="J132" s="28"/>
@@ -5694,22 +5739,18 @@
       <c r="O132" s="28"/>
       <c r="P132" s="28"/>
       <c r="Q132" s="28"/>
-      <c r="T132" s="61" t="s">
-        <v>760</v>
-      </c>
-      <c r="U132" s="61" t="s">
-        <v>760</v>
-      </c>
     </row>
     <row r="133" spans="1:26" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="A133" s="28" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="B133" s="28" t="s">
         <v>755</v>
       </c>
       <c r="C133" s="28"/>
-      <c r="D133" s="58"/>
+      <c r="D133" s="57" t="s">
+        <v>784</v>
+      </c>
       <c r="E133" s="28"/>
       <c r="F133" s="28"/>
       <c r="G133" s="28"/>
@@ -5726,20 +5767,18 @@
     </row>
     <row r="134" spans="1:26" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="A134" s="28" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="B134" s="28" t="s">
-        <v>761</v>
-      </c>
-      <c r="C134" s="28"/>
-      <c r="D134" s="58"/>
+        <v>756</v>
+      </c>
+      <c r="C134" s="59"/>
+      <c r="D134" s="59" t="s">
+        <v>757</v>
+      </c>
       <c r="E134" s="28"/>
-      <c r="F134" s="59" t="s">
-        <v>762</v>
-      </c>
-      <c r="G134" s="28" t="s">
-        <v>233</v>
-      </c>
+      <c r="F134" s="58"/>
+      <c r="G134" s="28"/>
       <c r="H134" s="28"/>
       <c r="I134" s="28"/>
       <c r="J134" s="28"/>
@@ -5750,18 +5789,22 @@
       <c r="O134" s="28"/>
       <c r="P134" s="28"/>
       <c r="Q134" s="28"/>
+      <c r="T134" s="60" t="s">
+        <v>758</v>
+      </c>
+      <c r="U134" s="60" t="s">
+        <v>758</v>
+      </c>
     </row>
     <row r="135" spans="1:26" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="A135" s="28" t="s">
-        <v>91</v>
+        <v>34</v>
       </c>
       <c r="B135" s="28" t="s">
-        <v>763</v>
+        <v>753</v>
       </c>
       <c r="C135" s="28"/>
-      <c r="D135" s="58" t="s">
-        <v>787</v>
-      </c>
+      <c r="D135" s="57"/>
       <c r="E135" s="28"/>
       <c r="F135" s="28"/>
       <c r="G135" s="28"/>
@@ -5778,16 +5821,20 @@
     </row>
     <row r="136" spans="1:26" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="A136" s="28" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B136" s="28" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="C136" s="28"/>
-      <c r="D136" s="58"/>
+      <c r="D136" s="57"/>
       <c r="E136" s="28"/>
-      <c r="F136" s="28"/>
-      <c r="G136" s="28"/>
+      <c r="F136" s="58" t="s">
+        <v>760</v>
+      </c>
+      <c r="G136" s="28" t="s">
+        <v>233</v>
+      </c>
       <c r="H136" s="28"/>
       <c r="I136" s="28"/>
       <c r="J136" s="28"/>
@@ -5801,10 +5848,14 @@
     </row>
     <row r="137" spans="1:26" s="50" customFormat="1" ht="36" customHeight="1">
       <c r="A137" s="28" t="s">
-        <v>34</v>
+        <v>91</v>
       </c>
       <c r="B137" s="28" t="s">
-        <v>726</v>
+        <v>761</v>
+      </c>
+      <c r="C137" s="28"/>
+      <c r="D137" s="57" t="s">
+        <v>785</v>
       </c>
       <c r="E137" s="28"/>
       <c r="F137" s="28"/>
@@ -5820,150 +5871,158 @@
       <c r="P137" s="28"/>
       <c r="Q137" s="28"/>
     </row>
-    <row r="138" spans="1:26" ht="14.25">
-      <c r="A138" s="1" t="s">
+    <row r="138" spans="1:26" s="50" customFormat="1" ht="36" customHeight="1">
+      <c r="A138" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="B138" s="28" t="s">
+        <v>759</v>
+      </c>
+      <c r="C138" s="28"/>
+      <c r="D138" s="57"/>
+      <c r="E138" s="28"/>
+      <c r="F138" s="28"/>
+      <c r="G138" s="28"/>
+      <c r="H138" s="28"/>
+      <c r="I138" s="28"/>
+      <c r="J138" s="28"/>
+      <c r="K138" s="28"/>
+      <c r="L138" s="28"/>
+      <c r="M138" s="28"/>
+      <c r="N138" s="28"/>
+      <c r="O138" s="28"/>
+      <c r="P138" s="28"/>
+      <c r="Q138" s="28"/>
+    </row>
+    <row r="139" spans="1:26" s="50" customFormat="1" ht="36" customHeight="1">
+      <c r="A139" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="B139" s="28" t="s">
+        <v>724</v>
+      </c>
+      <c r="E139" s="28"/>
+      <c r="F139" s="28"/>
+      <c r="G139" s="28"/>
+      <c r="H139" s="28"/>
+      <c r="I139" s="28"/>
+      <c r="J139" s="28"/>
+      <c r="K139" s="28"/>
+      <c r="L139" s="28"/>
+      <c r="M139" s="28"/>
+      <c r="N139" s="28"/>
+      <c r="O139" s="28"/>
+      <c r="P139" s="28"/>
+      <c r="Q139" s="28"/>
+    </row>
+    <row r="140" spans="1:26" ht="14.25">
+      <c r="A140" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B138" s="27" t="s">
+      <c r="B140" s="27" t="s">
         <v>246</v>
       </c>
-      <c r="C138" s="1" t="s">
+      <c r="C140" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="D138" s="1" t="s">
+      <c r="D140" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="F138" s="1" t="s">
+      <c r="F140" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="G138" s="1" t="s">
+      <c r="G140" s="1" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="139" spans="1:26" ht="14.25">
-      <c r="A139" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B139" s="27" t="s">
-        <v>250</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="D139" s="28" t="s">
-        <v>252</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G139" s="1"/>
-    </row>
-    <row r="140" spans="1:26" ht="13">
-      <c r="A140" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="B140" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="C140" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="D140" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="E140" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="F140" s="31" t="s">
-        <v>257</v>
-      </c>
-      <c r="G140" s="8"/>
-      <c r="H140" s="5"/>
-      <c r="I140" s="5"/>
-      <c r="J140" s="5"/>
-      <c r="K140" s="5"/>
-      <c r="L140" s="5"/>
-      <c r="M140" s="5"/>
-      <c r="N140" s="5"/>
-      <c r="O140" s="5"/>
-      <c r="P140" s="5"/>
-      <c r="Q140" s="5"/>
-      <c r="R140" s="5"/>
-      <c r="S140" s="5"/>
-      <c r="T140" s="5"/>
-      <c r="U140" s="5"/>
-      <c r="V140" s="5"/>
-      <c r="W140" s="5"/>
-      <c r="X140" s="5"/>
-      <c r="Y140" s="5"/>
-      <c r="Z140" s="5"/>
     </row>
     <row r="141" spans="1:26" ht="14.25">
       <c r="A141" s="1" t="s">
         <v>131</v>
       </c>
       <c r="B141" s="27" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="D141" s="28" t="s">
-        <v>260</v>
-      </c>
-      <c r="F141" s="19" t="s">
+        <v>252</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G141" s="1"/>
+    </row>
+    <row r="142" spans="1:26" s="61" customFormat="1" ht="14.25">
+      <c r="A142" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="B142" s="41" t="s">
+        <v>796</v>
+      </c>
+      <c r="C142" s="28" t="s">
+        <v>797</v>
+      </c>
+      <c r="D142" s="28" t="s">
+        <v>798</v>
+      </c>
+      <c r="E142" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="F142" s="28" t="s">
         <v>261</v>
       </c>
-      <c r="G141" s="1"/>
-    </row>
-    <row r="142" spans="1:26" ht="14.25">
-      <c r="A142" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B142" s="27" t="s">
-        <v>246</v>
-      </c>
-      <c r="C142" s="1"/>
-      <c r="F142" s="19"/>
-      <c r="G142" s="1"/>
-    </row>
-    <row r="143" spans="1:26" ht="14.25">
-      <c r="A143" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B143" s="27" t="s">
-        <v>262</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>263</v>
+      <c r="G142" s="28"/>
+    </row>
+    <row r="143" spans="1:26" s="55" customFormat="1" ht="14.25">
+      <c r="A143" s="28" t="s">
+        <v>786</v>
+      </c>
+      <c r="B143" s="41" t="s">
+        <v>787</v>
+      </c>
+      <c r="C143" s="28" t="s">
+        <v>788</v>
       </c>
       <c r="D143" s="28" t="s">
-        <v>264</v>
-      </c>
-      <c r="F143" s="19" t="s">
-        <v>265</v>
-      </c>
-      <c r="G143" s="1" t="s">
-        <v>99</v>
+        <v>789</v>
+      </c>
+      <c r="E143" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="F143" s="31" t="s">
+        <v>799</v>
+      </c>
+      <c r="G143" s="28"/>
+      <c r="I143" s="28" t="s">
+        <v>793</v>
+      </c>
+      <c r="J143" s="28" t="s">
+        <v>794</v>
+      </c>
+      <c r="K143" s="28" t="s">
+        <v>795</v>
       </c>
     </row>
     <row r="144" spans="1:26" ht="13">
-      <c r="A144" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="B144" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="C144" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="D144" s="18" t="s">
-        <v>269</v>
+      <c r="A144" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="B144" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="D144" s="6" t="s">
+        <v>256</v>
       </c>
       <c r="E144" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="F144" s="4"/>
+      <c r="F144" s="31" t="s">
+        <v>257</v>
+      </c>
       <c r="G144" s="8"/>
       <c r="H144" s="5"/>
       <c r="I144" s="5"/>
@@ -5985,147 +6044,74 @@
       <c r="Y144" s="5"/>
       <c r="Z144" s="5"/>
     </row>
-    <row r="145" spans="1:26" ht="13">
-      <c r="A145" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="B145" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="C145" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="D145" s="32" t="s">
-        <v>273</v>
-      </c>
-      <c r="E145" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="F145" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="G145" s="8"/>
-      <c r="H145" s="5"/>
-      <c r="I145" s="5"/>
-      <c r="J145" s="5"/>
-      <c r="K145" s="5"/>
-      <c r="L145" s="5"/>
-      <c r="M145" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="N145" s="5"/>
-      <c r="O145" s="5"/>
-      <c r="P145" s="5"/>
-      <c r="Q145" s="5"/>
-      <c r="R145" s="5"/>
-      <c r="S145" s="5"/>
-      <c r="T145" s="5"/>
-      <c r="U145" s="5"/>
-      <c r="V145" s="5"/>
-      <c r="W145" s="5"/>
-      <c r="X145" s="5"/>
-      <c r="Y145" s="5"/>
-      <c r="Z145" s="5"/>
-    </row>
-    <row r="146" spans="1:26" ht="13">
-      <c r="A146" s="4" t="s">
+    <row r="145" spans="1:26" ht="14.25">
+      <c r="A145" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B145" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D145" s="28" t="s">
+        <v>260</v>
+      </c>
+      <c r="F145" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="G145" s="1"/>
+    </row>
+    <row r="146" spans="1:26" ht="14.25">
+      <c r="A146" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B146" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="C146" s="1"/>
+      <c r="F146" s="19"/>
+      <c r="G146" s="1"/>
+    </row>
+    <row r="147" spans="1:26" ht="14.25">
+      <c r="A147" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B146" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="C146" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D146" s="5"/>
-      <c r="E146" s="12"/>
-      <c r="F146" s="4"/>
-      <c r="G146" s="4" t="s">
+      <c r="B147" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D147" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="F147" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="G147" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="H146" s="5"/>
-      <c r="I146" s="5"/>
-      <c r="J146" s="5"/>
-      <c r="K146" s="5"/>
-      <c r="L146" s="5"/>
-      <c r="M146" s="5"/>
-      <c r="N146" s="5"/>
-      <c r="O146" s="5"/>
-      <c r="P146" s="5"/>
-      <c r="Q146" s="5"/>
-      <c r="R146" s="5"/>
-      <c r="S146" s="5"/>
-      <c r="T146" s="5"/>
-      <c r="U146" s="5"/>
-      <c r="V146" s="5"/>
-      <c r="W146" s="5"/>
-      <c r="X146" s="5"/>
-      <c r="Y146" s="5"/>
-      <c r="Z146" s="5"/>
-    </row>
-    <row r="147" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A147" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="B147" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="C147" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="D147" s="18" t="s">
-        <v>280</v>
-      </c>
-      <c r="E147" s="12" t="s">
-        <v>281</v>
-      </c>
-      <c r="F147" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="G147" s="8"/>
-      <c r="H147" s="5"/>
-      <c r="I147" s="5"/>
-      <c r="J147" s="5"/>
-      <c r="K147" s="5"/>
-      <c r="L147" s="5"/>
-      <c r="M147" s="11" t="s">
-        <v>283</v>
-      </c>
-      <c r="N147" s="5"/>
-      <c r="O147" s="5"/>
-      <c r="P147" s="5"/>
-      <c r="Q147" s="5"/>
-      <c r="R147" s="5"/>
-      <c r="S147" s="5"/>
-      <c r="T147" s="5"/>
-      <c r="U147" s="5"/>
-      <c r="V147" s="5"/>
-      <c r="W147" s="5"/>
-      <c r="X147" s="5"/>
-      <c r="Y147" s="5"/>
-      <c r="Z147" s="5"/>
     </row>
     <row r="148" spans="1:26" ht="13">
       <c r="A148" s="4" t="s">
-        <v>284</v>
+        <v>266</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>285</v>
+        <v>267</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="D148" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="E148" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D148" s="18" t="s">
+        <v>269</v>
+      </c>
+      <c r="E148" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="F148" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="G148" s="4"/>
-      <c r="H148" s="4"/>
+      <c r="F148" s="4"/>
+      <c r="G148" s="8"/>
+      <c r="H148" s="5"/>
       <c r="I148" s="5"/>
       <c r="J148" s="5"/>
       <c r="K148" s="5"/>
@@ -6147,22 +6133,32 @@
     </row>
     <row r="149" spans="1:26" ht="13">
       <c r="A149" s="4" t="s">
-        <v>34</v>
+        <v>270</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="C149" s="4"/>
-      <c r="D149" s="4"/>
-      <c r="E149" s="4"/>
-      <c r="F149" s="4"/>
-      <c r="G149" s="4"/>
-      <c r="H149" s="4"/>
+        <v>271</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="D149" s="32" t="s">
+        <v>273</v>
+      </c>
+      <c r="E149" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="F149" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="G149" s="8"/>
+      <c r="H149" s="5"/>
       <c r="I149" s="5"/>
       <c r="J149" s="5"/>
       <c r="K149" s="5"/>
       <c r="L149" s="5"/>
-      <c r="M149" s="5"/>
+      <c r="M149" s="11" t="s">
+        <v>275</v>
+      </c>
       <c r="N149" s="5"/>
       <c r="O149" s="5"/>
       <c r="P149" s="5"/>
@@ -6179,23 +6175,21 @@
     </row>
     <row r="150" spans="1:26" ht="13">
       <c r="A150" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="B150" s="4" t="s">
-        <v>290</v>
+        <v>17</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>276</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="D150" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="E150" s="4" t="s">
-        <v>135</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="D150" s="5"/>
+      <c r="E150" s="12"/>
       <c r="F150" s="4"/>
-      <c r="G150" s="4"/>
-      <c r="H150" s="4"/>
+      <c r="G150" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="H150" s="5"/>
       <c r="I150" s="5"/>
       <c r="J150" s="5"/>
       <c r="K150" s="5"/>
@@ -6215,32 +6209,34 @@
       <c r="Y150" s="5"/>
       <c r="Z150" s="5"/>
     </row>
-    <row r="151" spans="1:26" ht="13">
+    <row r="151" spans="1:26" ht="15.75" customHeight="1">
       <c r="A151" s="4" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>294</v>
+        <v>278</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="D151" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="E151" s="4" t="s">
-        <v>135</v>
+        <v>279</v>
+      </c>
+      <c r="D151" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="E151" s="12" t="s">
+        <v>281</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="G151" s="4"/>
-      <c r="H151" s="4"/>
+        <v>282</v>
+      </c>
+      <c r="G151" s="8"/>
+      <c r="H151" s="5"/>
       <c r="I151" s="5"/>
       <c r="J151" s="5"/>
       <c r="K151" s="5"/>
       <c r="L151" s="5"/>
-      <c r="M151" s="5"/>
+      <c r="M151" s="11" t="s">
+        <v>283</v>
+      </c>
       <c r="N151" s="5"/>
       <c r="O151" s="5"/>
       <c r="P151" s="5"/>
@@ -6257,22 +6253,22 @@
     </row>
     <row r="152" spans="1:26" ht="13">
       <c r="A152" s="4" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>299</v>
+        <v>285</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="E152" s="4" t="s">
         <v>135</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="G152" s="4"/>
       <c r="H152" s="4"/>
@@ -6297,314 +6293,318 @@
     </row>
     <row r="153" spans="1:26" ht="13">
       <c r="A153" s="4" t="s">
-        <v>303</v>
+        <v>34</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="C153" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="D153" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="E153" s="4" t="s">
-        <v>135</v>
-      </c>
+        <v>276</v>
+      </c>
+      <c r="C153" s="4"/>
+      <c r="D153" s="4"/>
+      <c r="E153" s="4"/>
       <c r="F153" s="4"/>
       <c r="G153" s="4"/>
       <c r="H153" s="4"/>
-      <c r="I153" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="J153" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="K153" s="33" t="s">
-        <v>309</v>
-      </c>
+      <c r="I153" s="5"/>
+      <c r="J153" s="5"/>
+      <c r="K153" s="5"/>
+      <c r="L153" s="5"/>
+      <c r="M153" s="5"/>
+      <c r="N153" s="5"/>
+      <c r="O153" s="5"/>
+      <c r="P153" s="5"/>
+      <c r="Q153" s="5"/>
+      <c r="R153" s="5"/>
+      <c r="S153" s="5"/>
+      <c r="T153" s="5"/>
+      <c r="U153" s="5"/>
+      <c r="V153" s="5"/>
+      <c r="W153" s="5"/>
+      <c r="X153" s="5"/>
+      <c r="Y153" s="5"/>
+      <c r="Z153" s="5"/>
     </row>
     <row r="154" spans="1:26" ht="13">
       <c r="A154" s="4" t="s">
-        <v>310</v>
+        <v>289</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>311</v>
+        <v>290</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>313</v>
+        <v>292</v>
       </c>
       <c r="E154" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="F154" s="6" t="s">
-        <v>314</v>
-      </c>
+      <c r="F154" s="4"/>
       <c r="G154" s="4"/>
       <c r="H154" s="4"/>
-      <c r="I154" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="J154" s="10" t="s">
-        <v>308</v>
-      </c>
-      <c r="K154" s="33" t="s">
-        <v>309</v>
-      </c>
+      <c r="I154" s="5"/>
+      <c r="J154" s="5"/>
+      <c r="K154" s="5"/>
+      <c r="L154" s="5"/>
+      <c r="M154" s="5"/>
+      <c r="N154" s="5"/>
+      <c r="O154" s="5"/>
+      <c r="P154" s="5"/>
+      <c r="Q154" s="5"/>
+      <c r="R154" s="5"/>
+      <c r="S154" s="5"/>
+      <c r="T154" s="5"/>
+      <c r="U154" s="5"/>
+      <c r="V154" s="5"/>
+      <c r="W154" s="5"/>
+      <c r="X154" s="5"/>
+      <c r="Y154" s="5"/>
+      <c r="Z154" s="5"/>
     </row>
     <row r="155" spans="1:26" ht="13">
       <c r="A155" s="4" t="s">
-        <v>34</v>
+        <v>293</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="C155" s="4"/>
-      <c r="D155" s="4"/>
-      <c r="E155" s="4"/>
-      <c r="F155" s="4"/>
+        <v>294</v>
+      </c>
+      <c r="C155" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="D155" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="E155" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F155" s="4" t="s">
+        <v>297</v>
+      </c>
       <c r="G155" s="4"/>
       <c r="H155" s="4"/>
+      <c r="I155" s="5"/>
+      <c r="J155" s="5"/>
+      <c r="K155" s="5"/>
+      <c r="L155" s="5"/>
+      <c r="M155" s="5"/>
+      <c r="N155" s="5"/>
+      <c r="O155" s="5"/>
+      <c r="P155" s="5"/>
+      <c r="Q155" s="5"/>
+      <c r="R155" s="5"/>
+      <c r="S155" s="5"/>
+      <c r="T155" s="5"/>
+      <c r="U155" s="5"/>
+      <c r="V155" s="5"/>
+      <c r="W155" s="5"/>
+      <c r="X155" s="5"/>
+      <c r="Y155" s="5"/>
+      <c r="Z155" s="5"/>
     </row>
     <row r="156" spans="1:26" ht="13">
       <c r="A156" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B156" s="6" t="s">
-        <v>315</v>
+        <v>298</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>299</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>316</v>
+        <v>300</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="E156" s="4"/>
-      <c r="F156" s="6" t="s">
-        <v>318</v>
+        <v>301</v>
+      </c>
+      <c r="E156" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F156" s="4" t="s">
+        <v>302</v>
       </c>
       <c r="G156" s="4"/>
       <c r="H156" s="4"/>
+      <c r="I156" s="5"/>
+      <c r="J156" s="5"/>
+      <c r="K156" s="5"/>
+      <c r="L156" s="5"/>
+      <c r="M156" s="5"/>
+      <c r="N156" s="5"/>
+      <c r="O156" s="5"/>
+      <c r="P156" s="5"/>
+      <c r="Q156" s="5"/>
+      <c r="R156" s="5"/>
+      <c r="S156" s="5"/>
+      <c r="T156" s="5"/>
+      <c r="U156" s="5"/>
+      <c r="V156" s="5"/>
+      <c r="W156" s="5"/>
+      <c r="X156" s="5"/>
+      <c r="Y156" s="5"/>
+      <c r="Z156" s="5"/>
     </row>
     <row r="157" spans="1:26" ht="13">
-      <c r="A157" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="B157" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="C157" s="6" t="s">
-        <v>320</v>
+      <c r="A157" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>305</v>
       </c>
       <c r="D157" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="E157" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="E157" s="4" t="s">
         <v>135</v>
       </c>
       <c r="F157" s="4"/>
       <c r="G157" s="4"/>
       <c r="H157" s="4"/>
+      <c r="I157" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="J157" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="K157" s="33" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="158" spans="1:26" ht="13">
-      <c r="A158" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B158" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="C158" s="4"/>
-      <c r="D158" s="4"/>
-      <c r="E158" s="4"/>
-      <c r="F158" s="4"/>
+      <c r="A158" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D158" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="E158" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F158" s="6" t="s">
+        <v>314</v>
+      </c>
       <c r="G158" s="4"/>
       <c r="H158" s="4"/>
+      <c r="I158" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="J158" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="K158" s="33" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="159" spans="1:26" ht="13">
-      <c r="A159" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B159" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="C159" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="D159" s="6" t="s">
-        <v>317</v>
-      </c>
+      <c r="A159" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="C159" s="4"/>
+      <c r="D159" s="4"/>
       <c r="E159" s="4"/>
-      <c r="F159" s="6" t="s">
-        <v>323</v>
-      </c>
+      <c r="F159" s="4"/>
       <c r="G159" s="4"/>
       <c r="H159" s="4"/>
     </row>
     <row r="160" spans="1:26" ht="13">
-      <c r="A160" s="8" t="s">
-        <v>324</v>
-      </c>
-      <c r="B160" s="34" t="s">
-        <v>325</v>
-      </c>
-      <c r="C160" s="35" t="s">
-        <v>326</v>
-      </c>
-      <c r="D160" s="18" t="s">
-        <v>327</v>
-      </c>
-      <c r="E160" s="9" t="s">
+      <c r="A160" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="D160" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="E160" s="4"/>
+      <c r="F160" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="G160" s="4"/>
+      <c r="H160" s="4"/>
+    </row>
+    <row r="161" spans="1:26" ht="13">
+      <c r="A161" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B161" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="C161" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="D161" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="E161" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="F160" s="9"/>
-      <c r="G160" s="8"/>
-      <c r="H160" s="5"/>
-      <c r="I160" s="5"/>
-      <c r="J160" s="5"/>
-      <c r="K160" s="5"/>
-      <c r="L160" s="5"/>
-      <c r="M160" s="5"/>
-      <c r="N160" s="5"/>
-      <c r="O160" s="5"/>
-      <c r="P160" s="5"/>
-      <c r="Q160" s="5"/>
-      <c r="R160" s="5"/>
-      <c r="S160" s="5"/>
-      <c r="T160" s="5"/>
-      <c r="U160" s="5"/>
-      <c r="V160" s="5"/>
-      <c r="W160" s="5"/>
-      <c r="X160" s="5"/>
-      <c r="Y160" s="5"/>
-      <c r="Z160" s="5"/>
-    </row>
-    <row r="161" spans="1:26" ht="13">
-      <c r="A161" s="8" t="s">
+      <c r="F161" s="4"/>
+      <c r="G161" s="4"/>
+      <c r="H161" s="4"/>
+    </row>
+    <row r="162" spans="1:26" ht="13">
+      <c r="A162" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B162" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="C162" s="4"/>
+      <c r="D162" s="4"/>
+      <c r="E162" s="4"/>
+      <c r="F162" s="4"/>
+      <c r="G162" s="4"/>
+      <c r="H162" s="4"/>
+    </row>
+    <row r="163" spans="1:26" ht="13">
+      <c r="A163" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B161" s="34" t="s">
-        <v>328</v>
-      </c>
-      <c r="C161" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="D161" s="5"/>
-      <c r="E161" s="5"/>
-      <c r="F161" s="9"/>
-      <c r="G161" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="H161" s="5"/>
-      <c r="I161" s="5"/>
-      <c r="J161" s="5"/>
-      <c r="K161" s="5"/>
-      <c r="L161" s="5"/>
-      <c r="M161" s="5"/>
-      <c r="N161" s="5"/>
-      <c r="O161" s="5"/>
-      <c r="P161" s="5"/>
-      <c r="Q161" s="5"/>
-      <c r="R161" s="5"/>
-      <c r="S161" s="5"/>
-      <c r="T161" s="5"/>
-      <c r="U161" s="5"/>
-      <c r="V161" s="5"/>
-      <c r="W161" s="5"/>
-      <c r="X161" s="5"/>
-      <c r="Y161" s="5"/>
-      <c r="Z161" s="5"/>
-    </row>
-    <row r="162" spans="1:26" ht="13">
-      <c r="A162" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="B162" s="34" t="s">
-        <v>330</v>
-      </c>
-      <c r="C162" s="37" t="s">
-        <v>331</v>
-      </c>
-      <c r="D162" s="32" t="s">
-        <v>332</v>
-      </c>
-      <c r="E162" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="F162" s="9"/>
-      <c r="G162" s="8"/>
-      <c r="H162" s="5"/>
-      <c r="I162" s="5"/>
-      <c r="J162" s="5"/>
-      <c r="K162" s="5"/>
-      <c r="L162" s="5"/>
-      <c r="M162" s="5"/>
-      <c r="N162" s="5"/>
-      <c r="O162" s="5"/>
-      <c r="P162" s="5"/>
-      <c r="Q162" s="5"/>
-      <c r="R162" s="5"/>
-      <c r="S162" s="5"/>
-      <c r="T162" s="5"/>
-      <c r="U162" s="5"/>
-      <c r="V162" s="5"/>
-      <c r="W162" s="5"/>
-      <c r="X162" s="5"/>
-      <c r="Y162" s="5"/>
-      <c r="Z162" s="5"/>
-    </row>
-    <row r="163" spans="1:26" ht="13">
-      <c r="A163" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="B163" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="C163" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="D163" s="32" t="s">
-        <v>334</v>
-      </c>
-      <c r="E163" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="F163" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="G163" s="8"/>
-      <c r="H163" s="5"/>
-      <c r="I163" s="5"/>
-      <c r="J163" s="5"/>
-      <c r="K163" s="5"/>
-      <c r="L163" s="5"/>
-      <c r="M163" s="5"/>
-      <c r="N163" s="5"/>
-      <c r="O163" s="5"/>
-      <c r="P163" s="5"/>
-      <c r="Q163" s="5"/>
-      <c r="R163" s="5"/>
-      <c r="S163" s="5"/>
-      <c r="T163" s="5"/>
-      <c r="U163" s="5"/>
-      <c r="V163" s="5"/>
-      <c r="W163" s="5"/>
-      <c r="X163" s="5"/>
-      <c r="Y163" s="5"/>
-      <c r="Z163" s="5"/>
+      <c r="B163" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="D163" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="E163" s="4"/>
+      <c r="F163" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="G163" s="4"/>
+      <c r="H163" s="4"/>
     </row>
     <row r="164" spans="1:26" ht="13">
       <c r="A164" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B164" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="C164" s="38"/>
-      <c r="D164" s="5"/>
-      <c r="E164" s="5"/>
+        <v>324</v>
+      </c>
+      <c r="B164" s="34" t="s">
+        <v>325</v>
+      </c>
+      <c r="C164" s="35" t="s">
+        <v>326</v>
+      </c>
+      <c r="D164" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="E164" s="9" t="s">
+        <v>135</v>
+      </c>
       <c r="F164" s="9"/>
       <c r="G164" s="8"/>
       <c r="H164" s="5"/>
@@ -6631,10 +6631,10 @@
       <c r="A165" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B165" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="C165" s="38" t="s">
+      <c r="B165" s="34" t="s">
+        <v>328</v>
+      </c>
+      <c r="C165" s="36" t="s">
         <v>19</v>
       </c>
       <c r="D165" s="5"/>
@@ -6665,16 +6665,16 @@
     </row>
     <row r="166" spans="1:26" ht="13">
       <c r="A166" s="8" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="B166" s="34" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="C166" s="37" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="D166" s="32" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="E166" s="5" t="s">
         <v>135</v>
@@ -6706,7 +6706,7 @@
         <v>284</v>
       </c>
       <c r="B167" s="8" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="C167" s="8" t="s">
         <v>286</v>
@@ -6718,7 +6718,7 @@
         <v>135</v>
       </c>
       <c r="F167" s="9" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="G167" s="8"/>
       <c r="H167" s="5"/>
@@ -6746,9 +6746,9 @@
         <v>34</v>
       </c>
       <c r="B168" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="C168" s="8"/>
+        <v>328</v>
+      </c>
+      <c r="C168" s="38"/>
       <c r="D168" s="5"/>
       <c r="E168" s="5"/>
       <c r="F168" s="9"/>
@@ -6778,9 +6778,9 @@
         <v>17</v>
       </c>
       <c r="B169" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="C169" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="C169" s="38" t="s">
         <v>19</v>
       </c>
       <c r="D169" s="5"/>
@@ -6811,16 +6811,16 @@
     </row>
     <row r="170" spans="1:26" ht="13">
       <c r="A170" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="B170" s="8" t="s">
-        <v>345</v>
-      </c>
-      <c r="C170" s="18" t="s">
-        <v>346</v>
-      </c>
-      <c r="D170" s="18" t="s">
-        <v>347</v>
+        <v>337</v>
+      </c>
+      <c r="B170" s="34" t="s">
+        <v>338</v>
+      </c>
+      <c r="C170" s="37" t="s">
+        <v>339</v>
+      </c>
+      <c r="D170" s="32" t="s">
+        <v>340</v>
       </c>
       <c r="E170" s="5" t="s">
         <v>135</v>
@@ -6849,15 +6849,23 @@
     </row>
     <row r="171" spans="1:26" ht="13">
       <c r="A171" s="8" t="s">
-        <v>34</v>
+        <v>284</v>
       </c>
       <c r="B171" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="C171" s="8"/>
-      <c r="D171" s="5"/>
-      <c r="E171" s="5"/>
-      <c r="F171" s="9"/>
+        <v>341</v>
+      </c>
+      <c r="C171" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="D171" s="32" t="s">
+        <v>334</v>
+      </c>
+      <c r="E171" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F171" s="9" t="s">
+        <v>342</v>
+      </c>
       <c r="G171" s="8"/>
       <c r="H171" s="5"/>
       <c r="I171" s="5"/>
@@ -6881,20 +6889,16 @@
     </row>
     <row r="172" spans="1:26" ht="13">
       <c r="A172" s="8" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="B172" s="8" t="s">
-        <v>348</v>
-      </c>
-      <c r="C172" s="8" t="s">
-        <v>19</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="C172" s="8"/>
       <c r="D172" s="5"/>
       <c r="E172" s="5"/>
       <c r="F172" s="9"/>
-      <c r="G172" s="8" t="s">
-        <v>99</v>
-      </c>
+      <c r="G172" s="8"/>
       <c r="H172" s="5"/>
       <c r="I172" s="5"/>
       <c r="J172" s="5"/>
@@ -6917,24 +6921,20 @@
     </row>
     <row r="173" spans="1:26" ht="13">
       <c r="A173" s="8" t="s">
-        <v>349</v>
+        <v>17</v>
       </c>
       <c r="B173" s="8" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="C173" s="8" t="s">
-        <v>351</v>
-      </c>
-      <c r="D173" s="8" t="s">
-        <v>352</v>
-      </c>
-      <c r="E173" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="F173" s="9" t="s">
-        <v>353</v>
-      </c>
-      <c r="G173" s="8"/>
+        <v>19</v>
+      </c>
+      <c r="D173" s="5"/>
+      <c r="E173" s="5"/>
+      <c r="F173" s="9"/>
+      <c r="G173" s="8" t="s">
+        <v>99</v>
+      </c>
       <c r="H173" s="5"/>
       <c r="I173" s="5"/>
       <c r="J173" s="5"/>
@@ -6957,14 +6957,20 @@
     </row>
     <row r="174" spans="1:26" ht="13">
       <c r="A174" s="8" t="s">
-        <v>34</v>
+        <v>344</v>
       </c>
       <c r="B174" s="8" t="s">
-        <v>348</v>
-      </c>
-      <c r="C174" s="8"/>
-      <c r="D174" s="5"/>
-      <c r="E174" s="5"/>
+        <v>345</v>
+      </c>
+      <c r="C174" s="18" t="s">
+        <v>346</v>
+      </c>
+      <c r="D174" s="18" t="s">
+        <v>347</v>
+      </c>
+      <c r="E174" s="5" t="s">
+        <v>135</v>
+      </c>
       <c r="F174" s="9"/>
       <c r="G174" s="8"/>
       <c r="H174" s="5"/>
@@ -6989,20 +6995,16 @@
     </row>
     <row r="175" spans="1:26" ht="13">
       <c r="A175" s="8" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="B175" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="C175" s="8" t="s">
-        <v>19</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="C175" s="8"/>
       <c r="D175" s="5"/>
       <c r="E175" s="5"/>
       <c r="F175" s="9"/>
-      <c r="G175" s="8" t="s">
-        <v>99</v>
-      </c>
+      <c r="G175" s="8"/>
       <c r="H175" s="5"/>
       <c r="I175" s="5"/>
       <c r="J175" s="5"/>
@@ -7025,30 +7027,24 @@
     </row>
     <row r="176" spans="1:26" ht="13">
       <c r="A176" s="8" t="s">
-        <v>355</v>
+        <v>17</v>
       </c>
       <c r="B176" s="8" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="C176" s="8" t="s">
-        <v>357</v>
-      </c>
-      <c r="D176" s="18" t="s">
-        <v>358</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="D176" s="5"/>
       <c r="E176" s="5"/>
-      <c r="F176" s="9" t="s">
-        <v>353</v>
-      </c>
-      <c r="G176" s="8"/>
+      <c r="F176" s="9"/>
+      <c r="G176" s="8" t="s">
+        <v>99</v>
+      </c>
       <c r="H176" s="5"/>
-      <c r="I176" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="J176" s="11" t="s">
-        <v>360</v>
-      </c>
-      <c r="K176" s="15"/>
+      <c r="I176" s="5"/>
+      <c r="J176" s="5"/>
+      <c r="K176" s="5"/>
       <c r="L176" s="5"/>
       <c r="M176" s="5"/>
       <c r="N176" s="5"/>
@@ -7067,16 +7063,16 @@
     </row>
     <row r="177" spans="1:26" ht="13">
       <c r="A177" s="8" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="B177" s="8" t="s">
-        <v>362</v>
-      </c>
-      <c r="C177" s="39" t="s">
-        <v>363</v>
-      </c>
-      <c r="D177" s="32" t="s">
-        <v>364</v>
+        <v>350</v>
+      </c>
+      <c r="C177" s="8" t="s">
+        <v>351</v>
+      </c>
+      <c r="D177" s="8" t="s">
+        <v>352</v>
       </c>
       <c r="E177" s="5" t="s">
         <v>135</v>
@@ -7110,7 +7106,7 @@
         <v>34</v>
       </c>
       <c r="B178" s="8" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="C178" s="8"/>
       <c r="D178" s="5"/>
@@ -7142,7 +7138,7 @@
         <v>17</v>
       </c>
       <c r="B179" s="8" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="C179" s="8" t="s">
         <v>19</v>
@@ -7175,28 +7171,30 @@
     </row>
     <row r="180" spans="1:26" ht="13">
       <c r="A180" s="8" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="B180" s="8" t="s">
-        <v>366</v>
-      </c>
-      <c r="C180" s="39" t="s">
-        <v>367</v>
+        <v>356</v>
+      </c>
+      <c r="C180" s="8" t="s">
+        <v>357</v>
       </c>
       <c r="D180" s="18" t="s">
-        <v>368</v>
-      </c>
-      <c r="E180" s="5" t="s">
-        <v>135</v>
-      </c>
+        <v>358</v>
+      </c>
+      <c r="E180" s="5"/>
       <c r="F180" s="9" t="s">
         <v>353</v>
       </c>
       <c r="G180" s="8"/>
       <c r="H180" s="5"/>
-      <c r="I180" s="5"/>
-      <c r="J180" s="5"/>
-      <c r="K180" s="5"/>
+      <c r="I180" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="J180" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="K180" s="15"/>
       <c r="L180" s="5"/>
       <c r="M180" s="5"/>
       <c r="N180" s="5"/>
@@ -7215,30 +7213,28 @@
     </row>
     <row r="181" spans="1:26" ht="13">
       <c r="A181" s="8" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B181" s="8" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="C181" s="39" t="s">
-        <v>370</v>
-      </c>
-      <c r="D181" s="18" t="s">
-        <v>371</v>
-      </c>
-      <c r="E181" s="5"/>
+        <v>363</v>
+      </c>
+      <c r="D181" s="32" t="s">
+        <v>364</v>
+      </c>
+      <c r="E181" s="5" t="s">
+        <v>135</v>
+      </c>
       <c r="F181" s="9" t="s">
-        <v>372</v>
+        <v>353</v>
       </c>
       <c r="G181" s="8"/>
       <c r="H181" s="5"/>
-      <c r="I181" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="J181" s="11" t="s">
-        <v>374</v>
-      </c>
-      <c r="K181" s="15"/>
+      <c r="I181" s="5"/>
+      <c r="J181" s="5"/>
+      <c r="K181" s="5"/>
       <c r="L181" s="5"/>
       <c r="M181" s="5"/>
       <c r="N181" s="5"/>
@@ -7260,12 +7256,12 @@
         <v>34</v>
       </c>
       <c r="B182" s="8" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="C182" s="8"/>
       <c r="D182" s="5"/>
       <c r="E182" s="5"/>
-      <c r="F182" s="8"/>
+      <c r="F182" s="9"/>
       <c r="G182" s="8"/>
       <c r="H182" s="5"/>
       <c r="I182" s="5"/>
@@ -7288,218 +7284,376 @@
       <c r="Z182" s="5"/>
     </row>
     <row r="183" spans="1:26" ht="13">
-      <c r="A183" s="1" t="s">
+      <c r="A183" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B183" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="C183" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D183" s="5"/>
+      <c r="E183" s="5"/>
+      <c r="F183" s="9"/>
+      <c r="G183" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="H183" s="5"/>
+      <c r="I183" s="5"/>
+      <c r="J183" s="5"/>
+      <c r="K183" s="5"/>
+      <c r="L183" s="5"/>
+      <c r="M183" s="5"/>
+      <c r="N183" s="5"/>
+      <c r="O183" s="5"/>
+      <c r="P183" s="5"/>
+      <c r="Q183" s="5"/>
+      <c r="R183" s="5"/>
+      <c r="S183" s="5"/>
+      <c r="T183" s="5"/>
+      <c r="U183" s="5"/>
+      <c r="V183" s="5"/>
+      <c r="W183" s="5"/>
+      <c r="X183" s="5"/>
+      <c r="Y183" s="5"/>
+      <c r="Z183" s="5"/>
+    </row>
+    <row r="184" spans="1:26" ht="13">
+      <c r="A184" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="B184" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="C184" s="39" t="s">
+        <v>367</v>
+      </c>
+      <c r="D184" s="18" t="s">
+        <v>368</v>
+      </c>
+      <c r="E184" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F184" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="G184" s="8"/>
+      <c r="H184" s="5"/>
+      <c r="I184" s="5"/>
+      <c r="J184" s="5"/>
+      <c r="K184" s="5"/>
+      <c r="L184" s="5"/>
+      <c r="M184" s="5"/>
+      <c r="N184" s="5"/>
+      <c r="O184" s="5"/>
+      <c r="P184" s="5"/>
+      <c r="Q184" s="5"/>
+      <c r="R184" s="5"/>
+      <c r="S184" s="5"/>
+      <c r="T184" s="5"/>
+      <c r="U184" s="5"/>
+      <c r="V184" s="5"/>
+      <c r="W184" s="5"/>
+      <c r="X184" s="5"/>
+      <c r="Y184" s="5"/>
+      <c r="Z184" s="5"/>
+    </row>
+    <row r="185" spans="1:26" ht="13">
+      <c r="A185" s="8" t="s">
+        <v>355</v>
+      </c>
+      <c r="B185" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="C185" s="39" t="s">
+        <v>370</v>
+      </c>
+      <c r="D185" s="18" t="s">
+        <v>371</v>
+      </c>
+      <c r="E185" s="5"/>
+      <c r="F185" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="G185" s="8"/>
+      <c r="H185" s="5"/>
+      <c r="I185" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="J185" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="K185" s="15"/>
+      <c r="L185" s="5"/>
+      <c r="M185" s="5"/>
+      <c r="N185" s="5"/>
+      <c r="O185" s="5"/>
+      <c r="P185" s="5"/>
+      <c r="Q185" s="5"/>
+      <c r="R185" s="5"/>
+      <c r="S185" s="5"/>
+      <c r="T185" s="5"/>
+      <c r="U185" s="5"/>
+      <c r="V185" s="5"/>
+      <c r="W185" s="5"/>
+      <c r="X185" s="5"/>
+      <c r="Y185" s="5"/>
+      <c r="Z185" s="5"/>
+    </row>
+    <row r="186" spans="1:26" ht="13">
+      <c r="A186" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B183" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="C183" s="1"/>
-      <c r="F183" s="19"/>
-      <c r="G183" s="1"/>
-    </row>
-    <row r="184" spans="1:26" ht="13">
-      <c r="A184" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B184" s="40" t="s">
-        <v>375</v>
-      </c>
-      <c r="C184" s="18" t="s">
-        <v>376</v>
-      </c>
-      <c r="D184" s="18" t="s">
-        <v>377</v>
-      </c>
-      <c r="G184" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="185" spans="1:26" ht="13">
-      <c r="A185" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B185" s="40" t="s">
-        <v>378</v>
-      </c>
-      <c r="C185" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="G185" s="1"/>
-    </row>
-    <row r="186" spans="1:26" ht="13">
-      <c r="A186" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B186" s="40" t="s">
-        <v>375</v>
-      </c>
-      <c r="C186" s="1"/>
-      <c r="D186" s="28"/>
-      <c r="G186" s="1"/>
+      <c r="B186" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="C186" s="8"/>
+      <c r="D186" s="5"/>
+      <c r="E186" s="5"/>
+      <c r="F186" s="8"/>
+      <c r="G186" s="8"/>
+      <c r="H186" s="5"/>
+      <c r="I186" s="5"/>
+      <c r="J186" s="5"/>
+      <c r="K186" s="5"/>
+      <c r="L186" s="5"/>
+      <c r="M186" s="5"/>
+      <c r="N186" s="5"/>
+      <c r="O186" s="5"/>
+      <c r="P186" s="5"/>
+      <c r="Q186" s="5"/>
+      <c r="R186" s="5"/>
+      <c r="S186" s="5"/>
+      <c r="T186" s="5"/>
+      <c r="U186" s="5"/>
+      <c r="V186" s="5"/>
+      <c r="W186" s="5"/>
+      <c r="X186" s="5"/>
+      <c r="Y186" s="5"/>
+      <c r="Z186" s="5"/>
     </row>
     <row r="187" spans="1:26" ht="13">
       <c r="A187" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B187" s="40" t="s">
-        <v>381</v>
-      </c>
-      <c r="C187" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="D187" s="28" t="s">
-        <v>383</v>
-      </c>
-      <c r="G187" s="1" t="s">
-        <v>99</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B187" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="C187" s="1"/>
+      <c r="F187" s="19"/>
+      <c r="G187" s="1"/>
     </row>
     <row r="188" spans="1:26" ht="13">
       <c r="A188" s="1" t="s">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="B188" s="40" t="s">
-        <v>384</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="D188" s="28" t="s">
-        <v>386</v>
-      </c>
-      <c r="F188" s="1" t="s">
-        <v>387</v>
+        <v>375</v>
+      </c>
+      <c r="C188" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="D188" s="18" t="s">
+        <v>377</v>
+      </c>
+      <c r="G188" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="189" spans="1:26" ht="13">
       <c r="A189" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B189" s="1" t="s">
-        <v>388</v>
+      <c r="B189" s="40" t="s">
+        <v>378</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="D189" s="28" t="s">
-        <v>390</v>
-      </c>
-      <c r="F189" s="1" t="s">
-        <v>391</v>
-      </c>
+        <v>379</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="G189" s="1"/>
     </row>
     <row r="190" spans="1:26" ht="13">
       <c r="A190" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B190" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="C190" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="D190" s="28" t="s">
-        <v>394</v>
-      </c>
-      <c r="F190" s="1" t="s">
-        <v>395</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B190" s="40" t="s">
+        <v>375</v>
+      </c>
+      <c r="C190" s="1"/>
+      <c r="D190" s="28"/>
+      <c r="G190" s="1"/>
     </row>
     <row r="191" spans="1:26" ht="13">
       <c r="A191" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B191" s="1" t="s">
-        <v>396</v>
+        <v>17</v>
+      </c>
+      <c r="B191" s="40" t="s">
+        <v>381</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="D191" s="28" t="s">
-        <v>398</v>
-      </c>
-      <c r="F191" s="1" t="s">
-        <v>399</v>
+        <v>383</v>
+      </c>
+      <c r="G191" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="192" spans="1:26" ht="13">
       <c r="A192" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B192" s="40" t="s">
+        <v>384</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="D192" s="28" t="s">
+        <v>386</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12" ht="13">
+      <c r="A193" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="D193" s="28" t="s">
+        <v>390</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="194" spans="1:12" ht="13">
+      <c r="A194" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="D194" s="28" t="s">
+        <v>394</v>
+      </c>
+      <c r="F194" s="1" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12" ht="13">
+      <c r="A195" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="D195" s="28" t="s">
+        <v>806</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12" s="61" customFormat="1" ht="13">
+      <c r="A196" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="B196" s="28" t="s">
+        <v>800</v>
+      </c>
+      <c r="C196" s="28" t="s">
+        <v>801</v>
+      </c>
+      <c r="D196" s="28" t="s">
+        <v>804</v>
+      </c>
+      <c r="F196" s="28"/>
+    </row>
+    <row r="197" spans="1:12" ht="13">
+      <c r="A197" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B192" s="1" t="s">
+      <c r="B197" s="1" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="193" spans="1:12" ht="14.25">
-      <c r="A193" s="1" t="s">
+    <row r="198" spans="1:12" ht="14.25">
+      <c r="A198" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B193" s="27" t="s">
+      <c r="B198" s="27" t="s">
+        <v>399</v>
+      </c>
+      <c r="L198" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="L193" s="1" t="s">
+    </row>
+    <row r="199" spans="1:12" ht="14.25">
+      <c r="A199" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B199" s="27" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="194" spans="1:12" ht="14.25">
-      <c r="A194" s="1" t="s">
+      <c r="L199" s="1" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="200" spans="1:12" s="61" customFormat="1" ht="14.25">
+      <c r="A200" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="B194" s="27" t="s">
-        <v>402</v>
-      </c>
-      <c r="L194" s="1" t="s">
+      <c r="B200" s="41" t="s">
+        <v>802</v>
+      </c>
+      <c r="L200" s="28" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="201" spans="1:12" ht="14.25">
+      <c r="A201" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B201" s="27" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="195" spans="1:12" ht="14.25">
-      <c r="A195" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B195" s="27" t="s">
-        <v>404</v>
-      </c>
-      <c r="L195" s="1" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="198" spans="1:12" ht="14.25">
-      <c r="C198" s="27"/>
-    </row>
-    <row r="199" spans="1:12" ht="14.25">
-      <c r="B199" s="41"/>
-      <c r="C199" s="27"/>
-    </row>
-    <row r="201" spans="1:12" ht="14.25">
-      <c r="B201" s="41"/>
-    </row>
-    <row r="202" spans="1:12" ht="13">
-      <c r="B202" s="40"/>
-    </row>
-    <row r="203" spans="1:12" ht="14.25">
-      <c r="B203" s="41"/>
+      <c r="L201" s="1" t="s">
+        <v>803</v>
+      </c>
     </row>
     <row r="204" spans="1:12" ht="14.25">
-      <c r="B204" s="41"/>
-    </row>
-    <row r="205" spans="1:12" ht="13">
-      <c r="B205" s="40"/>
-    </row>
-    <row r="206" spans="1:12" ht="14.25">
-      <c r="B206" s="41"/>
-    </row>
-    <row r="207" spans="1:12" ht="13">
-      <c r="B207" s="40"/>
-    </row>
-    <row r="208" spans="1:12" ht="14.25">
-      <c r="B208" s="41"/>
-    </row>
-    <row r="209" spans="2:3" ht="13">
-      <c r="B209" s="40"/>
+      <c r="C204" s="27"/>
+    </row>
+    <row r="205" spans="1:12" ht="14.25">
+      <c r="B205" s="41"/>
+      <c r="C205" s="27"/>
+    </row>
+    <row r="207" spans="1:12" ht="14.25">
+      <c r="B207" s="41"/>
+    </row>
+    <row r="208" spans="1:12" ht="13">
+      <c r="B208" s="40"/>
+    </row>
+    <row r="209" spans="2:3" ht="14.25">
+      <c r="B209" s="41"/>
     </row>
     <row r="210" spans="2:3" ht="14.25">
       <c r="B210" s="41"/>
@@ -7507,24 +7661,42 @@
     <row r="211" spans="2:3" ht="13">
       <c r="B211" s="40"/>
     </row>
-    <row r="213" spans="2:3" ht="14.25">
-      <c r="C213" s="41"/>
-    </row>
-    <row r="214" spans="2:3" ht="13">
-      <c r="B214" s="40"/>
+    <row r="212" spans="2:3" ht="14.25">
+      <c r="B212" s="41"/>
+    </row>
+    <row r="213" spans="2:3" ht="13">
+      <c r="B213" s="40"/>
+    </row>
+    <row r="214" spans="2:3" ht="14.25">
+      <c r="B214" s="41"/>
     </row>
     <row r="215" spans="2:3" ht="13">
       <c r="B215" s="40"/>
     </row>
-    <row r="217" spans="2:3" ht="14.25">
-      <c r="B217" s="27"/>
-    </row>
-    <row r="218" spans="2:3" ht="14.25">
-      <c r="B218" s="41"/>
+    <row r="216" spans="2:3" ht="14.25">
+      <c r="B216" s="41"/>
+    </row>
+    <row r="217" spans="2:3" ht="13">
+      <c r="B217" s="40"/>
+    </row>
+    <row r="219" spans="2:3" ht="14.25">
+      <c r="C219" s="41"/>
+    </row>
+    <row r="220" spans="2:3" ht="13">
+      <c r="B220" s="40"/>
+    </row>
+    <row r="221" spans="2:3" ht="13">
+      <c r="B221" s="40"/>
+    </row>
+    <row r="223" spans="2:3" ht="14.25">
+      <c r="B223" s="27"/>
+    </row>
+    <row r="224" spans="2:3" ht="14.25">
+      <c r="B224" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="L31:Q31"/>
+    <mergeCell ref="L33:Q33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7545,7 +7717,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1">
       <c r="A1" s="42" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B1" s="42" t="s">
         <v>1</v>
@@ -7562,30 +7734,30 @@
     </row>
     <row r="2" spans="1:26" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>135</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>410</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="15.75" customHeight="1">
@@ -7593,13 +7765,13 @@
         <v>202</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="D4" s="28" t="s">
         <v>413</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="15.75" customHeight="1">
@@ -7607,13 +7779,13 @@
         <v>202</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>416</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="15.75" customHeight="1">
@@ -7621,13 +7793,13 @@
         <v>267</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -7657,13 +7829,13 @@
         <v>267</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -7693,13 +7865,13 @@
         <v>267</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="D8" s="18" t="s">
         <v>423</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>424</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>425</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
@@ -7729,16 +7901,16 @@
         <v>271</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="D9" s="18" t="s">
         <v>426</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>427</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>428</v>
-      </c>
       <c r="E9" s="5" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
@@ -7767,16 +7939,16 @@
         <v>271</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="D10" s="18" t="s">
         <v>429</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>430</v>
-      </c>
-      <c r="D10" s="18" t="s">
-        <v>431</v>
-      </c>
       <c r="E10" s="5" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
@@ -7805,16 +7977,16 @@
         <v>271</v>
       </c>
       <c r="B11" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="D11" s="18" t="s">
         <v>432</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>433</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>434</v>
-      </c>
       <c r="E11" s="5" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
@@ -7843,16 +8015,16 @@
         <v>271</v>
       </c>
       <c r="B12" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="D12" s="18" t="s">
         <v>435</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>437</v>
-      </c>
       <c r="E12" s="5" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
@@ -7881,16 +8053,16 @@
         <v>271</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="D13" s="18" t="s">
         <v>438</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>440</v>
-      </c>
       <c r="E13" s="5" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
@@ -7919,16 +8091,16 @@
         <v>271</v>
       </c>
       <c r="B14" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="D14" s="18" t="s">
         <v>441</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>442</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>443</v>
-      </c>
       <c r="E14" s="5" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
@@ -7957,16 +8129,16 @@
         <v>271</v>
       </c>
       <c r="B15" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="D15" s="18" t="s">
         <v>444</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>445</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>446</v>
-      </c>
       <c r="E15" s="5" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
@@ -7995,16 +8167,16 @@
         <v>271</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
@@ -8033,16 +8205,16 @@
         <v>271</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
@@ -8071,16 +8243,16 @@
         <v>271</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
@@ -8109,16 +8281,16 @@
         <v>271</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
@@ -8151,13 +8323,13 @@
         <v>chakechakedistricthospital</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
@@ -8190,13 +8362,13 @@
         <v>pujiniphcu+</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
@@ -8229,13 +8401,13 @@
         <v>tundauwaphcu+</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
@@ -8268,13 +8440,13 @@
         <v>vitongojiphcc</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
@@ -8307,13 +8479,13 @@
         <v>weshaphcu+</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
@@ -8346,13 +8518,13 @@
         <v>kondephcu+</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
@@ -8385,13 +8557,13 @@
         <v>makangalephcu+</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
@@ -8424,13 +8596,13 @@
         <v>maziwangombephcu+</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
@@ -8463,13 +8635,13 @@
         <v>micheweniphcc</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
@@ -8502,13 +8674,13 @@
         <v>wingwiphcu+</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
@@ -8541,13 +8713,13 @@
         <v>kiuyumbuyuniphcu+</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
@@ -8580,13 +8752,13 @@
         <v>bogoaphcu+</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
@@ -8619,13 +8791,13 @@
         <v>kengejaphcu+</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
@@ -8658,13 +8830,13 @@
         <v>abdallahmzeedistricthospital</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
@@ -8697,13 +8869,13 @@
         <v>michenzaniphcu+</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
@@ -8736,13 +8908,13 @@
         <v>fundophcu+</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
@@ -8775,13 +8947,13 @@
         <v>kojaniphcu+</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
@@ -8814,13 +8986,13 @@
         <v>makongeniphcu+</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
@@ -8853,13 +9025,13 @@
         <v>wetedistricthospital</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D38" s="18" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
@@ -8892,13 +9064,13 @@
         <v>mzambarauniphcu+</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
@@ -8931,13 +9103,13 @@
         <v>junguniphcu+</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
@@ -8970,13 +9142,13 @@
         <v>ukunjwiphcu+</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
@@ -9009,13 +9181,13 @@
         <v>uondwephcu+</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
@@ -9048,13 +9220,13 @@
         <v>chwakaphcu+</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
@@ -9087,13 +9259,13 @@
         <v>mweraphcu+</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
@@ -9126,13 +9298,13 @@
         <v>ungujaukuuphcu+</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
@@ -9165,13 +9337,13 @@
         <v>uziniphcu+</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
@@ -9204,13 +9376,13 @@
         <v>uroaphcu+</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
@@ -9243,13 +9415,13 @@
         <v>kivungedistricthospital</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D48" s="18" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
@@ -9282,13 +9454,13 @@
         <v>matemwephcu+</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
@@ -9321,13 +9493,13 @@
         <v>nungwiphcu+</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
@@ -9360,13 +9532,13 @@
         <v>pwanimchanganiphcu+</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
@@ -9399,13 +9571,13 @@
         <v>tumbatugomaniphcu+</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
@@ -9438,13 +9610,13 @@
         <v>kendwaphcu+</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
@@ -9477,13 +9649,13 @@
         <v>bumbwinimisufiniphcu+</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
@@ -9516,13 +9688,13 @@
         <v>dongevijibweniphcu+</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
@@ -9555,13 +9727,13 @@
         <v>kiongwephcu</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
@@ -9594,13 +9766,13 @@
         <v>kitopephcu</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
@@ -9633,13 +9805,13 @@
         <v>mahondaphcu+</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
@@ -9672,13 +9844,13 @@
         <v>jambianiphcu+</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="F59" s="5"/>
       <c r="G59" s="5"/>
@@ -9711,13 +9883,13 @@
         <v>makunduchidistricthospital</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
@@ -9750,13 +9922,13 @@
         <v>muyuniphcu+</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="F61" s="5"/>
       <c r="G61" s="5"/>
@@ -9789,13 +9961,13 @@
         <v>bwejuuphcu+</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="F62" s="5"/>
       <c r="G62" s="5"/>
@@ -9828,13 +10000,13 @@
         <v>chumbuniphcu+</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F63" s="5"/>
       <c r="G63" s="5"/>
@@ -9867,13 +10039,13 @@
         <v>mnazimmojahospital</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D64" s="18" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F64" s="5"/>
       <c r="G64" s="5"/>
@@ -9906,13 +10078,13 @@
         <v>mwembeladumchclinic</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F65" s="5"/>
       <c r="G65" s="5"/>
@@ -9945,13 +10117,13 @@
         <v>sebleniphcu+</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="5"/>
@@ -9984,13 +10156,13 @@
         <v>chukwaniphcu+</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="5"/>
@@ -10023,13 +10195,13 @@
         <v>fuoniphcu+</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="5"/>
@@ -10062,13 +10234,13 @@
         <v>kombeniphcu+</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
@@ -10101,13 +10273,13 @@
         <v>mtofaaniphcu+(kinuni)</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F70" s="5"/>
       <c r="G70" s="5"/>
@@ -10140,13 +10312,13 @@
         <v>bumbwisudiphcu+</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F71" s="5"/>
       <c r="G71" s="5"/>
@@ -10179,13 +10351,13 @@
         <v>selemphcu+</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F72" s="5"/>
       <c r="G72" s="5"/>
@@ -10218,13 +10390,13 @@
         <v>other</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D73" s="18" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F73" s="5"/>
       <c r="G73" s="5"/>
@@ -10257,13 +10429,13 @@
         <v>other</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D74" s="18" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F74" s="5"/>
       <c r="G74" s="5"/>
@@ -10296,13 +10468,13 @@
         <v>other</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D75" s="18" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F75" s="5"/>
       <c r="G75" s="5"/>
@@ -10335,13 +10507,13 @@
         <v>other</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D76" s="18" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F76" s="5"/>
       <c r="G76" s="5"/>
@@ -10374,13 +10546,13 @@
         <v>other</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D77" s="18" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F77" s="5"/>
       <c r="G77" s="5"/>
@@ -10413,13 +10585,13 @@
         <v>other</v>
       </c>
       <c r="C78" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="D78" s="18" t="s">
+        <v>512</v>
+      </c>
+      <c r="E78" s="5" t="s">
         <v>424</v>
-      </c>
-      <c r="D78" s="18" t="s">
-        <v>514</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>426</v>
       </c>
       <c r="F78" s="5"/>
       <c r="G78" s="5"/>
@@ -10452,13 +10624,13 @@
         <v>other</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D79" s="18" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="F79" s="5"/>
       <c r="G79" s="5"/>
@@ -10491,13 +10663,13 @@
         <v>other</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D80" s="18" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="F80" s="5"/>
       <c r="G80" s="5"/>
@@ -10530,13 +10702,13 @@
         <v>other</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D81" s="18" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F81" s="5"/>
       <c r="G81" s="5"/>
@@ -10569,13 +10741,13 @@
         <v>other</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D82" s="18" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F82" s="5"/>
       <c r="G82" s="5"/>
@@ -10608,13 +10780,13 @@
         <v>other</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D83" s="18" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="F83" s="5"/>
       <c r="G83" s="5"/>
@@ -10646,10 +10818,10 @@
         <v>135</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D84" s="32" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E84" s="5"/>
       <c r="F84" s="5"/>
@@ -10679,13 +10851,13 @@
         <v>290</v>
       </c>
       <c r="B85" s="5" t="s">
+        <v>515</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="D85" s="32" t="s">
         <v>517</v>
-      </c>
-      <c r="C85" s="5" t="s">
-        <v>518</v>
-      </c>
-      <c r="D85" s="32" t="s">
-        <v>519</v>
       </c>
       <c r="E85" s="15"/>
       <c r="F85" s="15"/>
@@ -10715,13 +10887,13 @@
         <v>290</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D86" s="32" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E86" s="5"/>
       <c r="F86" s="5"/>
@@ -10748,16 +10920,16 @@
     </row>
     <row r="87" spans="1:26" ht="13">
       <c r="A87" s="5" t="s">
+        <v>520</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>521</v>
+      </c>
+      <c r="C87" s="5" t="s">
         <v>522</v>
       </c>
-      <c r="B87" s="5" t="s">
+      <c r="D87" s="32" t="s">
         <v>523</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="D87" s="32" t="s">
-        <v>525</v>
       </c>
       <c r="E87" s="5"/>
       <c r="F87" s="5"/>
@@ -10784,16 +10956,16 @@
     </row>
     <row r="88" spans="1:26" ht="13">
       <c r="A88" s="5" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B88" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>525</v>
+      </c>
+      <c r="D88" s="32" t="s">
         <v>526</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="D88" s="32" t="s">
-        <v>528</v>
       </c>
       <c r="E88" s="5"/>
       <c r="F88" s="5"/>
@@ -10820,16 +10992,16 @@
     </row>
     <row r="89" spans="1:26" ht="13">
       <c r="A89" s="5" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B89" s="5" t="s">
+        <v>527</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>528</v>
+      </c>
+      <c r="D89" s="32" t="s">
         <v>529</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>530</v>
-      </c>
-      <c r="D89" s="32" t="s">
-        <v>531</v>
       </c>
       <c r="E89" s="5"/>
       <c r="F89" s="5"/>
@@ -10856,16 +11028,16 @@
     </row>
     <row r="90" spans="1:26" ht="13">
       <c r="A90" s="5" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B90" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="D90" s="32" t="s">
         <v>532</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>533</v>
-      </c>
-      <c r="D90" s="32" t="s">
-        <v>534</v>
       </c>
       <c r="E90" s="15"/>
       <c r="F90" s="5"/>
@@ -10892,16 +11064,16 @@
     </row>
     <row r="91" spans="1:26" ht="13">
       <c r="A91" s="5" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B91" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="D91" s="32" t="s">
         <v>535</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>536</v>
-      </c>
-      <c r="D91" s="32" t="s">
-        <v>537</v>
       </c>
       <c r="E91" s="5"/>
       <c r="F91" s="5"/>
@@ -10928,16 +11100,16 @@
     </row>
     <row r="92" spans="1:26" ht="13">
       <c r="A92" s="5" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D92" s="32" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E92" s="5"/>
       <c r="F92" s="5"/>
@@ -10967,13 +11139,13 @@
         <v>299</v>
       </c>
       <c r="B93" s="5" t="s">
+        <v>537</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>538</v>
+      </c>
+      <c r="D93" s="32" t="s">
         <v>539</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>540</v>
-      </c>
-      <c r="D93" s="32" t="s">
-        <v>541</v>
       </c>
       <c r="E93" s="5"/>
       <c r="F93" s="5"/>
@@ -11003,13 +11175,13 @@
         <v>299</v>
       </c>
       <c r="B94" s="5" t="s">
+        <v>540</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>541</v>
+      </c>
+      <c r="D94" s="32" t="s">
         <v>542</v>
-      </c>
-      <c r="C94" s="5" t="s">
-        <v>543</v>
-      </c>
-      <c r="D94" s="32" t="s">
-        <v>544</v>
       </c>
       <c r="E94" s="5"/>
       <c r="F94" s="5"/>
@@ -11039,13 +11211,13 @@
         <v>299</v>
       </c>
       <c r="B95" s="5" t="s">
+        <v>543</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>544</v>
+      </c>
+      <c r="D95" s="32" t="s">
         <v>545</v>
-      </c>
-      <c r="C95" s="5" t="s">
-        <v>546</v>
-      </c>
-      <c r="D95" s="32" t="s">
-        <v>547</v>
       </c>
       <c r="E95" s="5"/>
       <c r="F95" s="5"/>
@@ -11075,13 +11247,13 @@
         <v>299</v>
       </c>
       <c r="B96" s="5" t="s">
+        <v>546</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>547</v>
+      </c>
+      <c r="D96" s="32" t="s">
         <v>548</v>
-      </c>
-      <c r="C96" s="5" t="s">
-        <v>549</v>
-      </c>
-      <c r="D96" s="32" t="s">
-        <v>550</v>
       </c>
       <c r="E96" s="5"/>
       <c r="F96" s="5"/>
@@ -11111,13 +11283,13 @@
         <v>299</v>
       </c>
       <c r="B97" s="5" t="s">
+        <v>549</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>550</v>
+      </c>
+      <c r="D97" s="32" t="s">
         <v>551</v>
-      </c>
-      <c r="C97" s="5" t="s">
-        <v>552</v>
-      </c>
-      <c r="D97" s="32" t="s">
-        <v>553</v>
       </c>
       <c r="E97" s="5"/>
       <c r="F97" s="5"/>
@@ -11147,13 +11319,13 @@
         <v>299</v>
       </c>
       <c r="B98" s="5" t="s">
+        <v>552</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>553</v>
+      </c>
+      <c r="D98" s="32" t="s">
         <v>554</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>555</v>
-      </c>
-      <c r="D98" s="32" t="s">
-        <v>556</v>
       </c>
       <c r="E98" s="5"/>
       <c r="F98" s="5"/>
@@ -11183,13 +11355,13 @@
         <v>299</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D99" s="32" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E99" s="5"/>
       <c r="F99" s="5"/>
@@ -11219,13 +11391,13 @@
         <v>304</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="D100" s="32" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="101" spans="1:26" ht="13">
@@ -11233,13 +11405,13 @@
         <v>304</v>
       </c>
       <c r="B101" s="5" t="s">
+        <v>557</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>558</v>
+      </c>
+      <c r="D101" s="32" t="s">
         <v>559</v>
-      </c>
-      <c r="C101" s="5" t="s">
-        <v>560</v>
-      </c>
-      <c r="D101" s="32" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="102" spans="1:26" ht="13">
@@ -11247,13 +11419,13 @@
         <v>304</v>
       </c>
       <c r="B102" s="5" t="s">
+        <v>560</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>561</v>
+      </c>
+      <c r="D102" s="32" t="s">
         <v>562</v>
-      </c>
-      <c r="C102" s="5" t="s">
-        <v>563</v>
-      </c>
-      <c r="D102" s="32" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="103" spans="1:26" ht="13">
@@ -11261,13 +11433,13 @@
         <v>304</v>
       </c>
       <c r="B103" s="5" t="s">
+        <v>563</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>564</v>
+      </c>
+      <c r="D103" s="32" t="s">
         <v>565</v>
-      </c>
-      <c r="C103" s="5" t="s">
-        <v>566</v>
-      </c>
-      <c r="D103" s="32" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="104" spans="1:26" ht="13">
@@ -11275,13 +11447,13 @@
         <v>304</v>
       </c>
       <c r="B104" s="5" t="s">
+        <v>566</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>567</v>
+      </c>
+      <c r="D104" s="32" t="s">
         <v>568</v>
-      </c>
-      <c r="C104" s="5" t="s">
-        <v>569</v>
-      </c>
-      <c r="D104" s="32" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="105" spans="1:26" ht="13">
@@ -11289,13 +11461,13 @@
         <v>304</v>
       </c>
       <c r="B105" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="D105" s="32" t="s">
         <v>571</v>
-      </c>
-      <c r="C105" s="5" t="s">
-        <v>572</v>
-      </c>
-      <c r="D105" s="32" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="106" spans="1:26" ht="13">
@@ -11303,13 +11475,13 @@
         <v>304</v>
       </c>
       <c r="B106" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>573</v>
+      </c>
+      <c r="D106" s="32" t="s">
         <v>574</v>
-      </c>
-      <c r="C106" s="5" t="s">
-        <v>575</v>
-      </c>
-      <c r="D106" s="32" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="107" spans="1:26" ht="13">
@@ -11317,13 +11489,13 @@
         <v>304</v>
       </c>
       <c r="B107" s="5" t="s">
+        <v>575</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="D107" s="32" t="s">
         <v>577</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>578</v>
-      </c>
-      <c r="D107" s="32" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="108" spans="1:26" ht="13">
@@ -11331,13 +11503,13 @@
         <v>304</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D108" s="32" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="109" spans="1:26" ht="13">
@@ -11345,97 +11517,97 @@
         <v>304</v>
       </c>
       <c r="B109" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="C109" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="D109" s="32" t="s">
         <v>581</v>
-      </c>
-      <c r="C109" s="5" t="s">
-        <v>582</v>
-      </c>
-      <c r="D109" s="32" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="110" spans="1:26" ht="13">
       <c r="A110" s="5" t="s">
+        <v>582</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>583</v>
+      </c>
+      <c r="C110" s="5" t="s">
         <v>584</v>
       </c>
-      <c r="B110" s="5" t="s">
+      <c r="D110" s="32" t="s">
         <v>585</v>
-      </c>
-      <c r="C110" s="5" t="s">
-        <v>586</v>
-      </c>
-      <c r="D110" s="32" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="111" spans="1:26" ht="13">
       <c r="A111" s="5" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B111" s="5" t="s">
+        <v>586</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>587</v>
+      </c>
+      <c r="D111" s="32" t="s">
         <v>588</v>
-      </c>
-      <c r="C111" s="5" t="s">
-        <v>589</v>
-      </c>
-      <c r="D111" s="32" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="112" spans="1:26" ht="13">
       <c r="A112" s="5" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B112" s="5" t="s">
+        <v>589</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>590</v>
+      </c>
+      <c r="D112" s="32" t="s">
         <v>591</v>
-      </c>
-      <c r="C112" s="5" t="s">
-        <v>592</v>
-      </c>
-      <c r="D112" s="32" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="113" spans="1:26" ht="13">
       <c r="A113" s="5" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B113" s="5" t="s">
+        <v>592</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>593</v>
+      </c>
+      <c r="D113" s="32" t="s">
         <v>594</v>
-      </c>
-      <c r="C113" s="5" t="s">
-        <v>595</v>
-      </c>
-      <c r="D113" s="32" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="114" spans="1:26" ht="13">
       <c r="A114" s="5" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="D114" s="32" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="115" spans="1:26" ht="13">
       <c r="A115" s="5" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B115" s="5" t="s">
+        <v>579</v>
+      </c>
+      <c r="C115" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="D115" s="32" t="s">
         <v>581</v>
-      </c>
-      <c r="C115" s="5" t="s">
-        <v>582</v>
-      </c>
-      <c r="D115" s="32" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="116" spans="1:26" ht="13">
@@ -11443,13 +11615,13 @@
         <v>325</v>
       </c>
       <c r="B116" s="5" t="s">
+        <v>595</v>
+      </c>
+      <c r="C116" s="5" t="s">
+        <v>596</v>
+      </c>
+      <c r="D116" s="32" t="s">
         <v>597</v>
-      </c>
-      <c r="C116" s="5" t="s">
-        <v>598</v>
-      </c>
-      <c r="D116" s="32" t="s">
-        <v>599</v>
       </c>
       <c r="E116" s="5"/>
       <c r="F116" s="5"/>
@@ -11479,13 +11651,13 @@
         <v>325</v>
       </c>
       <c r="B117" s="5" t="s">
+        <v>598</v>
+      </c>
+      <c r="C117" s="5" t="s">
+        <v>599</v>
+      </c>
+      <c r="D117" s="32" t="s">
         <v>600</v>
-      </c>
-      <c r="C117" s="5" t="s">
-        <v>601</v>
-      </c>
-      <c r="D117" s="32" t="s">
-        <v>602</v>
       </c>
       <c r="E117" s="5"/>
       <c r="F117" s="5"/>
@@ -11515,13 +11687,13 @@
         <v>325</v>
       </c>
       <c r="B118" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>602</v>
+      </c>
+      <c r="D118" s="32" t="s">
         <v>603</v>
-      </c>
-      <c r="C118" s="5" t="s">
-        <v>604</v>
-      </c>
-      <c r="D118" s="32" t="s">
-        <v>605</v>
       </c>
       <c r="E118" s="5"/>
       <c r="F118" s="5"/>
@@ -11551,13 +11723,13 @@
         <v>325</v>
       </c>
       <c r="B119" s="5" t="s">
+        <v>604</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="D119" s="18" t="s">
         <v>606</v>
-      </c>
-      <c r="C119" s="5" t="s">
-        <v>607</v>
-      </c>
-      <c r="D119" s="18" t="s">
-        <v>608</v>
       </c>
       <c r="E119" s="5"/>
       <c r="F119" s="5"/>
@@ -11587,13 +11759,13 @@
         <v>330</v>
       </c>
       <c r="B120" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>608</v>
+      </c>
+      <c r="D120" s="32" t="s">
         <v>609</v>
-      </c>
-      <c r="C120" s="5" t="s">
-        <v>610</v>
-      </c>
-      <c r="D120" s="32" t="s">
-        <v>611</v>
       </c>
       <c r="E120" s="5"/>
       <c r="F120" s="5"/>
@@ -11623,13 +11795,13 @@
         <v>330</v>
       </c>
       <c r="B121" s="5" t="s">
+        <v>610</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>611</v>
+      </c>
+      <c r="D121" s="32" t="s">
         <v>612</v>
-      </c>
-      <c r="C121" s="5" t="s">
-        <v>613</v>
-      </c>
-      <c r="D121" s="32" t="s">
-        <v>614</v>
       </c>
       <c r="E121" s="5"/>
       <c r="F121" s="5"/>
@@ -11659,13 +11831,13 @@
         <v>330</v>
       </c>
       <c r="B122" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="D122" s="32" t="s">
         <v>615</v>
-      </c>
-      <c r="C122" s="5" t="s">
-        <v>616</v>
-      </c>
-      <c r="D122" s="32" t="s">
-        <v>617</v>
       </c>
       <c r="E122" s="5"/>
       <c r="F122" s="5"/>
@@ -11695,13 +11867,13 @@
         <v>330</v>
       </c>
       <c r="B123" s="5" t="s">
+        <v>616</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>617</v>
+      </c>
+      <c r="D123" s="32" t="s">
         <v>618</v>
-      </c>
-      <c r="C123" s="5" t="s">
-        <v>619</v>
-      </c>
-      <c r="D123" s="32" t="s">
-        <v>620</v>
       </c>
       <c r="E123" s="5"/>
       <c r="F123" s="5"/>
@@ -11731,13 +11903,13 @@
         <v>330</v>
       </c>
       <c r="B124" s="5" t="s">
+        <v>619</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>620</v>
+      </c>
+      <c r="D124" s="32" t="s">
         <v>621</v>
-      </c>
-      <c r="C124" s="5" t="s">
-        <v>622</v>
-      </c>
-      <c r="D124" s="32" t="s">
-        <v>623</v>
       </c>
       <c r="E124" s="5"/>
       <c r="F124" s="5"/>
@@ -11767,13 +11939,13 @@
         <v>330</v>
       </c>
       <c r="B125" s="5" t="s">
+        <v>622</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>623</v>
+      </c>
+      <c r="D125" s="32" t="s">
         <v>624</v>
-      </c>
-      <c r="C125" s="5" t="s">
-        <v>625</v>
-      </c>
-      <c r="D125" s="32" t="s">
-        <v>626</v>
       </c>
       <c r="E125" s="5"/>
       <c r="F125" s="5"/>
@@ -11803,13 +11975,13 @@
         <v>330</v>
       </c>
       <c r="B126" s="5" t="s">
+        <v>625</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>626</v>
+      </c>
+      <c r="D126" s="32" t="s">
         <v>627</v>
-      </c>
-      <c r="C126" s="5" t="s">
-        <v>628</v>
-      </c>
-      <c r="D126" s="32" t="s">
-        <v>629</v>
       </c>
       <c r="E126" s="5"/>
       <c r="F126" s="5"/>
@@ -11839,13 +12011,13 @@
         <v>330</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D127" s="32" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E127" s="5"/>
       <c r="F127" s="5"/>
@@ -11875,13 +12047,13 @@
         <v>330</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D128" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E128" s="5"/>
       <c r="F128" s="5"/>
@@ -11908,16 +12080,16 @@
     </row>
     <row r="129" spans="1:26" ht="13">
       <c r="A129" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="C129" s="5" t="s">
         <v>633</v>
       </c>
-      <c r="B129" s="5" t="s">
+      <c r="D129" s="32" t="s">
         <v>634</v>
-      </c>
-      <c r="C129" s="5" t="s">
-        <v>635</v>
-      </c>
-      <c r="D129" s="32" t="s">
-        <v>636</v>
       </c>
       <c r="E129" s="5"/>
       <c r="F129" s="5"/>
@@ -11944,16 +12116,16 @@
     </row>
     <row r="130" spans="1:26" ht="13">
       <c r="A130" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B130" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>636</v>
+      </c>
+      <c r="D130" s="32" t="s">
         <v>637</v>
-      </c>
-      <c r="C130" s="5" t="s">
-        <v>638</v>
-      </c>
-      <c r="D130" s="32" t="s">
-        <v>639</v>
       </c>
       <c r="E130" s="5"/>
       <c r="F130" s="5"/>
@@ -11980,16 +12152,16 @@
     </row>
     <row r="131" spans="1:26" ht="13">
       <c r="A131" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B131" s="5" t="s">
+        <v>638</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>639</v>
+      </c>
+      <c r="D131" s="32" t="s">
         <v>640</v>
-      </c>
-      <c r="C131" s="5" t="s">
-        <v>641</v>
-      </c>
-      <c r="D131" s="32" t="s">
-        <v>642</v>
       </c>
       <c r="E131" s="5"/>
       <c r="F131" s="5"/>
@@ -12016,16 +12188,16 @@
     </row>
     <row r="132" spans="1:26" ht="13">
       <c r="A132" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B132" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>642</v>
+      </c>
+      <c r="D132" s="32" t="s">
         <v>643</v>
-      </c>
-      <c r="C132" s="5" t="s">
-        <v>644</v>
-      </c>
-      <c r="D132" s="32" t="s">
-        <v>645</v>
       </c>
       <c r="E132" s="5"/>
       <c r="F132" s="5"/>
@@ -12052,16 +12224,16 @@
     </row>
     <row r="133" spans="1:26" ht="13">
       <c r="A133" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B133" s="5" t="s">
+        <v>644</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>645</v>
+      </c>
+      <c r="D133" s="32" t="s">
         <v>646</v>
-      </c>
-      <c r="C133" s="5" t="s">
-        <v>647</v>
-      </c>
-      <c r="D133" s="32" t="s">
-        <v>648</v>
       </c>
       <c r="E133" s="5"/>
       <c r="F133" s="5"/>
@@ -12088,16 +12260,16 @@
     </row>
     <row r="134" spans="1:26" ht="13">
       <c r="A134" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B134" s="5" t="s">
+        <v>647</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>648</v>
+      </c>
+      <c r="D134" s="32" t="s">
         <v>649</v>
-      </c>
-      <c r="C134" s="5" t="s">
-        <v>650</v>
-      </c>
-      <c r="D134" s="32" t="s">
-        <v>651</v>
       </c>
       <c r="E134" s="5"/>
       <c r="F134" s="5"/>
@@ -12124,16 +12296,16 @@
     </row>
     <row r="135" spans="1:26" ht="13">
       <c r="A135" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B135" s="5" t="s">
+        <v>650</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>651</v>
+      </c>
+      <c r="D135" s="32" t="s">
         <v>652</v>
-      </c>
-      <c r="C135" s="5" t="s">
-        <v>653</v>
-      </c>
-      <c r="D135" s="32" t="s">
-        <v>654</v>
       </c>
       <c r="E135" s="5"/>
       <c r="F135" s="5"/>
@@ -12160,16 +12332,16 @@
     </row>
     <row r="136" spans="1:26" ht="13">
       <c r="A136" s="5" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D136" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E136" s="5"/>
       <c r="F136" s="5"/>
@@ -12199,13 +12371,13 @@
         <v>338</v>
       </c>
       <c r="B137" s="5" t="s">
+        <v>654</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>655</v>
+      </c>
+      <c r="D137" s="18" t="s">
         <v>656</v>
-      </c>
-      <c r="C137" s="5" t="s">
-        <v>657</v>
-      </c>
-      <c r="D137" s="18" t="s">
-        <v>658</v>
       </c>
       <c r="E137" s="5"/>
       <c r="F137" s="5"/>
@@ -12235,13 +12407,13 @@
         <v>338</v>
       </c>
       <c r="B138" s="5" t="s">
+        <v>657</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>658</v>
+      </c>
+      <c r="D138" s="18" t="s">
         <v>659</v>
-      </c>
-      <c r="C138" s="5" t="s">
-        <v>660</v>
-      </c>
-      <c r="D138" s="18" t="s">
-        <v>661</v>
       </c>
       <c r="E138" s="5"/>
       <c r="F138" s="5"/>
@@ -12271,13 +12443,13 @@
         <v>338</v>
       </c>
       <c r="B139" s="5" t="s">
+        <v>660</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>661</v>
+      </c>
+      <c r="D139" s="32" t="s">
         <v>662</v>
-      </c>
-      <c r="C139" s="5" t="s">
-        <v>663</v>
-      </c>
-      <c r="D139" s="32" t="s">
-        <v>664</v>
       </c>
       <c r="E139" s="15"/>
       <c r="F139" s="5"/>
@@ -12307,13 +12479,13 @@
         <v>338</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="D140" s="32" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E140" s="5"/>
       <c r="F140" s="5"/>
@@ -12343,13 +12515,13 @@
         <v>338</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D141" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E141" s="5"/>
       <c r="F141" s="5"/>
@@ -12379,13 +12551,13 @@
         <v>345</v>
       </c>
       <c r="B142" s="5" t="s">
+        <v>667</v>
+      </c>
+      <c r="C142" s="43" t="s">
+        <v>668</v>
+      </c>
+      <c r="D142" s="5" t="s">
         <v>669</v>
-      </c>
-      <c r="C142" s="43" t="s">
-        <v>670</v>
-      </c>
-      <c r="D142" s="5" t="s">
-        <v>671</v>
       </c>
       <c r="E142" s="5"/>
       <c r="F142" s="5"/>
@@ -12415,13 +12587,13 @@
         <v>345</v>
       </c>
       <c r="B143" s="5" t="s">
+        <v>670</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>671</v>
+      </c>
+      <c r="D143" s="32" t="s">
         <v>672</v>
-      </c>
-      <c r="C143" s="5" t="s">
-        <v>673</v>
-      </c>
-      <c r="D143" s="32" t="s">
-        <v>674</v>
       </c>
       <c r="E143" s="5"/>
       <c r="F143" s="5"/>
@@ -12451,13 +12623,13 @@
         <v>345</v>
       </c>
       <c r="B144" s="5" t="s">
+        <v>673</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>674</v>
+      </c>
+      <c r="D144" s="32" t="s">
         <v>675</v>
-      </c>
-      <c r="C144" s="5" t="s">
-        <v>676</v>
-      </c>
-      <c r="D144" s="32" t="s">
-        <v>677</v>
       </c>
       <c r="E144" s="5"/>
       <c r="F144" s="5"/>
@@ -12487,13 +12659,13 @@
         <v>345</v>
       </c>
       <c r="B145" s="5" t="s">
+        <v>676</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>677</v>
+      </c>
+      <c r="D145" s="32" t="s">
         <v>678</v>
-      </c>
-      <c r="C145" s="5" t="s">
-        <v>679</v>
-      </c>
-      <c r="D145" s="32" t="s">
-        <v>680</v>
       </c>
       <c r="E145" s="5"/>
       <c r="F145" s="5"/>
@@ -12523,13 +12695,13 @@
         <v>345</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D146" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E146" s="5"/>
       <c r="F146" s="5"/>
@@ -12559,13 +12731,13 @@
         <v>362</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D147" s="32" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="E147" s="5"/>
       <c r="F147" s="5"/>
@@ -12595,13 +12767,13 @@
         <v>362</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D148" s="32" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="E148" s="5"/>
       <c r="F148" s="5"/>
@@ -12631,13 +12803,13 @@
         <v>362</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D149" s="32" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="E149" s="5"/>
       <c r="F149" s="5"/>
@@ -12667,13 +12839,13 @@
         <v>362</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="D150" s="32" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="E150" s="5"/>
       <c r="F150" s="5"/>
@@ -12703,13 +12875,13 @@
         <v>362</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D151" s="32" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E151" s="5"/>
       <c r="F151" s="5"/>
@@ -12739,13 +12911,13 @@
         <v>362</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="D152" s="32" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="E152" s="5"/>
       <c r="F152" s="5"/>
@@ -12775,13 +12947,13 @@
         <v>362</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D153" s="32" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="E153" s="5"/>
       <c r="F153" s="5"/>
@@ -12811,13 +12983,13 @@
         <v>362</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D154" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E154" s="5"/>
       <c r="F154" s="5"/>
@@ -12844,16 +13016,16 @@
     </row>
     <row r="155" spans="1:26" ht="13">
       <c r="A155" s="5" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B155" s="5" t="s">
         <v>135</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D155" s="32" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="E155" s="5"/>
       <c r="F155" s="5"/>
@@ -12880,16 +13052,16 @@
     </row>
     <row r="156" spans="1:26" ht="13">
       <c r="A156" s="5" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B156" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="C156" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="D156" s="32" t="s">
         <v>410</v>
-      </c>
-      <c r="C156" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="D156" s="32" t="s">
-        <v>412</v>
       </c>
       <c r="E156" s="5"/>
       <c r="F156" s="5"/>
@@ -12916,16 +13088,16 @@
     </row>
     <row r="157" spans="1:26" ht="13">
       <c r="A157" s="5" t="s">
+        <v>688</v>
+      </c>
+      <c r="B157" s="5" t="s">
         <v>690</v>
       </c>
-      <c r="B157" s="5" t="s">
-        <v>692</v>
-      </c>
       <c r="C157" s="5" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="D157" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E157" s="5"/>
       <c r="F157" s="5"/>
@@ -12955,13 +13127,13 @@
         <v>254</v>
       </c>
       <c r="B158" s="10" t="s">
+        <v>691</v>
+      </c>
+      <c r="C158" s="10" t="s">
+        <v>692</v>
+      </c>
+      <c r="D158" s="33" t="s">
         <v>693</v>
-      </c>
-      <c r="C158" s="10" t="s">
-        <v>694</v>
-      </c>
-      <c r="D158" s="33" t="s">
-        <v>695</v>
       </c>
       <c r="E158" s="5"/>
       <c r="F158" s="5"/>
@@ -12991,13 +13163,13 @@
         <v>254</v>
       </c>
       <c r="B159" s="10" t="s">
+        <v>694</v>
+      </c>
+      <c r="C159" s="44" t="s">
+        <v>695</v>
+      </c>
+      <c r="D159" s="33" t="s">
         <v>696</v>
-      </c>
-      <c r="C159" s="44" t="s">
-        <v>697</v>
-      </c>
-      <c r="D159" s="33" t="s">
-        <v>698</v>
       </c>
       <c r="E159" s="15"/>
       <c r="F159" s="15"/>
@@ -13027,13 +13199,13 @@
         <v>254</v>
       </c>
       <c r="B160" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="C160" s="45" t="s">
+        <v>698</v>
+      </c>
+      <c r="D160" s="46" t="s">
         <v>699</v>
-      </c>
-      <c r="C160" s="45" t="s">
-        <v>700</v>
-      </c>
-      <c r="D160" s="46" t="s">
-        <v>701</v>
       </c>
       <c r="E160" s="15"/>
       <c r="F160" s="15"/>
@@ -13063,13 +13235,13 @@
         <v>254</v>
       </c>
       <c r="B161" s="10" t="s">
+        <v>700</v>
+      </c>
+      <c r="C161" s="10" t="s">
+        <v>701</v>
+      </c>
+      <c r="D161" s="10" t="s">
         <v>702</v>
-      </c>
-      <c r="C161" s="10" t="s">
-        <v>703</v>
-      </c>
-      <c r="D161" s="10" t="s">
-        <v>704</v>
       </c>
       <c r="E161" s="5"/>
       <c r="F161" s="5"/>
@@ -13099,13 +13271,13 @@
         <v>254</v>
       </c>
       <c r="B162" s="10" t="s">
+        <v>703</v>
+      </c>
+      <c r="C162" s="44" t="s">
+        <v>704</v>
+      </c>
+      <c r="D162" s="33" t="s">
         <v>705</v>
-      </c>
-      <c r="C162" s="44" t="s">
-        <v>706</v>
-      </c>
-      <c r="D162" s="33" t="s">
-        <v>707</v>
       </c>
       <c r="E162" s="15"/>
       <c r="F162" s="15"/>
@@ -13135,13 +13307,13 @@
         <v>254</v>
       </c>
       <c r="B163" s="10" t="s">
+        <v>706</v>
+      </c>
+      <c r="C163" s="44" t="s">
+        <v>707</v>
+      </c>
+      <c r="D163" s="33" t="s">
         <v>708</v>
-      </c>
-      <c r="C163" s="44" t="s">
-        <v>709</v>
-      </c>
-      <c r="D163" s="33" t="s">
-        <v>710</v>
       </c>
       <c r="E163" s="15"/>
       <c r="F163" s="15"/>
@@ -13171,13 +13343,13 @@
         <v>254</v>
       </c>
       <c r="B164" s="10" t="s">
+        <v>709</v>
+      </c>
+      <c r="C164" s="10" t="s">
+        <v>710</v>
+      </c>
+      <c r="D164" s="10" t="s">
         <v>711</v>
-      </c>
-      <c r="C164" s="10" t="s">
-        <v>712</v>
-      </c>
-      <c r="D164" s="10" t="s">
-        <v>713</v>
       </c>
       <c r="E164" s="5"/>
       <c r="F164" s="5"/>
@@ -13204,44 +13376,44 @@
     </row>
     <row r="165" spans="1:26" s="50" customFormat="1" ht="13">
       <c r="A165" s="52" t="s">
+        <v>766</v>
+      </c>
+      <c r="B165" s="52" t="s">
+        <v>767</v>
+      </c>
+      <c r="C165" s="52" t="s">
         <v>768</v>
       </c>
-      <c r="B165" s="52" t="s">
+      <c r="D165" s="52" t="s">
         <v>769</v>
-      </c>
-      <c r="C165" s="52" t="s">
-        <v>770</v>
-      </c>
-      <c r="D165" s="52" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="166" spans="1:26" s="50" customFormat="1" ht="13">
       <c r="A166" s="52" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B166" s="52" t="s">
+        <v>770</v>
+      </c>
+      <c r="C166" s="52" t="s">
+        <v>771</v>
+      </c>
+      <c r="D166" s="52" t="s">
         <v>772</v>
-      </c>
-      <c r="C166" s="52" t="s">
-        <v>773</v>
-      </c>
-      <c r="D166" s="52" t="s">
-        <v>774</v>
       </c>
     </row>
     <row r="167" spans="1:26" s="50" customFormat="1" ht="13">
       <c r="A167" s="52" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B167" s="52" t="s">
+        <v>773</v>
+      </c>
+      <c r="C167" s="52" t="s">
+        <v>774</v>
+      </c>
+      <c r="D167" s="52" t="s">
         <v>775</v>
-      </c>
-      <c r="C167" s="52" t="s">
-        <v>776</v>
-      </c>
-      <c r="D167" s="52" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="168" spans="1:26" ht="13">
@@ -13298,36 +13470,36 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" customHeight="1">
       <c r="A1" s="42" t="s">
+        <v>712</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>713</v>
+      </c>
+      <c r="C1" s="42" t="s">
         <v>714</v>
       </c>
-      <c r="B1" s="42" t="s">
+      <c r="D1" s="42" t="s">
         <v>715</v>
       </c>
-      <c r="C1" s="42" t="s">
+      <c r="E1" s="42" t="s">
         <v>716</v>
       </c>
-      <c r="D1" s="42" t="s">
+      <c r="F1" s="42" t="s">
         <v>717</v>
-      </c>
-      <c r="E1" s="42" t="s">
-        <v>718</v>
-      </c>
-      <c r="F1" s="42" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>721</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>723</v>
       </c>
     </row>
   </sheetData>

--- a/forms/app/postpartum.xlsx
+++ b/forms/app/postpartum.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1480" uniqueCount="806">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1488" uniqueCount="806">
   <si>
     <t>type</t>
   </si>
@@ -2727,15 +2727,15 @@
     </xf>
     <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
@@ -3925,7 +3925,7 @@
       <c r="A46" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="B46" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C46" s="1"/>
@@ -3937,7 +3937,7 @@
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
-      <c r="L46" s="10" t="s">
+      <c r="L46" s="5" t="s">
         <v>93</v>
       </c>
       <c r="M46" s="1"/>
@@ -4029,7 +4029,7 @@
       <c r="C49" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D49" s="11" t="s">
+      <c r="D49" s="9" t="s">
         <v>99</v>
       </c>
       <c r="E49" s="1"/>
@@ -4179,7 +4179,7 @@
       <c r="A57" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B57" s="12" t="s">
+      <c r="B57" s="10" t="s">
         <v>105</v>
       </c>
     </row>
@@ -4187,7 +4187,7 @@
       <c r="A58" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B58" s="12" t="s">
+      <c r="B58" s="10" t="s">
         <v>121</v>
       </c>
       <c r="C58" s="1" t="s">
@@ -4201,7 +4201,7 @@
       <c r="A59" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B59" s="12" t="s">
+      <c r="B59" s="10" t="s">
         <v>124</v>
       </c>
       <c r="C59" s="1" t="s">
@@ -4215,7 +4215,7 @@
       <c r="A60" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B60" s="12" t="s">
+      <c r="B60" s="10" t="s">
         <v>121</v>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       <c r="A61" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B61" s="12" t="s">
+      <c r="B61" s="10" t="s">
         <v>127</v>
       </c>
       <c r="C61" s="1" t="s">
@@ -4237,7 +4237,7 @@
       <c r="A62" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B62" s="12" t="s">
+      <c r="B62" s="10" t="s">
         <v>130</v>
       </c>
       <c r="C62" s="1" t="s">
@@ -4251,7 +4251,7 @@
       <c r="A63" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B63" s="12" t="s">
+      <c r="B63" s="10" t="s">
         <v>133</v>
       </c>
       <c r="C63" s="1" t="s">
@@ -4265,7 +4265,7 @@
       <c r="A64" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B64" s="12" t="s">
+      <c r="B64" s="10" t="s">
         <v>134</v>
       </c>
       <c r="C64" s="1" t="s">
@@ -4279,10 +4279,10 @@
       <c r="A65" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B65" s="12" t="s">
+      <c r="B65" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="C65" s="13" t="s">
+      <c r="C65" s="11" t="s">
         <v>138</v>
       </c>
       <c r="D65" s="1" t="s">
@@ -4294,7 +4294,7 @@
       <c r="A66" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B66" s="12" t="s">
+      <c r="B66" s="10" t="s">
         <v>140</v>
       </c>
       <c r="C66" s="1" t="s">
@@ -4308,7 +4308,7 @@
       <c r="A67" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B67" s="12" t="s">
+      <c r="B67" s="10" t="s">
         <v>143</v>
       </c>
       <c r="C67" s="1" t="s">
@@ -4325,7 +4325,7 @@
       <c r="A68" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B68" s="12" t="s">
+      <c r="B68" s="10" t="s">
         <v>147</v>
       </c>
       <c r="C68" s="1" t="s">
@@ -4342,7 +4342,7 @@
       <c r="A69" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B69" s="12" t="s">
+      <c r="B69" s="10" t="s">
         <v>150</v>
       </c>
       <c r="C69" s="1" t="s">
@@ -4359,7 +4359,7 @@
       <c r="A70" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B70" s="12" t="s">
+      <c r="B70" s="10" t="s">
         <v>140</v>
       </c>
     </row>
@@ -4367,7 +4367,7 @@
       <c r="A71" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B71" s="12" t="s">
+      <c r="B71" s="10" t="s">
         <v>153</v>
       </c>
       <c r="C71" s="1" t="s">
@@ -4387,7 +4387,7 @@
       <c r="A72" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B72" s="12" t="s">
+      <c r="B72" s="10" t="s">
         <v>157</v>
       </c>
       <c r="C72" s="1" t="s">
@@ -4404,7 +4404,7 @@
       <c r="A73" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B73" s="12" t="s">
+      <c r="B73" s="10" t="s">
         <v>161</v>
       </c>
       <c r="C73" s="1" t="s">
@@ -4421,7 +4421,7 @@
       <c r="A74" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B74" s="12" t="s">
+      <c r="B74" s="10" t="s">
         <v>133</v>
       </c>
     </row>
@@ -4429,7 +4429,7 @@
       <c r="A75" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B75" s="12" t="s">
+      <c r="B75" s="10" t="s">
         <v>127</v>
       </c>
       <c r="C75" s="1"/>
@@ -4440,7 +4440,7 @@
       <c r="A76" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B76" s="12" t="s">
+      <c r="B76" s="10" t="s">
         <v>165</v>
       </c>
       <c r="C76" s="1" t="s">
@@ -4460,7 +4460,7 @@
       <c r="A77" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B77" s="12" t="s">
+      <c r="B77" s="10" t="s">
         <v>169</v>
       </c>
       <c r="C77" s="1" t="s">
@@ -4474,7 +4474,7 @@
       <c r="A78" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B78" s="12" t="s">
+      <c r="B78" s="10" t="s">
         <v>172</v>
       </c>
       <c r="C78" s="1" t="s">
@@ -4488,7 +4488,7 @@
       <c r="A79" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B79" s="12" t="s">
+      <c r="B79" s="10" t="s">
         <v>173</v>
       </c>
       <c r="C79" s="1" t="s">
@@ -4505,7 +4505,7 @@
       <c r="A80" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B80" s="12" t="s">
+      <c r="B80" s="10" t="s">
         <v>176</v>
       </c>
       <c r="C80" s="1" t="s">
@@ -4522,7 +4522,7 @@
       <c r="A81" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B81" s="12" t="s">
+      <c r="B81" s="10" t="s">
         <v>179</v>
       </c>
       <c r="C81" s="1" t="s">
@@ -4539,7 +4539,7 @@
       <c r="A82" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B82" s="12" t="s">
+      <c r="B82" s="10" t="s">
         <v>182</v>
       </c>
       <c r="C82" s="1" t="s">
@@ -4556,7 +4556,7 @@
       <c r="A83" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B83" s="12" t="s">
+      <c r="B83" s="10" t="s">
         <v>185</v>
       </c>
       <c r="C83" s="1" t="s">
@@ -4573,7 +4573,7 @@
       <c r="A84" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B84" s="12" t="s">
+      <c r="B84" s="10" t="s">
         <v>188</v>
       </c>
       <c r="C84" s="1" t="s">
@@ -4590,7 +4590,7 @@
       <c r="A85" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B85" s="12" t="s">
+      <c r="B85" s="10" t="s">
         <v>191</v>
       </c>
       <c r="C85" s="1" t="s">
@@ -4607,7 +4607,7 @@
       <c r="A86" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B86" s="12" t="s">
+      <c r="B86" s="10" t="s">
         <v>194</v>
       </c>
       <c r="C86" s="1" t="s">
@@ -4624,7 +4624,7 @@
       <c r="A87" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B87" s="12" t="s">
+      <c r="B87" s="10" t="s">
         <v>197</v>
       </c>
       <c r="C87" s="1" t="s">
@@ -4641,7 +4641,7 @@
       <c r="A88" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B88" s="12" t="s">
+      <c r="B88" s="10" t="s">
         <v>200</v>
       </c>
       <c r="C88" s="1" t="s">
@@ -4658,7 +4658,7 @@
       <c r="A89" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B89" s="12" t="s">
+      <c r="B89" s="10" t="s">
         <v>203</v>
       </c>
       <c r="C89" s="1" t="s">
@@ -4675,7 +4675,7 @@
       <c r="A90" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B90" s="12" t="s">
+      <c r="B90" s="10" t="s">
         <v>206</v>
       </c>
       <c r="C90" s="1" t="s">
@@ -4692,7 +4692,7 @@
       <c r="A91" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B91" s="12" t="s">
+      <c r="B91" s="10" t="s">
         <v>209</v>
       </c>
       <c r="C91" s="1" t="s">
@@ -4709,7 +4709,7 @@
       <c r="A92" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B92" s="12" t="s">
+      <c r="B92" s="10" t="s">
         <v>172</v>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       <c r="A93" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B93" s="12" t="s">
+      <c r="B93" s="10" t="s">
         <v>213</v>
       </c>
       <c r="C93" s="1" t="s">
@@ -4737,7 +4737,7 @@
       <c r="A94" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B94" s="12" t="s">
+      <c r="B94" s="10" t="s">
         <v>217</v>
       </c>
       <c r="C94" s="1" t="s">
@@ -4757,7 +4757,7 @@
       <c r="A95" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B95" s="12" t="s">
+      <c r="B95" s="10" t="s">
         <v>221</v>
       </c>
       <c r="C95" s="1" t="s">
@@ -4774,7 +4774,7 @@
       <c r="A96" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B96" s="12" t="s">
+      <c r="B96" s="10" t="s">
         <v>225</v>
       </c>
       <c r="C96" s="1" t="s">
@@ -4794,7 +4794,7 @@
       <c r="A97" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B97" s="12" t="s">
+      <c r="B97" s="10" t="s">
         <v>228</v>
       </c>
       <c r="C97" s="1" t="s">
@@ -4811,7 +4811,7 @@
       <c r="A98" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B98" s="12" t="s">
+      <c r="B98" s="10" t="s">
         <v>232</v>
       </c>
       <c r="C98" s="1" t="s">
@@ -4828,7 +4828,7 @@
       <c r="A99" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B99" s="12" t="s">
+      <c r="B99" s="10" t="s">
         <v>236</v>
       </c>
       <c r="C99" s="1" t="s">
@@ -4845,7 +4845,7 @@
       <c r="A100" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B100" s="12" t="s">
+      <c r="B100" s="10" t="s">
         <v>165</v>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       <c r="A101" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B101" s="12" t="s">
+      <c r="B101" s="10" t="s">
         <v>240</v>
       </c>
       <c r="C101" s="1" t="s">
@@ -4874,7 +4874,7 @@
       <c r="A102" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B102" s="12" t="s">
+      <c r="B102" s="10" t="s">
         <v>245</v>
       </c>
       <c r="C102" s="1" t="s">
@@ -4890,7 +4890,7 @@
       <c r="A103" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B103" s="12" t="s">
+      <c r="B103" s="10" t="s">
         <v>240</v>
       </c>
       <c r="C103" s="1"/>
@@ -4902,7 +4902,7 @@
       <c r="A104" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B104" s="12" t="s">
+      <c r="B104" s="10" t="s">
         <v>248</v>
       </c>
       <c r="C104" s="1" t="s">
@@ -4922,7 +4922,7 @@
       <c r="A105" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B105" s="12" t="s">
+      <c r="B105" s="10" t="s">
         <v>251</v>
       </c>
       <c r="C105" s="1" t="s">
@@ -4937,7 +4937,7 @@
       <c r="A106" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B106" s="12" t="s">
+      <c r="B106" s="10" t="s">
         <v>254</v>
       </c>
       <c r="C106" s="1" t="s">
@@ -4952,7 +4952,7 @@
       <c r="A107" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B107" s="12" t="s">
+      <c r="B107" s="10" t="s">
         <v>248</v>
       </c>
       <c r="C107" s="1"/>
@@ -4965,10 +4965,12 @@
       <c r="B108" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="C108" s="2"/>
+      <c r="C108" s="12" t="s">
+        <v>23</v>
+      </c>
       <c r="D108" s="2"/>
       <c r="E108" s="2"/>
-      <c r="F108" s="9" t="s">
+      <c r="F108" s="1" t="s">
         <v>258</v>
       </c>
       <c r="G108" s="2"/>
@@ -4999,7 +5001,9 @@
       <c r="B109" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="C109" s="1"/>
+      <c r="C109" s="13" t="s">
+        <v>23</v>
+      </c>
       <c r="D109" s="1"/>
       <c r="E109" s="1"/>
       <c r="F109" s="4"/>
@@ -5099,7 +5103,9 @@
       <c r="B112" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="C112" s="1"/>
+      <c r="C112" s="13" t="s">
+        <v>23</v>
+      </c>
       <c r="D112" s="14"/>
       <c r="E112" s="1"/>
       <c r="F112" s="1"/>
@@ -5233,7 +5239,9 @@
       <c r="B116" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="C116" s="1"/>
+      <c r="C116" s="13" t="s">
+        <v>23</v>
+      </c>
       <c r="D116" s="15"/>
       <c r="E116" s="1"/>
       <c r="F116" s="1"/>
@@ -5335,7 +5343,9 @@
       <c r="B119" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="C119" s="1"/>
+      <c r="C119" s="13" t="s">
+        <v>23</v>
+      </c>
       <c r="D119" s="15"/>
       <c r="E119" s="1"/>
       <c r="F119" s="1"/>
@@ -5471,7 +5481,9 @@
       <c r="B123" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="C123" s="1"/>
+      <c r="C123" s="13" t="s">
+        <v>23</v>
+      </c>
       <c r="D123" s="15"/>
       <c r="E123" s="1"/>
       <c r="F123" s="1" t="s">
@@ -5747,7 +5759,9 @@
       <c r="B131" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="C131" s="1"/>
+      <c r="C131" s="13" t="s">
+        <v>23</v>
+      </c>
       <c r="D131" s="15"/>
       <c r="E131" s="1"/>
       <c r="F131" s="1" t="s">
@@ -5887,7 +5901,9 @@
       <c r="B135" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="C135" s="1"/>
+      <c r="C135" s="13" t="s">
+        <v>23</v>
+      </c>
       <c r="D135" s="15"/>
       <c r="E135" s="1"/>
       <c r="F135" s="1" t="s">
@@ -6018,7 +6034,7 @@
       <c r="A139" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B139" s="12" t="s">
+      <c r="B139" s="10" t="s">
         <v>302</v>
       </c>
       <c r="C139" s="1" t="s">
@@ -6038,7 +6054,7 @@
       <c r="A140" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B140" s="12" t="s">
+      <c r="B140" s="10" t="s">
         <v>306</v>
       </c>
       <c r="C140" s="1" t="s">
@@ -6056,7 +6072,7 @@
       <c r="A141" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B141" s="12" t="s">
+      <c r="B141" s="10" t="s">
         <v>309</v>
       </c>
       <c r="C141" s="1" t="s">
@@ -6096,7 +6112,7 @@
       <c r="A142" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B142" s="12" t="s">
+      <c r="B142" s="10" t="s">
         <v>314</v>
       </c>
       <c r="C142" s="1" t="s">
@@ -6182,7 +6198,7 @@
       <c r="A144" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B144" s="12" t="s">
+      <c r="B144" s="10" t="s">
         <v>326</v>
       </c>
       <c r="C144" s="1" t="s">
@@ -6200,7 +6216,7 @@
       <c r="A145" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B145" s="12" t="s">
+      <c r="B145" s="10" t="s">
         <v>302</v>
       </c>
       <c r="C145" s="1"/>
@@ -6211,7 +6227,7 @@
       <c r="A146" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B146" s="12" t="s">
+      <c r="B146" s="10" t="s">
         <v>329</v>
       </c>
       <c r="C146" s="1" t="s">
@@ -7754,7 +7770,7 @@
       <c r="A197" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B197" s="12" t="s">
+      <c r="B197" s="10" t="s">
         <v>470</v>
       </c>
       <c r="L197" s="1" t="s">
@@ -7765,7 +7781,7 @@
       <c r="A198" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B198" s="12" t="s">
+      <c r="B198" s="10" t="s">
         <v>472</v>
       </c>
       <c r="L198" s="1" t="s">
@@ -7776,7 +7792,7 @@
       <c r="A199" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B199" s="12" t="s">
+      <c r="B199" s="10" t="s">
         <v>474</v>
       </c>
       <c r="C199" s="4"/>
@@ -7810,7 +7826,7 @@
       <c r="A200" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B200" s="12" t="s">
+      <c r="B200" s="10" t="s">
         <v>476</v>
       </c>
       <c r="L200" s="1" t="s">
@@ -7820,49 +7836,49 @@
     <row r="201" ht="15.75" customHeight="1"/>
     <row r="202" ht="15.75" customHeight="1"/>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="C203" s="12"/>
+      <c r="C203" s="10"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="B204" s="12"/>
-      <c r="C204" s="12"/>
+      <c r="B204" s="10"/>
+      <c r="C204" s="10"/>
     </row>
     <row r="205" ht="15.75" customHeight="1"/>
     <row r="206" ht="15.75" customHeight="1">
-      <c r="B206" s="12"/>
+      <c r="B206" s="10"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
       <c r="B207" s="1"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
-      <c r="B208" s="12"/>
+      <c r="B208" s="10"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
-      <c r="B209" s="12"/>
+      <c r="B209" s="10"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
       <c r="B210" s="1"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="B211" s="12"/>
+      <c r="B211" s="10"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
       <c r="B212" s="1"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="B213" s="12"/>
+      <c r="B213" s="10"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
       <c r="B214" s="1"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
-      <c r="B215" s="12"/>
+      <c r="B215" s="10"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
       <c r="B216" s="1"/>
     </row>
     <row r="217" ht="15.75" customHeight="1"/>
     <row r="218" ht="15.75" customHeight="1">
-      <c r="C218" s="12"/>
+      <c r="C218" s="10"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
       <c r="B219" s="1"/>
@@ -7872,10 +7888,10 @@
     </row>
     <row r="221" ht="15.75" customHeight="1"/>
     <row r="222" ht="15.75" customHeight="1">
-      <c r="B222" s="12"/>
+      <c r="B222" s="10"/>
     </row>
     <row r="223" ht="15.75" customHeight="1">
-      <c r="B223" s="12"/>
+      <c r="B223" s="10"/>
     </row>
     <row r="224" ht="15.75" customHeight="1"/>
     <row r="225" ht="15.75" customHeight="1"/>

--- a/forms/app/postpartum.xlsx
+++ b/forms/app/postpartum.xlsx
@@ -10,15 +10,15 @@
   <definedNames/>
   <calcPr/>
   <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataSignature="AMtx7miM+A92k+ZBwwNG0uPNoQqoxf5FDA=="/>
+    <ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="nqfSlJYhlJZcTcOxybwdZyGn2l9F5seQx9rRj70WKKA="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1488" uniqueCount="806">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="809">
   <si>
     <t>type</t>
   </si>
@@ -528,7 +528,7 @@
     <t>Inabidi uhudhurie kituo cha afya kwa ajili ya kufanyiwa uchunguzi juu ya kutoka damu nyingi</t>
   </si>
   <si>
-    <t>selected(${postpartum_bleeding_right_now},"no")</t>
+    <t>selected(${postpartum_severe_vaginal_bleeding},"yes") and selected(${postpartum_convulsions},"no") and selected(${postpartum_unconscious},"no") and selected(${postpartum_bleeding_right_now},"no")</t>
   </si>
   <si>
     <t>postpartum_emergency_referral_note</t>
@@ -700,7 +700,7 @@
     <t>Vipi hali ya mshono/kidonda chako cha operesheni?</t>
   </si>
   <si>
-    <t>${had_c_section}="yes"</t>
+    <t>${had_c_section}="true"</t>
   </si>
   <si>
     <t>client_been_facility_3_days</t>
@@ -741,7 +741,21 @@
 &lt;span style="color:red;font-style: italic"&gt;Usimsomee, jaza wewe&lt;/span&gt;</t>
   </si>
   <si>
-    <t>selected(${client_been_facility_3_days},"yes")</t>
+    <t>selected(${c_section_condition},"discharge_swelling") or 
+selected(${postpartum_pale_pallor},"yes") or
+selected(${postpartum_severe_frontal_headache},"yes") or
+selected(${postpartum_blurred_vision},"yes") or
+selected(${postpartum_urine},"yes") or
+selected(${postpartum_dizziness},"yes") or
+(selected(${postpartum_exhaustion},"yes") or
+selected(${postpartum_severe_lower_abdominal_pain},"yes") or
+selected(${postpartum_vaginal_discharge},"yes") or
+selected(${postpartum_fever_chills},"yes") or
+selected(${postpartum_breathing_difficulty},"yes") or
+selected(${postpartum_severe_pain_foot},"yes") or
+selected(${postpartum_behavior},"yes") or
+selected(${postpartum_breast},"yes")) and 
+selected(${client_been_facility_3_days},"yes")</t>
   </si>
   <si>
     <t>chv_thinks_needs_return_facility</t>
@@ -751,6 +765,23 @@
   </si>
   <si>
     <t>Kwa kuzingatia majadiliano yako na mteja, unadhani mteja anahitaji kurudi kituo cha afya kwa ajili ya uchunguzi zaidi?</t>
+  </si>
+  <si>
+    <t>(selected(${c_section_condition},"discharge_swelling") or 
+selected(${postpartum_pale_pallor},"yes") or
+selected(${postpartum_severe_frontal_headache},"yes") or
+selected(${postpartum_blurred_vision},"yes") or
+selected(${postpartum_urine},"yes") or
+selected(${postpartum_dizziness},"yes") or
+selected(${postpartum_exhaustion},"yes") or
+selected(${postpartum_severe_lower_abdominal_pain},"yes") or
+selected(${postpartum_vaginal_discharge},"yes") or
+selected(${postpartum_fever_chills},"yes") or
+selected(${postpartum_breathing_difficulty},"yes") or
+selected(${postpartum_severe_pain_foot},"yes") or
+selected(${postpartum_behavior},"yes") or
+selected(${postpartum_breast},"yes")) and 
+selected(${client_been_facility_3_days},"yes")</t>
   </si>
   <si>
     <t>postpartum_other_danger_sign_referral_note</t>
@@ -778,7 +809,22 @@
     <t>Tafadhali endelea kufuata ushauri na maelekezo ya matibabu uliyopatiwa kituo cha afya, kama hali yako itazidi kuwa mbaya, rudi kituo cha afya haraka.</t>
   </si>
   <si>
-    <t>selected(${chv_thinks_needs_return_facility},"no")</t>
+    <t>(selected(${c_section_condition},"discharge_swelling") or 
+selected(${postpartum_pale_pallor},"yes") or
+selected(${postpartum_severe_frontal_headache},"yes") or
+selected(${postpartum_blurred_vision},"yes") or
+selected(${postpartum_urine},"yes") or
+selected(${postpartum_dizziness},"yes") or
+selected(${postpartum_exhaustion},"yes") or
+selected(${postpartum_severe_lower_abdominal_pain},"yes") or
+selected(${postpartum_vaginal_discharge},"yes") or
+selected(${postpartum_fever_chills},"yes") or
+selected(${postpartum_breathing_difficulty},"yes") or
+selected(${postpartum_severe_pain_foot},"yes") or
+selected(${postpartum_behavior},"yes") or
+selected(${postpartum_breast},"yes")) and 
+selected(${client_been_facility_3_days},"yes") and
+selected(${chv_thinks_needs_return_facility},"no")</t>
   </si>
   <si>
     <t>postpartum_other_danger_sign_not_found_note</t>
@@ -790,7 +836,7 @@
     <t>Hakuna dalili za hatari zilizogundulika,iwapo utaona dalili yeyote kati zile tulizojadili, basi wahi kituo cha afya haraka.</t>
   </si>
   <si>
-    <t xml:space="preserve">(${had_c_section} = "yes" and
+    <t xml:space="preserve">(${had_c_section} = "true" and
 selected(${c_section_condition},"clean") and
 selected(${postpartum_pale_pallor},"no") and
 selected(${postpartum_severe_frontal_headache},"no") and
@@ -806,7 +852,7 @@
 selected(${postpartum_behavior},"no") and
 selected(${postpartum_breast},"no"))
 or
-(${had_c_section} = "no" and
+(${had_c_section} = "false" and
 selected(${postpartum_pale_pallor},"no") and
 selected(${postpartum_severe_frontal_headache},"no") and
 selected(${postpartum_blurred_vision},"no") and
@@ -1225,7 +1271,9 @@
     <t xml:space="preserve">yes </t>
   </si>
   <si>
-    <t>selected(${facility_district},"north_a") or 
+    <t xml:space="preserve">
+(selected(${facility_island},"unguja") or selected(${facility_island},"pemba")) and 
+(selected(${facility_district},"north_a") or 
 selected(${facility_district},"north_b") or 
 selected(${facility_district},"central") or 
 selected(${facility_district},"south") or 
@@ -1235,7 +1283,7 @@
 selected(${facility_district},"chakechake") or 
 selected(${facility_district},"micheweni") or 
 selected(${facility_district},"mkoani") or 
-selected(${facility_district},"wete")</t>
+selected(${facility_district},"wete"))</t>
   </si>
   <si>
     <t>choice_filter=${facility_district}</t>
@@ -1253,7 +1301,7 @@
     <t>Tafadhali kitaje</t>
   </si>
   <si>
-    <t>selected(${anc_visit_facility},"other")</t>
+    <t>(selected(${facility_island},"unguja") or selected(${facility_island},"pemba")) and selected(${anc_visit_facility},"other")</t>
   </si>
   <si>
     <t>select_one is_service_received</t>
@@ -1358,7 +1406,7 @@
     <t>research_questions</t>
   </si>
   <si>
-    <t>selected(${research_questions_consent},"yes")</t>
+    <t>${refer_postpartum_emergency_danger_sign_flag}=0 and ${show_research_questions} = "true" and selected(${research_questions_consent},"yes")</t>
   </si>
   <si>
     <t>select_one travel_time</t>
@@ -1505,7 +1553,7 @@
     <t>Ukijumuisha na wewe, kwa pamoja mume wako ana wenza wangapi?</t>
   </si>
   <si>
-    <t>selected(${more_than_one_wife},"yes")</t>
+    <t>selected(${marital_status},"married") and selected(${more_than_one_wife},"yes")</t>
   </si>
   <si>
     <t xml:space="preserve">.&gt;= 1 and .&lt;= 10 </t>
@@ -1598,6 +1646,9 @@
     <t>Kuhudhuria kituo cha afya kwaajili ya uchunguzi baada ya kujifungua</t>
   </si>
   <si>
+    <t>${refer_postpartum_pnc_visit}=1</t>
+  </si>
+  <si>
     <t>refer_postpartum_emergency_danger_sign_flag</t>
   </si>
   <si>
@@ -1607,10 +1658,13 @@
     <t>refer_postpartum_other_danger_sign_flag</t>
   </si>
   <si>
-    <t>if(selected(${chv_thinks_needs_return_facility},"yes") or selected(${client_been_facility_3_days},"no"),1,0)</t>
+    <t>if(selected(${c_section_condition},"discharge_swelling") and (selected(${chv_thinks_needs_return_facility},"yes") or selected(${client_been_facility_3_days},"no")),1,0)</t>
   </si>
   <si>
     <t>refer_postpartum_pnc_visit</t>
+  </si>
+  <si>
+    <t>`</t>
   </si>
   <si>
     <t>if(selected(${has_attended_facility_pnc},"no"),1,0)</t>
@@ -2728,19 +2782,19 @@
     <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -4058,7 +4112,7 @@
       <c r="C50" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" s="10" t="s">
         <v>103</v>
       </c>
       <c r="E50" s="1"/>
@@ -4179,7 +4233,7 @@
       <c r="A57" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B57" s="10" t="s">
+      <c r="B57" s="11" t="s">
         <v>105</v>
       </c>
     </row>
@@ -4187,7 +4241,7 @@
       <c r="A58" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B58" s="10" t="s">
+      <c r="B58" s="11" t="s">
         <v>121</v>
       </c>
       <c r="C58" s="1" t="s">
@@ -4201,7 +4255,7 @@
       <c r="A59" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B59" s="10" t="s">
+      <c r="B59" s="11" t="s">
         <v>124</v>
       </c>
       <c r="C59" s="1" t="s">
@@ -4215,7 +4269,7 @@
       <c r="A60" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B60" s="10" t="s">
+      <c r="B60" s="11" t="s">
         <v>121</v>
       </c>
     </row>
@@ -4223,7 +4277,7 @@
       <c r="A61" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B61" s="10" t="s">
+      <c r="B61" s="11" t="s">
         <v>127</v>
       </c>
       <c r="C61" s="1" t="s">
@@ -4237,7 +4291,7 @@
       <c r="A62" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B62" s="10" t="s">
+      <c r="B62" s="11" t="s">
         <v>130</v>
       </c>
       <c r="C62" s="1" t="s">
@@ -4251,7 +4305,7 @@
       <c r="A63" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B63" s="10" t="s">
+      <c r="B63" s="11" t="s">
         <v>133</v>
       </c>
       <c r="C63" s="1" t="s">
@@ -4265,7 +4319,7 @@
       <c r="A64" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B64" s="10" t="s">
+      <c r="B64" s="11" t="s">
         <v>134</v>
       </c>
       <c r="C64" s="1" t="s">
@@ -4279,10 +4333,10 @@
       <c r="A65" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B65" s="10" t="s">
+      <c r="B65" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="C65" s="11" t="s">
+      <c r="C65" s="12" t="s">
         <v>138</v>
       </c>
       <c r="D65" s="1" t="s">
@@ -4294,7 +4348,7 @@
       <c r="A66" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B66" s="10" t="s">
+      <c r="B66" s="11" t="s">
         <v>140</v>
       </c>
       <c r="C66" s="1" t="s">
@@ -4308,7 +4362,7 @@
       <c r="A67" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B67" s="10" t="s">
+      <c r="B67" s="11" t="s">
         <v>143</v>
       </c>
       <c r="C67" s="1" t="s">
@@ -4325,7 +4379,7 @@
       <c r="A68" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B68" s="10" t="s">
+      <c r="B68" s="11" t="s">
         <v>147</v>
       </c>
       <c r="C68" s="1" t="s">
@@ -4342,7 +4396,7 @@
       <c r="A69" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B69" s="10" t="s">
+      <c r="B69" s="11" t="s">
         <v>150</v>
       </c>
       <c r="C69" s="1" t="s">
@@ -4359,7 +4413,7 @@
       <c r="A70" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B70" s="10" t="s">
+      <c r="B70" s="11" t="s">
         <v>140</v>
       </c>
     </row>
@@ -4367,7 +4421,7 @@
       <c r="A71" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B71" s="10" t="s">
+      <c r="B71" s="11" t="s">
         <v>153</v>
       </c>
       <c r="C71" s="1" t="s">
@@ -4387,7 +4441,7 @@
       <c r="A72" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B72" s="10" t="s">
+      <c r="B72" s="11" t="s">
         <v>157</v>
       </c>
       <c r="C72" s="1" t="s">
@@ -4396,7 +4450,7 @@
       <c r="D72" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="F72" s="1" t="s">
+      <c r="F72" s="10" t="s">
         <v>160</v>
       </c>
     </row>
@@ -4404,7 +4458,7 @@
       <c r="A73" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B73" s="10" t="s">
+      <c r="B73" s="11" t="s">
         <v>161</v>
       </c>
       <c r="C73" s="1" t="s">
@@ -4421,7 +4475,7 @@
       <c r="A74" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B74" s="10" t="s">
+      <c r="B74" s="11" t="s">
         <v>133</v>
       </c>
     </row>
@@ -4429,7 +4483,7 @@
       <c r="A75" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B75" s="10" t="s">
+      <c r="B75" s="11" t="s">
         <v>127</v>
       </c>
       <c r="C75" s="1"/>
@@ -4440,7 +4494,7 @@
       <c r="A76" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B76" s="10" t="s">
+      <c r="B76" s="11" t="s">
         <v>165</v>
       </c>
       <c r="C76" s="1" t="s">
@@ -4460,7 +4514,7 @@
       <c r="A77" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B77" s="10" t="s">
+      <c r="B77" s="11" t="s">
         <v>169</v>
       </c>
       <c r="C77" s="1" t="s">
@@ -4474,7 +4528,7 @@
       <c r="A78" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B78" s="10" t="s">
+      <c r="B78" s="11" t="s">
         <v>172</v>
       </c>
       <c r="C78" s="1" t="s">
@@ -4488,7 +4542,7 @@
       <c r="A79" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B79" s="10" t="s">
+      <c r="B79" s="11" t="s">
         <v>173</v>
       </c>
       <c r="C79" s="1" t="s">
@@ -4505,7 +4559,7 @@
       <c r="A80" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B80" s="10" t="s">
+      <c r="B80" s="11" t="s">
         <v>176</v>
       </c>
       <c r="C80" s="1" t="s">
@@ -4522,7 +4576,7 @@
       <c r="A81" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B81" s="10" t="s">
+      <c r="B81" s="11" t="s">
         <v>179</v>
       </c>
       <c r="C81" s="1" t="s">
@@ -4539,7 +4593,7 @@
       <c r="A82" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B82" s="10" t="s">
+      <c r="B82" s="11" t="s">
         <v>182</v>
       </c>
       <c r="C82" s="1" t="s">
@@ -4556,7 +4610,7 @@
       <c r="A83" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B83" s="10" t="s">
+      <c r="B83" s="11" t="s">
         <v>185</v>
       </c>
       <c r="C83" s="1" t="s">
@@ -4573,7 +4627,7 @@
       <c r="A84" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B84" s="10" t="s">
+      <c r="B84" s="11" t="s">
         <v>188</v>
       </c>
       <c r="C84" s="1" t="s">
@@ -4590,7 +4644,7 @@
       <c r="A85" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B85" s="10" t="s">
+      <c r="B85" s="11" t="s">
         <v>191</v>
       </c>
       <c r="C85" s="1" t="s">
@@ -4607,7 +4661,7 @@
       <c r="A86" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B86" s="10" t="s">
+      <c r="B86" s="11" t="s">
         <v>194</v>
       </c>
       <c r="C86" s="1" t="s">
@@ -4624,7 +4678,7 @@
       <c r="A87" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B87" s="10" t="s">
+      <c r="B87" s="11" t="s">
         <v>197</v>
       </c>
       <c r="C87" s="1" t="s">
@@ -4641,7 +4695,7 @@
       <c r="A88" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B88" s="10" t="s">
+      <c r="B88" s="11" t="s">
         <v>200</v>
       </c>
       <c r="C88" s="1" t="s">
@@ -4658,7 +4712,7 @@
       <c r="A89" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B89" s="10" t="s">
+      <c r="B89" s="11" t="s">
         <v>203</v>
       </c>
       <c r="C89" s="1" t="s">
@@ -4675,7 +4729,7 @@
       <c r="A90" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B90" s="10" t="s">
+      <c r="B90" s="11" t="s">
         <v>206</v>
       </c>
       <c r="C90" s="1" t="s">
@@ -4692,7 +4746,7 @@
       <c r="A91" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B91" s="10" t="s">
+      <c r="B91" s="11" t="s">
         <v>209</v>
       </c>
       <c r="C91" s="1" t="s">
@@ -4709,7 +4763,7 @@
       <c r="A92" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B92" s="10" t="s">
+      <c r="B92" s="11" t="s">
         <v>172</v>
       </c>
     </row>
@@ -4717,7 +4771,7 @@
       <c r="A93" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B93" s="10" t="s">
+      <c r="B93" s="11" t="s">
         <v>213</v>
       </c>
       <c r="C93" s="1" t="s">
@@ -4729,7 +4783,7 @@
       <c r="E93" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="F93" s="1" t="s">
+      <c r="F93" s="10" t="s">
         <v>216</v>
       </c>
     </row>
@@ -4737,7 +4791,7 @@
       <c r="A94" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B94" s="10" t="s">
+      <c r="B94" s="11" t="s">
         <v>217</v>
       </c>
       <c r="C94" s="1" t="s">
@@ -4757,7 +4811,7 @@
       <c r="A95" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B95" s="10" t="s">
+      <c r="B95" s="11" t="s">
         <v>221</v>
       </c>
       <c r="C95" s="1" t="s">
@@ -4766,7 +4820,7 @@
       <c r="D95" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="F95" s="1" t="s">
+      <c r="F95" s="10" t="s">
         <v>224</v>
       </c>
     </row>
@@ -4774,7 +4828,7 @@
       <c r="A96" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B96" s="10" t="s">
+      <c r="B96" s="11" t="s">
         <v>225</v>
       </c>
       <c r="C96" s="1" t="s">
@@ -4786,66 +4840,66 @@
       <c r="E96" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="F96" s="1" t="s">
-        <v>224</v>
+      <c r="F96" s="10" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B97" s="10" t="s">
-        <v>228</v>
+      <c r="B97" s="11" t="s">
+        <v>229</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B98" s="10" t="s">
-        <v>232</v>
+      <c r="B98" s="11" t="s">
+        <v>233</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="F98" s="1" t="s">
         <v>235</v>
+      </c>
+      <c r="F98" s="10" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B99" s="10" t="s">
-        <v>236</v>
+      <c r="B99" s="11" t="s">
+        <v>237</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="F99" s="1" t="s">
         <v>239</v>
+      </c>
+      <c r="F99" s="10" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B100" s="10" t="s">
+      <c r="B100" s="11" t="s">
         <v>165</v>
       </c>
     </row>
@@ -4853,35 +4907,35 @@
       <c r="A101" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B101" s="10" t="s">
-        <v>240</v>
+      <c r="B101" s="11" t="s">
+        <v>241</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E101" s="1"/>
       <c r="F101" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B102" s="10" t="s">
-        <v>245</v>
+      <c r="B102" s="11" t="s">
+        <v>246</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F102" s="1"/>
       <c r="G102" s="1"/>
@@ -4890,8 +4944,8 @@
       <c r="A103" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B103" s="10" t="s">
-        <v>240</v>
+      <c r="B103" s="11" t="s">
+        <v>241</v>
       </c>
       <c r="C103" s="1"/>
       <c r="D103" s="1"/>
@@ -4902,14 +4956,14 @@
       <c r="A104" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B104" s="10" t="s">
-        <v>248</v>
+      <c r="B104" s="11" t="s">
+        <v>249</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>168</v>
@@ -4922,14 +4976,14 @@
       <c r="A105" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B105" s="10" t="s">
-        <v>251</v>
+      <c r="B105" s="11" t="s">
+        <v>252</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="G105" s="1"/>
     </row>
@@ -4937,14 +4991,14 @@
       <c r="A106" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B106" s="10" t="s">
-        <v>254</v>
+      <c r="B106" s="11" t="s">
+        <v>255</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G106" s="1"/>
     </row>
@@ -4952,8 +5006,8 @@
       <c r="A107" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B107" s="10" t="s">
-        <v>248</v>
+      <c r="B107" s="11" t="s">
+        <v>249</v>
       </c>
       <c r="C107" s="1"/>
       <c r="G107" s="1"/>
@@ -4963,15 +5017,15 @@
         <v>21</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="C108" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="C108" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" s="2"/>
       <c r="F108" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
@@ -4999,9 +5053,9 @@
         <v>21</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="C109" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="C109" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D109" s="1"/>
@@ -5035,11 +5089,11 @@
         <v>100</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C110" s="1"/>
-      <c r="D110" s="14" t="s">
-        <v>261</v>
+      <c r="D110" s="13" t="s">
+        <v>262</v>
       </c>
       <c r="E110" s="1"/>
       <c r="F110" s="1"/>
@@ -5069,10 +5123,10 @@
         <v>104</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C111" s="1"/>
-      <c r="D111" s="14"/>
+      <c r="D111" s="13"/>
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
       <c r="G111" s="1"/>
@@ -5101,12 +5155,12 @@
         <v>96</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C112" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="C112" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D112" s="14"/>
+      <c r="D112" s="13"/>
       <c r="E112" s="1"/>
       <c r="F112" s="1"/>
       <c r="G112" s="1" t="s">
@@ -5137,11 +5191,11 @@
         <v>100</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C113" s="1"/>
-      <c r="D113" s="15" t="s">
-        <v>264</v>
+      <c r="D113" s="14" t="s">
+        <v>265</v>
       </c>
       <c r="E113" s="1"/>
       <c r="F113" s="1"/>
@@ -5171,11 +5225,11 @@
         <v>100</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C114" s="1"/>
-      <c r="D114" s="15" t="s">
-        <v>266</v>
+      <c r="D114" s="14" t="s">
+        <v>267</v>
       </c>
       <c r="E114" s="1"/>
       <c r="F114" s="1"/>
@@ -5205,10 +5259,10 @@
         <v>39</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C115" s="1"/>
-      <c r="D115" s="15"/>
+      <c r="D115" s="14"/>
       <c r="E115" s="1"/>
       <c r="F115" s="1"/>
       <c r="G115" s="1"/>
@@ -5237,16 +5291,16 @@
         <v>96</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="C116" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="C116" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D116" s="15"/>
+      <c r="D116" s="14"/>
       <c r="E116" s="1"/>
       <c r="F116" s="1"/>
       <c r="G116" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H116" s="1"/>
       <c r="I116" s="1"/>
@@ -5273,14 +5327,14 @@
         <v>100</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C117" s="1"/>
-      <c r="D117" s="15" t="s">
-        <v>269</v>
+      <c r="D117" s="14" t="s">
+        <v>270</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F117" s="1"/>
       <c r="G117" s="1"/>
@@ -5309,10 +5363,10 @@
         <v>104</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C118" s="1"/>
-      <c r="D118" s="15"/>
+      <c r="D118" s="14"/>
       <c r="E118" s="1"/>
       <c r="F118" s="1"/>
       <c r="G118" s="1"/>
@@ -5341,12 +5395,12 @@
         <v>21</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="C119" s="13" t="s">
+        <v>272</v>
+      </c>
+      <c r="C119" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D119" s="15"/>
+      <c r="D119" s="14"/>
       <c r="E119" s="1"/>
       <c r="F119" s="1"/>
       <c r="G119" s="1" t="s">
@@ -5377,11 +5431,11 @@
         <v>100</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C120" s="1"/>
-      <c r="D120" s="15" t="s">
-        <v>273</v>
+      <c r="D120" s="14" t="s">
+        <v>274</v>
       </c>
       <c r="E120" s="1"/>
       <c r="F120" s="1"/>
@@ -5408,14 +5462,14 @@
     </row>
     <row r="121" ht="36.0" customHeight="1">
       <c r="A121" s="1" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C121" s="1"/>
-      <c r="D121" s="15" t="s">
-        <v>276</v>
+      <c r="D121" s="14" t="s">
+        <v>277</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>146</v>
@@ -5447,10 +5501,10 @@
         <v>39</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C122" s="1"/>
-      <c r="D122" s="15"/>
+      <c r="D122" s="14"/>
       <c r="E122" s="1"/>
       <c r="F122" s="1"/>
       <c r="G122" s="1"/>
@@ -5479,15 +5533,15 @@
         <v>21</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="C123" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="C123" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D123" s="15"/>
+      <c r="D123" s="14"/>
       <c r="E123" s="1"/>
       <c r="F123" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G123" s="1" t="s">
         <v>108</v>
@@ -5517,11 +5571,11 @@
         <v>100</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C124" s="1"/>
-      <c r="D124" s="15" t="s">
-        <v>280</v>
+      <c r="D124" s="14" t="s">
+        <v>281</v>
       </c>
       <c r="E124" s="1"/>
       <c r="F124" s="1"/>
@@ -5551,11 +5605,11 @@
         <v>142</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C125" s="1"/>
-      <c r="D125" s="15" t="s">
-        <v>282</v>
+      <c r="D125" s="14" t="s">
+        <v>283</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>146</v>
@@ -5587,11 +5641,11 @@
         <v>100</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C126" s="1"/>
-      <c r="D126" s="15" t="s">
-        <v>284</v>
+      <c r="D126" s="14" t="s">
+        <v>285</v>
       </c>
       <c r="E126" s="1"/>
       <c r="F126" s="1"/>
@@ -5621,11 +5675,11 @@
         <v>100</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C127" s="1"/>
-      <c r="D127" s="15" t="s">
-        <v>286</v>
+      <c r="D127" s="14" t="s">
+        <v>287</v>
       </c>
       <c r="E127" s="1"/>
       <c r="F127" s="1"/>
@@ -5655,11 +5709,11 @@
         <v>100</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C128" s="1"/>
-      <c r="D128" s="15" t="s">
-        <v>288</v>
+      <c r="D128" s="14" t="s">
+        <v>289</v>
       </c>
       <c r="E128" s="1"/>
       <c r="F128" s="1"/>
@@ -5689,7 +5743,7 @@
         <v>100</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C129" s="1"/>
       <c r="D129" s="1"/>
@@ -5707,10 +5761,10 @@
       <c r="P129" s="1"/>
       <c r="Q129" s="1"/>
       <c r="R129" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="S129" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="T129" s="4"/>
       <c r="U129" s="4"/>
@@ -5725,10 +5779,10 @@
         <v>39</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C130" s="1"/>
-      <c r="D130" s="15"/>
+      <c r="D130" s="14"/>
       <c r="E130" s="1"/>
       <c r="F130" s="1"/>
       <c r="G130" s="1"/>
@@ -5757,15 +5811,15 @@
         <v>21</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="C131" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="C131" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D131" s="15"/>
+      <c r="D131" s="14"/>
       <c r="E131" s="1"/>
       <c r="F131" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G131" s="1" t="s">
         <v>108</v>
@@ -5795,11 +5849,11 @@
         <v>100</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C132" s="1"/>
-      <c r="D132" s="15" t="s">
-        <v>294</v>
+      <c r="D132" s="14" t="s">
+        <v>295</v>
       </c>
       <c r="E132" s="1"/>
       <c r="F132" s="1"/>
@@ -5829,11 +5883,11 @@
         <v>100</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="C133" s="14"/>
-      <c r="D133" s="14" t="s">
         <v>296</v>
+      </c>
+      <c r="C133" s="13"/>
+      <c r="D133" s="13" t="s">
+        <v>297</v>
       </c>
       <c r="E133" s="1"/>
       <c r="F133" s="1"/>
@@ -5851,10 +5905,10 @@
       <c r="R133" s="4"/>
       <c r="S133" s="4"/>
       <c r="T133" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="U133" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="V133" s="4"/>
       <c r="W133" s="4"/>
@@ -5867,10 +5921,10 @@
         <v>39</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C134" s="1"/>
-      <c r="D134" s="15"/>
+      <c r="D134" s="14"/>
       <c r="E134" s="1"/>
       <c r="F134" s="1"/>
       <c r="G134" s="1"/>
@@ -5899,18 +5953,18 @@
         <v>21</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="C135" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="C135" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D135" s="15"/>
+      <c r="D135" s="14"/>
       <c r="E135" s="1"/>
       <c r="F135" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H135" s="1"/>
       <c r="I135" s="1"/>
@@ -5937,11 +5991,11 @@
         <v>100</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C136" s="1"/>
-      <c r="D136" s="15" t="s">
-        <v>301</v>
+      <c r="D136" s="14" t="s">
+        <v>302</v>
       </c>
       <c r="E136" s="1"/>
       <c r="F136" s="1"/>
@@ -5971,10 +6025,10 @@
         <v>39</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C137" s="1"/>
-      <c r="D137" s="15"/>
+      <c r="D137" s="14"/>
       <c r="E137" s="1"/>
       <c r="F137" s="1"/>
       <c r="G137" s="1"/>
@@ -6003,7 +6057,7 @@
         <v>39</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C138" s="4"/>
       <c r="D138" s="4"/>
@@ -6034,17 +6088,17 @@
       <c r="A139" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B139" s="10" t="s">
-        <v>302</v>
+      <c r="B139" s="11" t="s">
+        <v>303</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G139" s="1" t="s">
         <v>108</v>
@@ -6054,14 +6108,14 @@
       <c r="A140" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B140" s="10" t="s">
-        <v>306</v>
+      <c r="B140" s="11" t="s">
+        <v>307</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>146</v>
@@ -6072,20 +6126,20 @@
       <c r="A141" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B141" s="10" t="s">
-        <v>309</v>
+      <c r="B141" s="11" t="s">
+        <v>310</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>146</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G141" s="1"/>
       <c r="H141" s="4"/>
@@ -6110,33 +6164,33 @@
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="B142" s="10" t="s">
         <v>314</v>
       </c>
+      <c r="B142" s="11" t="s">
+        <v>315</v>
+      </c>
       <c r="C142" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>146</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G142" s="1"/>
       <c r="H142" s="4"/>
       <c r="I142" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K142" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L142" s="4"/>
       <c r="M142" s="4"/>
@@ -6156,22 +6210,22 @@
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E143" s="4" t="s">
         <v>146</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G143" s="1"/>
       <c r="H143" s="1"/>
@@ -6198,17 +6252,17 @@
       <c r="A144" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B144" s="10" t="s">
-        <v>326</v>
+      <c r="B144" s="11" t="s">
+        <v>327</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G144" s="1"/>
     </row>
@@ -6216,8 +6270,8 @@
       <c r="A145" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B145" s="10" t="s">
-        <v>302</v>
+      <c r="B145" s="11" t="s">
+        <v>303</v>
       </c>
       <c r="C145" s="1"/>
       <c r="F145" s="7"/>
@@ -6227,17 +6281,17 @@
       <c r="A146" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B146" s="10" t="s">
-        <v>329</v>
+      <c r="B146" s="11" t="s">
+        <v>330</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="G146" s="1" t="s">
         <v>108</v>
@@ -6245,16 +6299,16 @@
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E147" s="4" t="s">
         <v>146</v>
@@ -6283,22 +6337,22 @@
     </row>
     <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E148" s="4" t="s">
         <v>146</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G148" s="1"/>
       <c r="H148" s="1"/>
@@ -6307,7 +6361,7 @@
       <c r="K148" s="1"/>
       <c r="L148" s="1"/>
       <c r="M148" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N148" s="1"/>
       <c r="O148" s="1"/>
@@ -6328,7 +6382,7 @@
         <v>21</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C149" s="4" t="s">
         <v>23</v>
@@ -6361,22 +6415,22 @@
     </row>
     <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E150" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="F150" s="4" t="s">
         <v>349</v>
+      </c>
+      <c r="F150" s="15" t="s">
+        <v>350</v>
       </c>
       <c r="G150" s="1"/>
       <c r="H150" s="1"/>
@@ -6385,7 +6439,7 @@
       <c r="K150" s="1"/>
       <c r="L150" s="1"/>
       <c r="M150" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N150" s="1"/>
       <c r="O150" s="1"/>
@@ -6403,22 +6457,22 @@
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E151" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="F151" s="4" t="s">
-        <v>355</v>
+      <c r="F151" s="15" t="s">
+        <v>356</v>
       </c>
       <c r="G151" s="4"/>
       <c r="H151" s="4"/>
@@ -6446,7 +6500,7 @@
         <v>39</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C152" s="4"/>
       <c r="D152" s="4"/>
@@ -6475,16 +6529,16 @@
     </row>
     <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E153" s="4" t="s">
         <v>146</v>
@@ -6513,22 +6567,22 @@
     </row>
     <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E154" s="4" t="s">
         <v>146</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G154" s="4"/>
       <c r="H154" s="4"/>
@@ -6553,22 +6607,22 @@
     </row>
     <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E155" s="4" t="s">
         <v>146</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G155" s="4"/>
       <c r="H155" s="4"/>
@@ -6593,16 +6647,16 @@
     </row>
     <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E156" s="4" t="s">
         <v>146</v>
@@ -6611,44 +6665,44 @@
       <c r="G156" s="4"/>
       <c r="H156" s="4"/>
       <c r="I156" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K156" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E157" s="4" t="s">
         <v>146</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="G157" s="4"/>
       <c r="H157" s="4"/>
       <c r="I157" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K157" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="158" ht="15.75" customHeight="1">
@@ -6656,7 +6710,7 @@
         <v>39</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C158" s="4"/>
       <c r="D158" s="4"/>
@@ -6670,17 +6724,17 @@
         <v>96</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E159" s="4"/>
       <c r="F159" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="G159" s="4"/>
       <c r="H159" s="4"/>
@@ -6690,13 +6744,13 @@
         <v>142</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E160" s="4" t="s">
         <v>146</v>
@@ -6710,7 +6764,7 @@
         <v>39</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C161" s="4"/>
       <c r="D161" s="4"/>
@@ -6724,33 +6778,33 @@
         <v>21</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E162" s="4"/>
-      <c r="F162" s="4" t="s">
-        <v>390</v>
+      <c r="F162" s="15" t="s">
+        <v>391</v>
       </c>
       <c r="G162" s="4"/>
       <c r="H162" s="4"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B163" s="16" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C163" s="17" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>146</v>
@@ -6782,7 +6836,7 @@
         <v>21</v>
       </c>
       <c r="B164" s="16" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C164" s="18" t="s">
         <v>23</v>
@@ -6815,16 +6869,16 @@
     </row>
     <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="1" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B165" s="16" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C165" s="19" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>146</v>
@@ -6853,22 +6907,22 @@
     </row>
     <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>146</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G166" s="1"/>
       <c r="H166" s="1"/>
@@ -6896,7 +6950,7 @@
         <v>39</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C167" s="20"/>
       <c r="D167" s="1"/>
@@ -6928,7 +6982,7 @@
         <v>21</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C168" s="20" t="s">
         <v>23</v>
@@ -6961,16 +7015,16 @@
     </row>
     <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B169" s="16" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C169" s="19" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>146</v>
@@ -6999,22 +7053,22 @@
     </row>
     <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>146</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G170" s="1"/>
       <c r="H170" s="1"/>
@@ -7042,7 +7096,7 @@
         <v>39</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C171" s="1"/>
       <c r="D171" s="1"/>
@@ -7074,7 +7128,7 @@
         <v>21</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>23</v>
@@ -7107,16 +7161,16 @@
     </row>
     <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E173" s="1" t="s">
         <v>146</v>
@@ -7148,7 +7202,7 @@
         <v>39</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C174" s="1"/>
       <c r="D174" s="1"/>
@@ -7180,7 +7234,7 @@
         <v>21</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>23</v>
@@ -7213,22 +7267,22 @@
     </row>
     <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>146</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G176" s="1"/>
       <c r="H176" s="1"/>
@@ -7256,7 +7310,7 @@
         <v>39</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C177" s="1"/>
       <c r="D177" s="1"/>
@@ -7288,7 +7342,7 @@
         <v>21</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>23</v>
@@ -7321,28 +7375,28 @@
     </row>
     <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E179" s="1"/>
       <c r="F179" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G179" s="1"/>
       <c r="H179" s="1"/>
       <c r="I179" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K179" s="1"/>
       <c r="L179" s="1"/>
@@ -7363,22 +7417,22 @@
     </row>
     <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>146</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G180" s="1"/>
       <c r="H180" s="1"/>
@@ -7406,7 +7460,7 @@
         <v>39</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C181" s="1"/>
       <c r="D181" s="1"/>
@@ -7438,7 +7492,7 @@
         <v>21</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>23</v>
@@ -7471,22 +7525,22 @@
     </row>
     <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>146</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G183" s="1"/>
       <c r="H183" s="1"/>
@@ -7511,28 +7565,28 @@
     </row>
     <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="1" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E184" s="1"/>
-      <c r="F184" s="1" t="s">
-        <v>439</v>
+      <c r="F184" s="10" t="s">
+        <v>440</v>
       </c>
       <c r="G184" s="1"/>
       <c r="H184" s="1"/>
       <c r="I184" s="1" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J184" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K184" s="1"/>
       <c r="L184" s="1"/>
@@ -7556,7 +7610,7 @@
         <v>39</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C185" s="1"/>
       <c r="D185" s="1"/>
@@ -7588,7 +7642,7 @@
         <v>39</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C186" s="1"/>
       <c r="F186" s="7"/>
@@ -7599,13 +7653,13 @@
         <v>21</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G187" s="1" t="s">
         <v>108</v>
@@ -7616,13 +7670,13 @@
         <v>100</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="G188" s="1"/>
     </row>
@@ -7631,7 +7685,7 @@
         <v>39</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C189" s="1"/>
       <c r="D189" s="1"/>
@@ -7642,13 +7696,13 @@
         <v>21</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G190" s="1" t="s">
         <v>108</v>
@@ -7659,16 +7713,16 @@
         <v>100</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="192" ht="15.75" customHeight="1">
@@ -7676,16 +7730,16 @@
         <v>100</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="193" ht="15.75" customHeight="1">
@@ -7693,16 +7747,16 @@
         <v>100</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="194" ht="15.75" customHeight="1">
@@ -7710,16 +7764,16 @@
         <v>100</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="195" ht="15.75" customHeight="1">
@@ -7727,16 +7781,18 @@
         <v>100</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E195" s="4"/>
-      <c r="F195" s="1"/>
+      <c r="F195" s="10" t="s">
+        <v>471</v>
+      </c>
       <c r="G195" s="4"/>
       <c r="H195" s="4"/>
       <c r="I195" s="4"/>
@@ -7763,39 +7819,41 @@
         <v>39</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B197" s="10" t="s">
-        <v>470</v>
+      <c r="B197" s="11" t="s">
+        <v>472</v>
       </c>
       <c r="L197" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="198" ht="15.75" customHeight="1">
       <c r="A198" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B198" s="10" t="s">
-        <v>472</v>
-      </c>
-      <c r="L198" s="1" t="s">
-        <v>473</v>
+      <c r="B198" s="11" t="s">
+        <v>474</v>
+      </c>
+      <c r="L198" s="10" t="s">
+        <v>475</v>
       </c>
     </row>
     <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B199" s="10" t="s">
-        <v>474</v>
-      </c>
-      <c r="C199" s="4"/>
+      <c r="B199" s="11" t="s">
+        <v>476</v>
+      </c>
+      <c r="C199" s="15" t="s">
+        <v>477</v>
+      </c>
       <c r="D199" s="4"/>
       <c r="E199" s="4"/>
       <c r="F199" s="4"/>
@@ -7805,7 +7863,7 @@
       <c r="J199" s="4"/>
       <c r="K199" s="4"/>
       <c r="L199" s="1" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="M199" s="4"/>
       <c r="N199" s="4"/>
@@ -7826,59 +7884,59 @@
       <c r="A200" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B200" s="10" t="s">
-        <v>476</v>
+      <c r="B200" s="11" t="s">
+        <v>479</v>
       </c>
       <c r="L200" s="1" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="201" ht="15.75" customHeight="1"/>
     <row r="202" ht="15.75" customHeight="1"/>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="C203" s="10"/>
+      <c r="C203" s="11"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="B204" s="10"/>
-      <c r="C204" s="10"/>
+      <c r="B204" s="11"/>
+      <c r="C204" s="11"/>
     </row>
     <row r="205" ht="15.75" customHeight="1"/>
     <row r="206" ht="15.75" customHeight="1">
-      <c r="B206" s="10"/>
+      <c r="B206" s="11"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
       <c r="B207" s="1"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
-      <c r="B208" s="10"/>
+      <c r="B208" s="11"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
-      <c r="B209" s="10"/>
+      <c r="B209" s="11"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
       <c r="B210" s="1"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="B211" s="10"/>
+      <c r="B211" s="11"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
       <c r="B212" s="1"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="B213" s="10"/>
+      <c r="B213" s="11"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
       <c r="B214" s="1"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
-      <c r="B215" s="10"/>
+      <c r="B215" s="11"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
       <c r="B216" s="1"/>
     </row>
     <row r="217" ht="15.75" customHeight="1"/>
     <row r="218" ht="15.75" customHeight="1">
-      <c r="C218" s="10"/>
+      <c r="C218" s="11"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
       <c r="B219" s="1"/>
@@ -7888,10 +7946,10 @@
     </row>
     <row r="221" ht="15.75" customHeight="1"/>
     <row r="222" ht="15.75" customHeight="1">
-      <c r="B222" s="10"/>
+      <c r="B222" s="11"/>
     </row>
     <row r="223" ht="15.75" customHeight="1">
-      <c r="B223" s="10"/>
+      <c r="B223" s="11"/>
     </row>
     <row r="224" ht="15.75" customHeight="1"/>
     <row r="225" ht="15.75" customHeight="1"/>
@@ -8696,7 +8754,7 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="21" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B1" s="21" t="s">
         <v>1</v>
@@ -8713,30 +8771,30 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>146</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
@@ -8744,13 +8802,13 @@
         <v>213</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
@@ -8758,27 +8816,27 @@
         <v>213</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
@@ -8804,16 +8862,16 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
@@ -8839,16 +8897,16 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
@@ -8874,19 +8932,19 @@
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
@@ -8911,19 +8969,19 @@
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -8948,19 +9006,19 @@
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -8985,19 +9043,19 @@
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -9022,19 +9080,19 @@
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -9059,19 +9117,19 @@
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -9096,19 +9154,19 @@
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
@@ -9133,19 +9191,19 @@
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -9170,19 +9228,19 @@
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -9207,19 +9265,19 @@
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -9244,19 +9302,19 @@
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -9281,20 +9339,20 @@
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B20" s="1" t="str">
         <f t="shared" ref="B20:B83" si="1">LOWER(SUBSTITUTE(C20," ",""))</f>
         <v>chakechakedistricthospital</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -9319,20 +9377,20 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B21" s="1" t="str">
         <f t="shared" si="1"/>
         <v>pujiniphcu+</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
@@ -9357,20 +9415,20 @@
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B22" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tundauwaphcu+</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
@@ -9395,20 +9453,20 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B23" s="1" t="str">
         <f t="shared" si="1"/>
         <v>vitongojiphcc</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
@@ -9433,20 +9491,20 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B24" s="1" t="str">
         <f t="shared" si="1"/>
         <v>weshaphcu+</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
@@ -9471,20 +9529,20 @@
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B25" s="1" t="str">
         <f t="shared" si="1"/>
         <v>kondephcu+</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -9509,20 +9567,20 @@
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B26" s="1" t="str">
         <f t="shared" si="1"/>
         <v>makangalephcu+</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
@@ -9547,20 +9605,20 @@
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B27" s="1" t="str">
         <f t="shared" si="1"/>
         <v>maziwangombephcu+</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
@@ -9585,20 +9643,20 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B28" s="1" t="str">
         <f t="shared" si="1"/>
         <v>micheweniphcc</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
@@ -9623,20 +9681,20 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B29" s="1" t="str">
         <f t="shared" si="1"/>
         <v>wingwiphcu+</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
@@ -9661,20 +9719,20 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B30" s="1" t="str">
         <f t="shared" si="1"/>
         <v>kiuyumbuyuniphcu+</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
@@ -9699,20 +9757,20 @@
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B31" s="1" t="str">
         <f t="shared" si="1"/>
         <v>bogoaphcu+</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
@@ -9737,20 +9795,20 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B32" s="1" t="str">
         <f t="shared" si="1"/>
         <v>kengejaphcu+</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
@@ -9775,20 +9833,20 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B33" s="1" t="str">
         <f t="shared" si="1"/>
         <v>abdallahmzeedistricthospital</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
@@ -9813,20 +9871,20 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B34" s="1" t="str">
         <f t="shared" si="1"/>
         <v>michenzaniphcu+</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
@@ -9851,20 +9909,20 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B35" s="1" t="str">
         <f t="shared" si="1"/>
         <v>fundophcu+</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
@@ -9889,20 +9947,20 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B36" s="1" t="str">
         <f t="shared" si="1"/>
         <v>kojaniphcu+</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
@@ -9927,20 +9985,20 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B37" s="1" t="str">
         <f t="shared" si="1"/>
         <v>makongeniphcu+</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
@@ -9965,20 +10023,20 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B38" s="1" t="str">
         <f t="shared" si="1"/>
         <v>wetedistricthospital</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
@@ -10003,20 +10061,20 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B39" s="1" t="str">
         <f t="shared" si="1"/>
         <v>mzambarauniphcu+</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
@@ -10041,20 +10099,20 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B40" s="1" t="str">
         <f t="shared" si="1"/>
         <v>junguniphcu+</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
@@ -10079,20 +10137,20 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B41" s="1" t="str">
         <f t="shared" si="1"/>
         <v>ukunjwiphcu+</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
@@ -10117,20 +10175,20 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B42" s="1" t="str">
         <f t="shared" si="1"/>
         <v>uondwephcu+</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
@@ -10155,20 +10213,20 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B43" s="1" t="str">
         <f t="shared" si="1"/>
         <v>chwakaphcu+</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
@@ -10193,20 +10251,20 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B44" s="1" t="str">
         <f t="shared" si="1"/>
         <v>mweraphcu+</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
@@ -10231,20 +10289,20 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B45" s="1" t="str">
         <f t="shared" si="1"/>
         <v>ungujaukuuphcu+</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
@@ -10269,20 +10327,20 @@
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B46" s="1" t="str">
         <f t="shared" si="1"/>
         <v>uziniphcu+</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
@@ -10307,20 +10365,20 @@
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B47" s="1" t="str">
         <f t="shared" si="1"/>
         <v>uroaphcu+</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -10345,20 +10403,20 @@
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B48" s="1" t="str">
         <f t="shared" si="1"/>
         <v>kivungedistricthospital</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
@@ -10383,20 +10441,20 @@
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B49" s="1" t="str">
         <f t="shared" si="1"/>
         <v>matemwephcu+</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -10421,20 +10479,20 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B50" s="1" t="str">
         <f t="shared" si="1"/>
         <v>nungwiphcu+</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
@@ -10459,20 +10517,20 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B51" s="1" t="str">
         <f t="shared" si="1"/>
         <v>pwanimchanganiphcu+</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
@@ -10497,20 +10555,20 @@
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B52" s="1" t="str">
         <f t="shared" si="1"/>
         <v>tumbatugomaniphcu+</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
@@ -10535,20 +10593,20 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B53" s="1" t="str">
         <f t="shared" si="1"/>
         <v>kendwaphcu+</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
@@ -10573,20 +10631,20 @@
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B54" s="1" t="str">
         <f t="shared" si="1"/>
         <v>bumbwinimisufiniphcu+</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
@@ -10611,20 +10669,20 @@
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B55" s="1" t="str">
         <f t="shared" si="1"/>
         <v>dongevijibweniphcu+</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
@@ -10649,20 +10707,20 @@
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B56" s="1" t="str">
         <f t="shared" si="1"/>
         <v>kiongwephcu</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
@@ -10687,20 +10745,20 @@
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B57" s="1" t="str">
         <f t="shared" si="1"/>
         <v>kitopephcu</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
@@ -10725,20 +10783,20 @@
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B58" s="1" t="str">
         <f t="shared" si="1"/>
         <v>mahondaphcu+</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
@@ -10763,20 +10821,20 @@
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B59" s="1" t="str">
         <f t="shared" si="1"/>
         <v>jambianiphcu+</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
@@ -10801,20 +10859,20 @@
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B60" s="1" t="str">
         <f t="shared" si="1"/>
         <v>makunduchidistricthospital</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
@@ -10839,20 +10897,20 @@
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B61" s="1" t="str">
         <f t="shared" si="1"/>
         <v>muyuniphcu+</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
@@ -10877,20 +10935,20 @@
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B62" s="1" t="str">
         <f t="shared" si="1"/>
         <v>bwejuuphcu+</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
@@ -10915,20 +10973,20 @@
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B63" s="1" t="str">
         <f t="shared" si="1"/>
         <v>chumbuniphcu+</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
@@ -10953,20 +11011,20 @@
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B64" s="1" t="str">
         <f t="shared" si="1"/>
         <v>mnazimmojahospital</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
@@ -10991,20 +11049,20 @@
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B65" s="1" t="str">
         <f t="shared" si="1"/>
         <v>mwembeladumchclinic</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
@@ -11029,20 +11087,20 @@
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B66" s="1" t="str">
         <f t="shared" si="1"/>
         <v>sebleniphcu+</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
@@ -11067,20 +11125,20 @@
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B67" s="1" t="str">
         <f t="shared" si="1"/>
         <v>chukwaniphcu+</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
@@ -11105,20 +11163,20 @@
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B68" s="1" t="str">
         <f t="shared" si="1"/>
         <v>fuoniphcu+</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
@@ -11143,20 +11201,20 @@
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B69" s="1" t="str">
         <f t="shared" si="1"/>
         <v>kombeniphcu+</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
@@ -11181,20 +11239,20 @@
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B70" s="1" t="str">
         <f t="shared" si="1"/>
         <v>mtofaaniphcu+(kinuni)</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
@@ -11219,20 +11277,20 @@
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B71" s="1" t="str">
         <f t="shared" si="1"/>
         <v>bumbwisudiphcu+</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
@@ -11257,20 +11315,20 @@
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B72" s="1" t="str">
         <f t="shared" si="1"/>
         <v>selemphcu+</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
@@ -11295,20 +11353,20 @@
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B73" s="1" t="str">
         <f t="shared" si="1"/>
         <v>other</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
@@ -11333,20 +11391,20 @@
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B74" s="1" t="str">
         <f t="shared" si="1"/>
         <v>other</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
@@ -11371,20 +11429,20 @@
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B75" s="1" t="str">
         <f t="shared" si="1"/>
         <v>other</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
@@ -11409,20 +11467,20 @@
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B76" s="1" t="str">
         <f t="shared" si="1"/>
         <v>other</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
@@ -11447,20 +11505,20 @@
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B77" s="1" t="str">
         <f t="shared" si="1"/>
         <v>other</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
@@ -11485,20 +11543,20 @@
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B78" s="1" t="str">
         <f t="shared" si="1"/>
         <v>other</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
@@ -11523,20 +11581,20 @@
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B79" s="1" t="str">
         <f t="shared" si="1"/>
         <v>other</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
@@ -11561,20 +11619,20 @@
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B80" s="1" t="str">
         <f t="shared" si="1"/>
         <v>other</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
@@ -11599,20 +11657,20 @@
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B81" s="1" t="str">
         <f t="shared" si="1"/>
         <v>other</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="F81" s="1"/>
       <c r="G81" s="1"/>
@@ -11637,20 +11695,20 @@
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B82" s="1" t="str">
         <f t="shared" si="1"/>
         <v>other</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="F82" s="1"/>
       <c r="G82" s="1"/>
@@ -11675,20 +11733,20 @@
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B83" s="1" t="str">
         <f t="shared" si="1"/>
         <v>other</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="F83" s="1"/>
       <c r="G83" s="1"/>
@@ -11713,16 +11771,16 @@
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>146</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
@@ -11748,16 +11806,16 @@
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
@@ -11783,16 +11841,16 @@
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="E86" s="1"/>
       <c r="F86" s="1"/>
@@ -11818,16 +11876,16 @@
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="1" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="E87" s="1"/>
       <c r="F87" s="1"/>
@@ -11853,16 +11911,16 @@
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="1" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
@@ -11888,16 +11946,16 @@
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="1" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="E89" s="1"/>
       <c r="F89" s="1"/>
@@ -11923,16 +11981,16 @@
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="1" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E90" s="1"/>
       <c r="F90" s="1"/>
@@ -11958,16 +12016,16 @@
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="1" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="E91" s="1"/>
       <c r="F91" s="1"/>
@@ -11993,16 +12051,16 @@
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="1" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="E92" s="1"/>
       <c r="F92" s="1"/>
@@ -12028,16 +12086,16 @@
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="E93" s="1"/>
       <c r="F93" s="1"/>
@@ -12063,16 +12121,16 @@
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="E94" s="1"/>
       <c r="F94" s="1"/>
@@ -12098,16 +12156,16 @@
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="E95" s="1"/>
       <c r="F95" s="1"/>
@@ -12133,16 +12191,16 @@
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="E96" s="1"/>
       <c r="F96" s="1"/>
@@ -12168,16 +12226,16 @@
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="E97" s="1"/>
       <c r="F97" s="1"/>
@@ -12203,16 +12261,16 @@
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="E98" s="1"/>
       <c r="F98" s="1"/>
@@ -12238,16 +12296,16 @@
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="E99" s="1"/>
       <c r="F99" s="1"/>
@@ -12273,240 +12331,240 @@
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="1" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="1" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="1" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="1" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="1" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>653</v>
-      </c>
       <c r="C115" s="1" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="E116" s="1"/>
       <c r="F116" s="1"/>
@@ -12532,16 +12590,16 @@
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="E117" s="1"/>
       <c r="F117" s="1"/>
@@ -12567,16 +12625,16 @@
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="E118" s="1"/>
       <c r="F118" s="1"/>
@@ -12602,16 +12660,16 @@
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="E119" s="1"/>
       <c r="F119" s="1"/>
@@ -12637,16 +12695,16 @@
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="E120" s="1"/>
       <c r="F120" s="1"/>
@@ -12672,16 +12730,16 @@
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="E121" s="1"/>
       <c r="F121" s="1"/>
@@ -12707,16 +12765,16 @@
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="E122" s="1"/>
       <c r="F122" s="1"/>
@@ -12742,16 +12800,16 @@
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="E123" s="1"/>
       <c r="F123" s="1"/>
@@ -12777,16 +12835,16 @@
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="E124" s="1"/>
       <c r="F124" s="1"/>
@@ -12812,16 +12870,16 @@
     </row>
     <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="E125" s="1"/>
       <c r="F125" s="1"/>
@@ -12847,16 +12905,16 @@
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="E126" s="1"/>
       <c r="F126" s="1"/>
@@ -12882,16 +12940,16 @@
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="E127" s="1"/>
       <c r="F127" s="1"/>
@@ -12917,16 +12975,16 @@
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="E128" s="1"/>
       <c r="F128" s="1"/>
@@ -12952,16 +13010,16 @@
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="1" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
@@ -12987,16 +13045,16 @@
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="1" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="E130" s="1"/>
       <c r="F130" s="1"/>
@@ -13022,16 +13080,16 @@
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="1" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="E131" s="1"/>
       <c r="F131" s="1"/>
@@ -13057,16 +13115,16 @@
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="1" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="E132" s="1"/>
       <c r="F132" s="1"/>
@@ -13092,16 +13150,16 @@
     </row>
     <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="1" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="E133" s="1"/>
       <c r="F133" s="1"/>
@@ -13127,16 +13185,16 @@
     </row>
     <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="1" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="E134" s="1"/>
       <c r="F134" s="1"/>
@@ -13162,16 +13220,16 @@
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="1" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
@@ -13197,16 +13255,16 @@
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="1" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="E136" s="1"/>
       <c r="F136" s="1"/>
@@ -13232,16 +13290,16 @@
     </row>
     <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="E137" s="1"/>
       <c r="F137" s="1"/>
@@ -13267,16 +13325,16 @@
     </row>
     <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="E138" s="1"/>
       <c r="F138" s="1"/>
@@ -13302,16 +13360,16 @@
     </row>
     <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="E139" s="1"/>
       <c r="F139" s="1"/>
@@ -13337,16 +13395,16 @@
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="E140" s="1"/>
       <c r="F140" s="1"/>
@@ -13372,16 +13430,16 @@
     </row>
     <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="E141" s="1"/>
       <c r="F141" s="1"/>
@@ -13407,16 +13465,16 @@
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="C142" s="19" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="E142" s="1"/>
       <c r="F142" s="1"/>
@@ -13442,16 +13500,16 @@
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="E143" s="1"/>
       <c r="F143" s="1"/>
@@ -13477,16 +13535,16 @@
     </row>
     <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="E144" s="1"/>
       <c r="F144" s="1"/>
@@ -13512,16 +13570,16 @@
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="E145" s="1"/>
       <c r="F145" s="1"/>
@@ -13547,16 +13605,16 @@
     </row>
     <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="E146" s="1"/>
       <c r="F146" s="1"/>
@@ -13582,16 +13640,16 @@
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="E147" s="1"/>
       <c r="F147" s="1"/>
@@ -13617,16 +13675,16 @@
     </row>
     <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="E148" s="1"/>
       <c r="F148" s="1"/>
@@ -13652,16 +13710,16 @@
     </row>
     <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="E149" s="1"/>
       <c r="F149" s="1"/>
@@ -13687,16 +13745,16 @@
     </row>
     <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="E150" s="1"/>
       <c r="F150" s="1"/>
@@ -13722,16 +13780,16 @@
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="E151" s="1"/>
       <c r="F151" s="1"/>
@@ -13757,16 +13815,16 @@
     </row>
     <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="E152" s="1"/>
       <c r="F152" s="1"/>
@@ -13792,16 +13850,16 @@
     </row>
     <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="E153" s="1"/>
       <c r="F153" s="1"/>
@@ -13827,16 +13885,16 @@
     </row>
     <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="E154" s="1"/>
       <c r="F154" s="1"/>
@@ -13862,16 +13920,16 @@
     </row>
     <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="1" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>146</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="E155" s="1"/>
       <c r="F155" s="1"/>
@@ -13897,16 +13955,16 @@
     </row>
     <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="1" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="E156" s="1"/>
       <c r="F156" s="1"/>
@@ -13932,16 +13990,16 @@
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="1" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="E157" s="1"/>
       <c r="F157" s="1"/>
@@ -13967,16 +14025,16 @@
     </row>
     <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="E158" s="1"/>
       <c r="F158" s="1"/>
@@ -14002,16 +14060,16 @@
     </row>
     <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="E159" s="1"/>
       <c r="F159" s="1"/>
@@ -14037,16 +14095,16 @@
     </row>
     <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="E160" s="1"/>
       <c r="F160" s="1"/>
@@ -14072,16 +14130,16 @@
     </row>
     <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="E161" s="1"/>
       <c r="F161" s="1"/>
@@ -14107,16 +14165,16 @@
     </row>
     <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="E162" s="1"/>
       <c r="F162" s="1"/>
@@ -14142,16 +14200,16 @@
     </row>
     <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="E163" s="1"/>
       <c r="F163" s="1"/>
@@ -14177,16 +14235,16 @@
     </row>
     <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="E164" s="1"/>
       <c r="F164" s="1"/>
@@ -14212,16 +14270,16 @@
     </row>
     <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="4" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="E165" s="4"/>
       <c r="F165" s="4"/>
@@ -14248,16 +14306,16 @@
     </row>
     <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="4" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="E166" s="4"/>
       <c r="F166" s="4"/>
@@ -14284,16 +14342,16 @@
     </row>
     <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="4" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="E167" s="4"/>
       <c r="F167" s="4"/>
@@ -15203,36 +15261,36 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="21" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="B1" s="21" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="D1" s="21" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="F1" s="21" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1"/>
